--- a/data/constituents_summary.xlsx
+++ b/data/constituents_summary.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huck4481\Documents\GitHub\hysteresis\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\hysteresis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E391545-C2C5-496B-870D-7849A200E4F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C71EA0-DD8D-4903-BA0C-C92B4BC01519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="623" xr2:uid="{FEC01F85-CDE9-417C-893C-E562E55652ED}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="179">
   <si>
     <t>Volume filtered (mL)</t>
   </si>
@@ -401,30 +401,6 @@
     <t xml:space="preserve">Grab Samples </t>
   </si>
   <si>
-    <t>GS #1 UP 7/17/21</t>
-  </si>
-  <si>
-    <t>GS #1 DOWN 7/17/21</t>
-  </si>
-  <si>
-    <t>GS #2 UP 7/19/21</t>
-  </si>
-  <si>
-    <t>GS #2 DOWN 7/19/21</t>
-  </si>
-  <si>
-    <t>GS #4 UP 8/5/21</t>
-  </si>
-  <si>
-    <t>GS #4 DOWN 8/5/21</t>
-  </si>
-  <si>
-    <t>GS #5 UP 8/13/21</t>
-  </si>
-  <si>
-    <t>GS #5 DOWN 8/13/21</t>
-  </si>
-  <si>
     <t>VC-BER-7</t>
   </si>
   <si>
@@ -449,82 +425,154 @@
     <t>VC-BER-14</t>
   </si>
   <si>
-    <t>GSLB DOC 8/24/22</t>
-  </si>
-  <si>
-    <t>GSU 7/12/22</t>
-  </si>
-  <si>
-    <t>GSU 8/11/22</t>
-  </si>
-  <si>
-    <t>GSUB 8/24/22</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> S1 Downstream /B 3/12/22</t>
-  </si>
-  <si>
-    <t>GS1 Upstream Bottom 3/12/22</t>
-  </si>
-  <si>
-    <t>GSL 7/12/22</t>
-  </si>
-  <si>
-    <t>GSLB  3/18/22</t>
-  </si>
-  <si>
-    <t>GSUB 3/18/22</t>
-  </si>
-  <si>
-    <t>GSL 8/11/22</t>
-  </si>
-  <si>
-    <t>GSLB 4/13/23</t>
-  </si>
-  <si>
-    <t>GSLT 4/13/23</t>
-  </si>
-  <si>
-    <t>GSUB 4/13/23</t>
-  </si>
-  <si>
-    <t>GSUT 4/13/23</t>
-  </si>
-  <si>
-    <t>GSLB 3/18/23</t>
-  </si>
-  <si>
-    <t>GSLT 3/18/23</t>
-  </si>
-  <si>
-    <t>GSUB 3/18/23</t>
-  </si>
-  <si>
-    <t>GSUT 3/18/23</t>
-  </si>
-  <si>
-    <t>GSLB 3/19/23</t>
-  </si>
-  <si>
-    <t>GSLT 3/19/23</t>
-  </si>
-  <si>
-    <t>GSUB 3/19/23</t>
-  </si>
-  <si>
-    <t>GSUT 3/19/23</t>
-  </si>
-  <si>
-    <t>GSLB 3/22/23</t>
-  </si>
-  <si>
-    <t>GSLT 3/22/23</t>
-  </si>
-  <si>
-    <t>GSUB 3/22/23</t>
-  </si>
-  <si>
-    <t>GSUT 3/22/23</t>
+    <t>GSU1</t>
+  </si>
+  <si>
+    <t>GSD1</t>
+  </si>
+  <si>
+    <t>GSU2</t>
+  </si>
+  <si>
+    <t>GSD2</t>
+  </si>
+  <si>
+    <t>GSU4</t>
+  </si>
+  <si>
+    <t>GSD5</t>
+  </si>
+  <si>
+    <t>GSD4</t>
+  </si>
+  <si>
+    <t>GSU5</t>
+  </si>
+  <si>
+    <t>GSU6</t>
+  </si>
+  <si>
+    <t>GSD6</t>
+  </si>
+  <si>
+    <t>GSU7</t>
+  </si>
+  <si>
+    <t>GSD7</t>
+  </si>
+  <si>
+    <t>GSU8</t>
+  </si>
+  <si>
+    <t>GSD8</t>
+  </si>
+  <si>
+    <t>GSU9</t>
+  </si>
+  <si>
+    <t>GSD9</t>
+  </si>
+  <si>
+    <t>GSU10</t>
+  </si>
+  <si>
+    <t>GSD10</t>
+  </si>
+  <si>
+    <t>GSUB11</t>
+  </si>
+  <si>
+    <t>GSUT11</t>
+  </si>
+  <si>
+    <t>GSDB 11</t>
+  </si>
+  <si>
+    <t>GSDT 11</t>
+  </si>
+  <si>
+    <t>GSUB12</t>
+  </si>
+  <si>
+    <t>GSUT12</t>
+  </si>
+  <si>
+    <t>GSDB12</t>
+  </si>
+  <si>
+    <t>GSDT12</t>
+  </si>
+  <si>
+    <t>GSUB13</t>
+  </si>
+  <si>
+    <t>GSUT13</t>
+  </si>
+  <si>
+    <t>GSDB13</t>
+  </si>
+  <si>
+    <t>GSDT13</t>
+  </si>
+  <si>
+    <t>GSUB14</t>
+  </si>
+  <si>
+    <t>GSUT14</t>
+  </si>
+  <si>
+    <t>GSDT14</t>
+  </si>
+  <si>
+    <t>GSDB14</t>
+  </si>
+  <si>
+    <t>GSU15</t>
+  </si>
+  <si>
+    <t>GSD16</t>
+  </si>
+  <si>
+    <t>GSU16</t>
+  </si>
+  <si>
+    <t>Summer 2021</t>
+  </si>
+  <si>
+    <t>Summer 2022</t>
+  </si>
+  <si>
+    <t>Summer 2023</t>
+  </si>
+  <si>
+    <t>Spring 2022</t>
+  </si>
+  <si>
+    <t>Spring 2023</t>
+  </si>
+  <si>
+    <t>Grab Samples</t>
+  </si>
+  <si>
+    <t>SS (uL/L)</t>
+  </si>
+  <si>
+    <t>SSC (mg/L)</t>
+  </si>
+  <si>
+    <t>SRP (mg/L)</t>
+  </si>
+  <si>
+    <t>TP (mg/L)</t>
+  </si>
+  <si>
+    <t>POC (mg/L)</t>
+  </si>
+  <si>
+    <t>DOC (mg/L)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting Concentrations for hysteresis patterns </t>
   </si>
 </sst>
 </file>
@@ -535,7 +583,7 @@
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -599,17 +647,11 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="14">
@@ -687,12 +729,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -771,12 +813,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="247">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -793,25 +859,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -906,15 +965,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1012,7 +1064,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1222,49 +1274,300 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="14" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3720,6 +4023,9 @@
                 </c:pt>
                 <c:pt idx="30" formatCode="0.000">
                   <c:v>8.0850000000000009</c:v>
+                </c:pt>
+                <c:pt idx="31" formatCode="General">
+                  <c:v>2.7629999999999999</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="General">
                   <c:v>3.1280000000000001</c:v>
@@ -10572,7 +10878,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E898195B-C2B1-40DF-A713-EC36D1F92D07}">
-  <dimension ref="A1:Q123"/>
+  <dimension ref="A1:X126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="5" customWidth="1"/>
@@ -10587,321 +10893,322 @@
     <col min="14" max="14" width="12.140625" customWidth="1"/>
     <col min="15" max="15" width="18" customWidth="1"/>
     <col min="16" max="16" width="18.42578125" customWidth="1"/>
+    <col min="17" max="17" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="154" t="s">
+    <row r="1" spans="1:16" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="144" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="155" t="s">
+      <c r="B1" s="145" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="156" t="s">
+      <c r="C1" s="146" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="156" t="s">
+      <c r="D1" s="146" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="156" t="s">
+      <c r="E1" s="146" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="156" t="s">
+      <c r="F1" s="146" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="156" t="s">
+      <c r="G1" s="146" t="s">
         <v>97</v>
       </c>
-      <c r="H1" s="156" t="s">
+      <c r="H1" s="146" t="s">
         <v>72</v>
       </c>
-      <c r="I1" s="156" t="s">
+      <c r="I1" s="146" t="s">
         <v>70</v>
       </c>
-      <c r="J1" s="156" t="s">
+      <c r="J1" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="K1" s="155" t="s">
+      <c r="K1" s="145" t="s">
         <v>117</v>
       </c>
-      <c r="L1" s="156" t="s">
+      <c r="L1" s="146" t="s">
         <v>118</v>
       </c>
-      <c r="M1" s="156" t="s">
+      <c r="M1" s="146" t="s">
         <v>119</v>
       </c>
-      <c r="N1" s="156" t="s">
+      <c r="N1" s="146" t="s">
         <v>61</v>
       </c>
-      <c r="O1" s="156" t="s">
+      <c r="O1" s="146" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="65" t="s">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="55" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="65">
+      <c r="B2" s="55">
         <v>240.43</v>
       </c>
-      <c r="C2" s="65">
+      <c r="C2" s="55">
         <v>0.24310000000000001</v>
       </c>
-      <c r="D2" s="65">
+      <c r="D2" s="55">
         <v>0.37830000000000003</v>
       </c>
-      <c r="E2" s="65">
+      <c r="E2" s="55">
         <f>D2-C2</f>
         <v>0.13520000000000001</v>
       </c>
-      <c r="F2" s="66">
+      <c r="F2" s="56">
         <f>E2/B2*1000*1000</f>
         <v>562.3258328827518</v>
       </c>
-      <c r="G2" s="65">
+      <c r="G2" s="55">
         <v>339.78248000000002</v>
       </c>
-      <c r="H2" s="67">
+      <c r="H2" s="57">
         <v>12.42059499105352</v>
       </c>
-      <c r="I2" s="68">
+      <c r="I2" s="58">
         <f>H2/B2*1000</f>
         <v>51.659921769552554</v>
       </c>
-      <c r="J2" s="69">
+      <c r="J2" s="59">
         <v>9.1790000000000003</v>
       </c>
-      <c r="K2" s="65">
+      <c r="K2" s="55">
         <v>1.19</v>
       </c>
-      <c r="L2" s="65">
+      <c r="L2" s="55">
         <v>6.2E-2</v>
       </c>
-      <c r="M2" s="65">
+      <c r="M2" s="55">
         <v>0.36</v>
       </c>
-      <c r="N2" s="65" t="s">
+      <c r="N2" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="O2" s="20">
+      <c r="O2" s="13">
         <v>44400.659722222219</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="233" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="65" t="s">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="B3" s="65">
+      <c r="B3" s="55">
         <v>257.18</v>
       </c>
-      <c r="C3" s="65">
+      <c r="C3" s="55">
         <v>0.2412</v>
       </c>
-      <c r="D3" s="65">
+      <c r="D3" s="55">
         <v>0.377</v>
       </c>
-      <c r="E3" s="65">
+      <c r="E3" s="55">
         <f t="shared" ref="E3:E37" si="0">D3-C3</f>
         <v>0.1358</v>
       </c>
-      <c r="F3" s="66">
+      <c r="F3" s="56">
         <f t="shared" ref="F3:F32" si="1">E3/B3*1000*1000</f>
         <v>528.03483941208492</v>
       </c>
-      <c r="G3" s="65">
+      <c r="G3" s="55">
         <v>457.12</v>
       </c>
-      <c r="H3" s="67">
+      <c r="H3" s="57">
         <v>12.917667659613238</v>
       </c>
-      <c r="I3" s="68">
+      <c r="I3" s="58">
         <f t="shared" ref="I3:I12" si="2">H3/B3*1000</f>
         <v>50.228119059076278</v>
       </c>
-      <c r="J3" s="69">
+      <c r="J3" s="59">
         <v>12.625</v>
       </c>
-      <c r="K3" s="65">
+      <c r="K3" s="55">
         <v>1.63</v>
       </c>
-      <c r="L3" s="65">
+      <c r="L3" s="55">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="M3" s="65">
+      <c r="M3" s="55">
         <v>0.44500000000000001</v>
       </c>
-      <c r="N3" s="65" t="s">
+      <c r="N3" s="55" t="s">
         <v>74</v>
       </c>
-      <c r="O3" s="20">
+      <c r="O3" s="13">
         <v>44400.67291666667</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="234" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="65" t="s">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="65">
+      <c r="B4" s="55">
         <v>279.39000000000004</v>
       </c>
-      <c r="C4" s="65">
+      <c r="C4" s="55">
         <v>0.23849999999999999</v>
       </c>
-      <c r="D4" s="65">
+      <c r="D4" s="55">
         <v>0.27850000000000003</v>
       </c>
-      <c r="E4" s="65">
+      <c r="E4" s="55">
         <f t="shared" si="0"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="F4" s="66">
+      <c r="F4" s="56">
         <f>E4/B4*1000*1000</f>
         <v>143.16904685207069</v>
       </c>
-      <c r="G4" s="65">
+      <c r="G4" s="55">
         <v>152.79</v>
       </c>
-      <c r="H4" s="67">
+      <c r="H4" s="57">
         <v>4.05181995661607</v>
       </c>
-      <c r="I4" s="68">
+      <c r="I4" s="58">
         <f>H4/B4*1000</f>
         <v>14.502380030123016</v>
       </c>
-      <c r="J4" s="69">
+      <c r="J4" s="59">
         <v>13.388</v>
       </c>
-      <c r="K4" s="65">
+      <c r="K4" s="55">
         <v>0.77</v>
       </c>
-      <c r="L4" s="65">
+      <c r="L4" s="55">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="M4" s="65">
+      <c r="M4" s="55">
         <v>0.248</v>
       </c>
-      <c r="N4" s="65" t="s">
+      <c r="N4" s="55" t="s">
         <v>84</v>
       </c>
-      <c r="O4" s="20">
+      <c r="O4" s="13">
         <v>44400.694444444445</v>
       </c>
-      <c r="P4" s="12" t="s">
+      <c r="P4" s="235" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="65" t="s">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="65">
+      <c r="B5" s="55">
         <v>297.24</v>
       </c>
-      <c r="C5" s="65">
+      <c r="C5" s="55">
         <v>0.24379999999999999</v>
       </c>
-      <c r="D5" s="65">
+      <c r="D5" s="55">
         <v>0.26840000000000003</v>
       </c>
-      <c r="E5" s="65">
+      <c r="E5" s="55">
         <f t="shared" si="0"/>
         <v>2.4600000000000039E-2</v>
       </c>
-      <c r="F5" s="66">
+      <c r="F5" s="56">
         <f t="shared" si="1"/>
         <v>82.761404925313002</v>
       </c>
-      <c r="G5" s="65">
+      <c r="G5" s="55">
         <v>168.45</v>
       </c>
-      <c r="H5" s="67">
+      <c r="H5" s="57">
         <v>3.4720828614205299</v>
       </c>
-      <c r="I5" s="68">
+      <c r="I5" s="58">
         <f t="shared" si="2"/>
         <v>11.68107543204323</v>
       </c>
-      <c r="J5" s="69">
+      <c r="J5" s="59">
         <v>12.997</v>
       </c>
-      <c r="K5" s="65">
+      <c r="K5" s="55">
         <v>0.5</v>
       </c>
-      <c r="L5" s="65">
+      <c r="L5" s="55">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="M5" s="65">
+      <c r="M5" s="55">
         <v>0.214</v>
       </c>
-      <c r="N5" s="65" t="s">
+      <c r="N5" s="55" t="s">
         <v>75</v>
       </c>
-      <c r="O5" s="20">
+      <c r="O5" s="13">
         <v>44400.704861111109</v>
       </c>
-      <c r="P5" s="9" t="s">
+      <c r="P5" s="236" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="65" t="s">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="55" t="s">
         <v>89</v>
       </c>
-      <c r="B6" s="65">
+      <c r="B6" s="55">
         <v>262.73</v>
       </c>
-      <c r="C6" s="65">
+      <c r="C6" s="55">
         <v>0.2414</v>
       </c>
-      <c r="D6" s="65">
+      <c r="D6" s="55">
         <v>0.25109999999999999</v>
       </c>
-      <c r="E6" s="65">
+      <c r="E6" s="55">
         <f t="shared" si="0"/>
         <v>9.6999999999999864E-3</v>
       </c>
-      <c r="F6" s="66">
+      <c r="F6" s="56">
         <f t="shared" si="1"/>
         <v>36.920031971986397</v>
       </c>
-      <c r="G6" s="65">
+      <c r="G6" s="55">
         <v>43.15</v>
       </c>
-      <c r="H6" s="67">
+      <c r="H6" s="57">
         <v>1.6843076180902734</v>
       </c>
-      <c r="I6" s="68">
+      <c r="I6" s="58">
         <f t="shared" si="2"/>
         <v>6.4107928979951785</v>
       </c>
-      <c r="J6" s="69">
+      <c r="J6" s="59">
         <v>12.868</v>
       </c>
-      <c r="K6" s="65">
+      <c r="K6" s="55">
         <v>0.1</v>
       </c>
-      <c r="L6" s="65">
+      <c r="L6" s="55">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="M6" s="65">
+      <c r="M6" s="55">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="N6" s="65" t="s">
+      <c r="N6" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="O6" s="20">
+      <c r="O6" s="13">
         <v>44400.804861111108</v>
       </c>
-      <c r="P6" s="11" t="s">
+      <c r="P6" s="237" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>90</v>
       </c>
@@ -10918,21 +11225,21 @@
         <f t="shared" si="0"/>
         <v>5.9999999999999776E-3</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="10">
         <f t="shared" si="1"/>
         <v>22.011886418665991</v>
       </c>
       <c r="G7" s="4">
         <v>17.7</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="18">
         <v>1.3097205793723499</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="19">
         <f t="shared" si="2"/>
         <v>4.8049034388889487</v>
       </c>
-      <c r="J7" s="33">
+      <c r="J7" s="26">
         <v>11.551</v>
       </c>
       <c r="K7" s="4">
@@ -10947,14 +11254,14 @@
       <c r="N7" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="O7" s="20">
+      <c r="O7" s="13">
         <v>44400.876388888886</v>
       </c>
-      <c r="P7" s="16" t="s">
+      <c r="P7" s="238" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>91</v>
       </c>
@@ -10971,21 +11278,21 @@
         <f t="shared" si="0"/>
         <v>1.5399999999999997E-2</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="10">
         <f t="shared" si="1"/>
         <v>68.980963045912645</v>
       </c>
       <c r="G8" s="4">
         <v>92.06</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="18">
         <v>2.4792040459396865</v>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="19">
         <f t="shared" si="2"/>
         <v>11.105057316639133</v>
       </c>
-      <c r="J8" s="33">
+      <c r="J8" s="26">
         <v>4.5220000000000002</v>
       </c>
       <c r="K8" s="4">
@@ -11000,14 +11307,14 @@
       <c r="N8" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="O8" s="20">
+      <c r="O8" s="13">
         <v>44400.620833333334</v>
       </c>
-      <c r="P8" s="15" t="s">
+      <c r="P8" s="239" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>92</v>
       </c>
@@ -11024,21 +11331,21 @@
         <f t="shared" si="0"/>
         <v>2.579999999999999E-2</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="10">
         <f t="shared" si="1"/>
         <v>124.47532204371103</v>
       </c>
       <c r="G9" s="4">
         <v>95.69</v>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="18">
         <v>6.1584312598812998</v>
       </c>
-      <c r="I9" s="26">
+      <c r="I9" s="19">
         <f t="shared" si="2"/>
         <v>29.712120711541949</v>
       </c>
-      <c r="J9" s="33">
+      <c r="J9" s="26">
         <v>4.4359999999999999</v>
       </c>
       <c r="K9" s="4">
@@ -11053,11 +11360,11 @@
       <c r="N9" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="O9" s="20">
+      <c r="O9" s="13">
         <v>44400.626388888886</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>93</v>
       </c>
@@ -11074,21 +11381,21 @@
         <f t="shared" si="0"/>
         <v>9.1399999999999981E-2</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="10">
         <f t="shared" si="1"/>
         <v>359.22024838861807</v>
       </c>
       <c r="G10" s="4">
         <v>403.51499999999999</v>
       </c>
-      <c r="H10" s="25">
+      <c r="H10" s="18">
         <v>10.503118006915519</v>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="19">
         <f t="shared" si="2"/>
         <v>41.279350758196514</v>
       </c>
-      <c r="J10" s="33">
+      <c r="J10" s="26">
         <v>12.442</v>
       </c>
       <c r="K10" s="4">
@@ -11103,11 +11410,11 @@
       <c r="N10" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="O10" s="20">
+      <c r="O10" s="13">
         <v>44400.675694444442</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>94</v>
       </c>
@@ -11124,21 +11431,21 @@
         <f t="shared" si="0"/>
         <v>2.7199999999999974E-2</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="10">
         <f t="shared" si="1"/>
         <v>86.111374932725383</v>
       </c>
       <c r="G11" s="4">
         <v>124.04</v>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="18">
         <v>3.0083665576103797</v>
       </c>
-      <c r="I11" s="26">
+      <c r="I11" s="19">
         <f t="shared" si="2"/>
         <v>9.5240654624066199</v>
       </c>
-      <c r="J11" s="33">
+      <c r="J11" s="26">
         <v>12.977</v>
       </c>
       <c r="K11" s="4">
@@ -11153,11 +11460,11 @@
       <c r="N11" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="O11" s="20">
+      <c r="O11" s="13">
         <v>44400.706944444442</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>95</v>
       </c>
@@ -11174,21 +11481,21 @@
         <f>D12-C12</f>
         <v>8.3000000000000018E-3</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="10">
         <f>E12/B12*1000*1000</f>
         <v>37.228078044404583</v>
       </c>
       <c r="G12" s="4">
         <v>65.3</v>
       </c>
-      <c r="H12" s="25">
+      <c r="H12" s="18">
         <v>1.4577906907522695</v>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="19">
         <f t="shared" si="2"/>
         <v>6.5386440491243301</v>
       </c>
-      <c r="J12" s="33">
+      <c r="J12" s="26">
         <v>13.108000000000001</v>
       </c>
       <c r="K12" s="4">
@@ -11203,111 +11510,111 @@
       <c r="N12" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="O12" s="20">
+      <c r="O12" s="13">
         <v>44400.748611111114</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="71" t="s">
+    <row r="13" spans="1:16" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="B13" s="71">
+      <c r="B13" s="61">
         <v>213.57</v>
       </c>
-      <c r="C13" s="71">
+      <c r="C13" s="61">
         <v>0.24249999999999999</v>
       </c>
-      <c r="D13" s="71">
+      <c r="D13" s="61">
         <v>0.249</v>
       </c>
-      <c r="E13" s="71">
+      <c r="E13" s="61">
         <f t="shared" si="0"/>
         <v>6.5000000000000058E-3</v>
       </c>
-      <c r="F13" s="72">
+      <c r="F13" s="62">
         <f t="shared" si="1"/>
         <v>30.434986187198604</v>
       </c>
-      <c r="G13" s="71">
+      <c r="G13" s="61">
         <v>42.87</v>
       </c>
-      <c r="H13" s="73">
+      <c r="H13" s="63">
         <v>1.2189465182507433</v>
       </c>
-      <c r="I13" s="74">
+      <c r="I13" s="64">
         <f>H13/B13*1000</f>
         <v>5.7074800685992573</v>
       </c>
-      <c r="J13" s="75">
+      <c r="J13" s="65">
         <v>12.073</v>
       </c>
-      <c r="K13" s="71">
+      <c r="K13" s="61">
         <v>0.06</v>
       </c>
-      <c r="L13" s="71">
+      <c r="L13" s="61">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="M13" s="71">
+      <c r="M13" s="61">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="N13" s="71" t="s">
+      <c r="N13" s="61" t="s">
         <v>83</v>
       </c>
-      <c r="O13" s="76">
+      <c r="O13" s="66">
         <v>44400.842361111114</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="80" t="s">
+    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="70" t="s">
         <v>98</v>
       </c>
-      <c r="B14" s="80">
+      <c r="B14" s="70">
         <v>119.53</v>
       </c>
-      <c r="C14" s="80">
+      <c r="C14" s="70">
         <v>0.24010000000000001</v>
       </c>
-      <c r="D14" s="80">
+      <c r="D14" s="70">
         <v>0.247</v>
       </c>
-      <c r="E14" s="80">
+      <c r="E14" s="70">
         <f>D14-C14</f>
         <v>6.8999999999999895E-3</v>
       </c>
-      <c r="F14" s="81">
+      <c r="F14" s="71">
         <f>E14/B14*1000*1000</f>
         <v>57.726093867648203</v>
       </c>
-      <c r="G14" s="80">
+      <c r="G14" s="70">
         <v>206.82</v>
       </c>
-      <c r="H14" s="82">
+      <c r="H14" s="72">
         <v>0.81093355630223884</v>
       </c>
-      <c r="I14" s="83">
+      <c r="I14" s="73">
         <f>H14/B14*1000</f>
         <v>6.7843516799317234</v>
       </c>
-      <c r="J14" s="84">
+      <c r="J14" s="74">
         <v>4.9130000000000003</v>
       </c>
-      <c r="K14" s="80">
+      <c r="K14" s="70">
         <v>0.48</v>
       </c>
-      <c r="L14" s="80">
+      <c r="L14" s="70">
         <v>1.49059E-2</v>
       </c>
-      <c r="M14" s="80">
+      <c r="M14" s="70">
         <v>9.9315000000000001E-2</v>
       </c>
-      <c r="N14" s="85">
+      <c r="N14" s="75">
         <v>95</v>
       </c>
-      <c r="O14" s="86">
+      <c r="O14" s="76">
         <v>44776.626388888886</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>99</v>
       </c>
@@ -11324,21 +11631,21 @@
         <f t="shared" ref="E15:E20" si="3">D15-C15</f>
         <v>5.7000000000000106E-3</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="11">
         <f t="shared" ref="F15:F20" si="4">E15/B15*1000*1000</f>
         <v>48.064760941057514</v>
       </c>
       <c r="G15" s="3">
         <v>142.53</v>
       </c>
-      <c r="H15" s="27">
+      <c r="H15" s="20">
         <v>0.67779828329961622</v>
       </c>
-      <c r="I15" s="28">
+      <c r="I15" s="21">
         <f t="shared" ref="I15:I20" si="5">H15/B15*1000</f>
         <v>5.7154758689570473</v>
       </c>
-      <c r="J15" s="34">
+      <c r="J15" s="27">
         <v>6.55</v>
       </c>
       <c r="K15" s="3">
@@ -11350,16 +11657,14 @@
       <c r="M15" s="3">
         <v>0.1012671</v>
       </c>
-      <c r="N15" s="44">
+      <c r="N15" s="37">
         <v>96</v>
       </c>
-      <c r="O15" s="20">
+      <c r="O15" s="13">
         <v>44776.636805555558</v>
       </c>
-      <c r="P15" s="50"/>
-      <c r="Q15" s="50"/>
     </row>
-    <row r="16" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>100</v>
       </c>
@@ -11376,21 +11681,21 @@
         <f t="shared" si="3"/>
         <v>6.7000000000000115E-3</v>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="11">
         <f t="shared" si="4"/>
         <v>55.003694277973992</v>
       </c>
       <c r="G16" s="3">
         <v>55.06</v>
       </c>
-      <c r="H16" s="87">
+      <c r="H16" s="77">
         <v>0.63223097869840805</v>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="21">
         <f t="shared" si="5"/>
         <v>5.1903043978196211</v>
       </c>
-      <c r="J16" s="34">
+      <c r="J16" s="27">
         <v>8.0350000000000001</v>
       </c>
       <c r="K16" s="3">
@@ -11402,14 +11707,13 @@
       <c r="M16" s="3">
         <v>8.5650299999999999E-2</v>
       </c>
-      <c r="N16" s="44">
+      <c r="N16" s="37">
         <v>97</v>
       </c>
-      <c r="O16" s="20">
+      <c r="O16" s="13">
         <v>44776.657638888886</v>
       </c>
-      <c r="P16" s="51"/>
-      <c r="Q16" s="50"/>
+      <c r="P16" s="42"/>
     </row>
     <row r="17" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
@@ -11428,34 +11732,32 @@
         <f t="shared" si="3"/>
         <v>5.2999999999999992E-3</v>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="11">
         <f t="shared" si="4"/>
         <v>45.164039198977413</v>
       </c>
       <c r="G17" s="3">
         <v>66.040000000000006</v>
       </c>
-      <c r="H17" s="27">
+      <c r="H17" s="20">
         <v>0.64059153994189177</v>
       </c>
-      <c r="I17" s="28">
+      <c r="I17" s="21">
         <f t="shared" si="5"/>
         <v>5.4588115887677189</v>
       </c>
-      <c r="J17" s="34">
+      <c r="J17" s="27">
         <v>8.6910000000000007</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
-      <c r="N17" s="44">
+      <c r="N17" s="37">
         <v>98</v>
       </c>
-      <c r="O17" s="20">
+      <c r="O17" s="13">
         <v>44776.678472222222</v>
       </c>
-      <c r="P17" s="50"/>
-      <c r="Q17" s="50"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
@@ -11474,34 +11776,32 @@
         <f>D18-C18</f>
         <v>2.0999999999999908E-3</v>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="11">
         <f t="shared" si="4"/>
         <v>17.425939756036765</v>
       </c>
       <c r="G18" s="3">
         <v>39.15</v>
       </c>
-      <c r="H18" s="27">
+      <c r="H18" s="20">
         <v>0.3795284226614497</v>
       </c>
-      <c r="I18" s="28">
+      <c r="I18" s="21">
         <f>H19/B19*1000</f>
         <v>2.0882180227795768</v>
       </c>
-      <c r="J18" s="34">
+      <c r="J18" s="27">
         <v>8.1240000000000006</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
-      <c r="N18" s="44">
+      <c r="N18" s="37">
         <v>99</v>
       </c>
-      <c r="O18" s="20">
+      <c r="O18" s="13">
         <v>44776.751388888886</v>
       </c>
-      <c r="P18" s="50"/>
-      <c r="Q18" s="50"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
@@ -11520,21 +11820,21 @@
         <f>D19-C19</f>
         <v>1.4000000000000123E-3</v>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="11">
         <f t="shared" si="4"/>
         <v>11.446324912108677</v>
       </c>
       <c r="G19" s="3">
         <v>23.32</v>
       </c>
-      <c r="H19" s="27">
+      <c r="H19" s="20">
         <v>0.25540994636617004</v>
       </c>
-      <c r="I19" s="28">
+      <c r="I19" s="21">
         <f>H18/B18*1000</f>
         <v>3.1493521090486243</v>
       </c>
-      <c r="J19" s="34">
+      <c r="J19" s="27">
         <v>8.0730000000000004</v>
       </c>
       <c r="K19" s="3">
@@ -11546,931 +11846,932 @@
       <c r="M19" s="3">
         <v>4.46562E-2</v>
       </c>
-      <c r="N19" s="44">
+      <c r="N19" s="37">
         <v>100</v>
       </c>
-      <c r="O19" s="20">
+      <c r="O19" s="13">
         <v>44776.761805555558</v>
       </c>
-      <c r="P19" s="52"/>
-      <c r="Q19" s="52"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
     </row>
     <row r="20" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="88" t="s">
+      <c r="A20" s="78" t="s">
         <v>104</v>
       </c>
-      <c r="B20" s="88">
+      <c r="B20" s="78">
         <v>122.5</v>
       </c>
-      <c r="C20" s="88">
+      <c r="C20" s="78">
         <v>0.2417</v>
       </c>
-      <c r="D20" s="88">
+      <c r="D20" s="78">
         <v>0.24249999999999999</v>
       </c>
-      <c r="E20" s="88">
+      <c r="E20" s="78">
         <f t="shared" si="3"/>
         <v>7.9999999999999516E-4</v>
       </c>
-      <c r="F20" s="89">
+      <c r="F20" s="79">
         <f t="shared" si="4"/>
         <v>6.5306122448979194</v>
       </c>
-      <c r="G20" s="88">
+      <c r="G20" s="78">
         <v>0</v>
       </c>
-      <c r="H20" s="90">
+      <c r="H20" s="80">
         <v>0.26461862273170189</v>
       </c>
-      <c r="I20" s="91">
+      <c r="I20" s="81">
         <f t="shared" si="5"/>
         <v>2.1601520222996071</v>
       </c>
-      <c r="J20" s="92">
+      <c r="J20" s="82">
         <v>3.1280000000000001</v>
       </c>
-      <c r="K20" s="88"/>
-      <c r="L20" s="88"/>
-      <c r="M20" s="88"/>
-      <c r="N20" s="93">
+      <c r="K20" s="78"/>
+      <c r="L20" s="78"/>
+      <c r="M20" s="78"/>
+      <c r="N20" s="83">
         <v>101</v>
       </c>
-      <c r="O20" s="76">
+      <c r="O20" s="66">
         <v>44776.793055555558</v>
       </c>
-      <c r="Q20" s="50"/>
     </row>
     <row r="21" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="94" t="s">
+      <c r="A21" s="84" t="s">
         <v>105</v>
       </c>
-      <c r="B21" s="94">
+      <c r="B21" s="84">
         <v>117.93</v>
       </c>
-      <c r="C21" s="94">
+      <c r="C21" s="84">
         <v>0.24030000000000001</v>
       </c>
-      <c r="D21" s="94">
+      <c r="D21" s="84">
         <v>0.24129999999999999</v>
       </c>
-      <c r="E21" s="94">
+      <c r="E21" s="84">
         <f t="shared" si="0"/>
         <v>9.9999999999997313E-4</v>
       </c>
-      <c r="F21" s="95">
+      <c r="F21" s="85">
         <f t="shared" si="1"/>
         <v>8.4796065462560257</v>
       </c>
-      <c r="G21" s="94">
+      <c r="G21" s="84">
         <v>0</v>
       </c>
-      <c r="H21" s="96">
+      <c r="H21" s="86">
         <v>0.17978326915702031</v>
       </c>
-      <c r="I21" s="97">
-        <f t="shared" ref="I15:I77" si="6">H21/B21*1000</f>
+      <c r="I21" s="87">
+        <f t="shared" ref="I21:I77" si="6">H21/B21*1000</f>
         <v>1.5244913860512195</v>
       </c>
-      <c r="J21" s="98">
+      <c r="J21" s="88">
         <v>3.359</v>
       </c>
-      <c r="K21" s="94"/>
-      <c r="L21" s="94"/>
-      <c r="M21" s="94"/>
-      <c r="N21" s="99">
+      <c r="K21" s="84"/>
+      <c r="L21" s="84"/>
+      <c r="M21" s="84"/>
+      <c r="N21" s="89">
         <v>102</v>
       </c>
-      <c r="O21" s="86">
+      <c r="O21" s="76">
         <v>44781.571527777778</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="6">
         <v>121</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="6">
         <v>0.24199999999999999</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="6">
         <v>0.24329999999999999</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="6">
         <f t="shared" si="0"/>
         <v>1.2999999999999956E-3</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="7">
         <f t="shared" si="1"/>
         <v>10.743801652892525</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="6">
         <v>0</v>
       </c>
-      <c r="H22" s="24">
+      <c r="H22" s="17">
         <v>0.20670824007668936</v>
       </c>
-      <c r="I22" s="29">
+      <c r="I22" s="22">
         <f t="shared" si="6"/>
         <v>1.7083325626172676</v>
       </c>
-      <c r="J22" s="35">
+      <c r="J22" s="28">
         <v>3.4239999999999999</v>
       </c>
-      <c r="K22" s="8">
+      <c r="K22" s="6">
         <v>0.1</v>
       </c>
-      <c r="L22" s="8">
+      <c r="L22" s="6">
         <v>1.1474099999999999E-2</v>
       </c>
-      <c r="M22" s="8">
+      <c r="M22" s="6">
         <v>2.90394E-2</v>
       </c>
-      <c r="N22" s="30">
+      <c r="N22" s="23">
         <v>103</v>
       </c>
-      <c r="O22" s="20">
+      <c r="O22" s="13">
         <v>44781.581944444442</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="6">
         <v>120.98</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="6">
         <v>0.23780000000000001</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="6">
         <v>0.2402</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="6">
         <f t="shared" si="0"/>
         <v>2.3999999999999855E-3</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="7">
         <f t="shared" si="1"/>
         <v>19.837989750371843</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="6">
         <v>52.87</v>
       </c>
-      <c r="H23" s="24">
+      <c r="H23" s="17">
         <v>0.37004991918953345</v>
       </c>
-      <c r="I23" s="29">
+      <c r="I23" s="22">
         <f t="shared" si="6"/>
         <v>3.0587693766699737</v>
       </c>
-      <c r="J23" s="35">
+      <c r="J23" s="28">
         <v>3.9</v>
       </c>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="30">
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="23">
         <v>104</v>
       </c>
-      <c r="O23" s="20">
+      <c r="O23" s="13">
         <v>44781.592361111114</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="6">
         <v>122.22</v>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="6">
         <v>0.2427</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="6">
         <v>0.2487</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="6">
         <f t="shared" si="0"/>
         <v>6.0000000000000053E-3</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="7">
         <f t="shared" si="1"/>
         <v>49.091801669121296</v>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="6">
         <v>204.03</v>
       </c>
-      <c r="H24" s="24">
+      <c r="H24" s="17">
         <v>0.65572150300064624</v>
       </c>
-      <c r="I24" s="29">
+      <c r="I24" s="22">
         <f t="shared" si="6"/>
         <v>5.365091662580971</v>
       </c>
-      <c r="J24" s="35">
+      <c r="J24" s="28">
         <v>5.2789999999999999</v>
       </c>
-      <c r="K24" s="8">
+      <c r="K24" s="6">
         <v>0.11</v>
       </c>
-      <c r="L24" s="8">
+      <c r="L24" s="6">
         <v>2.6917199999999999E-2</v>
       </c>
-      <c r="M24" s="8">
+      <c r="M24" s="6">
         <v>6.3819200000000006E-2</v>
       </c>
-      <c r="N24" s="30">
+      <c r="N24" s="23">
         <v>105</v>
       </c>
-      <c r="O24" s="20">
+      <c r="O24" s="13">
         <v>44781.602777777778</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="6">
         <v>121.52</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="6">
         <v>0.23899999999999999</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="6">
         <v>0.24329999999999999</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E25" s="6">
         <f t="shared" si="0"/>
         <v>4.2999999999999983E-3</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="7">
         <f t="shared" si="1"/>
         <v>35.385121790651731</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="6">
         <v>105.77</v>
       </c>
-      <c r="H25" s="24">
+      <c r="H25" s="17">
         <v>0.62239773814796806</v>
       </c>
-      <c r="I25" s="29">
+      <c r="I25" s="22">
         <f t="shared" si="6"/>
         <v>5.1217720387423311</v>
       </c>
-      <c r="J25" s="35">
+      <c r="J25" s="28">
         <v>7.2069999999999999</v>
       </c>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="30">
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="23">
         <v>106</v>
       </c>
-      <c r="O25" s="20">
+      <c r="O25" s="13">
         <v>44781.613194444442</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="6">
         <v>122.46</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="6">
         <v>0.23760000000000001</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="6">
         <v>0.24049999999999999</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="6">
         <f t="shared" si="0"/>
         <v>2.8999999999999859E-3</v>
       </c>
-      <c r="F26" s="10">
+      <c r="F26" s="7">
         <f t="shared" si="1"/>
         <v>23.681202025150956</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="6">
         <v>68.83</v>
       </c>
-      <c r="H26" s="24">
+      <c r="H26" s="17">
         <v>0.27757088646634936</v>
       </c>
-      <c r="I26" s="29">
+      <c r="I26" s="22">
         <f t="shared" si="6"/>
         <v>2.2666249098999622</v>
       </c>
-      <c r="J26" s="35">
+      <c r="J26" s="28">
         <v>7.75</v>
       </c>
-      <c r="K26" s="8">
+      <c r="K26" s="6">
         <v>0.17</v>
       </c>
-      <c r="L26" s="8">
+      <c r="L26" s="6">
         <v>5.09398E-2</v>
       </c>
-      <c r="M26" s="8">
+      <c r="M26" s="6">
         <v>7.3937699999999995E-2</v>
       </c>
-      <c r="N26" s="30">
+      <c r="N26" s="23">
         <v>107</v>
       </c>
-      <c r="O26" s="20">
+      <c r="O26" s="13">
         <v>44781.640972222223</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="6">
         <v>121.35</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="6">
         <v>0.24160000000000001</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="6">
         <v>0.24279999999999999</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="6">
         <f t="shared" si="0"/>
         <v>1.1999999999999789E-3</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="7">
         <f t="shared" si="1"/>
         <v>9.8887515451172572</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G27" s="6">
         <v>36.65</v>
       </c>
-      <c r="H27" s="24">
+      <c r="H27" s="17">
         <v>0.23932675048380125</v>
       </c>
-      <c r="I27" s="29">
+      <c r="I27" s="22">
         <f t="shared" si="6"/>
         <v>1.9722023113621858</v>
       </c>
-      <c r="J27" s="35">
+      <c r="J27" s="28">
         <v>8.41</v>
       </c>
-      <c r="K27" s="8">
+      <c r="K27" s="6">
         <v>0.28999999999999998</v>
       </c>
-      <c r="L27" s="8">
+      <c r="L27" s="6">
         <v>3.8928499999999998E-2</v>
       </c>
-      <c r="M27" s="8">
+      <c r="M27" s="6">
         <v>4.0751999999999997E-2</v>
       </c>
-      <c r="N27" s="30">
+      <c r="N27" s="23">
         <v>108</v>
       </c>
-      <c r="O27" s="20">
+      <c r="O27" s="13">
         <v>44781.675694444442</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="6">
         <v>119.95</v>
       </c>
-      <c r="C28" s="8">
+      <c r="C28" s="6">
         <v>0.24410000000000001</v>
       </c>
-      <c r="D28" s="10">
+      <c r="D28" s="7">
         <v>0.24505360250000002</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="7">
         <f t="shared" si="0"/>
         <v>9.5360250000001145E-4</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="7">
         <f t="shared" si="1"/>
         <v>7.9500000000000943</v>
       </c>
-      <c r="G28" s="8">
+      <c r="G28" s="6">
         <v>25.92</v>
       </c>
-      <c r="H28" s="24">
+      <c r="H28" s="17">
         <v>0.18463063927826467</v>
       </c>
-      <c r="I28" s="29">
+      <c r="I28" s="22">
         <f t="shared" si="6"/>
         <v>1.5392300064882425</v>
       </c>
-      <c r="J28" s="35">
+      <c r="J28" s="28">
         <v>2.7050000000000001</v>
       </c>
-      <c r="K28" s="10"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="30">
+      <c r="K28" s="7"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="23">
         <v>110</v>
       </c>
-      <c r="O28" s="20">
+      <c r="O28" s="13">
         <v>44781.696527777778</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="6">
         <v>122.53</v>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="6">
         <v>0.2424</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="6">
         <v>0.2429</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="6">
         <f t="shared" si="0"/>
         <v>5.0000000000000044E-4</v>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="7">
         <f t="shared" si="1"/>
         <v>4.080633314290381</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="6">
         <v>21.67</v>
       </c>
-      <c r="H29" s="24">
+      <c r="H29" s="17">
         <v>0.18608289987021998</v>
       </c>
-      <c r="I29" s="29">
+      <c r="I29" s="22">
         <f>H29/B29*1000</f>
         <v>1.5186721608603606</v>
       </c>
-      <c r="J29" s="35">
+      <c r="J29" s="28">
         <v>8.4209999999999994</v>
       </c>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="30">
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="23">
         <v>111</v>
       </c>
-      <c r="O29" s="20">
+      <c r="O29" s="13">
         <v>44781.706944444442</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="6">
         <v>121.54</v>
       </c>
-      <c r="C30" s="8">
+      <c r="C30" s="6">
         <v>0.23649999999999999</v>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="6">
         <v>0.23669999999999999</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E30" s="6">
         <f t="shared" si="0"/>
         <v>2.0000000000000573E-4</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="7">
         <f t="shared" si="1"/>
         <v>1.6455487905216861</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="6">
         <v>19.05</v>
       </c>
-      <c r="H30" s="24">
+      <c r="H30" s="17">
         <v>0.19585625568188858</v>
       </c>
-      <c r="I30" s="29">
+      <c r="I30" s="22">
         <f t="shared" si="6"/>
         <v>1.6114551232671432</v>
       </c>
-      <c r="J30" s="35">
+      <c r="J30" s="28">
         <v>8.1829999999999998</v>
       </c>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
-      <c r="N30" s="30">
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="23">
         <v>112</v>
       </c>
-      <c r="O30" s="20">
+      <c r="O30" s="13">
         <v>44781.727777777778</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31" s="6">
         <v>118.38</v>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="6">
         <v>0.23619999999999999</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="6">
         <v>0.23630000000000001</v>
       </c>
-      <c r="E31" s="8">
+      <c r="E31" s="6">
         <f t="shared" si="0"/>
         <v>1.0000000000001674E-4</v>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="7">
         <f t="shared" si="1"/>
         <v>0.84473728670397652</v>
       </c>
-      <c r="G31" s="8">
+      <c r="G31" s="6">
         <v>18.36</v>
       </c>
-      <c r="H31" s="24">
+      <c r="H31" s="17">
         <v>0.20604215861937406</v>
       </c>
-      <c r="I31" s="29">
+      <c r="I31" s="22">
         <f t="shared" si="6"/>
         <v>1.7405149401873126</v>
       </c>
-      <c r="J31" s="35">
+      <c r="J31" s="28">
         <v>2.742</v>
       </c>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
-      <c r="M31" s="8"/>
-      <c r="N31" s="30">
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="23">
         <v>113</v>
       </c>
-      <c r="O31" s="20">
+      <c r="O31" s="13">
         <v>44781.748611111114</v>
       </c>
     </row>
     <row r="32" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="100" t="s">
+      <c r="A32" s="90" t="s">
         <v>116</v>
       </c>
-      <c r="B32" s="100">
+      <c r="B32" s="90">
         <v>122.39</v>
       </c>
-      <c r="C32" s="100">
+      <c r="C32" s="90">
         <v>0.23980000000000001</v>
       </c>
-      <c r="D32" s="100">
+      <c r="D32" s="90">
         <v>0.24049999999999999</v>
       </c>
-      <c r="E32" s="100">
+      <c r="E32" s="90">
         <f t="shared" si="0"/>
         <v>6.9999999999997842E-4</v>
       </c>
-      <c r="F32" s="101">
+      <c r="F32" s="91">
         <f t="shared" si="1"/>
         <v>5.7194215213659483</v>
       </c>
-      <c r="G32" s="100">
+      <c r="G32" s="90">
         <v>0</v>
       </c>
-      <c r="H32" s="102">
+      <c r="H32" s="92">
         <v>0.18269018151077018</v>
       </c>
-      <c r="I32" s="103">
+      <c r="I32" s="93">
         <f t="shared" si="6"/>
         <v>1.4926887941071181</v>
       </c>
-      <c r="J32" s="104">
+      <c r="J32" s="94">
         <v>8.0850000000000009</v>
       </c>
-      <c r="K32" s="100">
+      <c r="K32" s="90">
         <v>0.06</v>
       </c>
-      <c r="L32" s="100">
+      <c r="L32" s="90">
         <v>3.0349000000000001E-2</v>
       </c>
-      <c r="M32" s="100">
+      <c r="M32" s="90">
         <v>3.4895700000000002E-2</v>
       </c>
-      <c r="N32" s="105">
+      <c r="N32" s="95">
         <v>114</v>
       </c>
-      <c r="O32" s="76">
+      <c r="O32" s="66">
         <v>44781.759027777778</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" s="106" t="s">
+      <c r="A33" s="96" t="s">
         <v>62</v>
       </c>
-      <c r="B33" s="106">
+      <c r="B33" s="96">
         <v>100</v>
       </c>
-      <c r="C33" s="106">
+      <c r="C33" s="96">
         <v>0.2336</v>
       </c>
-      <c r="D33" s="106">
+      <c r="D33" s="96">
         <v>0.25230000000000002</v>
       </c>
-      <c r="E33" s="106">
+      <c r="E33" s="96">
         <f t="shared" si="0"/>
         <v>1.8700000000000022E-2</v>
       </c>
-      <c r="F33" s="107">
+      <c r="F33" s="97">
         <f>E33/B33*1000*1000</f>
         <v>187.00000000000023</v>
       </c>
-      <c r="G33" s="107"/>
-      <c r="H33" s="108">
+      <c r="G33" s="97"/>
+      <c r="H33" s="98">
         <v>2.9943162613702401</v>
       </c>
-      <c r="I33" s="109">
+      <c r="I33" s="99">
         <f>H33/B33*1000</f>
         <v>29.943162613702402</v>
       </c>
-      <c r="J33" s="110"/>
-      <c r="K33" s="106">
+      <c r="J33" s="100">
+        <v>2.7629999999999999</v>
+      </c>
+      <c r="K33" s="96">
         <v>1.89E-2</v>
       </c>
-      <c r="L33" s="106"/>
-      <c r="M33" s="106"/>
-      <c r="N33" s="111">
+      <c r="L33" s="96"/>
+      <c r="M33" s="96"/>
+      <c r="N33" s="101">
         <v>439</v>
       </c>
-      <c r="O33" s="86">
+      <c r="O33" s="76">
         <v>45136.619444444441</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" s="53" t="s">
+      <c r="A34" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="B34" s="53">
+      <c r="B34" s="43">
         <v>90</v>
       </c>
-      <c r="C34" s="53">
+      <c r="C34" s="43">
         <v>0.2349</v>
       </c>
-      <c r="D34" s="53">
+      <c r="D34" s="43">
         <v>0.24479999999999999</v>
       </c>
-      <c r="E34" s="53">
+      <c r="E34" s="43">
         <f t="shared" si="0"/>
         <v>9.8999999999999921E-3</v>
       </c>
-      <c r="F34" s="54">
+      <c r="F34" s="44">
         <f t="shared" ref="F34:F50" si="7">E34/B34*1000*1000</f>
         <v>109.9999999999999</v>
       </c>
-      <c r="G34" s="53">
+      <c r="G34" s="43">
         <v>271.06</v>
       </c>
-      <c r="H34" s="55">
+      <c r="H34" s="45">
         <v>0.86155236948536007</v>
       </c>
-      <c r="I34" s="56">
+      <c r="I34" s="46">
         <f t="shared" si="6"/>
         <v>9.5728041053928887</v>
       </c>
-      <c r="J34" s="57">
+      <c r="J34" s="47">
         <v>3.1280000000000001</v>
       </c>
-      <c r="K34" s="53">
+      <c r="K34" s="43">
         <v>6.9500000000000006E-2</v>
       </c>
-      <c r="L34" s="53"/>
-      <c r="M34" s="53"/>
-      <c r="N34" s="58">
+      <c r="L34" s="43"/>
+      <c r="M34" s="43"/>
+      <c r="N34" s="48">
         <v>440</v>
       </c>
-      <c r="O34" s="20">
+      <c r="O34" s="13">
         <v>45136.629861111112</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="53" t="s">
+      <c r="A35" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="53">
+      <c r="B35" s="43">
         <v>90</v>
       </c>
-      <c r="C35" s="53">
+      <c r="C35" s="43">
         <v>0.23330000000000001</v>
       </c>
-      <c r="D35" s="53">
+      <c r="D35" s="43">
         <v>0.23810000000000001</v>
       </c>
-      <c r="E35" s="53">
+      <c r="E35" s="43">
         <f t="shared" si="0"/>
         <v>4.7999999999999987E-3</v>
       </c>
-      <c r="F35" s="54">
+      <c r="F35" s="44">
         <f t="shared" si="7"/>
         <v>53.333333333333321</v>
       </c>
-      <c r="G35" s="53">
+      <c r="G35" s="43">
         <v>249.50899999999999</v>
       </c>
-      <c r="H35" s="55">
+      <c r="H35" s="45">
         <v>0.62402435211444007</v>
       </c>
-      <c r="I35" s="56">
+      <c r="I35" s="46">
         <f t="shared" si="6"/>
         <v>6.9336039123826678</v>
       </c>
-      <c r="J35" s="57">
+      <c r="J35" s="47">
         <v>3.5529999999999999</v>
       </c>
-      <c r="K35" s="53">
+      <c r="K35" s="43">
         <v>4.1099999999999998E-2</v>
       </c>
-      <c r="L35" s="53"/>
-      <c r="M35" s="53"/>
-      <c r="N35" s="58">
+      <c r="L35" s="43"/>
+      <c r="M35" s="43"/>
+      <c r="N35" s="48">
         <v>441</v>
       </c>
-      <c r="O35" s="20">
+      <c r="O35" s="13">
         <v>45136.640277777777</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36" s="53" t="s">
+      <c r="A36" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="B36" s="53">
+      <c r="B36" s="43">
         <v>100</v>
       </c>
-      <c r="C36" s="53">
+      <c r="C36" s="43">
         <v>0.23699999999999999</v>
       </c>
-      <c r="D36" s="53">
+      <c r="D36" s="43">
         <v>0.245</v>
       </c>
-      <c r="E36" s="53">
+      <c r="E36" s="43">
         <f t="shared" si="0"/>
         <v>8.0000000000000071E-3</v>
       </c>
-      <c r="F36" s="54">
+      <c r="F36" s="44">
         <f t="shared" si="7"/>
         <v>80.000000000000071</v>
       </c>
-      <c r="G36" s="53">
+      <c r="G36" s="43">
         <v>244.85599999999999</v>
       </c>
-      <c r="H36" s="55">
+      <c r="H36" s="45">
         <v>0.74831808175628001</v>
       </c>
-      <c r="I36" s="56">
+      <c r="I36" s="46">
         <f t="shared" si="6"/>
         <v>7.4831808175628005</v>
       </c>
-      <c r="J36" s="57">
+      <c r="J36" s="47">
         <v>3.9260000000000002</v>
       </c>
-      <c r="K36" s="53">
+      <c r="K36" s="43">
         <v>7.5700000000000003E-2</v>
       </c>
-      <c r="L36" s="53"/>
-      <c r="M36" s="53"/>
-      <c r="N36" s="58">
+      <c r="L36" s="43"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="48">
         <v>442</v>
       </c>
-      <c r="O36" s="20">
+      <c r="O36" s="13">
         <v>45136.650694444441</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" s="53" t="s">
+      <c r="A37" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="B37" s="53">
+      <c r="B37" s="43">
         <v>90</v>
       </c>
-      <c r="C37" s="53">
+      <c r="C37" s="43">
         <v>0.2404</v>
       </c>
-      <c r="D37" s="53">
+      <c r="D37" s="43">
         <v>0.24429999999999999</v>
       </c>
-      <c r="E37" s="53">
+      <c r="E37" s="43">
         <f t="shared" si="0"/>
         <v>3.8999999999999868E-3</v>
       </c>
-      <c r="F37" s="54">
+      <c r="F37" s="44">
         <f t="shared" si="7"/>
         <v>43.333333333333179</v>
       </c>
-      <c r="G37" s="53">
+      <c r="G37" s="43">
         <v>233.25</v>
       </c>
-      <c r="H37" s="55">
+      <c r="H37" s="45">
         <v>0.53337838091197998</v>
       </c>
-      <c r="I37" s="56">
+      <c r="I37" s="46">
         <f t="shared" si="6"/>
         <v>5.9264264545775553</v>
       </c>
-      <c r="J37" s="57">
+      <c r="J37" s="47">
         <v>4.1580000000000004</v>
       </c>
-      <c r="K37" s="53">
+      <c r="K37" s="43">
         <v>6.6299999999999998E-2</v>
       </c>
-      <c r="L37" s="53"/>
-      <c r="M37" s="53"/>
-      <c r="N37" s="58">
+      <c r="L37" s="43"/>
+      <c r="M37" s="43"/>
+      <c r="N37" s="48">
         <v>443</v>
       </c>
-      <c r="O37" s="20">
+      <c r="O37" s="13">
         <v>45136.661111111112</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="53" t="s">
+      <c r="A38" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="B38" s="53">
+      <c r="B38" s="43">
         <v>90</v>
       </c>
-      <c r="C38" s="53">
+      <c r="C38" s="43">
         <v>0.23810000000000001</v>
       </c>
-      <c r="D38" s="53">
+      <c r="D38" s="43">
         <v>0.24640000000000001</v>
       </c>
-      <c r="E38" s="53">
+      <c r="E38" s="43">
         <v>8.3000000000000018E-3</v>
       </c>
-      <c r="F38" s="54">
+      <c r="F38" s="44">
         <f t="shared" si="7"/>
         <v>92.222222222222243</v>
       </c>
-      <c r="G38" s="53">
+      <c r="G38" s="43">
         <v>124.5634</v>
       </c>
-      <c r="H38" s="55">
+      <c r="H38" s="45">
         <v>0.74561143823581988</v>
       </c>
-      <c r="I38" s="56">
+      <c r="I38" s="46">
         <f t="shared" si="6"/>
         <v>8.2845715359535532</v>
       </c>
-      <c r="J38" s="57">
+      <c r="J38" s="47">
         <v>4.5709999999999997</v>
       </c>
-      <c r="K38" s="53">
+      <c r="K38" s="43">
         <v>3.6499999999999998E-2</v>
       </c>
-      <c r="L38" s="53"/>
-      <c r="M38" s="53"/>
-      <c r="N38" s="58">
+      <c r="L38" s="43"/>
+      <c r="M38" s="43"/>
+      <c r="N38" s="48">
         <v>444</v>
       </c>
-      <c r="O38" s="20">
+      <c r="O38" s="13">
         <v>45136.671527777777</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" s="53" t="s">
+      <c r="A39" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="B39" s="53">
+      <c r="B39" s="43">
         <v>90</v>
       </c>
-      <c r="C39" s="53">
+      <c r="C39" s="43">
         <v>0.24129999999999999</v>
       </c>
-      <c r="D39" s="53">
+      <c r="D39" s="43">
         <v>0.246</v>
       </c>
-      <c r="E39" s="53">
+      <c r="E39" s="43">
         <v>4.7000000000000097E-3</v>
       </c>
-      <c r="F39" s="54">
+      <c r="F39" s="44">
         <f t="shared" si="7"/>
         <v>52.222222222222328</v>
       </c>
-      <c r="G39" s="53">
+      <c r="G39" s="43">
         <v>9.89</v>
       </c>
-      <c r="H39" s="55">
+      <c r="H39" s="45">
         <v>0.93145151485235989</v>
       </c>
-      <c r="I39" s="56">
+      <c r="I39" s="46">
         <f t="shared" si="6"/>
         <v>10.349461276137333</v>
       </c>
-      <c r="J39" s="57">
+      <c r="J39" s="47">
         <v>5.15</v>
       </c>
-      <c r="K39" s="53">
+      <c r="K39" s="43">
         <v>2.12E-2</v>
       </c>
-      <c r="L39" s="53"/>
-      <c r="M39" s="53"/>
-      <c r="N39" s="58">
+      <c r="L39" s="43"/>
+      <c r="M39" s="43"/>
+      <c r="N39" s="48">
         <v>445</v>
       </c>
-      <c r="O39" s="20">
+      <c r="O39" s="13">
         <v>45136.681944444441</v>
       </c>
     </row>
@@ -12491,21 +12792,21 @@
         <f t="shared" ref="E40:E49" si="8">D40-C40</f>
         <v>8.9999999999999802E-3</v>
       </c>
-      <c r="F40" s="19">
+      <c r="F40" s="12">
         <f t="shared" si="7"/>
         <v>99.999999999999773</v>
       </c>
       <c r="G40" s="1">
         <v>327.45299999999997</v>
       </c>
-      <c r="H40" s="31">
+      <c r="H40" s="24">
         <v>1.2514082631396399</v>
       </c>
-      <c r="I40" s="32">
+      <c r="I40" s="25">
         <f t="shared" si="6"/>
         <v>13.904536257107111</v>
       </c>
-      <c r="J40" s="36">
+      <c r="J40" s="29">
         <v>8.5760000000000005</v>
       </c>
       <c r="K40" s="1">
@@ -12513,10 +12814,10 @@
       </c>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
-      <c r="N40" s="45">
+      <c r="N40" s="38">
         <v>446</v>
       </c>
-      <c r="O40" s="20">
+      <c r="O40" s="13">
         <v>45136.636111111111</v>
       </c>
     </row>
@@ -12537,21 +12838,21 @@
         <f t="shared" si="8"/>
         <v>9.5000000000000084E-3</v>
       </c>
-      <c r="F41" s="19">
+      <c r="F41" s="12">
         <f t="shared" si="7"/>
         <v>105.55555555555566</v>
       </c>
       <c r="G41" s="1">
         <v>241.809</v>
       </c>
-      <c r="H41" s="31">
+      <c r="H41" s="24">
         <v>1.00317261593764</v>
       </c>
-      <c r="I41" s="32">
+      <c r="I41" s="25">
         <f t="shared" si="6"/>
         <v>11.14636239930711</v>
       </c>
-      <c r="J41" s="36">
+      <c r="J41" s="29">
         <v>4.0309999999999997</v>
       </c>
       <c r="K41" s="1">
@@ -12559,10 +12860,10 @@
       </c>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
-      <c r="N41" s="45">
+      <c r="N41" s="38">
         <v>447</v>
       </c>
-      <c r="O41" s="20">
+      <c r="O41" s="13">
         <v>45136.646527777775</v>
       </c>
     </row>
@@ -12583,21 +12884,21 @@
         <f t="shared" si="8"/>
         <v>4.500000000000004E-3</v>
       </c>
-      <c r="F42" s="19">
+      <c r="F42" s="12">
         <f t="shared" si="7"/>
         <v>50.000000000000043</v>
       </c>
       <c r="G42" s="1">
         <v>158.52500000000001</v>
       </c>
-      <c r="H42" s="31">
+      <c r="H42" s="24">
         <v>0.67066455629003996</v>
       </c>
-      <c r="I42" s="32">
+      <c r="I42" s="25">
         <f t="shared" si="6"/>
         <v>7.4518284032226658</v>
       </c>
-      <c r="J42" s="36">
+      <c r="J42" s="29">
         <v>4.1859999999999999</v>
       </c>
       <c r="K42" s="1">
@@ -12605,10 +12906,10 @@
       </c>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
-      <c r="N42" s="45">
+      <c r="N42" s="38">
         <v>448</v>
       </c>
-      <c r="O42" s="20">
+      <c r="O42" s="13">
         <v>45136.656944444447</v>
       </c>
     </row>
@@ -12629,21 +12930,21 @@
         <f t="shared" si="8"/>
         <v>6.1999999999999833E-3</v>
       </c>
-      <c r="F43" s="19">
+      <c r="F43" s="12">
         <f t="shared" si="7"/>
         <v>68.888888888888701</v>
       </c>
       <c r="G43" s="1">
         <v>132.47200000000001</v>
       </c>
-      <c r="H43" s="31">
+      <c r="H43" s="24">
         <v>0.67506134010429997</v>
       </c>
-      <c r="I43" s="32">
+      <c r="I43" s="25">
         <f t="shared" si="6"/>
         <v>7.5006815567144436</v>
       </c>
-      <c r="J43" s="36">
+      <c r="J43" s="29">
         <v>4.351</v>
       </c>
       <c r="K43" s="1">
@@ -12651,10 +12952,10 @@
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
-      <c r="N43" s="45">
+      <c r="N43" s="38">
         <v>449</v>
       </c>
-      <c r="O43" s="20">
+      <c r="O43" s="13">
         <v>45136.667361111111</v>
       </c>
     </row>
@@ -12675,18 +12976,18 @@
         <f t="shared" si="8"/>
         <v>4.599999999999993E-3</v>
       </c>
-      <c r="F44" s="19">
+      <c r="F44" s="12">
         <f t="shared" si="7"/>
         <v>51.111111111111029</v>
       </c>
       <c r="G44" s="1">
         <v>98.91</v>
       </c>
-      <c r="H44" s="31">
+      <c r="H44" s="24">
         <v>0</v>
       </c>
-      <c r="I44" s="32"/>
-      <c r="J44" s="36">
+      <c r="I44" s="25"/>
+      <c r="J44" s="29">
         <v>4.3109999999999999</v>
       </c>
       <c r="K44" s="1">
@@ -12694,10 +12995,10 @@
       </c>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
-      <c r="N44" s="45">
+      <c r="N44" s="38">
         <v>450</v>
       </c>
-      <c r="O44" s="20">
+      <c r="O44" s="13">
         <v>45136.677777777775</v>
       </c>
     </row>
@@ -12718,21 +13019,21 @@
         <f t="shared" si="8"/>
         <v>4.2999999999999983E-3</v>
       </c>
-      <c r="F45" s="19">
+      <c r="F45" s="12">
         <f t="shared" si="7"/>
         <v>45.263157894736821</v>
       </c>
       <c r="G45" s="1">
         <v>90.356999999999999</v>
       </c>
-      <c r="H45" s="31">
+      <c r="H45" s="24">
         <v>0.56237380340356002</v>
       </c>
-      <c r="I45" s="32">
+      <c r="I45" s="25">
         <f t="shared" si="6"/>
         <v>5.9197242463532636</v>
       </c>
-      <c r="J45" s="36">
+      <c r="J45" s="29">
         <v>4.4720000000000004</v>
       </c>
       <c r="K45" s="1">
@@ -12740,10 +13041,10 @@
       </c>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
-      <c r="N45" s="45">
+      <c r="N45" s="38">
         <v>451</v>
       </c>
-      <c r="O45" s="20">
+      <c r="O45" s="13">
         <v>45136.688194444447</v>
       </c>
     </row>
@@ -12764,27 +13065,27 @@
         <f t="shared" si="8"/>
         <v>2.4000000000000132E-3</v>
       </c>
-      <c r="F46" s="19">
+      <c r="F46" s="12">
         <f t="shared" si="7"/>
         <v>20.00000000000011</v>
       </c>
       <c r="G46" s="1">
         <v>84.561999999999998</v>
       </c>
-      <c r="H46" s="31">
+      <c r="H46" s="24">
         <v>0</v>
       </c>
-      <c r="I46" s="32"/>
-      <c r="J46" s="36">
+      <c r="I46" s="25"/>
+      <c r="J46" s="29">
         <v>4.6630000000000003</v>
       </c>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
-      <c r="N46" s="45">
+      <c r="N46" s="38">
         <v>452</v>
       </c>
-      <c r="O46" s="20">
+      <c r="O46" s="13">
         <v>45136.698611111111</v>
       </c>
     </row>
@@ -12805,21 +13106,21 @@
         <f t="shared" si="8"/>
         <v>1.7000000000000071E-3</v>
       </c>
-      <c r="F47" s="19">
+      <c r="F47" s="12">
         <f t="shared" si="7"/>
         <v>15.454545454545519</v>
       </c>
       <c r="G47" s="1">
         <v>59.01</v>
       </c>
-      <c r="H47" s="31">
+      <c r="H47" s="24">
         <v>0.32430437517212002</v>
       </c>
-      <c r="I47" s="32">
+      <c r="I47" s="25">
         <f t="shared" si="6"/>
         <v>2.9482215924738182</v>
       </c>
-      <c r="J47" s="36">
+      <c r="J47" s="29">
         <v>4.9740000000000002</v>
       </c>
       <c r="K47" s="1">
@@ -12827,10 +13128,10 @@
       </c>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
-      <c r="N47" s="45">
+      <c r="N47" s="38">
         <v>453</v>
       </c>
-      <c r="O47" s="20">
+      <c r="O47" s="13">
         <v>45136.719444444447</v>
       </c>
     </row>
@@ -12851,18 +13152,18 @@
         <f t="shared" si="8"/>
         <v>2.600000000000019E-3</v>
       </c>
-      <c r="F48" s="19">
+      <c r="F48" s="12">
         <f t="shared" si="7"/>
         <v>26.000000000000188</v>
       </c>
       <c r="G48" s="1">
         <v>42.72</v>
       </c>
-      <c r="H48" s="31">
+      <c r="H48" s="24">
         <v>0</v>
       </c>
-      <c r="I48" s="32"/>
-      <c r="J48" s="36">
+      <c r="I48" s="25"/>
+      <c r="J48" s="29">
         <v>4.9390000000000001</v>
       </c>
       <c r="K48" s="1">
@@ -12870,284 +13171,284 @@
       </c>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
-      <c r="N48" s="45">
+      <c r="N48" s="38">
         <v>454</v>
       </c>
-      <c r="O48" s="20">
+      <c r="O48" s="13">
         <v>45136.740277777775</v>
       </c>
     </row>
     <row r="49" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="112" t="s">
+      <c r="A49" s="102" t="s">
         <v>37</v>
       </c>
-      <c r="B49" s="112">
+      <c r="B49" s="102">
         <v>100</v>
       </c>
-      <c r="C49" s="112">
+      <c r="C49" s="102">
         <v>0.22919999999999999</v>
       </c>
-      <c r="D49" s="112">
+      <c r="D49" s="102">
         <v>0.23130000000000001</v>
       </c>
-      <c r="E49" s="112">
+      <c r="E49" s="102">
         <f t="shared" si="8"/>
         <v>2.1000000000000185E-3</v>
       </c>
-      <c r="F49" s="113">
+      <c r="F49" s="103">
         <f t="shared" si="7"/>
         <v>21.000000000000185</v>
       </c>
-      <c r="G49" s="112">
+      <c r="G49" s="102">
         <v>98.146000000000001</v>
       </c>
-      <c r="H49" s="114">
+      <c r="H49" s="104">
         <v>0.42750517220431999</v>
       </c>
-      <c r="I49" s="115">
+      <c r="I49" s="105">
         <f t="shared" si="6"/>
         <v>4.2750517220431998</v>
       </c>
-      <c r="J49" s="116">
+      <c r="J49" s="106">
         <v>5.2530000000000001</v>
       </c>
-      <c r="K49" s="112"/>
-      <c r="L49" s="112"/>
-      <c r="M49" s="112"/>
-      <c r="N49" s="117">
+      <c r="K49" s="102"/>
+      <c r="L49" s="102"/>
+      <c r="M49" s="102"/>
+      <c r="N49" s="107">
         <v>455</v>
       </c>
-      <c r="O49" s="76">
+      <c r="O49" s="66">
         <v>45136.771527777775</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="118" t="s">
+      <c r="A50" s="108" t="s">
         <v>7</v>
       </c>
-      <c r="B50" s="118">
+      <c r="B50" s="108">
         <v>260</v>
       </c>
-      <c r="C50" s="118">
+      <c r="C50" s="108">
         <v>0.2351</v>
       </c>
-      <c r="D50" s="118">
+      <c r="D50" s="108">
         <v>0.25490000000000002</v>
       </c>
-      <c r="E50" s="118">
+      <c r="E50" s="108">
         <f t="shared" ref="E50:E67" si="9">D50-C50</f>
         <v>1.9800000000000012E-2</v>
       </c>
-      <c r="F50" s="119">
+      <c r="F50" s="109">
         <f t="shared" si="7"/>
         <v>76.153846153846203</v>
       </c>
-      <c r="G50" s="118">
+      <c r="G50" s="108">
         <v>210.458</v>
       </c>
-      <c r="H50" s="120">
+      <c r="H50" s="110">
         <v>2.0222215051616801</v>
       </c>
-      <c r="I50" s="121">
+      <c r="I50" s="111">
         <f t="shared" si="6"/>
         <v>7.7777750198526157</v>
       </c>
-      <c r="J50" s="122">
+      <c r="J50" s="112">
         <v>4.4729999999999999</v>
       </c>
-      <c r="K50" s="118">
+      <c r="K50" s="108">
         <v>6.83E-2</v>
       </c>
-      <c r="L50" s="118"/>
-      <c r="M50" s="118"/>
-      <c r="N50" s="123">
+      <c r="L50" s="108"/>
+      <c r="M50" s="108"/>
+      <c r="N50" s="113">
         <v>456</v>
       </c>
-      <c r="O50" s="86">
+      <c r="O50" s="76">
         <v>45151.78125</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" s="59" t="s">
+      <c r="A51" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="B51" s="59">
+      <c r="B51" s="49">
         <v>250</v>
       </c>
-      <c r="C51" s="59">
+      <c r="C51" s="49">
         <v>0.2339</v>
       </c>
-      <c r="D51" s="59">
+      <c r="D51" s="49">
         <v>0.2442</v>
       </c>
-      <c r="E51" s="59">
+      <c r="E51" s="49">
         <f t="shared" si="9"/>
         <v>1.0300000000000004E-2</v>
       </c>
-      <c r="F51" s="60">
+      <c r="F51" s="50">
         <f t="shared" ref="F51:F67" si="10">E51/B51*1000*1000</f>
         <v>41.200000000000017</v>
       </c>
-      <c r="G51" s="59">
+      <c r="G51" s="49">
         <v>116.066</v>
       </c>
-      <c r="H51" s="61">
+      <c r="H51" s="51">
         <v>1.1336781018156401</v>
       </c>
-      <c r="I51" s="62">
+      <c r="I51" s="52">
         <f t="shared" si="6"/>
         <v>4.5347124072625604</v>
       </c>
-      <c r="J51" s="63">
+      <c r="J51" s="53">
         <v>3.9359999999999999</v>
       </c>
-      <c r="K51" s="59">
+      <c r="K51" s="49">
         <v>9.6100000000000005E-2</v>
       </c>
-      <c r="L51" s="59"/>
-      <c r="M51" s="59"/>
-      <c r="N51" s="64">
+      <c r="L51" s="49"/>
+      <c r="M51" s="49"/>
+      <c r="N51" s="54">
         <v>457</v>
       </c>
-      <c r="O51" s="20">
+      <c r="O51" s="13">
         <v>45151.790277777778</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="59" t="s">
+      <c r="A52" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="B52" s="59">
+      <c r="B52" s="49">
         <v>250</v>
       </c>
-      <c r="C52" s="59">
+      <c r="C52" s="49">
         <v>0.23799999999999999</v>
       </c>
-      <c r="D52" s="59">
+      <c r="D52" s="49">
         <v>0.24790000000000001</v>
       </c>
-      <c r="E52" s="59">
+      <c r="E52" s="49">
         <f t="shared" si="9"/>
         <v>9.9000000000000199E-3</v>
       </c>
-      <c r="F52" s="60">
+      <c r="F52" s="50">
         <f t="shared" si="10"/>
         <v>39.60000000000008</v>
       </c>
-      <c r="G52" s="59">
+      <c r="G52" s="49">
         <v>113.258</v>
       </c>
-      <c r="H52" s="61">
+      <c r="H52" s="51">
         <v>1.4723180433944001</v>
       </c>
-      <c r="I52" s="62">
+      <c r="I52" s="52">
         <f t="shared" si="6"/>
         <v>5.8892721735776004</v>
       </c>
-      <c r="J52" s="63">
+      <c r="J52" s="53">
         <v>3.9430000000000001</v>
       </c>
-      <c r="K52" s="59">
+      <c r="K52" s="49">
         <v>9.6799999999999997E-2</v>
       </c>
-      <c r="L52" s="59"/>
-      <c r="M52" s="59"/>
-      <c r="N52" s="64">
+      <c r="L52" s="49"/>
+      <c r="M52" s="49"/>
+      <c r="N52" s="54">
         <v>458</v>
       </c>
-      <c r="O52" s="20">
+      <c r="O52" s="13">
         <v>45151.793055555558</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" s="59" t="s">
+      <c r="A53" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="B53" s="59">
+      <c r="B53" s="49">
         <v>250</v>
       </c>
-      <c r="C53" s="59">
+      <c r="C53" s="49">
         <v>0.23469999999999999</v>
       </c>
-      <c r="D53" s="59">
+      <c r="D53" s="49">
         <v>0.24160000000000001</v>
       </c>
-      <c r="E53" s="59">
+      <c r="E53" s="49">
         <f t="shared" si="9"/>
         <v>6.9000000000000172E-3</v>
       </c>
-      <c r="F53" s="60">
+      <c r="F53" s="50">
         <f t="shared" si="10"/>
         <v>27.600000000000069</v>
       </c>
-      <c r="G53" s="59">
+      <c r="G53" s="49">
         <v>81.150000000000006</v>
       </c>
-      <c r="H53" s="61">
+      <c r="H53" s="51">
         <v>1.2008849810370801</v>
       </c>
-      <c r="I53" s="62">
+      <c r="I53" s="52">
         <f t="shared" si="6"/>
         <v>4.8035399241483203</v>
       </c>
-      <c r="J53" s="63">
+      <c r="J53" s="53">
         <v>4.0389999999999997</v>
       </c>
-      <c r="K53" s="59">
+      <c r="K53" s="49">
         <v>9.06E-2</v>
       </c>
-      <c r="L53" s="59"/>
-      <c r="M53" s="59"/>
-      <c r="N53" s="64">
+      <c r="L53" s="49"/>
+      <c r="M53" s="49"/>
+      <c r="N53" s="54">
         <v>459</v>
       </c>
-      <c r="O53" s="20">
+      <c r="O53" s="13">
         <v>45151.798611111109</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" s="59" t="s">
+      <c r="A54" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="B54" s="59">
+      <c r="B54" s="49">
         <v>240</v>
       </c>
-      <c r="C54" s="59">
+      <c r="C54" s="49">
         <v>0.2374</v>
       </c>
-      <c r="D54" s="59">
+      <c r="D54" s="49">
         <v>0.2424</v>
       </c>
-      <c r="E54" s="59">
+      <c r="E54" s="49">
         <f t="shared" si="9"/>
         <v>5.0000000000000044E-3</v>
       </c>
-      <c r="F54" s="60">
+      <c r="F54" s="50">
         <f t="shared" si="10"/>
         <v>20.833333333333353</v>
       </c>
-      <c r="G54" s="59">
+      <c r="G54" s="49">
         <v>56.15</v>
       </c>
-      <c r="H54" s="61">
+      <c r="H54" s="51">
         <v>0.70097364508676874</v>
       </c>
-      <c r="I54" s="62">
+      <c r="I54" s="52">
         <f t="shared" si="6"/>
         <v>2.9207235211948697</v>
       </c>
-      <c r="J54" s="63">
+      <c r="J54" s="53">
         <v>2.786</v>
       </c>
-      <c r="K54" s="59">
+      <c r="K54" s="49">
         <v>3.9199999999999999E-2</v>
       </c>
-      <c r="L54" s="59"/>
-      <c r="M54" s="59"/>
-      <c r="N54" s="64">
+      <c r="L54" s="49"/>
+      <c r="M54" s="49"/>
+      <c r="N54" s="54">
         <v>460</v>
       </c>
-      <c r="O54" s="20">
+      <c r="O54" s="13">
         <v>45151.876388888886</v>
       </c>
     </row>
@@ -13168,21 +13469,21 @@
         <f t="shared" si="9"/>
         <v>1.0800000000000004E-2</v>
       </c>
-      <c r="F55" s="21">
+      <c r="F55" s="14">
         <f t="shared" si="10"/>
         <v>43.200000000000017</v>
       </c>
       <c r="G55" s="2">
         <v>183.80799999999999</v>
       </c>
-      <c r="H55" s="37">
+      <c r="H55" s="30">
         <v>1.3888700852562501</v>
       </c>
-      <c r="I55" s="38">
+      <c r="I55" s="31">
         <f t="shared" si="6"/>
         <v>5.5554803410250004</v>
       </c>
-      <c r="J55" s="39">
+      <c r="J55" s="32">
         <v>9.9</v>
       </c>
       <c r="K55" s="2">
@@ -13190,10 +13491,10 @@
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
-      <c r="N55" s="46">
+      <c r="N55" s="39">
         <v>461</v>
       </c>
-      <c r="O55" s="20">
+      <c r="O55" s="13">
         <v>45151.78125</v>
       </c>
     </row>
@@ -13214,21 +13515,21 @@
         <f t="shared" si="9"/>
         <v>7.5999999999999956E-3</v>
       </c>
-      <c r="F56" s="21">
+      <c r="F56" s="14">
         <f t="shared" si="10"/>
         <v>29.230769230769212</v>
       </c>
       <c r="G56" s="2">
         <v>83.528000000000006</v>
       </c>
-      <c r="H56" s="37">
+      <c r="H56" s="30">
         <v>1.3211677463677476</v>
       </c>
-      <c r="I56" s="38">
+      <c r="I56" s="31">
         <f t="shared" si="6"/>
         <v>5.0814144091067215</v>
       </c>
-      <c r="J56" s="39">
+      <c r="J56" s="32">
         <v>3.379</v>
       </c>
       <c r="K56" s="2">
@@ -13236,10 +13537,10 @@
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
-      <c r="N56" s="46">
+      <c r="N56" s="39">
         <v>462</v>
       </c>
-      <c r="O56" s="20">
+      <c r="O56" s="13">
         <v>45151.791666666664</v>
       </c>
     </row>
@@ -13260,21 +13561,21 @@
         <f t="shared" si="9"/>
         <v>6.5000000000000058E-3</v>
       </c>
-      <c r="F57" s="21">
+      <c r="F57" s="14">
         <f t="shared" si="10"/>
         <v>25.000000000000021</v>
       </c>
       <c r="G57" s="2">
         <v>72.105000000000004</v>
       </c>
-      <c r="H57" s="37">
+      <c r="H57" s="30">
         <v>1.243345664936105</v>
       </c>
-      <c r="I57" s="38">
+      <c r="I57" s="31">
         <f t="shared" si="6"/>
         <v>4.7820987112927114</v>
       </c>
-      <c r="J57" s="39">
+      <c r="J57" s="32">
         <v>3.1909999999999998</v>
       </c>
       <c r="K57" s="2">
@@ -13282,10 +13583,10 @@
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
-      <c r="N57" s="46">
+      <c r="N57" s="39">
         <v>463</v>
       </c>
-      <c r="O57" s="20">
+      <c r="O57" s="13">
         <v>45151.802083333336</v>
       </c>
     </row>
@@ -13306,21 +13607,21 @@
         <f t="shared" si="9"/>
         <v>5.6999999999999829E-3</v>
       </c>
-      <c r="F58" s="21">
+      <c r="F58" s="14">
         <f t="shared" si="10"/>
         <v>23.749999999999932</v>
       </c>
       <c r="G58" s="2">
         <v>67.606999999999999</v>
       </c>
-      <c r="H58" s="37">
+      <c r="H58" s="30">
         <v>0.96877795638711239</v>
       </c>
-      <c r="I58" s="38">
+      <c r="I58" s="31">
         <f t="shared" si="6"/>
         <v>4.036574818279635</v>
       </c>
-      <c r="J58" s="39">
+      <c r="J58" s="32">
         <v>3.1280000000000001</v>
       </c>
       <c r="K58" s="2">
@@ -13328,10 +13629,10 @@
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
-      <c r="N58" s="46">
+      <c r="N58" s="39">
         <v>464</v>
       </c>
-      <c r="O58" s="20">
+      <c r="O58" s="13">
         <v>45151.8125</v>
       </c>
     </row>
@@ -13352,16 +13653,16 @@
         <f t="shared" si="9"/>
         <v>2.0000000000000018E-3</v>
       </c>
-      <c r="F59" s="21">
+      <c r="F59" s="14">
         <f t="shared" si="10"/>
         <v>22.222222222222243</v>
       </c>
       <c r="G59" s="2">
         <v>70.3</v>
       </c>
-      <c r="H59" s="37"/>
-      <c r="I59" s="38"/>
-      <c r="J59" s="39">
+      <c r="H59" s="30"/>
+      <c r="I59" s="31"/>
+      <c r="J59" s="32">
         <v>3.3319999999999999</v>
       </c>
       <c r="K59" s="2">
@@ -13369,10 +13670,10 @@
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
-      <c r="N59" s="46">
+      <c r="N59" s="39">
         <v>465</v>
       </c>
-      <c r="O59" s="20">
+      <c r="O59" s="13">
         <v>45151.822916666664</v>
       </c>
     </row>
@@ -13393,21 +13694,21 @@
         <f t="shared" si="9"/>
         <v>2.0000000000000018E-3</v>
       </c>
-      <c r="F60" s="21">
+      <c r="F60" s="14">
         <f t="shared" si="10"/>
         <v>22.222222222222243</v>
       </c>
       <c r="G60" s="2">
         <v>67.88</v>
       </c>
-      <c r="H60" s="37">
+      <c r="H60" s="30">
         <v>0.46451618132306999</v>
       </c>
-      <c r="I60" s="38">
+      <c r="I60" s="31">
         <f t="shared" si="6"/>
         <v>5.1612909035896664</v>
       </c>
-      <c r="J60" s="39">
+      <c r="J60" s="32">
         <v>3.1309999999999998</v>
       </c>
       <c r="K60" s="2">
@@ -13415,10 +13716,10 @@
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
-      <c r="N60" s="46">
+      <c r="N60" s="39">
         <v>466</v>
       </c>
-      <c r="O60" s="20">
+      <c r="O60" s="13">
         <v>45151.833333333336</v>
       </c>
     </row>
@@ -13439,16 +13740,16 @@
         <f t="shared" si="9"/>
         <v>2.2999999999999965E-3</v>
       </c>
-      <c r="F61" s="21">
+      <c r="F61" s="14">
         <f t="shared" si="10"/>
         <v>21.90476190476187</v>
       </c>
       <c r="G61" s="2">
         <v>84.66</v>
       </c>
-      <c r="H61" s="37"/>
-      <c r="I61" s="38"/>
-      <c r="J61" s="39">
+      <c r="H61" s="30"/>
+      <c r="I61" s="31"/>
+      <c r="J61" s="32">
         <v>3.286</v>
       </c>
       <c r="K61" s="2">
@@ -13456,10 +13757,10 @@
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
-      <c r="N61" s="46">
+      <c r="N61" s="39">
         <v>467</v>
       </c>
-      <c r="O61" s="20">
+      <c r="O61" s="13">
         <v>45151.84375</v>
       </c>
     </row>
@@ -13480,21 +13781,21 @@
         <f t="shared" si="9"/>
         <v>1.799999999999996E-3</v>
       </c>
-      <c r="F62" s="21">
+      <c r="F62" s="14">
         <f t="shared" si="10"/>
         <v>17.999999999999961</v>
       </c>
       <c r="G62" s="2">
         <v>67.569999999999993</v>
       </c>
-      <c r="H62" s="37">
+      <c r="H62" s="30">
         <v>0.51244036630343248</v>
       </c>
-      <c r="I62" s="38">
+      <c r="I62" s="31">
         <f t="shared" si="6"/>
         <v>5.1244036630343253</v>
       </c>
-      <c r="J62" s="39">
+      <c r="J62" s="32">
         <v>2.9169999999999998</v>
       </c>
       <c r="K62" s="2">
@@ -13502,10 +13803,10 @@
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
-      <c r="N62" s="46">
+      <c r="N62" s="39">
         <v>468</v>
       </c>
-      <c r="O62" s="20">
+      <c r="O62" s="13">
         <v>45151.854166666664</v>
       </c>
     </row>
@@ -13526,16 +13827,16 @@
         <f t="shared" si="9"/>
         <v>4.0999999999999925E-3</v>
       </c>
-      <c r="F63" s="21">
+      <c r="F63" s="14">
         <f t="shared" si="10"/>
         <v>20.499999999999964</v>
       </c>
       <c r="G63" s="2">
         <v>54.936</v>
       </c>
-      <c r="H63" s="37"/>
-      <c r="I63" s="38"/>
-      <c r="J63" s="39">
+      <c r="H63" s="30"/>
+      <c r="I63" s="31"/>
+      <c r="J63" s="32">
         <v>2.548</v>
       </c>
       <c r="K63" s="2">
@@ -13543,10 +13844,10 @@
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
-      <c r="N63" s="46">
+      <c r="N63" s="39">
         <v>469</v>
       </c>
-      <c r="O63" s="20">
+      <c r="O63" s="13">
         <v>45151.864583333336</v>
       </c>
     </row>
@@ -13567,16 +13868,16 @@
         <f t="shared" si="9"/>
         <v>2.7000000000000079E-3</v>
       </c>
-      <c r="F64" s="21">
+      <c r="F64" s="14">
         <f t="shared" si="10"/>
         <v>12.558139534883757</v>
       </c>
       <c r="G64" s="2">
         <v>75.337999999999994</v>
       </c>
-      <c r="H64" s="37"/>
-      <c r="I64" s="38"/>
-      <c r="J64" s="39">
+      <c r="H64" s="30"/>
+      <c r="I64" s="31"/>
+      <c r="J64" s="32">
         <v>2.5049999999999999</v>
       </c>
       <c r="K64" s="2">
@@ -13584,10 +13885,10 @@
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
-      <c r="N64" s="46">
+      <c r="N64" s="39">
         <v>470</v>
       </c>
-      <c r="O64" s="20">
+      <c r="O64" s="13">
         <v>45151.875</v>
       </c>
     </row>
@@ -13608,16 +13909,16 @@
         <f t="shared" si="9"/>
         <v>4.500000000000004E-3</v>
       </c>
-      <c r="F65" s="21">
+      <c r="F65" s="14">
         <f t="shared" si="10"/>
         <v>18.000000000000014</v>
       </c>
       <c r="G65" s="2">
         <v>59.165999999999997</v>
       </c>
-      <c r="H65" s="37"/>
-      <c r="I65" s="38"/>
-      <c r="J65" s="39">
+      <c r="H65" s="30"/>
+      <c r="I65" s="31"/>
+      <c r="J65" s="32">
         <v>2.508</v>
       </c>
       <c r="K65" s="2">
@@ -13625,10 +13926,10 @@
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
-      <c r="N65" s="46">
+      <c r="N65" s="39">
         <v>471</v>
       </c>
-      <c r="O65" s="20">
+      <c r="O65" s="13">
         <v>45151.885416666664</v>
       </c>
     </row>
@@ -13649,21 +13950,21 @@
         <f t="shared" si="9"/>
         <v>5.0000000000000044E-3</v>
       </c>
-      <c r="F66" s="21">
+      <c r="F66" s="14">
         <f t="shared" si="10"/>
         <v>20.000000000000018</v>
       </c>
       <c r="G66" s="2">
         <v>50.774000000000001</v>
       </c>
-      <c r="H66" s="37">
+      <c r="H66" s="30">
         <v>0.81061645169894003</v>
       </c>
-      <c r="I66" s="38">
+      <c r="I66" s="31">
         <f t="shared" si="6"/>
         <v>3.2424658067957601</v>
       </c>
-      <c r="J66" s="39">
+      <c r="J66" s="32">
         <v>2.4820000000000002</v>
       </c>
       <c r="K66" s="2">
@@ -13671,2309 +13972,2694 @@
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
-      <c r="N66" s="46">
+      <c r="N66" s="39">
         <v>472</v>
       </c>
-      <c r="O66" s="20">
+      <c r="O66" s="13">
         <v>45151.895833333336</v>
       </c>
     </row>
     <row r="67" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="124" t="s">
+      <c r="A67" s="114" t="s">
         <v>65</v>
       </c>
-      <c r="B67" s="124">
+      <c r="B67" s="114">
         <v>120</v>
       </c>
-      <c r="C67" s="124">
+      <c r="C67" s="114">
         <v>0.2329</v>
       </c>
-      <c r="D67" s="124">
+      <c r="D67" s="114">
         <v>0.2349</v>
       </c>
-      <c r="E67" s="124">
+      <c r="E67" s="114">
         <f t="shared" si="9"/>
         <v>2.0000000000000018E-3</v>
       </c>
-      <c r="F67" s="125">
+      <c r="F67" s="115">
         <f t="shared" si="10"/>
         <v>16.666666666666682</v>
       </c>
-      <c r="G67" s="125"/>
-      <c r="H67" s="126"/>
-      <c r="I67" s="127"/>
-      <c r="J67" s="128">
+      <c r="G67" s="115"/>
+      <c r="H67" s="116"/>
+      <c r="I67" s="117"/>
+      <c r="J67" s="118">
         <v>3.1379999999999999</v>
       </c>
-      <c r="K67" s="124"/>
-      <c r="L67" s="124"/>
-      <c r="M67" s="124"/>
-      <c r="N67" s="129">
+      <c r="K67" s="114"/>
+      <c r="L67" s="114"/>
+      <c r="M67" s="114"/>
+      <c r="N67" s="119">
         <v>473</v>
       </c>
-      <c r="O67" s="76">
+      <c r="O67" s="66">
         <v>45151.90625</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A68" s="134" t="s">
+      <c r="A68" s="124" t="s">
         <v>38</v>
       </c>
-      <c r="B68" s="134">
+      <c r="B68" s="124">
         <v>190</v>
       </c>
-      <c r="C68" s="134">
+      <c r="C68" s="124">
         <v>0.23569999999999999</v>
       </c>
-      <c r="D68" s="134">
+      <c r="D68" s="124">
         <v>0.2505</v>
       </c>
-      <c r="E68" s="134">
+      <c r="E68" s="124">
         <f t="shared" ref="E68:E75" si="11">D68-C68</f>
         <v>1.4800000000000008E-2</v>
       </c>
-      <c r="F68" s="135">
+      <c r="F68" s="125">
         <f t="shared" ref="F68:F75" si="12">E68/B68*1000*1000</f>
         <v>77.894736842105289</v>
       </c>
-      <c r="G68" s="134">
+      <c r="G68" s="124">
         <v>232.05199999999999</v>
       </c>
-      <c r="H68" s="136">
+      <c r="H68" s="126">
         <v>2.4072173760262299</v>
       </c>
-      <c r="I68" s="137">
+      <c r="I68" s="127">
         <f t="shared" si="6"/>
         <v>12.669565136980157</v>
       </c>
-      <c r="J68" s="138">
+      <c r="J68" s="128">
         <v>3.1040000000000001</v>
       </c>
-      <c r="K68" s="134">
+      <c r="K68" s="124">
         <v>5.8700000000000002E-2</v>
       </c>
-      <c r="L68" s="134"/>
-      <c r="M68" s="134"/>
-      <c r="N68" s="139">
+      <c r="L68" s="124"/>
+      <c r="M68" s="124"/>
+      <c r="N68" s="129">
         <v>476</v>
       </c>
-      <c r="O68" s="86">
+      <c r="O68" s="76">
         <v>45166.513888888891</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A69" s="13" t="s">
+      <c r="A69" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B69" s="13">
+      <c r="B69" s="8">
         <v>200</v>
       </c>
-      <c r="C69" s="13">
+      <c r="C69" s="8">
         <v>0.23250000000000001</v>
       </c>
-      <c r="D69" s="13">
+      <c r="D69" s="8">
         <v>0.24110000000000001</v>
       </c>
-      <c r="E69" s="13">
+      <c r="E69" s="8">
         <f t="shared" si="11"/>
         <v>8.5999999999999965E-3</v>
       </c>
-      <c r="F69" s="22">
+      <c r="F69" s="15">
         <f t="shared" si="12"/>
         <v>42.999999999999986</v>
       </c>
-      <c r="G69" s="13">
+      <c r="G69" s="8">
         <v>143.89599999999999</v>
       </c>
-      <c r="H69" s="40">
+      <c r="H69" s="33">
         <v>1.25426288924901</v>
       </c>
-      <c r="I69" s="41">
+      <c r="I69" s="34">
         <f t="shared" si="6"/>
         <v>6.2713144462450501</v>
       </c>
-      <c r="J69" s="42">
+      <c r="J69" s="35">
         <v>3.3050000000000002</v>
       </c>
-      <c r="K69" s="13">
+      <c r="K69" s="8">
         <v>0.12139999999999999</v>
       </c>
-      <c r="L69" s="13"/>
-      <c r="M69" s="13"/>
-      <c r="N69" s="47">
+      <c r="L69" s="8"/>
+      <c r="M69" s="8"/>
+      <c r="N69" s="40">
         <v>477</v>
       </c>
-      <c r="O69" s="20">
+      <c r="O69" s="13">
         <v>45166.524305555555</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A70" s="13" t="s">
+      <c r="A70" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B70" s="13">
+      <c r="B70" s="8">
         <v>200</v>
       </c>
-      <c r="C70" s="13">
+      <c r="C70" s="8">
         <v>0.2399</v>
       </c>
-      <c r="D70" s="13">
+      <c r="D70" s="8">
         <v>0.24709999999999999</v>
       </c>
-      <c r="E70" s="13">
+      <c r="E70" s="8">
         <f t="shared" si="11"/>
         <v>7.1999999999999842E-3</v>
       </c>
-      <c r="F70" s="22">
+      <c r="F70" s="15">
         <f t="shared" si="12"/>
         <v>35.999999999999922</v>
       </c>
-      <c r="G70" s="13">
+      <c r="G70" s="8">
         <v>104.006</v>
       </c>
-      <c r="H70" s="40">
+      <c r="H70" s="33">
         <v>1.13454858480537</v>
       </c>
-      <c r="I70" s="41">
+      <c r="I70" s="34">
         <f t="shared" si="6"/>
         <v>5.6727429240268501</v>
       </c>
-      <c r="J70" s="42">
+      <c r="J70" s="35">
         <v>3.3359999999999999</v>
       </c>
-      <c r="K70" s="13">
+      <c r="K70" s="8">
         <v>2.3699999999999999E-2</v>
       </c>
-      <c r="L70" s="13"/>
-      <c r="M70" s="13"/>
-      <c r="N70" s="47">
+      <c r="L70" s="8"/>
+      <c r="M70" s="8"/>
+      <c r="N70" s="40">
         <v>478</v>
       </c>
-      <c r="O70" s="20">
+      <c r="O70" s="13">
         <v>45166.534722222219</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A71" s="13" t="s">
+      <c r="A71" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B71" s="13">
+      <c r="B71" s="8">
         <v>215</v>
       </c>
-      <c r="C71" s="13">
+      <c r="C71" s="8">
         <v>0.2288</v>
       </c>
-      <c r="D71" s="13">
+      <c r="D71" s="8">
         <v>0.23499999999999999</v>
       </c>
-      <c r="E71" s="13">
+      <c r="E71" s="8">
         <f t="shared" si="11"/>
         <v>6.1999999999999833E-3</v>
       </c>
-      <c r="F71" s="22">
+      <c r="F71" s="15">
         <f t="shared" si="12"/>
         <v>28.837209302325505</v>
       </c>
-      <c r="G71" s="13">
+      <c r="G71" s="8">
         <v>88.144000000000005</v>
       </c>
-      <c r="H71" s="40">
+      <c r="H71" s="33">
         <v>0.99956471075489506</v>
       </c>
-      <c r="I71" s="41">
+      <c r="I71" s="34">
         <f t="shared" si="6"/>
         <v>4.6491381895576511</v>
       </c>
-      <c r="J71" s="42">
+      <c r="J71" s="35">
         <v>3.1989999999999998</v>
       </c>
-      <c r="K71" s="13">
+      <c r="K71" s="8">
         <v>9.7699999999999995E-2</v>
       </c>
-      <c r="L71" s="13"/>
-      <c r="M71" s="13"/>
-      <c r="N71" s="47">
+      <c r="L71" s="8"/>
+      <c r="M71" s="8"/>
+      <c r="N71" s="40">
         <v>479</v>
       </c>
-      <c r="O71" s="20">
+      <c r="O71" s="13">
         <v>45166.545138888891</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A72" s="13" t="s">
+      <c r="A72" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B72" s="13">
+      <c r="B72" s="8">
         <v>220</v>
       </c>
-      <c r="C72" s="13">
+      <c r="C72" s="8">
         <v>0.23330000000000001</v>
       </c>
-      <c r="D72" s="13">
+      <c r="D72" s="8">
         <v>0.23980000000000001</v>
       </c>
-      <c r="E72" s="13">
+      <c r="E72" s="8">
         <f t="shared" si="11"/>
         <v>6.5000000000000058E-3</v>
       </c>
-      <c r="F72" s="22">
+      <c r="F72" s="15">
         <f t="shared" si="12"/>
         <v>29.545454545454572</v>
       </c>
-      <c r="G72" s="13">
+      <c r="G72" s="8">
         <v>92.256</v>
       </c>
-      <c r="H72" s="40">
+      <c r="H72" s="33">
         <v>1.1932436975735501</v>
       </c>
-      <c r="I72" s="41">
+      <c r="I72" s="34">
         <f t="shared" si="6"/>
         <v>5.4238349889706816</v>
       </c>
-      <c r="J72" s="42">
+      <c r="J72" s="35">
         <v>3.226</v>
       </c>
-      <c r="K72" s="13">
+      <c r="K72" s="8">
         <v>0.17730000000000001</v>
       </c>
-      <c r="L72" s="13"/>
-      <c r="M72" s="13"/>
-      <c r="N72" s="47">
+      <c r="L72" s="8"/>
+      <c r="M72" s="8"/>
+      <c r="N72" s="40">
         <v>480</v>
       </c>
-      <c r="O72" s="20">
+      <c r="O72" s="13">
         <v>45166.555555555555</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A73" s="13" t="s">
+      <c r="A73" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B73" s="13">
+      <c r="B73" s="8">
         <v>190</v>
       </c>
-      <c r="C73" s="13">
+      <c r="C73" s="8">
         <v>0.2316</v>
       </c>
-      <c r="D73" s="13">
+      <c r="D73" s="8">
         <v>0.23669999999999999</v>
       </c>
-      <c r="E73" s="13">
+      <c r="E73" s="8">
         <f t="shared" si="11"/>
         <v>5.0999999999999934E-3</v>
       </c>
-      <c r="F73" s="22">
+      <c r="F73" s="15">
         <f t="shared" si="12"/>
         <v>26.842105263157862</v>
       </c>
-      <c r="G73" s="13">
+      <c r="G73" s="8">
         <v>82.494</v>
       </c>
-      <c r="H73" s="40">
+      <c r="H73" s="33">
         <v>0.85419170023644253</v>
       </c>
-      <c r="I73" s="41">
+      <c r="I73" s="34">
         <f t="shared" si="6"/>
         <v>4.495745790718118</v>
       </c>
-      <c r="J73" s="42">
+      <c r="J73" s="35">
         <v>3.206</v>
       </c>
-      <c r="K73" s="13"/>
-      <c r="L73" s="13"/>
-      <c r="M73" s="13"/>
-      <c r="N73" s="47">
+      <c r="K73" s="8"/>
+      <c r="L73" s="8"/>
+      <c r="M73" s="8"/>
+      <c r="N73" s="40">
         <v>481</v>
       </c>
-      <c r="O73" s="20">
+      <c r="O73" s="13">
         <v>45166.586805555555</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A74" s="13" t="s">
+      <c r="A74" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B74" s="13">
+      <c r="B74" s="8">
         <v>200</v>
       </c>
-      <c r="C74" s="13">
+      <c r="C74" s="8">
         <v>0.22189999999999999</v>
       </c>
-      <c r="D74" s="13">
+      <c r="D74" s="8">
         <v>0.22670000000000001</v>
       </c>
-      <c r="E74" s="13">
+      <c r="E74" s="8">
         <f t="shared" si="11"/>
         <v>4.8000000000000265E-3</v>
       </c>
-      <c r="F74" s="22">
+      <c r="F74" s="15">
         <f t="shared" si="12"/>
         <v>24.000000000000131</v>
       </c>
-      <c r="G74" s="13">
+      <c r="G74" s="8">
         <v>69.394999999999996</v>
       </c>
-      <c r="H74" s="40">
+      <c r="H74" s="33">
         <v>0</v>
       </c>
-      <c r="I74" s="41"/>
-      <c r="J74" s="42">
+      <c r="I74" s="34"/>
+      <c r="J74" s="35">
         <v>3.262</v>
       </c>
-      <c r="K74" s="13">
+      <c r="K74" s="8">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="L74" s="13"/>
-      <c r="M74" s="13"/>
-      <c r="N74" s="47">
+      <c r="L74" s="8"/>
+      <c r="M74" s="8"/>
+      <c r="N74" s="40">
         <v>482</v>
       </c>
-      <c r="O74" s="20">
+      <c r="O74" s="13">
         <v>45166.607638888891</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="140" t="s">
+      <c r="A75" s="130" t="s">
         <v>66</v>
       </c>
-      <c r="B75" s="140">
+      <c r="B75" s="130">
         <v>140</v>
       </c>
-      <c r="C75" s="140">
+      <c r="C75" s="130">
         <v>0.2235</v>
       </c>
-      <c r="D75" s="140">
+      <c r="D75" s="130">
         <v>0.2268</v>
       </c>
-      <c r="E75" s="140">
+      <c r="E75" s="130">
         <f t="shared" si="11"/>
         <v>3.2999999999999974E-3</v>
       </c>
-      <c r="F75" s="141">
+      <c r="F75" s="131">
         <f t="shared" si="12"/>
         <v>23.571428571428555</v>
       </c>
-      <c r="G75" s="140">
+      <c r="G75" s="130">
         <v>0</v>
       </c>
-      <c r="H75" s="142">
+      <c r="H75" s="132">
         <v>0</v>
       </c>
-      <c r="I75" s="143"/>
-      <c r="J75" s="144">
+      <c r="I75" s="133"/>
+      <c r="J75" s="134">
         <v>4.2779999999999996</v>
       </c>
-      <c r="K75" s="140"/>
-      <c r="L75" s="140"/>
-      <c r="M75" s="140"/>
-      <c r="N75" s="145">
+      <c r="K75" s="130"/>
+      <c r="L75" s="130"/>
+      <c r="M75" s="130"/>
+      <c r="N75" s="135">
         <v>483</v>
       </c>
-      <c r="O75" s="76">
+      <c r="O75" s="66">
         <v>45166.638888888891</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A76" s="146" t="s">
+      <c r="A76" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="B76" s="146">
+      <c r="B76" s="136">
         <v>250</v>
       </c>
-      <c r="C76" s="146">
+      <c r="C76" s="136">
         <v>0.23899999999999999</v>
       </c>
-      <c r="D76" s="146">
+      <c r="D76" s="136">
         <v>0.24840000000000001</v>
       </c>
-      <c r="E76" s="146">
+      <c r="E76" s="136">
         <f t="shared" ref="E76:E87" si="13">D76-C76</f>
         <v>9.4000000000000195E-3</v>
       </c>
-      <c r="F76" s="147">
+      <c r="F76" s="137">
         <f t="shared" ref="F76:F87" si="14">E76/B76*1000*1000</f>
         <v>37.60000000000008</v>
       </c>
-      <c r="G76" s="94">
+      <c r="G76" s="84">
         <v>63.87</v>
       </c>
-      <c r="H76" s="96">
+      <c r="H76" s="86">
         <v>1.3348544727944125</v>
       </c>
-      <c r="I76" s="97">
+      <c r="I76" s="87">
         <f t="shared" si="6"/>
         <v>5.33941789117765</v>
       </c>
-      <c r="J76" s="148">
+      <c r="J76" s="138">
         <v>5.4009999999999998</v>
       </c>
-      <c r="K76" s="146"/>
-      <c r="L76" s="146"/>
-      <c r="M76" s="146"/>
-      <c r="N76" s="149">
+      <c r="K76" s="136"/>
+      <c r="L76" s="136"/>
+      <c r="M76" s="136"/>
+      <c r="N76" s="139">
         <v>484</v>
       </c>
-      <c r="O76" s="86">
+      <c r="O76" s="76">
         <v>45183.744444444441</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A77" s="14" t="s">
+      <c r="A77" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B77" s="14">
+      <c r="B77" s="9">
         <v>260</v>
       </c>
-      <c r="C77" s="14">
+      <c r="C77" s="9">
         <v>0.2356</v>
       </c>
-      <c r="D77" s="14">
+      <c r="D77" s="9">
         <v>0.24379999999999999</v>
       </c>
-      <c r="E77" s="14">
+      <c r="E77" s="9">
         <f t="shared" si="13"/>
         <v>8.1999999999999851E-3</v>
       </c>
-      <c r="F77" s="23">
+      <c r="F77" s="16">
         <f t="shared" si="14"/>
         <v>31.53846153846148</v>
       </c>
-      <c r="G77" s="8">
+      <c r="G77" s="6">
         <v>75.400000000000006</v>
       </c>
-      <c r="H77" s="24">
+      <c r="H77" s="17">
         <v>1.1993748002938676</v>
       </c>
-      <c r="I77" s="29">
+      <c r="I77" s="22">
         <f t="shared" si="6"/>
         <v>4.6129800011302597</v>
       </c>
-      <c r="J77" s="43">
+      <c r="J77" s="36">
         <v>4.8639999999999999</v>
       </c>
-      <c r="K77" s="14"/>
-      <c r="L77" s="14"/>
-      <c r="M77" s="14"/>
-      <c r="N77" s="48">
+      <c r="K77" s="9"/>
+      <c r="L77" s="9"/>
+      <c r="M77" s="9"/>
+      <c r="N77" s="41">
         <v>485</v>
       </c>
-      <c r="O77" s="20">
+      <c r="O77" s="13">
         <v>45183.754861111112</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A78" s="14" t="s">
+      <c r="A78" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B78" s="14">
+      <c r="B78" s="9">
         <v>260</v>
       </c>
-      <c r="C78" s="14">
+      <c r="C78" s="9">
         <v>0.23300000000000001</v>
       </c>
-      <c r="D78" s="14">
+      <c r="D78" s="9">
         <v>0.24030000000000001</v>
       </c>
-      <c r="E78" s="14">
+      <c r="E78" s="9">
         <f t="shared" si="13"/>
         <v>7.3000000000000009E-3</v>
       </c>
-      <c r="F78" s="23">
+      <c r="F78" s="16">
         <f t="shared" si="14"/>
         <v>28.076923076923084</v>
       </c>
-      <c r="G78" s="8">
+      <c r="G78" s="6">
         <v>70.75</v>
       </c>
-      <c r="H78" s="24">
+      <c r="H78" s="17">
         <v>1.1397797508432075</v>
       </c>
-      <c r="I78" s="29">
+      <c r="I78" s="22">
         <f t="shared" ref="I78:I87" si="15">H78/B78*1000</f>
         <v>4.3837682724738745</v>
       </c>
-      <c r="J78" s="43">
+      <c r="J78" s="36">
         <v>4.6319999999999997</v>
       </c>
-      <c r="K78" s="14"/>
-      <c r="L78" s="14"/>
-      <c r="M78" s="14"/>
-      <c r="N78" s="48">
+      <c r="K78" s="9"/>
+      <c r="L78" s="9"/>
+      <c r="M78" s="9"/>
+      <c r="N78" s="41">
         <v>486</v>
       </c>
-      <c r="O78" s="20">
+      <c r="O78" s="13">
         <v>45183.765277777777</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A79" s="14" t="s">
+      <c r="A79" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B79" s="14">
+      <c r="B79" s="9">
         <v>250</v>
       </c>
-      <c r="C79" s="14">
+      <c r="C79" s="9">
         <v>0.2351</v>
       </c>
-      <c r="D79" s="14">
+      <c r="D79" s="9">
         <v>0.24099999999999999</v>
       </c>
-      <c r="E79" s="14">
+      <c r="E79" s="9">
         <f t="shared" si="13"/>
         <v>5.8999999999999886E-3</v>
       </c>
-      <c r="F79" s="23">
+      <c r="F79" s="16">
         <f t="shared" si="14"/>
         <v>23.599999999999955</v>
       </c>
-      <c r="G79" s="8">
+      <c r="G79" s="6">
         <v>82.6</v>
       </c>
-      <c r="H79" s="24">
+      <c r="H79" s="17">
         <v>1.0275484426400625</v>
       </c>
-      <c r="I79" s="29">
+      <c r="I79" s="22">
         <f t="shared" si="15"/>
         <v>4.11019377056025</v>
       </c>
-      <c r="J79" s="43">
+      <c r="J79" s="36">
         <v>4.1559999999999997</v>
       </c>
-      <c r="K79" s="14"/>
-      <c r="L79" s="14"/>
-      <c r="M79" s="14"/>
-      <c r="N79" s="48">
+      <c r="K79" s="9"/>
+      <c r="L79" s="9"/>
+      <c r="M79" s="9"/>
+      <c r="N79" s="41">
         <v>487</v>
       </c>
-      <c r="O79" s="20">
+      <c r="O79" s="13">
         <v>45183.775694444441</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A80" s="14" t="s">
+      <c r="A80" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B80" s="14">
+      <c r="B80" s="9">
         <v>255</v>
       </c>
-      <c r="C80" s="14">
+      <c r="C80" s="9">
         <v>0.23710000000000001</v>
       </c>
-      <c r="D80" s="14">
+      <c r="D80" s="9">
         <v>0.24249999999999999</v>
       </c>
-      <c r="E80" s="14">
+      <c r="E80" s="9">
         <f t="shared" si="13"/>
         <v>5.3999999999999881E-3</v>
       </c>
-      <c r="F80" s="23">
+      <c r="F80" s="16">
         <f t="shared" si="14"/>
         <v>21.176470588235247</v>
       </c>
-      <c r="G80" s="8">
+      <c r="G80" s="6">
         <v>54.12</v>
       </c>
-      <c r="H80" s="24">
+      <c r="H80" s="17">
         <v>0</v>
       </c>
-      <c r="I80" s="29"/>
-      <c r="J80" s="43">
+      <c r="I80" s="22"/>
+      <c r="J80" s="36">
         <v>3.2890000000000001</v>
       </c>
-      <c r="K80" s="14"/>
-      <c r="L80" s="14"/>
-      <c r="M80" s="14"/>
-      <c r="N80" s="48">
+      <c r="K80" s="9"/>
+      <c r="L80" s="9"/>
+      <c r="M80" s="9"/>
+      <c r="N80" s="41">
         <v>488</v>
       </c>
-      <c r="O80" s="20">
+      <c r="O80" s="13">
         <v>45183.786111111112</v>
       </c>
     </row>
-    <row r="81" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="150" t="s">
+    <row r="81" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="140" t="s">
         <v>50</v>
       </c>
-      <c r="B81" s="150">
+      <c r="B81" s="140">
         <v>255</v>
       </c>
-      <c r="C81" s="150">
+      <c r="C81" s="140">
         <v>0.23580000000000001</v>
       </c>
-      <c r="D81" s="150">
+      <c r="D81" s="140">
         <v>0.2417</v>
       </c>
-      <c r="E81" s="150">
+      <c r="E81" s="140">
         <f t="shared" si="13"/>
         <v>5.8999999999999886E-3</v>
       </c>
-      <c r="F81" s="151">
+      <c r="F81" s="141">
         <f t="shared" si="14"/>
         <v>23.137254901960741</v>
       </c>
-      <c r="G81" s="151"/>
-      <c r="H81" s="102">
+      <c r="G81" s="141"/>
+      <c r="H81" s="92">
         <v>0.95984970198324493</v>
       </c>
-      <c r="I81" s="103">
+      <c r="I81" s="93">
         <f t="shared" si="15"/>
         <v>3.7641164783656667</v>
       </c>
-      <c r="J81" s="152">
+      <c r="J81" s="142">
         <v>8.7289999999999992</v>
       </c>
-      <c r="K81" s="150"/>
-      <c r="L81" s="150"/>
-      <c r="M81" s="150"/>
-      <c r="N81" s="153">
+      <c r="K81" s="140"/>
+      <c r="L81" s="140"/>
+      <c r="M81" s="140"/>
+      <c r="N81" s="143">
         <v>489</v>
       </c>
-      <c r="O81" s="76">
+      <c r="O81" s="66">
         <v>45183.79791666667</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A82" s="130" t="s">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A82" s="120" t="s">
         <v>51</v>
       </c>
-      <c r="B82" s="130">
+      <c r="B82" s="120">
         <v>260</v>
       </c>
-      <c r="C82" s="130">
+      <c r="C82" s="120">
         <v>0.23469999999999999</v>
       </c>
-      <c r="D82" s="130">
+      <c r="D82" s="120">
         <v>0.2427</v>
       </c>
-      <c r="E82" s="130">
+      <c r="E82" s="120">
         <f t="shared" si="13"/>
         <v>8.0000000000000071E-3</v>
       </c>
-      <c r="F82" s="131">
+      <c r="F82" s="121">
         <f t="shared" si="14"/>
         <v>30.769230769230795</v>
       </c>
-      <c r="G82" s="77">
+      <c r="G82" s="67">
         <v>95.962999999999994</v>
       </c>
-      <c r="H82" s="78">
+      <c r="H82" s="68">
         <v>1.3355551810699124</v>
       </c>
-      <c r="I82" s="79">
+      <c r="I82" s="69">
         <f t="shared" si="15"/>
         <v>5.1367506964227401</v>
       </c>
-      <c r="J82" s="132">
+      <c r="J82" s="122">
         <v>8.7050000000000001</v>
       </c>
-      <c r="K82" s="130"/>
-      <c r="L82" s="130"/>
-      <c r="M82" s="130"/>
-      <c r="N82" s="133">
+      <c r="K82" s="120"/>
+      <c r="L82" s="120"/>
+      <c r="M82" s="120"/>
+      <c r="N82" s="123">
         <v>490</v>
       </c>
-      <c r="O82" s="70">
+      <c r="O82" s="60">
         <v>45183.739583333336</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A83" s="14" t="s">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A83" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B83" s="14">
+      <c r="B83" s="9">
         <v>265</v>
       </c>
-      <c r="C83" s="14">
+      <c r="C83" s="9">
         <v>0.24060000000000001</v>
       </c>
-      <c r="D83" s="14">
+      <c r="D83" s="9">
         <v>0.24859999999999999</v>
       </c>
-      <c r="E83" s="14">
+      <c r="E83" s="9">
         <f t="shared" si="13"/>
         <v>7.9999999999999793E-3</v>
       </c>
-      <c r="F83" s="23">
+      <c r="F83" s="16">
         <f t="shared" si="14"/>
         <v>30.188679245282938</v>
       </c>
-      <c r="G83" s="8">
+      <c r="G83" s="6">
         <v>80.180000000000007</v>
       </c>
-      <c r="H83" s="24">
+      <c r="H83" s="17">
         <v>1.1113195373306999</v>
       </c>
-      <c r="I83" s="29">
+      <c r="I83" s="22">
         <f t="shared" si="15"/>
         <v>4.1936586314366027</v>
       </c>
-      <c r="J83" s="43">
+      <c r="J83" s="36">
         <v>3.1509999999999998</v>
       </c>
-      <c r="K83" s="14"/>
-      <c r="L83" s="14"/>
-      <c r="M83" s="14"/>
-      <c r="N83" s="48">
+      <c r="K83" s="9"/>
+      <c r="L83" s="9"/>
+      <c r="M83" s="9"/>
+      <c r="N83" s="41">
         <v>491</v>
       </c>
-      <c r="O83" s="20">
+      <c r="O83" s="13">
         <v>45183.75</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A84" s="14" t="s">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A84" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B84" s="14">
+      <c r="B84" s="9">
         <v>240</v>
       </c>
-      <c r="C84" s="14">
+      <c r="C84" s="9">
         <v>0.2384</v>
       </c>
-      <c r="D84" s="14">
+      <c r="D84" s="9">
         <v>0.24540000000000001</v>
       </c>
-      <c r="E84" s="14">
+      <c r="E84" s="9">
         <f t="shared" si="13"/>
         <v>7.0000000000000062E-3</v>
       </c>
-      <c r="F84" s="23">
+      <c r="F84" s="16">
         <f t="shared" si="14"/>
         <v>29.166666666666696</v>
       </c>
-      <c r="G84" s="8">
+      <c r="G84" s="6">
         <v>70.510000000000005</v>
       </c>
-      <c r="H84" s="24">
+      <c r="H84" s="17">
         <v>1.0044204297234951</v>
       </c>
-      <c r="I84" s="29">
+      <c r="I84" s="22">
         <f t="shared" si="15"/>
         <v>4.1850851238478963</v>
       </c>
-      <c r="J84" s="43">
+      <c r="J84" s="36">
         <v>2.3119999999999998</v>
       </c>
-      <c r="K84" s="14"/>
-      <c r="L84" s="14"/>
-      <c r="M84" s="14"/>
-      <c r="N84" s="48">
+      <c r="K84" s="9"/>
+      <c r="L84" s="9"/>
+      <c r="M84" s="9"/>
+      <c r="N84" s="41">
         <v>492</v>
       </c>
-      <c r="O84" s="20">
+      <c r="O84" s="13">
         <v>45183.760416666664</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A85" s="14" t="s">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A85" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B85" s="14">
+      <c r="B85" s="9">
         <v>240</v>
       </c>
-      <c r="C85" s="14">
+      <c r="C85" s="9">
         <v>0.23369999999999999</v>
       </c>
-      <c r="D85" s="14">
+      <c r="D85" s="9">
         <v>0.23860000000000001</v>
       </c>
-      <c r="E85" s="14">
+      <c r="E85" s="9">
         <f t="shared" si="13"/>
         <v>4.9000000000000155E-3</v>
       </c>
-      <c r="F85" s="23">
+      <c r="F85" s="16">
         <f>E85/B85*1000*1000</f>
         <v>20.416666666666732</v>
       </c>
-      <c r="G85" s="8">
+      <c r="G85" s="6">
         <v>64.436999999999998</v>
       </c>
-      <c r="H85" s="24">
+      <c r="H85" s="17">
         <v>0.71189129550605745</v>
       </c>
-      <c r="I85" s="29">
+      <c r="I85" s="22">
         <f t="shared" si="15"/>
         <v>2.9662137312752392</v>
       </c>
-      <c r="J85" s="43">
+      <c r="J85" s="36">
         <v>0.74299999999999999</v>
       </c>
-      <c r="K85" s="14"/>
-      <c r="L85" s="14"/>
-      <c r="M85" s="14"/>
-      <c r="N85" s="48">
+      <c r="K85" s="9"/>
+      <c r="L85" s="9"/>
+      <c r="M85" s="9"/>
+      <c r="N85" s="41">
         <v>493</v>
       </c>
-      <c r="O85" s="20">
+      <c r="O85" s="13">
         <v>45183.78125</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A86" s="14" t="s">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A86" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B86" s="14">
+      <c r="B86" s="9">
         <v>250</v>
       </c>
-      <c r="C86" s="14">
+      <c r="C86" s="9">
         <v>0.2354</v>
       </c>
-      <c r="D86" s="14">
+      <c r="D86" s="9">
         <v>0.2399</v>
       </c>
-      <c r="E86" s="14">
+      <c r="E86" s="9">
         <f t="shared" si="13"/>
         <v>4.500000000000004E-3</v>
       </c>
-      <c r="F86" s="23">
+      <c r="F86" s="16">
         <f t="shared" si="14"/>
         <v>18.000000000000014</v>
       </c>
-      <c r="G86" s="8">
+      <c r="G86" s="6">
         <v>46.07</v>
       </c>
-      <c r="H86" s="24">
+      <c r="H86" s="17">
         <v>0</v>
       </c>
-      <c r="I86" s="29"/>
-      <c r="J86" s="43"/>
-      <c r="K86" s="14"/>
-      <c r="L86" s="14"/>
-      <c r="M86" s="14"/>
-      <c r="N86" s="48">
+      <c r="I86" s="22"/>
+      <c r="J86" s="36"/>
+      <c r="K86" s="9"/>
+      <c r="L86" s="9"/>
+      <c r="M86" s="9"/>
+      <c r="N86" s="41">
         <v>494</v>
       </c>
-      <c r="O86" s="20">
+      <c r="O86" s="13">
         <v>45183.802083333336</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A87" s="14" t="s">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A87" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B87" s="14">
+      <c r="B87" s="9">
         <v>100</v>
       </c>
-      <c r="C87" s="14">
+      <c r="C87" s="9">
         <v>0.23680000000000001</v>
       </c>
-      <c r="D87" s="14">
+      <c r="D87" s="9">
         <v>0.2387</v>
       </c>
-      <c r="E87" s="14">
+      <c r="E87" s="9">
         <f t="shared" si="13"/>
         <v>1.899999999999985E-3</v>
       </c>
-      <c r="F87" s="23">
+      <c r="F87" s="16">
         <f t="shared" si="14"/>
         <v>18.999999999999851</v>
       </c>
-      <c r="G87" s="8">
+      <c r="G87" s="6">
         <v>39.299999999999997</v>
       </c>
-      <c r="H87" s="24">
+      <c r="H87" s="17">
         <v>0.47449365167919122</v>
       </c>
-      <c r="I87" s="29">
+      <c r="I87" s="22">
         <f t="shared" si="15"/>
         <v>4.7449365167919124</v>
       </c>
-      <c r="J87" s="43">
+      <c r="J87" s="36">
         <v>0</v>
       </c>
-      <c r="K87" s="14"/>
-      <c r="L87" s="14"/>
-      <c r="M87" s="14"/>
-      <c r="N87" s="48">
+      <c r="K87" s="9"/>
+      <c r="L87" s="9"/>
+      <c r="M87" s="9"/>
+      <c r="N87" s="41">
         <v>495</v>
       </c>
-      <c r="O87" s="20">
+      <c r="O87" s="13">
         <v>45183.833333333336</v>
       </c>
     </row>
-    <row r="89" spans="1:15" ht="45" x14ac:dyDescent="0.25">
-      <c r="A89" s="154" t="s">
+    <row r="89" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="A89" s="144" t="s">
         <v>120</v>
       </c>
-      <c r="B89" s="155" t="s">
+      <c r="B89" s="145" t="s">
         <v>0</v>
       </c>
-      <c r="C89" s="156" t="s">
+      <c r="C89" s="146" t="s">
         <v>2</v>
       </c>
-      <c r="D89" s="156" t="s">
+      <c r="D89" s="146" t="s">
         <v>3</v>
       </c>
-      <c r="E89" s="156" t="s">
+      <c r="E89" s="146" t="s">
         <v>71</v>
       </c>
-      <c r="F89" s="156" t="s">
+      <c r="F89" s="146" t="s">
         <v>4</v>
       </c>
-      <c r="G89" s="156" t="s">
+      <c r="G89" s="146" t="s">
         <v>97</v>
       </c>
-      <c r="H89" s="156" t="s">
+      <c r="H89" s="146" t="s">
         <v>72</v>
       </c>
-      <c r="I89" s="156" t="s">
+      <c r="I89" s="146" t="s">
         <v>70</v>
       </c>
-      <c r="J89" s="156" t="s">
+      <c r="J89" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="K89" s="155" t="s">
+      <c r="K89" s="145" t="s">
         <v>117</v>
       </c>
-      <c r="L89" s="156" t="s">
+      <c r="L89" s="146" t="s">
         <v>118</v>
       </c>
-      <c r="M89" s="156" t="s">
+      <c r="M89" s="146" t="s">
         <v>119</v>
       </c>
-      <c r="N89" s="156" t="s">
+      <c r="N89" s="241" t="s">
         <v>61</v>
       </c>
-      <c r="O89" s="156" t="s">
+      <c r="O89" s="146" t="s">
         <v>67</v>
       </c>
+      <c r="P89" s="242" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A90" s="49" t="s">
-        <v>121</v>
-      </c>
-      <c r="B90" s="157">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B90" s="2">
         <v>287.25</v>
       </c>
-      <c r="C90" s="157">
+      <c r="C90" s="2">
         <v>0.2442</v>
       </c>
-      <c r="D90" s="157">
+      <c r="D90" s="2">
         <v>0.24560000000000001</v>
       </c>
-      <c r="E90" s="157">
+      <c r="E90" s="2">
         <f>D90-C90</f>
         <v>1.4000000000000123E-3</v>
       </c>
-      <c r="F90" s="158">
+      <c r="F90" s="147">
         <f>(E90*1000)/(B90/1000)</f>
         <v>4.8738033072237155</v>
       </c>
-      <c r="G90" s="157"/>
-      <c r="H90" s="159">
+      <c r="G90" s="2">
+        <v>0</v>
+      </c>
+      <c r="H90" s="148">
         <v>1.046437323968445</v>
       </c>
-      <c r="I90" s="160">
+      <c r="I90" s="149">
         <f>H90/(B90/1000)</f>
         <v>3.6429497788283549</v>
       </c>
-      <c r="J90" s="157"/>
-      <c r="K90" s="157"/>
-      <c r="L90" s="162">
+      <c r="J90" s="2"/>
+      <c r="K90" s="2"/>
+      <c r="L90" s="150">
         <v>0.03</v>
       </c>
-      <c r="M90" s="162">
+      <c r="M90" s="150">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="N90" s="157" t="s">
-        <v>129</v>
-      </c>
-      <c r="O90" s="161">
+      <c r="N90" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="O90" s="243">
         <v>44394</v>
       </c>
+      <c r="P90" s="237" t="s">
+        <v>166</v>
+      </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A91" s="49" t="s">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A91" s="151" t="s">
+        <v>130</v>
+      </c>
+      <c r="B91" s="151">
+        <v>159.59</v>
+      </c>
+      <c r="C91" s="151">
+        <v>0.2402</v>
+      </c>
+      <c r="D91" s="151">
+        <v>0.24030000000000001</v>
+      </c>
+      <c r="E91" s="151">
+        <f t="shared" ref="E91:E130" si="16">D91-C91</f>
+        <v>1.0000000000001674E-4</v>
+      </c>
+      <c r="F91" s="152">
+        <f t="shared" ref="F91:F130" si="17">(E91*1000)/(B91/1000)</f>
+        <v>0.62660567704753889</v>
+      </c>
+      <c r="G91" s="151">
+        <v>0</v>
+      </c>
+      <c r="H91" s="148">
+        <v>0.39719240842078224</v>
+      </c>
+      <c r="I91" s="153">
+        <f t="shared" ref="I91:I128" si="18">H91/(B91/1000)</f>
+        <v>2.4888301799660519</v>
+      </c>
+      <c r="J91" s="151"/>
+      <c r="K91" s="151"/>
+      <c r="L91" s="150">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="M91" s="150">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="N91" s="151" t="s">
         <v>122</v>
       </c>
-      <c r="B91" s="157">
-        <v>159.59</v>
-      </c>
-      <c r="C91" s="157">
-        <v>0.2402</v>
-      </c>
-      <c r="D91" s="157">
-        <v>0.24030000000000001</v>
-      </c>
-      <c r="E91" s="157">
-        <f t="shared" ref="E91:E123" si="16">D91-C91</f>
-        <v>1.0000000000001674E-4</v>
-      </c>
-      <c r="F91" s="158">
-        <f t="shared" ref="F91:F123" si="17">(E91*1000)/(B91/1000)</f>
-        <v>0.62660567704753889</v>
-      </c>
-      <c r="G91" s="157"/>
-      <c r="H91" s="159">
-        <v>0.39719240842078224</v>
-      </c>
-      <c r="I91" s="160">
-        <f t="shared" ref="I91:I97" si="18">H91/(B91/1000)</f>
-        <v>2.4888301799660519</v>
-      </c>
-      <c r="J91" s="157"/>
-      <c r="K91" s="157"/>
-      <c r="L91" s="162">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="M91" s="162">
-        <v>3.6999999999999998E-2</v>
-      </c>
-      <c r="N91" s="157" t="s">
-        <v>130</v>
-      </c>
-      <c r="O91" s="161">
+      <c r="O91" s="154">
         <v>44394</v>
       </c>
+      <c r="P91" s="236" t="s">
+        <v>169</v>
+      </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A92" s="49" t="s">
-        <v>123</v>
-      </c>
-      <c r="B92" s="157">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A92" s="151" t="s">
+        <v>131</v>
+      </c>
+      <c r="B92" s="151">
         <v>134.51</v>
       </c>
-      <c r="C92" s="157">
+      <c r="C92" s="151">
         <v>0.2412</v>
       </c>
-      <c r="D92" s="157">
+      <c r="D92" s="151">
         <v>0.24179999999999999</v>
       </c>
-      <c r="E92" s="157">
+      <c r="E92" s="151">
         <f t="shared" si="16"/>
         <v>5.9999999999998943E-4</v>
       </c>
-      <c r="F92" s="158">
+      <c r="F92" s="152">
         <f t="shared" si="17"/>
         <v>4.4606348970335992</v>
       </c>
-      <c r="G92" s="157"/>
-      <c r="H92" s="159">
+      <c r="G92" s="151">
+        <v>0</v>
+      </c>
+      <c r="H92" s="148">
         <v>0.33234237884337697</v>
       </c>
-      <c r="I92" s="160">
+      <c r="I92" s="153">
         <f t="shared" si="18"/>
         <v>2.4707633547199239</v>
       </c>
-      <c r="J92" s="157"/>
-      <c r="K92" s="157"/>
-      <c r="L92" s="162">
+      <c r="J92" s="151"/>
+      <c r="K92" s="151"/>
+      <c r="L92" s="150">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="M92" s="162">
+      <c r="M92" s="150">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="N92" s="157" t="s">
-        <v>131</v>
-      </c>
-      <c r="O92" s="161">
+      <c r="N92" s="151" t="s">
+        <v>123</v>
+      </c>
+      <c r="O92" s="154">
         <v>44396</v>
       </c>
+      <c r="P92" s="233" t="s">
+        <v>167</v>
+      </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A93" s="49" t="s">
-        <v>124</v>
-      </c>
-      <c r="B93" s="157">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A93" s="151" t="s">
+        <v>132</v>
+      </c>
+      <c r="B93" s="151">
         <v>117.22999999999999</v>
       </c>
-      <c r="C93" s="157">
+      <c r="C93" s="151">
         <v>0.2407</v>
       </c>
-      <c r="D93" s="157">
+      <c r="D93" s="151">
         <v>0.24160000000000001</v>
       </c>
-      <c r="E93" s="157">
+      <c r="E93" s="151">
         <f t="shared" si="16"/>
         <v>9.000000000000119E-4</v>
       </c>
-      <c r="F93" s="158">
+      <c r="F93" s="152">
         <f t="shared" si="17"/>
         <v>7.6772157297621089</v>
       </c>
-      <c r="G93" s="157"/>
-      <c r="H93" s="159">
+      <c r="G93" s="151">
+        <v>0</v>
+      </c>
+      <c r="H93" s="148">
         <v>0.33481118985762565</v>
       </c>
-      <c r="I93" s="160">
+      <c r="I93" s="153">
         <f t="shared" si="18"/>
         <v>2.8560197036392192</v>
       </c>
-      <c r="J93" s="157"/>
-      <c r="K93" s="157"/>
-      <c r="L93" s="162">
+      <c r="J93" s="151"/>
+      <c r="K93" s="151"/>
+      <c r="L93" s="150">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="M93" s="162">
+      <c r="M93" s="150">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="N93" s="157" t="s">
-        <v>132</v>
-      </c>
-      <c r="O93" s="161">
+      <c r="N93" s="151" t="s">
+        <v>124</v>
+      </c>
+      <c r="O93" s="154">
         <v>44396</v>
       </c>
+      <c r="P93" s="235" t="s">
+        <v>170</v>
+      </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A94" s="49" t="s">
-        <v>125</v>
-      </c>
-      <c r="B94" s="157">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A94" s="151" t="s">
+        <v>133</v>
+      </c>
+      <c r="B94" s="151">
         <v>333.45</v>
       </c>
-      <c r="C94" s="157">
+      <c r="C94" s="151">
         <v>0.24099999999999999</v>
       </c>
-      <c r="D94" s="157">
+      <c r="D94" s="151">
         <v>0.24249999999999999</v>
       </c>
-      <c r="E94" s="157">
+      <c r="E94" s="151">
         <f t="shared" si="16"/>
         <v>1.5000000000000013E-3</v>
       </c>
-      <c r="F94" s="158">
+      <c r="F94" s="152">
         <f t="shared" si="17"/>
         <v>4.4984255510571343</v>
       </c>
-      <c r="G94" s="157"/>
-      <c r="H94" s="159">
+      <c r="G94" s="151">
+        <v>0</v>
+      </c>
+      <c r="H94" s="148">
         <v>0.49779418859739377</v>
       </c>
-      <c r="I94" s="160">
+      <c r="I94" s="153">
         <f t="shared" si="18"/>
         <v>1.4928600647695121</v>
       </c>
-      <c r="J94" s="157"/>
-      <c r="K94" s="157"/>
-      <c r="L94" s="162">
+      <c r="J94" s="151"/>
+      <c r="K94" s="151"/>
+      <c r="L94" s="150">
         <v>2.4E-2</v>
       </c>
-      <c r="M94" s="162">
+      <c r="M94" s="150">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="N94" s="157" t="s">
-        <v>133</v>
-      </c>
-      <c r="O94" s="161">
+      <c r="N94" s="151" t="s">
+        <v>125</v>
+      </c>
+      <c r="O94" s="154">
         <v>44413</v>
       </c>
+      <c r="P94" s="240" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A95" s="49" t="s">
-        <v>126</v>
-      </c>
-      <c r="B95" s="157">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A95" s="151" t="s">
+        <v>135</v>
+      </c>
+      <c r="B95" s="151">
         <v>318</v>
       </c>
-      <c r="C95" s="157">
+      <c r="C95" s="151">
         <v>0.24160000000000001</v>
       </c>
-      <c r="D95" s="157">
+      <c r="D95" s="151">
         <v>0.24329999999999999</v>
       </c>
-      <c r="E95" s="157">
+      <c r="E95" s="151">
         <f t="shared" si="16"/>
         <v>1.6999999999999793E-3</v>
       </c>
-      <c r="F95" s="158">
+      <c r="F95" s="152">
         <f t="shared" si="17"/>
         <v>5.345911949685469</v>
       </c>
-      <c r="G95" s="157"/>
-      <c r="H95" s="159">
+      <c r="G95" s="151">
+        <v>0</v>
+      </c>
+      <c r="H95" s="148">
         <v>0.47710769568542255</v>
       </c>
-      <c r="I95" s="160">
+      <c r="I95" s="153">
         <f t="shared" si="18"/>
         <v>1.5003386656774294</v>
       </c>
-      <c r="J95" s="157"/>
-      <c r="K95" s="157"/>
-      <c r="L95" s="162">
+      <c r="J95" s="151"/>
+      <c r="K95" s="151"/>
+      <c r="L95" s="150">
         <v>2.4E-2</v>
       </c>
-      <c r="M95" s="162">
+      <c r="M95" s="150">
         <v>2.3E-2</v>
       </c>
-      <c r="N95" s="157" t="s">
-        <v>134</v>
-      </c>
-      <c r="O95" s="161">
+      <c r="N95" s="151" t="s">
+        <v>126</v>
+      </c>
+      <c r="O95" s="154">
         <v>44413</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A96" s="49" t="s">
-        <v>127</v>
-      </c>
-      <c r="B96" s="157">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A96" s="151" t="s">
+        <v>136</v>
+      </c>
+      <c r="B96" s="151">
         <v>293.42</v>
       </c>
-      <c r="C96" s="157">
+      <c r="C96" s="151">
         <v>0.24</v>
       </c>
-      <c r="D96" s="157">
+      <c r="D96" s="151">
         <v>0.24360000000000001</v>
       </c>
-      <c r="E96" s="157">
+      <c r="E96" s="151">
         <f t="shared" si="16"/>
         <v>3.6000000000000199E-3</v>
       </c>
-      <c r="F96" s="158">
+      <c r="F96" s="152">
         <f t="shared" si="17"/>
         <v>12.269102310681003</v>
       </c>
-      <c r="G96" s="157"/>
-      <c r="H96" s="159">
+      <c r="G96" s="151">
+        <v>0</v>
+      </c>
+      <c r="H96" s="148">
         <v>0.75074101119692438</v>
       </c>
-      <c r="I96" s="160">
+      <c r="I96" s="153">
         <f t="shared" si="18"/>
         <v>2.5585884097775349</v>
       </c>
-      <c r="J96" s="157"/>
-      <c r="K96" s="157"/>
-      <c r="L96" s="162">
+      <c r="J96" s="151"/>
+      <c r="K96" s="151"/>
+      <c r="L96" s="150">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="M96" s="162">
+      <c r="M96" s="150">
         <v>2.4E-2</v>
       </c>
-      <c r="N96" s="157" t="s">
-        <v>135</v>
-      </c>
-      <c r="O96" s="161">
+      <c r="N96" s="151" t="s">
+        <v>127</v>
+      </c>
+      <c r="O96" s="154">
         <v>44421</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A97" s="49" t="s">
-        <v>128</v>
-      </c>
-      <c r="B97" s="157">
+    <row r="97" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="155" t="s">
+        <v>134</v>
+      </c>
+      <c r="B97" s="155">
         <v>341.46</v>
       </c>
-      <c r="C97" s="157">
+      <c r="C97" s="155">
         <v>0.2407</v>
       </c>
-      <c r="D97" s="157">
+      <c r="D97" s="155">
         <v>0.2424</v>
       </c>
-      <c r="E97" s="157">
+      <c r="E97" s="155">
         <f t="shared" si="16"/>
         <v>1.7000000000000071E-3</v>
       </c>
-      <c r="F97" s="158">
+      <c r="F97" s="156">
         <f t="shared" si="17"/>
         <v>4.9786212147835975</v>
       </c>
-      <c r="G97" s="157"/>
-      <c r="H97" s="159">
+      <c r="G97" s="155">
+        <v>0</v>
+      </c>
+      <c r="H97" s="157">
         <v>0.58988878338277129</v>
       </c>
-      <c r="I97" s="160">
+      <c r="I97" s="158">
         <f t="shared" si="18"/>
         <v>1.72754871253667</v>
       </c>
-      <c r="J97" s="157"/>
-      <c r="K97" s="157"/>
-      <c r="L97" s="162">
+      <c r="J97" s="155"/>
+      <c r="K97" s="155"/>
+      <c r="L97" s="159">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="M97" s="162">
+      <c r="M97" s="159">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="N97" s="157" t="s">
-        <v>136</v>
-      </c>
-      <c r="O97" s="161">
+      <c r="N97" s="155" t="s">
+        <v>128</v>
+      </c>
+      <c r="O97" s="160">
         <v>44421</v>
       </c>
+      <c r="Q97" t="s">
+        <v>178</v>
+      </c>
     </row>
-    <row r="98" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A98" s="157" t="s">
-        <v>141</v>
-      </c>
-      <c r="B98" s="157">
+    <row r="98" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A98" s="161" t="s">
+        <v>137</v>
+      </c>
+      <c r="B98" s="162">
+        <v>119.13</v>
+      </c>
+      <c r="C98" s="161">
+        <v>0.23960000000000001</v>
+      </c>
+      <c r="D98" s="161">
+        <v>0.2404</v>
+      </c>
+      <c r="E98" s="161">
+        <f>D98-C98</f>
+        <v>7.9999999999999516E-4</v>
+      </c>
+      <c r="F98" s="163">
+        <f>(E98*1000)/(B98/1000)</f>
+        <v>6.7153529757407471</v>
+      </c>
+      <c r="G98" s="161">
+        <v>0</v>
+      </c>
+      <c r="H98" s="161"/>
+      <c r="I98" s="164"/>
+      <c r="J98" s="165">
+        <v>1.482</v>
+      </c>
+      <c r="K98" s="161"/>
+      <c r="L98" s="161"/>
+      <c r="M98" s="161"/>
+      <c r="N98" s="166">
+        <v>121</v>
+      </c>
+      <c r="O98" s="167">
+        <v>44632</v>
+      </c>
+      <c r="R98" t="s">
+        <v>172</v>
+      </c>
+      <c r="S98" t="s">
+        <v>173</v>
+      </c>
+      <c r="T98" t="s">
+        <v>174</v>
+      </c>
+      <c r="U98" t="s">
+        <v>175</v>
+      </c>
+      <c r="V98" t="s">
+        <v>117</v>
+      </c>
+      <c r="W98" t="s">
+        <v>176</v>
+      </c>
+      <c r="X98" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="99" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A99" s="168" t="s">
+        <v>138</v>
+      </c>
+      <c r="B99" s="168">
         <v>121.65</v>
       </c>
-      <c r="C98" s="157">
+      <c r="C99" s="168">
         <v>0.23630000000000001</v>
       </c>
-      <c r="D98" s="157">
+      <c r="D99" s="168">
         <v>0.23730000000000001</v>
       </c>
-      <c r="E98" s="157">
+      <c r="E99" s="168">
         <f t="shared" si="16"/>
         <v>1.0000000000000009E-3</v>
       </c>
-      <c r="F98" s="158">
+      <c r="F99" s="169">
         <f t="shared" si="17"/>
         <v>8.2203041512536039</v>
       </c>
-      <c r="G98" s="157"/>
-      <c r="H98" s="157"/>
-      <c r="I98" s="167"/>
-      <c r="J98" s="168">
+      <c r="G99" s="168">
+        <v>0</v>
+      </c>
+      <c r="H99" s="168"/>
+      <c r="I99" s="170"/>
+      <c r="J99" s="171">
         <v>1.538</v>
       </c>
-      <c r="K98" s="157"/>
-      <c r="L98" s="157"/>
-      <c r="M98" s="157"/>
-      <c r="N98" s="169">
+      <c r="K99" s="168"/>
+      <c r="L99" s="168"/>
+      <c r="M99" s="168"/>
+      <c r="N99" s="172">
         <v>120</v>
       </c>
-      <c r="O98" s="161">
+      <c r="O99" s="173">
         <v>44632</v>
       </c>
+      <c r="Q99" s="233" t="s">
+        <v>5</v>
+      </c>
+      <c r="R99">
+        <v>0</v>
+      </c>
+      <c r="S99" s="244">
+        <f>AVERAGE(F90:F93)</f>
+        <v>4.409564902766741</v>
+      </c>
+      <c r="T99" s="244">
+        <f>AVERAGE(L90:L93)</f>
+        <v>2.6249999999999996E-2</v>
+      </c>
+      <c r="U99" s="244">
+        <f>AVERAGE(M90:M93)</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="V99">
+        <v>0</v>
+      </c>
+      <c r="W99" s="245">
+        <f>AVERAGE(I90:I93)</f>
+        <v>2.8646407542883878</v>
+      </c>
+      <c r="X99" s="244">
+        <f>AVERAGE(J98:J101)</f>
+        <v>1.754</v>
+      </c>
     </row>
-    <row r="99" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A99" s="157" t="s">
+    <row r="100" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A100" s="168" t="s">
+        <v>139</v>
+      </c>
+      <c r="B100" s="168">
+        <v>119.19</v>
+      </c>
+      <c r="C100" s="168">
+        <v>0.2397</v>
+      </c>
+      <c r="D100" s="168">
+        <v>0.2409</v>
+      </c>
+      <c r="E100" s="168">
+        <f>D100-C100</f>
+        <v>1.2000000000000066E-3</v>
+      </c>
+      <c r="F100" s="169">
+        <f>(E100*1000)/(B100/1000)</f>
+        <v>10.067958721369298</v>
+      </c>
+      <c r="G100" s="168">
+        <v>0</v>
+      </c>
+      <c r="H100" s="168"/>
+      <c r="I100" s="170"/>
+      <c r="J100" s="168">
+        <v>2.238</v>
+      </c>
+      <c r="K100" s="168"/>
+      <c r="L100" s="168"/>
+      <c r="M100" s="168"/>
+      <c r="N100" s="172">
+        <v>129</v>
+      </c>
+      <c r="O100" s="173">
+        <v>44638</v>
+      </c>
+      <c r="Q100" s="234" t="s">
+        <v>6</v>
+      </c>
+      <c r="R100">
+        <v>0</v>
+      </c>
+      <c r="S100" s="244">
+        <f>AVERAGE(F102:F103)</f>
+        <v>2.9274423582748486</v>
+      </c>
+      <c r="T100" s="244">
+        <f>AVERAGE(L102:L103)</f>
+        <v>1.9785000000000011E-3</v>
+      </c>
+      <c r="U100" s="244">
+        <f>AVERAGE(M94:M97)</f>
+        <v>2.2749999999999999E-2</v>
+      </c>
+      <c r="V100">
+        <v>0</v>
+      </c>
+      <c r="W100" s="245">
+        <f>AVERAGE(I94:I97)</f>
+        <v>1.8198339631902867</v>
+      </c>
+      <c r="X100" s="244">
+        <f>AVERAGE(J102:J103)</f>
+        <v>2.8035000000000001</v>
+      </c>
+    </row>
+    <row r="101" spans="1:24" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="174" t="s">
+        <v>140</v>
+      </c>
+      <c r="B101" s="174">
+        <v>120.77</v>
+      </c>
+      <c r="C101" s="174">
+        <v>0.23830000000000001</v>
+      </c>
+      <c r="D101" s="174">
+        <v>0.23899999999999999</v>
+      </c>
+      <c r="E101" s="174">
+        <f>D101-C101</f>
+        <v>6.9999999999997842E-4</v>
+      </c>
+      <c r="F101" s="175">
+        <f>(E101*1000)/(B101/1000)</f>
+        <v>5.7961414258506121</v>
+      </c>
+      <c r="G101" s="174">
+        <v>0</v>
+      </c>
+      <c r="H101" s="174"/>
+      <c r="I101" s="176"/>
+      <c r="J101" s="177">
+        <v>1.758</v>
+      </c>
+      <c r="K101" s="174"/>
+      <c r="L101" s="178"/>
+      <c r="M101" s="174"/>
+      <c r="N101" s="179">
+        <v>124</v>
+      </c>
+      <c r="O101" s="180">
+        <v>44638</v>
+      </c>
+      <c r="Q101" s="235" t="s">
+        <v>56</v>
+      </c>
+      <c r="R101">
+        <v>0</v>
+      </c>
+      <c r="S101" s="244">
+        <f>AVERAGE(F102:F103)</f>
+        <v>2.9274423582748486</v>
+      </c>
+      <c r="T101" s="244">
+        <f>AVERAGE(L102:L103)</f>
+        <v>1.9785000000000011E-3</v>
+      </c>
+      <c r="U101" s="244">
+        <f>AVERAGE(M94:M97)</f>
+        <v>2.2749999999999999E-2</v>
+      </c>
+      <c r="V101">
+        <v>0</v>
+      </c>
+      <c r="W101" s="245">
+        <f>I21</f>
+        <v>1.5244913860512195</v>
+      </c>
+      <c r="X101" s="244">
+        <f>AVERAGE(J102:J103)</f>
+        <v>2.8035000000000001</v>
+      </c>
+    </row>
+    <row r="102" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A102" s="181" t="s">
+        <v>141</v>
+      </c>
+      <c r="B102" s="181">
+        <v>119.31</v>
+      </c>
+      <c r="C102" s="181">
+        <v>0.2397</v>
+      </c>
+      <c r="D102" s="181">
+        <v>0.24030000000000001</v>
+      </c>
+      <c r="E102" s="181">
+        <f>D102-C102</f>
+        <v>6.0000000000001719E-4</v>
+      </c>
+      <c r="F102" s="182">
+        <f>(E102*1000)/(B102/1000)</f>
+        <v>5.0289162685442728</v>
+      </c>
+      <c r="G102" s="181">
+        <v>0</v>
+      </c>
+      <c r="H102" s="181"/>
+      <c r="I102" s="183"/>
+      <c r="J102" s="184">
+        <v>3.294</v>
+      </c>
+      <c r="K102" s="181"/>
+      <c r="L102" s="185">
+        <v>2.2415999999999998E-3</v>
+      </c>
+      <c r="M102" s="181"/>
+      <c r="N102" s="186">
+        <v>126</v>
+      </c>
+      <c r="O102" s="187">
+        <v>44754</v>
+      </c>
+      <c r="Q102" s="236" t="s">
+        <v>58</v>
+      </c>
+      <c r="R102">
+        <v>0</v>
+      </c>
+      <c r="S102" s="245">
+        <f>F124</f>
+        <v>13.333333333333346</v>
+      </c>
+      <c r="T102" s="244"/>
+      <c r="U102" s="244"/>
+      <c r="V102">
+        <v>0</v>
+      </c>
+      <c r="W102" s="245">
+        <f>I124</f>
+        <v>8.767983246000001E-2</v>
+      </c>
+      <c r="X102" s="244">
+        <f>AVERAGE(J102:J103)</f>
+        <v>2.8035000000000001</v>
+      </c>
+    </row>
+    <row r="103" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A103" s="188" t="s">
         <v>142</v>
       </c>
-      <c r="B99" s="170">
-        <v>119.13</v>
-      </c>
-      <c r="C99" s="157">
-        <v>0.23960000000000001</v>
-      </c>
-      <c r="D99" s="157">
+      <c r="B103" s="188">
+        <v>121.07</v>
+      </c>
+      <c r="C103" s="188">
+        <v>0.24099999999999999</v>
+      </c>
+      <c r="D103" s="188">
+        <v>0.24110000000000001</v>
+      </c>
+      <c r="E103" s="188">
+        <f>D103-C103</f>
+        <v>1.0000000000001674E-4</v>
+      </c>
+      <c r="F103" s="189">
+        <f>(E103*1000)/(B103/1000)</f>
+        <v>0.82596844800542446</v>
+      </c>
+      <c r="G103" s="188">
+        <v>0</v>
+      </c>
+      <c r="H103" s="188"/>
+      <c r="I103" s="190"/>
+      <c r="J103" s="191">
+        <v>2.3130000000000002</v>
+      </c>
+      <c r="K103" s="188"/>
+      <c r="L103" s="192">
+        <v>1.7154000000000023E-3</v>
+      </c>
+      <c r="M103" s="188"/>
+      <c r="N103" s="193">
+        <v>123</v>
+      </c>
+      <c r="O103" s="194">
+        <v>44754</v>
+      </c>
+      <c r="Q103" s="237" t="s">
+        <v>57</v>
+      </c>
+      <c r="R103">
+        <v>0</v>
+      </c>
+      <c r="S103" s="245">
+        <f>F124</f>
+        <v>13.333333333333346</v>
+      </c>
+      <c r="T103" s="244"/>
+      <c r="U103" s="244"/>
+      <c r="V103">
+        <v>0</v>
+      </c>
+      <c r="W103" s="245">
+        <f>I124</f>
+        <v>8.767983246000001E-2</v>
+      </c>
+      <c r="X103" s="244">
+        <f>AVERAGE(J106:J107)</f>
+        <v>3.4509999999999996</v>
+      </c>
+    </row>
+    <row r="104" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A104" s="188" t="s">
+        <v>143</v>
+      </c>
+      <c r="B104" s="188">
+        <v>120.11</v>
+      </c>
+      <c r="C104" s="188">
+        <v>0.23680000000000001</v>
+      </c>
+      <c r="D104" s="188">
+        <v>0.23749999999999999</v>
+      </c>
+      <c r="E104" s="188">
+        <f>D104-C104</f>
+        <v>6.9999999999997842E-4</v>
+      </c>
+      <c r="F104" s="189">
+        <f>(E104*1000)/(B104/1000)</f>
+        <v>5.8279910082422646</v>
+      </c>
+      <c r="G104" s="188">
+        <v>0</v>
+      </c>
+      <c r="H104" s="188"/>
+      <c r="I104" s="190"/>
+      <c r="J104" s="188">
+        <v>3.6389999999999998</v>
+      </c>
+      <c r="K104" s="188"/>
+      <c r="L104" s="192">
+        <v>2.2415999999999998E-3</v>
+      </c>
+      <c r="M104" s="188"/>
+      <c r="N104" s="193">
+        <v>127</v>
+      </c>
+      <c r="O104" s="194">
+        <v>44784</v>
+      </c>
+      <c r="Q104" s="238" t="s">
+        <v>59</v>
+      </c>
+      <c r="R104">
+        <v>0</v>
+      </c>
+      <c r="S104" s="245">
+        <f>AVERAGE(F125:F126)</f>
+        <v>5.52380952380949</v>
+      </c>
+      <c r="T104" s="244"/>
+      <c r="U104" s="244"/>
+      <c r="V104">
+        <v>0</v>
+      </c>
+      <c r="W104" s="245">
+        <f>I124</f>
+        <v>8.767983246000001E-2</v>
+      </c>
+      <c r="X104" s="244">
+        <f>AVERAGE(J125:J126)</f>
+        <v>1.1215000000000002</v>
+      </c>
+    </row>
+    <row r="105" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A105" s="188" t="s">
+        <v>144</v>
+      </c>
+      <c r="B105" s="188">
+        <v>121.37</v>
+      </c>
+      <c r="C105" s="188">
+        <v>0.2329</v>
+      </c>
+      <c r="D105" s="188">
+        <v>0.2331</v>
+      </c>
+      <c r="E105" s="188">
+        <f>D105-C105</f>
+        <v>2.0000000000000573E-4</v>
+      </c>
+      <c r="F105" s="189">
+        <f>(E105*1000)/(B105/1000)</f>
+        <v>1.6478536705940983</v>
+      </c>
+      <c r="G105" s="188">
+        <v>0</v>
+      </c>
+      <c r="H105" s="188"/>
+      <c r="I105" s="190"/>
+      <c r="J105" s="191">
+        <v>3.1560000000000001</v>
+      </c>
+      <c r="K105" s="188"/>
+      <c r="L105" s="192">
+        <v>1.0137999999999987E-3</v>
+      </c>
+      <c r="M105" s="188"/>
+      <c r="N105" s="193">
+        <v>122</v>
+      </c>
+      <c r="O105" s="194">
+        <v>44784</v>
+      </c>
+      <c r="Q105" s="239" t="s">
+        <v>60</v>
+      </c>
+      <c r="R105">
+        <v>0</v>
+      </c>
+      <c r="S105" s="245">
+        <f>AVERAGE(F125:F126)</f>
+        <v>5.52380952380949</v>
+      </c>
+      <c r="T105" s="244"/>
+      <c r="U105" s="244"/>
+      <c r="V105">
+        <v>0</v>
+      </c>
+      <c r="W105" s="245">
+        <f>I124</f>
+        <v>8.767983246000001E-2</v>
+      </c>
+      <c r="X105" s="244">
+        <f>AVERAGE(J125:J126)</f>
+        <v>1.1215000000000002</v>
+      </c>
+    </row>
+    <row r="106" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A106" s="188" t="s">
+        <v>145</v>
+      </c>
+      <c r="B106" s="188">
+        <v>107.41</v>
+      </c>
+      <c r="C106" s="188">
+        <v>0.23749999999999999</v>
+      </c>
+      <c r="D106" s="188">
+        <v>0.23749999999999999</v>
+      </c>
+      <c r="E106" s="188">
+        <f>D106-C106</f>
+        <v>0</v>
+      </c>
+      <c r="F106" s="189">
+        <f>(E106*1000)/(B106/1000)</f>
+        <v>0</v>
+      </c>
+      <c r="G106" s="188">
+        <v>0</v>
+      </c>
+      <c r="H106" s="188"/>
+      <c r="I106" s="190"/>
+      <c r="J106" s="188">
+        <v>3.6909999999999998</v>
+      </c>
+      <c r="K106" s="188"/>
+      <c r="L106" s="188"/>
+      <c r="M106" s="188"/>
+      <c r="N106" s="193">
+        <v>128</v>
+      </c>
+      <c r="O106" s="194">
+        <v>44797</v>
+      </c>
+    </row>
+    <row r="107" spans="1:24" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="195" t="s">
+        <v>146</v>
+      </c>
+      <c r="B107" s="195">
+        <v>104.74</v>
+      </c>
+      <c r="C107" s="195">
+        <v>0.23330000000000001</v>
+      </c>
+      <c r="D107" s="195">
+        <v>0.2334</v>
+      </c>
+      <c r="E107" s="195">
+        <f>D107-C107</f>
+        <v>9.9999999999988987E-5</v>
+      </c>
+      <c r="F107" s="196">
+        <f>(E107*1000)/(B107/1000)</f>
+        <v>0.9547450830627171</v>
+      </c>
+      <c r="G107" s="195">
+        <v>0</v>
+      </c>
+      <c r="H107" s="195"/>
+      <c r="I107" s="197"/>
+      <c r="J107" s="198">
+        <v>3.2109999999999999</v>
+      </c>
+      <c r="K107" s="195"/>
+      <c r="L107" s="199"/>
+      <c r="M107" s="195"/>
+      <c r="N107" s="200">
+        <v>125</v>
+      </c>
+      <c r="O107" s="201">
+        <v>44797</v>
+      </c>
+    </row>
+    <row r="108" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A108" s="202" t="s">
+        <v>147</v>
+      </c>
+      <c r="B108" s="203">
+        <v>119.19</v>
+      </c>
+      <c r="C108" s="203">
+        <v>0.23039999999999999</v>
+      </c>
+      <c r="D108" s="203">
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="E108" s="203">
+        <f>D108-C108</f>
+        <v>2.600000000000019E-3</v>
+      </c>
+      <c r="F108" s="204">
+        <f>(E108*1000)/(B108/1000)</f>
+        <v>21.813910562966853</v>
+      </c>
+      <c r="G108" s="203">
+        <v>0</v>
+      </c>
+      <c r="H108" s="203"/>
+      <c r="I108" s="205"/>
+      <c r="J108" s="203">
+        <v>2.319</v>
+      </c>
+      <c r="K108" s="203"/>
+      <c r="L108" s="203"/>
+      <c r="M108" s="203"/>
+      <c r="N108" s="206">
+        <v>136</v>
+      </c>
+      <c r="O108" s="207">
+        <v>45003</v>
+      </c>
+    </row>
+    <row r="109" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A109" s="202" t="s">
+        <v>148</v>
+      </c>
+      <c r="B109" s="203">
+        <v>200</v>
+      </c>
+      <c r="C109" s="203">
+        <v>0.223</v>
+      </c>
+      <c r="D109" s="203">
+        <v>0.2288</v>
+      </c>
+      <c r="E109" s="203">
+        <f>D109-C109</f>
+        <v>5.7999999999999996E-3</v>
+      </c>
+      <c r="F109" s="204">
+        <f>(E109*1000)/(B109/1000)</f>
+        <v>28.999999999999996</v>
+      </c>
+      <c r="G109" s="203">
+        <v>0</v>
+      </c>
+      <c r="H109" s="203"/>
+      <c r="I109" s="205"/>
+      <c r="J109" s="203">
+        <v>2.254</v>
+      </c>
+      <c r="K109" s="203"/>
+      <c r="L109" s="203"/>
+      <c r="M109" s="203"/>
+      <c r="N109" s="206">
+        <v>137</v>
+      </c>
+      <c r="O109" s="207">
+        <v>45003</v>
+      </c>
+    </row>
+    <row r="110" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A110" s="208" t="s">
+        <v>149</v>
+      </c>
+      <c r="B110" s="209">
+        <v>120.77</v>
+      </c>
+      <c r="C110" s="209">
+        <v>0.23499999999999999</v>
+      </c>
+      <c r="D110" s="209">
+        <v>0.23599999999999999</v>
+      </c>
+      <c r="E110" s="209">
+        <f>D110-C110</f>
+        <v>1.0000000000000009E-3</v>
+      </c>
+      <c r="F110" s="210">
+        <f>(E110*1000)/(B110/1000)</f>
+        <v>8.2802020369297082</v>
+      </c>
+      <c r="G110" s="209">
+        <v>0</v>
+      </c>
+      <c r="H110" s="209"/>
+      <c r="I110" s="211"/>
+      <c r="J110" s="209">
+        <v>2.4380000000000002</v>
+      </c>
+      <c r="K110" s="209"/>
+      <c r="L110" s="209"/>
+      <c r="M110" s="209"/>
+      <c r="N110" s="212">
+        <v>134</v>
+      </c>
+      <c r="O110" s="213">
+        <v>45003</v>
+      </c>
+    </row>
+    <row r="111" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A111" s="202" t="s">
+        <v>150</v>
+      </c>
+      <c r="B111" s="203">
+        <v>190</v>
+      </c>
+      <c r="C111" s="203">
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="D111" s="203">
+        <v>0.23380000000000001</v>
+      </c>
+      <c r="E111" s="203">
+        <f>D111-C111</f>
+        <v>7.9999999999999516E-4</v>
+      </c>
+      <c r="F111" s="204">
+        <f>(E111*1000)/(B111/1000)</f>
+        <v>4.2105263157894486</v>
+      </c>
+      <c r="G111" s="203">
+        <v>0</v>
+      </c>
+      <c r="H111" s="203"/>
+      <c r="I111" s="205"/>
+      <c r="J111" s="203">
+        <v>2.302</v>
+      </c>
+      <c r="K111" s="203"/>
+      <c r="L111" s="203"/>
+      <c r="M111" s="203"/>
+      <c r="N111" s="206">
+        <v>135</v>
+      </c>
+      <c r="O111" s="207">
+        <v>45003</v>
+      </c>
+    </row>
+    <row r="112" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A112" s="202" t="s">
+        <v>151</v>
+      </c>
+      <c r="B112" s="203">
+        <v>210</v>
+      </c>
+      <c r="C112" s="203">
+        <v>0.23499999999999999</v>
+      </c>
+      <c r="D112" s="203">
         <v>0.2404</v>
       </c>
-      <c r="E99" s="157">
-        <f t="shared" si="16"/>
-        <v>7.9999999999999516E-4</v>
-      </c>
-      <c r="F99" s="158">
-        <f t="shared" si="17"/>
-        <v>6.7153529757407471</v>
-      </c>
-      <c r="G99" s="157"/>
-      <c r="H99" s="157"/>
-      <c r="I99" s="167"/>
-      <c r="J99" s="168">
-        <v>1.482</v>
-      </c>
-      <c r="K99" s="157"/>
-      <c r="L99" s="157"/>
-      <c r="M99" s="157"/>
-      <c r="N99" s="169">
-        <v>121</v>
-      </c>
-      <c r="O99" s="161">
-        <v>44632</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A100" s="171" t="s">
-        <v>146</v>
-      </c>
-      <c r="B100" s="157">
-        <v>121.37</v>
-      </c>
-      <c r="C100" s="157">
-        <v>0.2329</v>
-      </c>
-      <c r="D100" s="157">
-        <v>0.2331</v>
-      </c>
-      <c r="E100" s="157">
-        <f t="shared" si="16"/>
-        <v>2.0000000000000573E-4</v>
-      </c>
-      <c r="F100" s="158">
-        <f t="shared" si="17"/>
-        <v>1.6478536705940983</v>
-      </c>
-      <c r="G100" s="157"/>
-      <c r="H100" s="157"/>
-      <c r="I100" s="167"/>
-      <c r="J100" s="168">
-        <v>3.1560000000000001</v>
-      </c>
-      <c r="K100" s="157"/>
-      <c r="L100" s="158">
-        <v>1.0137999999999987E-3</v>
-      </c>
-      <c r="M100" s="157"/>
-      <c r="N100" s="169">
-        <v>122</v>
-      </c>
-      <c r="O100" s="161">
-        <v>44784</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A101" s="171" t="s">
-        <v>143</v>
-      </c>
-      <c r="B101" s="157">
-        <v>121.07</v>
-      </c>
-      <c r="C101" s="157">
-        <v>0.24099999999999999</v>
-      </c>
-      <c r="D101" s="157">
-        <v>0.24110000000000001</v>
-      </c>
-      <c r="E101" s="157">
-        <f t="shared" si="16"/>
-        <v>1.0000000000001674E-4</v>
-      </c>
-      <c r="F101" s="158">
-        <f t="shared" si="17"/>
-        <v>0.82596844800542446</v>
-      </c>
-      <c r="G101" s="157"/>
-      <c r="H101" s="157"/>
-      <c r="I101" s="167"/>
-      <c r="J101" s="168">
-        <v>2.3130000000000002</v>
-      </c>
-      <c r="K101" s="157"/>
-      <c r="L101" s="158">
-        <v>1.7154000000000023E-3</v>
-      </c>
-      <c r="M101" s="157"/>
-      <c r="N101" s="169">
-        <v>123</v>
-      </c>
-      <c r="O101" s="161">
-        <v>44754</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A102" s="157" t="s">
-        <v>144</v>
-      </c>
-      <c r="B102" s="157">
-        <v>120.77</v>
-      </c>
-      <c r="C102" s="157">
-        <v>0.23830000000000001</v>
-      </c>
-      <c r="D102" s="157">
-        <v>0.23899999999999999</v>
-      </c>
-      <c r="E102" s="157">
-        <f t="shared" si="16"/>
-        <v>6.9999999999997842E-4</v>
-      </c>
-      <c r="F102" s="158">
-        <f t="shared" si="17"/>
-        <v>5.7961414258506121</v>
-      </c>
-      <c r="G102" s="157"/>
-      <c r="H102" s="157"/>
-      <c r="I102" s="167"/>
-      <c r="J102" s="168">
-        <v>1.758</v>
-      </c>
-      <c r="K102" s="157"/>
-      <c r="L102" s="158"/>
-      <c r="M102" s="157"/>
-      <c r="N102" s="169">
-        <v>124</v>
-      </c>
-      <c r="O102" s="161">
-        <v>44638</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A103" s="157" t="s">
-        <v>137</v>
-      </c>
-      <c r="B103" s="157">
-        <v>104.74</v>
-      </c>
-      <c r="C103" s="157">
-        <v>0.23330000000000001</v>
-      </c>
-      <c r="D103" s="157">
-        <v>0.2334</v>
-      </c>
-      <c r="E103" s="157">
-        <f t="shared" si="16"/>
-        <v>9.9999999999988987E-5</v>
-      </c>
-      <c r="F103" s="158">
-        <f t="shared" si="17"/>
-        <v>0.9547450830627171</v>
-      </c>
-      <c r="G103" s="157"/>
-      <c r="H103" s="157"/>
-      <c r="I103" s="167"/>
-      <c r="J103" s="168">
-        <v>3.2109999999999999</v>
-      </c>
-      <c r="K103" s="157"/>
-      <c r="L103" s="158"/>
-      <c r="M103" s="157"/>
-      <c r="N103" s="169">
-        <v>125</v>
-      </c>
-      <c r="O103" s="161">
-        <v>44797</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A104" s="171" t="s">
-        <v>138</v>
-      </c>
-      <c r="B104" s="157">
-        <v>119.31</v>
-      </c>
-      <c r="C104" s="157">
-        <v>0.2397</v>
-      </c>
-      <c r="D104" s="157">
-        <v>0.24030000000000001</v>
-      </c>
-      <c r="E104" s="157">
-        <f t="shared" si="16"/>
-        <v>6.0000000000001719E-4</v>
-      </c>
-      <c r="F104" s="158">
-        <f t="shared" si="17"/>
-        <v>5.0289162685442728</v>
-      </c>
-      <c r="G104" s="157"/>
-      <c r="H104" s="157"/>
-      <c r="I104" s="167"/>
-      <c r="J104" s="168">
-        <v>3.294</v>
-      </c>
-      <c r="K104" s="157"/>
-      <c r="L104" s="158">
-        <v>2.2415999999999998E-3</v>
-      </c>
-      <c r="M104" s="157"/>
-      <c r="N104" s="169">
-        <v>126</v>
-      </c>
-      <c r="O104" s="161">
-        <v>44754</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="171" t="s">
-        <v>139</v>
-      </c>
-      <c r="B105" s="157">
-        <v>120.11</v>
-      </c>
-      <c r="C105" s="157">
-        <v>0.23680000000000001</v>
-      </c>
-      <c r="D105" s="157">
-        <v>0.23749999999999999</v>
-      </c>
-      <c r="E105" s="157">
-        <f t="shared" si="16"/>
-        <v>6.9999999999997842E-4</v>
-      </c>
-      <c r="F105" s="158">
-        <f t="shared" si="17"/>
-        <v>5.8279910082422646</v>
-      </c>
-      <c r="G105" s="157"/>
-      <c r="H105" s="157"/>
-      <c r="I105" s="167"/>
-      <c r="J105" s="171">
-        <v>3.6389999999999998</v>
-      </c>
-      <c r="K105" s="157"/>
-      <c r="L105" s="158">
-        <v>2.2415999999999998E-3</v>
-      </c>
-      <c r="M105" s="157"/>
-      <c r="N105" s="169">
-        <v>127</v>
-      </c>
-      <c r="O105" s="161">
-        <v>44784</v>
-      </c>
-    </row>
-    <row r="106" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A106" s="157" t="s">
+      <c r="E112" s="203">
+        <f>D112-C112</f>
+        <v>5.4000000000000159E-3</v>
+      </c>
+      <c r="F112" s="204">
+        <f>(E112*1000)/(B112/1000)</f>
+        <v>25.714285714285793</v>
+      </c>
+      <c r="G112" s="203">
+        <v>0</v>
+      </c>
+      <c r="H112" s="203"/>
+      <c r="I112" s="205"/>
+      <c r="J112" s="203">
+        <v>2.1970000000000001</v>
+      </c>
+      <c r="K112" s="203"/>
+      <c r="L112" s="203"/>
+      <c r="M112" s="203"/>
+      <c r="N112" s="206">
         <v>140</v>
       </c>
-      <c r="B106" s="157">
-        <v>107.41</v>
-      </c>
-      <c r="C106" s="157">
-        <v>0.23749999999999999</v>
-      </c>
-      <c r="D106" s="157">
-        <v>0.23749999999999999</v>
-      </c>
-      <c r="E106" s="157">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="F106" s="158">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="G106" s="157"/>
-      <c r="H106" s="157"/>
-      <c r="I106" s="167"/>
-      <c r="J106" s="171">
-        <v>3.6909999999999998</v>
-      </c>
-      <c r="K106" s="157"/>
-      <c r="L106" s="157"/>
-      <c r="M106" s="157"/>
-      <c r="N106" s="169">
-        <v>128</v>
-      </c>
-      <c r="O106" s="161">
-        <v>44797</v>
-      </c>
-    </row>
-    <row r="107" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A107" s="157" t="s">
-        <v>145</v>
-      </c>
-      <c r="B107" s="157">
-        <v>119.19</v>
-      </c>
-      <c r="C107" s="157">
-        <v>0.2397</v>
-      </c>
-      <c r="D107" s="157">
-        <v>0.2409</v>
-      </c>
-      <c r="E107" s="157">
-        <f t="shared" si="16"/>
-        <v>1.2000000000000066E-3</v>
-      </c>
-      <c r="F107" s="158">
-        <f t="shared" si="17"/>
-        <v>10.067958721369298</v>
-      </c>
-      <c r="G107" s="157"/>
-      <c r="H107" s="157"/>
-      <c r="I107" s="167"/>
-      <c r="J107" s="171">
-        <v>2.238</v>
-      </c>
-      <c r="K107" s="157"/>
-      <c r="L107" s="157"/>
-      <c r="M107" s="157"/>
-      <c r="N107" s="169">
-        <v>129</v>
-      </c>
-      <c r="O107" s="161">
-        <v>44638</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A108" s="164" t="s">
-        <v>147</v>
-      </c>
-      <c r="B108" s="165">
-        <v>150</v>
-      </c>
-      <c r="C108" s="165">
-        <v>0.23400000000000001</v>
-      </c>
-      <c r="D108" s="165">
-        <v>0.23599999999999999</v>
-      </c>
-      <c r="E108" s="157">
-        <f t="shared" si="16"/>
-        <v>1.999999999999974E-3</v>
-      </c>
-      <c r="F108" s="158">
-        <f t="shared" si="17"/>
-        <v>13.33333333333316</v>
-      </c>
-      <c r="G108" s="49"/>
-      <c r="H108" s="49"/>
-      <c r="I108" s="49"/>
-      <c r="J108" s="166">
-        <v>4.4409999999999998</v>
-      </c>
-      <c r="K108" s="49"/>
-      <c r="L108" s="49"/>
-      <c r="M108" s="49"/>
-      <c r="N108" s="163">
-        <f>N107+1</f>
-        <v>130</v>
-      </c>
-      <c r="O108" s="161">
-        <v>45029</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A109" s="164" t="s">
-        <v>148</v>
-      </c>
-      <c r="B109" s="165">
-        <v>150</v>
-      </c>
-      <c r="C109" s="165">
-        <v>0.23899999999999999</v>
-      </c>
-      <c r="D109" s="165">
-        <v>0.24</v>
-      </c>
-      <c r="E109" s="157">
-        <f t="shared" si="16"/>
-        <v>1.0000000000000009E-3</v>
-      </c>
-      <c r="F109" s="158">
-        <f t="shared" si="17"/>
-        <v>6.6666666666666732</v>
-      </c>
-      <c r="G109" s="49"/>
-      <c r="H109" s="49"/>
-      <c r="I109" s="49"/>
-      <c r="J109" s="166">
-        <v>4.4930000000000003</v>
-      </c>
-      <c r="K109" s="49"/>
-      <c r="L109" s="49"/>
-      <c r="M109" s="49"/>
-      <c r="N109" s="163">
-        <f t="shared" ref="N109:N123" si="19">N108+1</f>
-        <v>131</v>
-      </c>
-      <c r="O109" s="161">
-        <v>45029</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A110" s="164" t="s">
-        <v>149</v>
-      </c>
-      <c r="B110" s="165">
-        <v>150</v>
-      </c>
-      <c r="C110" s="165">
-        <v>0.23499999999999999</v>
-      </c>
-      <c r="D110" s="165">
-        <v>0.23669999999999999</v>
-      </c>
-      <c r="E110" s="157">
-        <f t="shared" si="16"/>
-        <v>1.7000000000000071E-3</v>
-      </c>
-      <c r="F110" s="158">
-        <f t="shared" si="17"/>
-        <v>11.33333333333338</v>
-      </c>
-      <c r="G110" s="49"/>
-      <c r="H110" s="49"/>
-      <c r="I110" s="49"/>
-      <c r="J110" s="166">
-        <v>4.3840000000000003</v>
-      </c>
-      <c r="K110" s="49"/>
-      <c r="L110" s="49"/>
-      <c r="M110" s="49"/>
-      <c r="N110" s="163">
-        <f t="shared" si="19"/>
-        <v>132</v>
-      </c>
-      <c r="O110" s="161">
-        <v>45029</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A111" s="164" t="s">
-        <v>150</v>
-      </c>
-      <c r="B111" s="165">
-        <v>145</v>
-      </c>
-      <c r="C111" s="165">
-        <v>0.22500000000000001</v>
-      </c>
-      <c r="D111" s="165">
-        <v>0.22739999999999999</v>
-      </c>
-      <c r="E111" s="157">
-        <f t="shared" si="16"/>
-        <v>2.3999999999999855E-3</v>
-      </c>
-      <c r="F111" s="158">
-        <f t="shared" si="17"/>
-        <v>16.551724137930933</v>
-      </c>
-      <c r="G111" s="49"/>
-      <c r="H111" s="49"/>
-      <c r="I111" s="49"/>
-      <c r="J111" s="166">
-        <v>4.49</v>
-      </c>
-      <c r="K111" s="49"/>
-      <c r="L111" s="49"/>
-      <c r="M111" s="49"/>
-      <c r="N111" s="163">
-        <f t="shared" si="19"/>
-        <v>133</v>
-      </c>
-      <c r="O111" s="161">
-        <v>45029</v>
-      </c>
-    </row>
-    <row r="112" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A112" s="164" t="s">
-        <v>151</v>
-      </c>
-      <c r="B112" s="165">
-        <v>120.77</v>
-      </c>
-      <c r="C112" s="165">
-        <v>0.23499999999999999</v>
-      </c>
-      <c r="D112" s="165">
-        <v>0.23599999999999999</v>
-      </c>
-      <c r="E112" s="157">
-        <f t="shared" si="16"/>
-        <v>1.0000000000000009E-3</v>
-      </c>
-      <c r="F112" s="158">
-        <f t="shared" si="17"/>
-        <v>8.2802020369297082</v>
-      </c>
-      <c r="G112" s="49"/>
-      <c r="H112" s="49"/>
-      <c r="I112" s="49"/>
-      <c r="J112" s="166">
-        <v>2.4380000000000002</v>
-      </c>
-      <c r="K112" s="49"/>
-      <c r="L112" s="49"/>
-      <c r="M112" s="49"/>
-      <c r="N112" s="163">
-        <f t="shared" si="19"/>
-        <v>134</v>
-      </c>
-      <c r="O112" s="161">
-        <v>45003</v>
+      <c r="O112" s="207">
+        <v>45004</v>
       </c>
     </row>
     <row r="113" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A113" s="164" t="s">
+      <c r="A113" s="202" t="s">
         <v>152</v>
       </c>
-      <c r="B113" s="165">
-        <v>190</v>
-      </c>
-      <c r="C113" s="165">
+      <c r="B113" s="203">
+        <v>200</v>
+      </c>
+      <c r="C113" s="203">
         <v>0.23300000000000001</v>
       </c>
-      <c r="D113" s="165">
-        <v>0.23380000000000001</v>
-      </c>
-      <c r="E113" s="157">
-        <f t="shared" si="16"/>
-        <v>7.9999999999999516E-4</v>
-      </c>
-      <c r="F113" s="158">
-        <f t="shared" si="17"/>
-        <v>4.2105263157894486</v>
-      </c>
-      <c r="G113" s="49"/>
-      <c r="H113" s="49"/>
-      <c r="I113" s="49"/>
-      <c r="J113" s="166">
-        <v>2.302</v>
-      </c>
-      <c r="K113" s="49"/>
-      <c r="L113" s="49"/>
-      <c r="M113" s="49"/>
-      <c r="N113" s="163">
-        <f t="shared" si="19"/>
-        <v>135</v>
-      </c>
-      <c r="O113" s="161">
-        <v>45003</v>
+      <c r="D113" s="203">
+        <v>0.23519999999999999</v>
+      </c>
+      <c r="E113" s="203">
+        <f>D113-C113</f>
+        <v>2.1999999999999797E-3</v>
+      </c>
+      <c r="F113" s="204">
+        <f>(E113*1000)/(B113/1000)</f>
+        <v>10.999999999999899</v>
+      </c>
+      <c r="G113" s="203">
+        <v>0</v>
+      </c>
+      <c r="H113" s="203"/>
+      <c r="I113" s="205"/>
+      <c r="J113" s="203">
+        <v>2.2629999999999999</v>
+      </c>
+      <c r="K113" s="203"/>
+      <c r="L113" s="203"/>
+      <c r="M113" s="203"/>
+      <c r="N113" s="206">
+        <v>141</v>
+      </c>
+      <c r="O113" s="207">
+        <v>45004</v>
       </c>
     </row>
     <row r="114" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A114" s="164" t="s">
+      <c r="A114" s="202" t="s">
         <v>153</v>
       </c>
-      <c r="B114" s="165">
-        <v>119.19</v>
-      </c>
-      <c r="C114" s="165">
-        <v>0.23039999999999999</v>
-      </c>
-      <c r="D114" s="165">
-        <v>0.23300000000000001</v>
-      </c>
-      <c r="E114" s="157">
-        <f t="shared" si="16"/>
-        <v>2.600000000000019E-3</v>
-      </c>
-      <c r="F114" s="158">
-        <f t="shared" si="17"/>
-        <v>21.813910562966853</v>
-      </c>
-      <c r="G114" s="49"/>
-      <c r="H114" s="49"/>
-      <c r="I114" s="49"/>
-      <c r="J114" s="166">
-        <v>2.319</v>
-      </c>
-      <c r="K114" s="49"/>
-      <c r="L114" s="49"/>
-      <c r="M114" s="49"/>
-      <c r="N114" s="163">
-        <f t="shared" si="19"/>
-        <v>136</v>
-      </c>
-      <c r="O114" s="161">
-        <v>45003</v>
+      <c r="B114" s="203">
+        <v>200</v>
+      </c>
+      <c r="C114" s="203">
+        <v>0.23499999999999999</v>
+      </c>
+      <c r="D114" s="203">
+        <v>0.23649999999999999</v>
+      </c>
+      <c r="E114" s="203">
+        <f>D114-C114</f>
+        <v>1.5000000000000013E-3</v>
+      </c>
+      <c r="F114" s="204">
+        <f>(E114*1000)/(B114/1000)</f>
+        <v>7.5000000000000062</v>
+      </c>
+      <c r="G114" s="203">
+        <v>0</v>
+      </c>
+      <c r="H114" s="203"/>
+      <c r="I114" s="205"/>
+      <c r="J114" s="203">
+        <v>2.2879999999999998</v>
+      </c>
+      <c r="K114" s="203"/>
+      <c r="L114" s="203"/>
+      <c r="M114" s="203"/>
+      <c r="N114" s="206">
+        <v>138</v>
+      </c>
+      <c r="O114" s="207">
+        <v>45004</v>
       </c>
     </row>
     <row r="115" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A115" s="164" t="s">
+      <c r="A115" s="202" t="s">
         <v>154</v>
       </c>
-      <c r="B115" s="165">
-        <v>200</v>
-      </c>
-      <c r="C115" s="165">
-        <v>0.223</v>
-      </c>
-      <c r="D115" s="165">
-        <v>0.2288</v>
-      </c>
-      <c r="E115" s="157">
-        <f t="shared" si="16"/>
-        <v>5.7999999999999996E-3</v>
-      </c>
-      <c r="F115" s="158">
-        <f t="shared" si="17"/>
-        <v>28.999999999999996</v>
-      </c>
-      <c r="G115" s="49"/>
-      <c r="H115" s="49"/>
-      <c r="I115" s="49"/>
-      <c r="J115" s="166">
-        <v>2.254</v>
-      </c>
-      <c r="K115" s="49"/>
-      <c r="L115" s="49"/>
-      <c r="M115" s="49"/>
-      <c r="N115" s="163">
-        <f t="shared" si="19"/>
-        <v>137</v>
-      </c>
-      <c r="O115" s="161">
-        <v>45003</v>
+      <c r="B115" s="203">
+        <v>190</v>
+      </c>
+      <c r="C115" s="203">
+        <v>0.23</v>
+      </c>
+      <c r="D115" s="203">
+        <v>0.2319</v>
+      </c>
+      <c r="E115" s="203">
+        <f>D115-C115</f>
+        <v>1.899999999999985E-3</v>
+      </c>
+      <c r="F115" s="204">
+        <f>(E115*1000)/(B115/1000)</f>
+        <v>9.9999999999999218</v>
+      </c>
+      <c r="G115" s="203">
+        <v>0</v>
+      </c>
+      <c r="H115" s="203"/>
+      <c r="I115" s="205"/>
+      <c r="J115" s="203">
+        <v>2.1789999999999998</v>
+      </c>
+      <c r="K115" s="203"/>
+      <c r="L115" s="203"/>
+      <c r="M115" s="203"/>
+      <c r="N115" s="206">
+        <v>139</v>
+      </c>
+      <c r="O115" s="207">
+        <v>45004</v>
       </c>
     </row>
     <row r="116" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A116" s="164" t="s">
+      <c r="A116" s="202" t="s">
         <v>155</v>
       </c>
-      <c r="B116" s="165">
+      <c r="B116" s="203">
         <v>200</v>
       </c>
-      <c r="C116" s="165">
+      <c r="C116" s="203">
         <v>0.23499999999999999</v>
       </c>
-      <c r="D116" s="165">
-        <v>0.23649999999999999</v>
-      </c>
-      <c r="E116" s="157">
-        <f t="shared" si="16"/>
-        <v>1.5000000000000013E-3</v>
-      </c>
-      <c r="F116" s="158">
-        <f t="shared" si="17"/>
-        <v>7.5000000000000062</v>
-      </c>
-      <c r="G116" s="49"/>
-      <c r="H116" s="49"/>
-      <c r="I116" s="49"/>
-      <c r="J116" s="166">
-        <v>2.2879999999999998</v>
-      </c>
-      <c r="K116" s="49"/>
-      <c r="L116" s="49"/>
-      <c r="M116" s="49"/>
-      <c r="N116" s="163">
-        <f t="shared" si="19"/>
-        <v>138</v>
-      </c>
-      <c r="O116" s="161">
-        <v>45004</v>
+      <c r="D116" s="203">
+        <v>0.2424</v>
+      </c>
+      <c r="E116" s="203">
+        <f>D116-C116</f>
+        <v>7.4000000000000177E-3</v>
+      </c>
+      <c r="F116" s="204">
+        <f>(E116*1000)/(B116/1000)</f>
+        <v>37.000000000000085</v>
+      </c>
+      <c r="G116" s="214"/>
+      <c r="H116" s="203"/>
+      <c r="I116" s="205"/>
+      <c r="J116" s="203">
+        <v>2.1349999999999998</v>
+      </c>
+      <c r="K116" s="203"/>
+      <c r="L116" s="203"/>
+      <c r="M116" s="203"/>
+      <c r="N116" s="206">
+        <v>144</v>
+      </c>
+      <c r="O116" s="207">
+        <v>45007</v>
       </c>
     </row>
     <row r="117" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" s="164" t="s">
+      <c r="A117" s="202" t="s">
         <v>156</v>
       </c>
-      <c r="B117" s="165">
+      <c r="B117" s="203">
         <v>190</v>
       </c>
-      <c r="C117" s="165">
-        <v>0.23</v>
-      </c>
-      <c r="D117" s="165">
-        <v>0.2319</v>
-      </c>
-      <c r="E117" s="157">
-        <f t="shared" si="16"/>
-        <v>1.899999999999985E-3</v>
-      </c>
-      <c r="F117" s="158">
-        <f t="shared" si="17"/>
-        <v>9.9999999999999218</v>
-      </c>
-      <c r="G117" s="49"/>
-      <c r="H117" s="49"/>
-      <c r="I117" s="49"/>
-      <c r="J117" s="166">
-        <v>2.1789999999999998</v>
-      </c>
-      <c r="K117" s="49"/>
-      <c r="L117" s="49"/>
-      <c r="M117" s="49"/>
-      <c r="N117" s="163">
-        <f t="shared" si="19"/>
-        <v>139</v>
-      </c>
-      <c r="O117" s="161">
-        <v>45004</v>
+      <c r="C117" s="203">
+        <v>0.23330000000000001</v>
+      </c>
+      <c r="D117" s="203">
+        <v>0.23699999999999999</v>
+      </c>
+      <c r="E117" s="203">
+        <f>D117-C117</f>
+        <v>3.6999999999999811E-3</v>
+      </c>
+      <c r="F117" s="204">
+        <f>(E117*1000)/(B117/1000)</f>
+        <v>19.473684210526216</v>
+      </c>
+      <c r="G117" s="203"/>
+      <c r="H117" s="203"/>
+      <c r="I117" s="205"/>
+      <c r="J117" s="203">
+        <v>2.1480000000000001</v>
+      </c>
+      <c r="K117" s="203"/>
+      <c r="L117" s="203"/>
+      <c r="M117" s="203"/>
+      <c r="N117" s="206">
+        <v>143</v>
+      </c>
+      <c r="O117" s="207">
+        <v>45007</v>
       </c>
     </row>
     <row r="118" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A118" s="164" t="s">
+      <c r="A118" s="202" t="s">
         <v>157</v>
       </c>
-      <c r="B118" s="165">
-        <v>210</v>
-      </c>
-      <c r="C118" s="165">
-        <v>0.23499999999999999</v>
-      </c>
-      <c r="D118" s="165">
-        <v>0.2404</v>
-      </c>
-      <c r="E118" s="157">
-        <f t="shared" si="16"/>
-        <v>5.4000000000000159E-3</v>
-      </c>
-      <c r="F118" s="158">
-        <f t="shared" si="17"/>
-        <v>25.714285714285793</v>
-      </c>
-      <c r="G118" s="49"/>
-      <c r="H118" s="49"/>
-      <c r="I118" s="49"/>
-      <c r="J118" s="166">
-        <v>2.1970000000000001</v>
-      </c>
-      <c r="K118" s="49"/>
-      <c r="L118" s="49"/>
-      <c r="M118" s="49"/>
-      <c r="N118" s="163">
-        <f t="shared" si="19"/>
-        <v>140</v>
-      </c>
-      <c r="O118" s="161">
-        <v>45004</v>
+      <c r="B118" s="203">
+        <v>200</v>
+      </c>
+      <c r="C118" s="203">
+        <v>0.222</v>
+      </c>
+      <c r="D118" s="203">
+        <v>0.22900000000000001</v>
+      </c>
+      <c r="E118" s="203">
+        <f>D118-C118</f>
+        <v>7.0000000000000062E-3</v>
+      </c>
+      <c r="F118" s="204">
+        <f>(E118*1000)/(B118/1000)</f>
+        <v>35.000000000000028</v>
+      </c>
+      <c r="G118" s="203"/>
+      <c r="H118" s="203"/>
+      <c r="I118" s="205"/>
+      <c r="J118" s="203">
+        <v>2.1960000000000002</v>
+      </c>
+      <c r="K118" s="203"/>
+      <c r="L118" s="203"/>
+      <c r="M118" s="203"/>
+      <c r="N118" s="206">
+        <v>142</v>
+      </c>
+      <c r="O118" s="207">
+        <v>45007</v>
       </c>
     </row>
     <row r="119" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A119" s="164" t="s">
+      <c r="A119" s="202" t="s">
         <v>158</v>
       </c>
-      <c r="B119" s="165">
+      <c r="B119" s="203">
         <v>200</v>
       </c>
-      <c r="C119" s="165">
-        <v>0.23300000000000001</v>
-      </c>
-      <c r="D119" s="165">
-        <v>0.23519999999999999</v>
-      </c>
-      <c r="E119" s="157">
-        <f t="shared" si="16"/>
-        <v>2.1999999999999797E-3</v>
-      </c>
-      <c r="F119" s="158">
-        <f t="shared" si="17"/>
-        <v>10.999999999999899</v>
-      </c>
-      <c r="G119" s="49"/>
-      <c r="H119" s="49"/>
-      <c r="I119" s="49"/>
-      <c r="J119" s="166">
-        <v>2.2629999999999999</v>
-      </c>
-      <c r="K119" s="49"/>
-      <c r="L119" s="49"/>
-      <c r="M119" s="49"/>
-      <c r="N119" s="163">
-        <f t="shared" si="19"/>
-        <v>141</v>
-      </c>
-      <c r="O119" s="161">
-        <v>45004</v>
+      <c r="C119" s="203">
+        <v>0.23599999999999999</v>
+      </c>
+      <c r="D119" s="203">
+        <v>0.2366</v>
+      </c>
+      <c r="E119" s="203">
+        <f>D119-C119</f>
+        <v>6.0000000000001719E-4</v>
+      </c>
+      <c r="F119" s="204">
+        <f>(E119*1000)/(B119/1000)</f>
+        <v>3.0000000000000857</v>
+      </c>
+      <c r="G119" s="203"/>
+      <c r="H119" s="203"/>
+      <c r="I119" s="205"/>
+      <c r="J119" s="203">
+        <v>2.0670000000000002</v>
+      </c>
+      <c r="K119" s="203"/>
+      <c r="L119" s="203"/>
+      <c r="M119" s="203"/>
+      <c r="N119" s="206">
+        <v>145</v>
+      </c>
+      <c r="O119" s="207">
+        <v>45007</v>
       </c>
     </row>
     <row r="120" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A120" s="164" t="s">
+      <c r="A120" s="202" t="s">
         <v>159</v>
       </c>
-      <c r="B120" s="165">
-        <v>200</v>
-      </c>
-      <c r="C120" s="165">
-        <v>0.222</v>
-      </c>
-      <c r="D120" s="165">
-        <v>0.22900000000000001</v>
-      </c>
-      <c r="E120" s="157">
-        <f t="shared" si="16"/>
-        <v>7.0000000000000062E-3</v>
-      </c>
-      <c r="F120" s="158">
-        <f t="shared" si="17"/>
-        <v>35.000000000000028</v>
-      </c>
-      <c r="G120" s="49"/>
-      <c r="H120" s="49"/>
-      <c r="I120" s="49"/>
-      <c r="J120" s="166">
-        <v>2.1960000000000002</v>
-      </c>
-      <c r="K120" s="49"/>
-      <c r="L120" s="49"/>
-      <c r="M120" s="49"/>
-      <c r="N120" s="163">
-        <f t="shared" si="19"/>
-        <v>142</v>
-      </c>
-      <c r="O120" s="161">
-        <v>45007</v>
+      <c r="B120" s="203">
+        <v>150</v>
+      </c>
+      <c r="C120" s="203">
+        <v>0.23499999999999999</v>
+      </c>
+      <c r="D120" s="203">
+        <v>0.23669999999999999</v>
+      </c>
+      <c r="E120" s="203">
+        <f>D120-C120</f>
+        <v>1.7000000000000071E-3</v>
+      </c>
+      <c r="F120" s="204">
+        <f>(E120*1000)/(B120/1000)</f>
+        <v>11.33333333333338</v>
+      </c>
+      <c r="G120" s="9">
+        <v>115.20499999999998</v>
+      </c>
+      <c r="H120" s="203"/>
+      <c r="I120" s="205"/>
+      <c r="J120" s="203">
+        <v>4.3840000000000003</v>
+      </c>
+      <c r="K120" s="203"/>
+      <c r="L120" s="203"/>
+      <c r="M120" s="203"/>
+      <c r="N120" s="206">
+        <v>132</v>
+      </c>
+      <c r="O120" s="207">
+        <v>45029</v>
       </c>
     </row>
     <row r="121" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A121" s="164" t="s">
+      <c r="A121" s="202" t="s">
         <v>160</v>
       </c>
-      <c r="B121" s="165">
-        <v>190</v>
-      </c>
-      <c r="C121" s="165">
-        <v>0.23330000000000001</v>
-      </c>
-      <c r="D121" s="165">
-        <v>0.23699999999999999</v>
-      </c>
-      <c r="E121" s="157">
-        <f t="shared" si="16"/>
-        <v>3.6999999999999811E-3</v>
-      </c>
-      <c r="F121" s="158">
-        <f t="shared" si="17"/>
-        <v>19.473684210526216</v>
-      </c>
-      <c r="G121" s="49"/>
-      <c r="H121" s="49"/>
-      <c r="I121" s="49"/>
-      <c r="J121" s="166">
-        <v>2.1480000000000001</v>
-      </c>
-      <c r="K121" s="49"/>
-      <c r="L121" s="49"/>
-      <c r="M121" s="49"/>
-      <c r="N121" s="163">
-        <f>N120+1</f>
-        <v>143</v>
-      </c>
-      <c r="O121" s="161">
-        <v>45007</v>
+      <c r="B121" s="203">
+        <v>145</v>
+      </c>
+      <c r="C121" s="203">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="D121" s="203">
+        <v>0.22739999999999999</v>
+      </c>
+      <c r="E121" s="203">
+        <f>D121-C121</f>
+        <v>2.3999999999999855E-3</v>
+      </c>
+      <c r="F121" s="204">
+        <f>(E121*1000)/(B121/1000)</f>
+        <v>16.551724137930933</v>
+      </c>
+      <c r="G121" s="9">
+        <v>106.28000000000002</v>
+      </c>
+      <c r="H121" s="203"/>
+      <c r="I121" s="205"/>
+      <c r="J121" s="203">
+        <v>4.49</v>
+      </c>
+      <c r="K121" s="203"/>
+      <c r="L121" s="203"/>
+      <c r="M121" s="203"/>
+      <c r="N121" s="206">
+        <v>133</v>
+      </c>
+      <c r="O121" s="207">
+        <v>45029</v>
       </c>
     </row>
     <row r="122" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A122" s="164" t="s">
+      <c r="A122" s="202" t="s">
         <v>161</v>
       </c>
-      <c r="B122" s="165">
+      <c r="B122" s="203">
+        <v>150</v>
+      </c>
+      <c r="C122" s="203">
+        <v>0.23899999999999999</v>
+      </c>
+      <c r="D122" s="203">
+        <v>0.24</v>
+      </c>
+      <c r="E122" s="203">
+        <f>D122-C122</f>
+        <v>1.0000000000000009E-3</v>
+      </c>
+      <c r="F122" s="204">
+        <f>(E122*1000)/(B122/1000)</f>
+        <v>6.6666666666666732</v>
+      </c>
+      <c r="G122" s="9">
+        <v>118.6825</v>
+      </c>
+      <c r="H122" s="203"/>
+      <c r="I122" s="205"/>
+      <c r="J122" s="203">
+        <v>4.4930000000000003</v>
+      </c>
+      <c r="K122" s="203"/>
+      <c r="L122" s="203"/>
+      <c r="M122" s="203"/>
+      <c r="N122" s="206">
+        <v>131</v>
+      </c>
+      <c r="O122" s="207">
+        <v>45029</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="215" t="s">
+        <v>162</v>
+      </c>
+      <c r="B123" s="216">
         <v>200</v>
       </c>
-      <c r="C122" s="165">
-        <v>0.23499999999999999</v>
-      </c>
-      <c r="D122" s="165">
-        <v>0.2424</v>
-      </c>
-      <c r="E122" s="157">
-        <f t="shared" si="16"/>
-        <v>7.4000000000000177E-3</v>
-      </c>
-      <c r="F122" s="158">
-        <f t="shared" si="17"/>
-        <v>37.000000000000085</v>
-      </c>
-      <c r="G122" s="49"/>
-      <c r="H122" s="49"/>
-      <c r="I122" s="49"/>
-      <c r="J122" s="166">
-        <v>2.1349999999999998</v>
-      </c>
-      <c r="K122" s="49"/>
-      <c r="L122" s="49"/>
-      <c r="M122" s="49"/>
-      <c r="N122" s="163">
-        <f t="shared" si="19"/>
-        <v>144</v>
-      </c>
-      <c r="O122" s="161">
-        <v>45007</v>
+      <c r="C123" s="216">
+        <v>0.23400000000000001</v>
+      </c>
+      <c r="D123" s="216">
+        <v>0.23530000000000001</v>
+      </c>
+      <c r="E123" s="216">
+        <f>D123-C123</f>
+        <v>1.2999999999999956E-3</v>
+      </c>
+      <c r="F123" s="217">
+        <f>(E123*1000)/(B123/1000)</f>
+        <v>6.4999999999999778</v>
+      </c>
+      <c r="G123" s="140">
+        <v>73.134999999999991</v>
+      </c>
+      <c r="H123" s="216"/>
+      <c r="I123" s="218"/>
+      <c r="J123" s="216">
+        <v>4.4409999999999998</v>
+      </c>
+      <c r="K123" s="216"/>
+      <c r="L123" s="216"/>
+      <c r="M123" s="216"/>
+      <c r="N123" s="219">
+        <v>130</v>
+      </c>
+      <c r="O123" s="220">
+        <v>45029</v>
       </c>
     </row>
-    <row r="123" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A123" s="164" t="s">
-        <v>162</v>
-      </c>
-      <c r="B123" s="165">
-        <v>200</v>
-      </c>
-      <c r="C123" s="165">
-        <v>0.23599999999999999</v>
-      </c>
-      <c r="D123" s="165">
-        <v>0.2366</v>
-      </c>
-      <c r="E123" s="157">
-        <f t="shared" si="16"/>
-        <v>6.0000000000001719E-4</v>
-      </c>
-      <c r="F123" s="158">
-        <f t="shared" si="17"/>
-        <v>3.0000000000000857</v>
-      </c>
-      <c r="G123" s="49"/>
-      <c r="H123" s="49"/>
-      <c r="I123" s="49"/>
-      <c r="J123" s="166">
-        <v>2.0670000000000002</v>
-      </c>
-      <c r="K123" s="49"/>
-      <c r="L123" s="49"/>
-      <c r="M123" s="49"/>
-      <c r="N123" s="163">
-        <f t="shared" si="19"/>
-        <v>145</v>
-      </c>
-      <c r="O123" s="161">
-        <v>45007</v>
+    <row r="124" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A124" s="221" t="s">
+        <v>163</v>
+      </c>
+      <c r="B124" s="222">
+        <v>150</v>
+      </c>
+      <c r="C124" s="246">
+        <v>0.23319999999999999</v>
+      </c>
+      <c r="D124" s="246">
+        <v>0.23519999999999999</v>
+      </c>
+      <c r="E124" s="222">
+        <f>D124-C124</f>
+        <v>2.0000000000000018E-3</v>
+      </c>
+      <c r="F124" s="223">
+        <f>(E124*1000)/(B124/1000)</f>
+        <v>13.333333333333346</v>
+      </c>
+      <c r="G124" s="222">
+        <v>0</v>
+      </c>
+      <c r="H124" s="224">
+        <v>1.3151974869000001E-2</v>
+      </c>
+      <c r="I124" s="225">
+        <f>H124/(B124/1000)</f>
+        <v>8.767983246000001E-2</v>
+      </c>
+      <c r="J124" s="222"/>
+      <c r="K124" s="222"/>
+      <c r="L124" s="222"/>
+      <c r="M124" s="222"/>
+      <c r="N124" s="226">
+        <v>436</v>
+      </c>
+      <c r="O124" s="227">
+        <v>45127</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A125" s="228" t="s">
+        <v>165</v>
+      </c>
+      <c r="B125" s="229">
+        <v>140</v>
+      </c>
+      <c r="C125" s="246">
+        <v>0.2331</v>
+      </c>
+      <c r="D125" s="246">
+        <v>0.2339</v>
+      </c>
+      <c r="E125" s="229">
+        <f>D125-C125</f>
+        <v>7.9999999999999516E-4</v>
+      </c>
+      <c r="F125" s="230">
+        <f>(E125*1000)/(B125/1000)</f>
+        <v>5.7142857142856789</v>
+      </c>
+      <c r="G125" s="229">
+        <v>0</v>
+      </c>
+      <c r="H125" s="229"/>
+      <c r="I125" s="229"/>
+      <c r="J125" s="229">
+        <v>1.127</v>
+      </c>
+      <c r="K125" s="229"/>
+      <c r="L125" s="229"/>
+      <c r="M125" s="229"/>
+      <c r="N125" s="231">
+        <v>475</v>
+      </c>
+      <c r="O125" s="232">
+        <v>45154</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A126" s="228" t="s">
+        <v>164</v>
+      </c>
+      <c r="B126" s="229">
+        <v>150</v>
+      </c>
+      <c r="C126" s="246">
+        <v>0.24030000000000001</v>
+      </c>
+      <c r="D126" s="246">
+        <v>0.24110000000000001</v>
+      </c>
+      <c r="E126" s="229">
+        <f>D126-C126</f>
+        <v>7.9999999999999516E-4</v>
+      </c>
+      <c r="F126" s="230">
+        <f>(E126*1000)/(B126/1000)</f>
+        <v>5.3333333333333011</v>
+      </c>
+      <c r="G126" s="229">
+        <v>0</v>
+      </c>
+      <c r="H126" s="229"/>
+      <c r="I126" s="229"/>
+      <c r="J126" s="229">
+        <v>1.1160000000000001</v>
+      </c>
+      <c r="K126" s="229"/>
+      <c r="L126" s="229"/>
+      <c r="M126" s="229"/>
+      <c r="N126" s="231">
+        <v>474</v>
+      </c>
+      <c r="O126" s="232">
+        <v>45153</v>
       </c>
     </row>
   </sheetData>

--- a/data/constituents_summary.xlsx
+++ b/data/constituents_summary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\hysteresis\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huck4481\Documents\GitHub\hysteresis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C71EA0-DD8D-4903-BA0C-C92B4BC01519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B378C0-5ECD-49EC-ABC4-5A0609525D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="623" xr2:uid="{FEC01F85-CDE9-417C-893C-E562E55652ED}"/>
+    <workbookView xWindow="-25320" yWindow="360" windowWidth="25440" windowHeight="15270" tabRatio="623" xr2:uid="{FEC01F85-CDE9-417C-893C-E562E55652ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -842,7 +842,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="247">
+  <cellXfs count="231">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1286,46 +1286,34 @@
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1334,16 +1322,13 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1352,193 +1337,163 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1559,7 +1514,7 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1567,9 +1522,6 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10992,7 +10944,7 @@
       <c r="O2" s="13">
         <v>44400.659722222219</v>
       </c>
-      <c r="P2" s="233" t="s">
+      <c r="P2" s="219" t="s">
         <v>5</v>
       </c>
     </row>
@@ -11045,7 +10997,7 @@
       <c r="O3" s="13">
         <v>44400.67291666667</v>
       </c>
-      <c r="P3" s="234" t="s">
+      <c r="P3" s="220" t="s">
         <v>6</v>
       </c>
     </row>
@@ -11098,7 +11050,7 @@
       <c r="O4" s="13">
         <v>44400.694444444445</v>
       </c>
-      <c r="P4" s="235" t="s">
+      <c r="P4" s="201" t="s">
         <v>56</v>
       </c>
     </row>
@@ -11151,7 +11103,7 @@
       <c r="O5" s="13">
         <v>44400.704861111109</v>
       </c>
-      <c r="P5" s="236" t="s">
+      <c r="P5" s="221" t="s">
         <v>58</v>
       </c>
     </row>
@@ -11204,7 +11156,7 @@
       <c r="O6" s="13">
         <v>44400.804861111108</v>
       </c>
-      <c r="P6" s="237" t="s">
+      <c r="P6" s="222" t="s">
         <v>57</v>
       </c>
     </row>
@@ -11257,7 +11209,7 @@
       <c r="O7" s="13">
         <v>44400.876388888886</v>
       </c>
-      <c r="P7" s="238" t="s">
+      <c r="P7" s="223" t="s">
         <v>59</v>
       </c>
     </row>
@@ -11310,7 +11262,7 @@
       <c r="O8" s="13">
         <v>44400.620833333334</v>
       </c>
-      <c r="P8" s="239" t="s">
+      <c r="P8" s="224" t="s">
         <v>60</v>
       </c>
     </row>
@@ -13495,7 +13447,7 @@
         <v>461</v>
       </c>
       <c r="O55" s="13">
-        <v>45151.78125</v>
+        <v>45151.791666666664</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
@@ -13541,7 +13493,7 @@
         <v>462</v>
       </c>
       <c r="O56" s="13">
-        <v>45151.791666666664</v>
+        <v>45151.802083333336</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
@@ -13587,7 +13539,7 @@
         <v>463</v>
       </c>
       <c r="O57" s="13">
-        <v>45151.802083333336</v>
+        <v>45151.8125</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
@@ -13633,7 +13585,7 @@
         <v>464</v>
       </c>
       <c r="O58" s="13">
-        <v>45151.8125</v>
+        <v>45151.822916666664</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
@@ -13674,7 +13626,7 @@
         <v>465</v>
       </c>
       <c r="O59" s="13">
-        <v>45151.822916666664</v>
+        <v>45151.833333333336</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
@@ -13720,7 +13672,7 @@
         <v>466</v>
       </c>
       <c r="O60" s="13">
-        <v>45151.833333333336</v>
+        <v>45151.84375</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
@@ -13761,7 +13713,7 @@
         <v>467</v>
       </c>
       <c r="O61" s="13">
-        <v>45151.84375</v>
+        <v>45151.854166666664</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
@@ -13807,7 +13759,7 @@
         <v>468</v>
       </c>
       <c r="O62" s="13">
-        <v>45151.854166666664</v>
+        <v>45151.864583333336</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
@@ -13848,7 +13800,7 @@
         <v>469</v>
       </c>
       <c r="O63" s="13">
-        <v>45151.864583333336</v>
+        <v>45151.875</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
@@ -13889,7 +13841,7 @@
         <v>470</v>
       </c>
       <c r="O64" s="13">
-        <v>45151.875</v>
+        <v>45151.885416666664</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
@@ -13930,7 +13882,7 @@
         <v>471</v>
       </c>
       <c r="O65" s="13">
-        <v>45151.885416666664</v>
+        <v>45151.895833333336</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
@@ -13976,7 +13928,7 @@
         <v>472</v>
       </c>
       <c r="O66" s="13">
-        <v>45151.895833333336</v>
+        <v>45151.90625</v>
       </c>
     </row>
     <row r="67" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -14013,7 +13965,7 @@
         <v>473</v>
       </c>
       <c r="O67" s="66">
-        <v>45151.90625</v>
+        <v>45151.916666666664</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
@@ -14932,13 +14884,13 @@
       <c r="M89" s="146" t="s">
         <v>119</v>
       </c>
-      <c r="N89" s="241" t="s">
+      <c r="N89" s="226" t="s">
         <v>61</v>
       </c>
       <c r="O89" s="146" t="s">
         <v>67</v>
       </c>
-      <c r="P89" s="242" t="s">
+      <c r="P89" s="227" t="s">
         <v>171</v>
       </c>
     </row>
@@ -14984,344 +14936,344 @@
       <c r="N90" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="O90" s="243">
+      <c r="O90" s="228">
         <v>44394</v>
       </c>
-      <c r="P90" s="237" t="s">
+      <c r="P90" s="222" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A91" s="151" t="s">
+      <c r="A91" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B91" s="151">
+      <c r="B91" s="2">
         <v>159.59</v>
       </c>
-      <c r="C91" s="151">
+      <c r="C91" s="2">
         <v>0.2402</v>
       </c>
-      <c r="D91" s="151">
+      <c r="D91" s="2">
         <v>0.24030000000000001</v>
       </c>
-      <c r="E91" s="151">
-        <f t="shared" ref="E91:E130" si="16">D91-C91</f>
+      <c r="E91" s="2">
+        <f t="shared" ref="E91:E99" si="16">D91-C91</f>
         <v>1.0000000000001674E-4</v>
       </c>
-      <c r="F91" s="152">
-        <f t="shared" ref="F91:F130" si="17">(E91*1000)/(B91/1000)</f>
+      <c r="F91" s="147">
+        <f t="shared" ref="F91:F99" si="17">(E91*1000)/(B91/1000)</f>
         <v>0.62660567704753889</v>
       </c>
-      <c r="G91" s="151">
+      <c r="G91" s="2">
         <v>0</v>
       </c>
       <c r="H91" s="148">
         <v>0.39719240842078224</v>
       </c>
-      <c r="I91" s="153">
-        <f t="shared" ref="I91:I128" si="18">H91/(B91/1000)</f>
+      <c r="I91" s="149">
+        <f t="shared" ref="I91:I97" si="18">H91/(B91/1000)</f>
         <v>2.4888301799660519</v>
       </c>
-      <c r="J91" s="151"/>
-      <c r="K91" s="151"/>
+      <c r="J91" s="2"/>
+      <c r="K91" s="2"/>
       <c r="L91" s="150">
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="M91" s="150">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="N91" s="151" t="s">
+      <c r="N91" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="O91" s="154">
+      <c r="O91" s="151">
         <v>44394</v>
       </c>
-      <c r="P91" s="236" t="s">
+      <c r="P91" s="221" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A92" s="151" t="s">
+      <c r="A92" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B92" s="151">
+      <c r="B92" s="2">
         <v>134.51</v>
       </c>
-      <c r="C92" s="151">
+      <c r="C92" s="2">
         <v>0.2412</v>
       </c>
-      <c r="D92" s="151">
+      <c r="D92" s="2">
         <v>0.24179999999999999</v>
       </c>
-      <c r="E92" s="151">
+      <c r="E92" s="2">
         <f t="shared" si="16"/>
         <v>5.9999999999998943E-4</v>
       </c>
-      <c r="F92" s="152">
+      <c r="F92" s="147">
         <f t="shared" si="17"/>
         <v>4.4606348970335992</v>
       </c>
-      <c r="G92" s="151">
+      <c r="G92" s="2">
         <v>0</v>
       </c>
       <c r="H92" s="148">
         <v>0.33234237884337697</v>
       </c>
-      <c r="I92" s="153">
+      <c r="I92" s="149">
         <f t="shared" si="18"/>
         <v>2.4707633547199239</v>
       </c>
-      <c r="J92" s="151"/>
-      <c r="K92" s="151"/>
+      <c r="J92" s="2"/>
+      <c r="K92" s="2"/>
       <c r="L92" s="150">
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="M92" s="150">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="N92" s="151" t="s">
+      <c r="N92" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="O92" s="154">
+      <c r="O92" s="151">
         <v>44396</v>
       </c>
-      <c r="P92" s="233" t="s">
+      <c r="P92" s="219" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A93" s="151" t="s">
+      <c r="A93" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B93" s="151">
+      <c r="B93" s="2">
         <v>117.22999999999999</v>
       </c>
-      <c r="C93" s="151">
+      <c r="C93" s="2">
         <v>0.2407</v>
       </c>
-      <c r="D93" s="151">
+      <c r="D93" s="2">
         <v>0.24160000000000001</v>
       </c>
-      <c r="E93" s="151">
+      <c r="E93" s="2">
         <f t="shared" si="16"/>
         <v>9.000000000000119E-4</v>
       </c>
-      <c r="F93" s="152">
+      <c r="F93" s="147">
         <f t="shared" si="17"/>
         <v>7.6772157297621089</v>
       </c>
-      <c r="G93" s="151">
+      <c r="G93" s="2">
         <v>0</v>
       </c>
       <c r="H93" s="148">
         <v>0.33481118985762565</v>
       </c>
-      <c r="I93" s="153">
+      <c r="I93" s="149">
         <f t="shared" si="18"/>
         <v>2.8560197036392192</v>
       </c>
-      <c r="J93" s="151"/>
-      <c r="K93" s="151"/>
+      <c r="J93" s="2"/>
+      <c r="K93" s="2"/>
       <c r="L93" s="150">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M93" s="150">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="N93" s="151" t="s">
+      <c r="N93" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="O93" s="154">
+      <c r="O93" s="151">
         <v>44396</v>
       </c>
-      <c r="P93" s="235" t="s">
+      <c r="P93" s="201" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A94" s="151" t="s">
+      <c r="A94" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B94" s="151">
+      <c r="B94" s="2">
         <v>333.45</v>
       </c>
-      <c r="C94" s="151">
+      <c r="C94" s="2">
         <v>0.24099999999999999</v>
       </c>
-      <c r="D94" s="151">
+      <c r="D94" s="2">
         <v>0.24249999999999999</v>
       </c>
-      <c r="E94" s="151">
+      <c r="E94" s="2">
         <f t="shared" si="16"/>
         <v>1.5000000000000013E-3</v>
       </c>
-      <c r="F94" s="152">
+      <c r="F94" s="147">
         <f t="shared" si="17"/>
         <v>4.4984255510571343</v>
       </c>
-      <c r="G94" s="151">
+      <c r="G94" s="2">
         <v>0</v>
       </c>
       <c r="H94" s="148">
         <v>0.49779418859739377</v>
       </c>
-      <c r="I94" s="153">
+      <c r="I94" s="149">
         <f t="shared" si="18"/>
         <v>1.4928600647695121</v>
       </c>
-      <c r="J94" s="151"/>
-      <c r="K94" s="151"/>
+      <c r="J94" s="2"/>
+      <c r="K94" s="2"/>
       <c r="L94" s="150">
         <v>2.4E-2</v>
       </c>
       <c r="M94" s="150">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="N94" s="151" t="s">
+      <c r="N94" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="O94" s="154">
+      <c r="O94" s="151">
         <v>44413</v>
       </c>
-      <c r="P94" s="240" t="s">
+      <c r="P94" s="225" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A95" s="151" t="s">
+      <c r="A95" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B95" s="151">
+      <c r="B95" s="2">
         <v>318</v>
       </c>
-      <c r="C95" s="151">
+      <c r="C95" s="2">
         <v>0.24160000000000001</v>
       </c>
-      <c r="D95" s="151">
+      <c r="D95" s="2">
         <v>0.24329999999999999</v>
       </c>
-      <c r="E95" s="151">
+      <c r="E95" s="2">
         <f t="shared" si="16"/>
         <v>1.6999999999999793E-3</v>
       </c>
-      <c r="F95" s="152">
+      <c r="F95" s="147">
         <f t="shared" si="17"/>
         <v>5.345911949685469</v>
       </c>
-      <c r="G95" s="151">
+      <c r="G95" s="2">
         <v>0</v>
       </c>
       <c r="H95" s="148">
         <v>0.47710769568542255</v>
       </c>
-      <c r="I95" s="153">
+      <c r="I95" s="149">
         <f t="shared" si="18"/>
         <v>1.5003386656774294</v>
       </c>
-      <c r="J95" s="151"/>
-      <c r="K95" s="151"/>
+      <c r="J95" s="2"/>
+      <c r="K95" s="2"/>
       <c r="L95" s="150">
         <v>2.4E-2</v>
       </c>
       <c r="M95" s="150">
         <v>2.3E-2</v>
       </c>
-      <c r="N95" s="151" t="s">
+      <c r="N95" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="O95" s="154">
+      <c r="O95" s="151">
         <v>44413</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A96" s="151" t="s">
+      <c r="A96" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B96" s="151">
+      <c r="B96" s="2">
         <v>293.42</v>
       </c>
-      <c r="C96" s="151">
+      <c r="C96" s="2">
         <v>0.24</v>
       </c>
-      <c r="D96" s="151">
+      <c r="D96" s="2">
         <v>0.24360000000000001</v>
       </c>
-      <c r="E96" s="151">
+      <c r="E96" s="2">
         <f t="shared" si="16"/>
         <v>3.6000000000000199E-3</v>
       </c>
-      <c r="F96" s="152">
+      <c r="F96" s="147">
         <f t="shared" si="17"/>
         <v>12.269102310681003</v>
       </c>
-      <c r="G96" s="151">
+      <c r="G96" s="2">
         <v>0</v>
       </c>
       <c r="H96" s="148">
         <v>0.75074101119692438</v>
       </c>
-      <c r="I96" s="153">
+      <c r="I96" s="149">
         <f t="shared" si="18"/>
         <v>2.5585884097775349</v>
       </c>
-      <c r="J96" s="151"/>
-      <c r="K96" s="151"/>
+      <c r="J96" s="2"/>
+      <c r="K96" s="2"/>
       <c r="L96" s="150">
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="M96" s="150">
         <v>2.4E-2</v>
       </c>
-      <c r="N96" s="151" t="s">
+      <c r="N96" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="O96" s="154">
+      <c r="O96" s="151">
         <v>44421</v>
       </c>
     </row>
     <row r="97" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="155" t="s">
+      <c r="A97" s="114" t="s">
         <v>134</v>
       </c>
-      <c r="B97" s="155">
+      <c r="B97" s="114">
         <v>341.46</v>
       </c>
-      <c r="C97" s="155">
+      <c r="C97" s="114">
         <v>0.2407</v>
       </c>
-      <c r="D97" s="155">
+      <c r="D97" s="114">
         <v>0.2424</v>
       </c>
-      <c r="E97" s="155">
+      <c r="E97" s="114">
         <f t="shared" si="16"/>
         <v>1.7000000000000071E-3</v>
       </c>
-      <c r="F97" s="156">
+      <c r="F97" s="152">
         <f t="shared" si="17"/>
         <v>4.9786212147835975</v>
       </c>
-      <c r="G97" s="155">
+      <c r="G97" s="114">
         <v>0</v>
       </c>
-      <c r="H97" s="157">
+      <c r="H97" s="153">
         <v>0.58988878338277129</v>
       </c>
-      <c r="I97" s="158">
+      <c r="I97" s="154">
         <f t="shared" si="18"/>
         <v>1.72754871253667</v>
       </c>
-      <c r="J97" s="155"/>
-      <c r="K97" s="155"/>
-      <c r="L97" s="159">
+      <c r="J97" s="114"/>
+      <c r="K97" s="114"/>
+      <c r="L97" s="155">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="M97" s="159">
+      <c r="M97" s="155">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="N97" s="155" t="s">
+      <c r="N97" s="114" t="s">
         <v>128</v>
       </c>
-      <c r="O97" s="160">
+      <c r="O97" s="156">
         <v>44421</v>
       </c>
       <c r="Q97" t="s">
@@ -15329,41 +15281,41 @@
       </c>
     </row>
     <row r="98" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A98" s="161" t="s">
+      <c r="A98" s="157" t="s">
         <v>137</v>
       </c>
-      <c r="B98" s="162">
+      <c r="B98" s="158">
         <v>119.13</v>
       </c>
-      <c r="C98" s="161">
+      <c r="C98" s="157">
         <v>0.23960000000000001</v>
       </c>
-      <c r="D98" s="161">
+      <c r="D98" s="157">
         <v>0.2404</v>
       </c>
-      <c r="E98" s="161">
+      <c r="E98" s="157">
         <f>D98-C98</f>
         <v>7.9999999999999516E-4</v>
       </c>
-      <c r="F98" s="163">
+      <c r="F98" s="159">
         <f>(E98*1000)/(B98/1000)</f>
         <v>6.7153529757407471</v>
       </c>
-      <c r="G98" s="161">
+      <c r="G98" s="157">
         <v>0</v>
       </c>
-      <c r="H98" s="161"/>
-      <c r="I98" s="164"/>
-      <c r="J98" s="165">
+      <c r="H98" s="157"/>
+      <c r="I98" s="160"/>
+      <c r="J98" s="161">
         <v>1.482</v>
       </c>
-      <c r="K98" s="161"/>
-      <c r="L98" s="161"/>
-      <c r="M98" s="161"/>
-      <c r="N98" s="166">
+      <c r="K98" s="157"/>
+      <c r="L98" s="157"/>
+      <c r="M98" s="157"/>
+      <c r="N98" s="162">
         <v>121</v>
       </c>
-      <c r="O98" s="167">
+      <c r="O98" s="163">
         <v>44632</v>
       </c>
       <c r="R98" t="s">
@@ -15389,1276 +15341,1276 @@
       </c>
     </row>
     <row r="99" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A99" s="168" t="s">
+      <c r="A99" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B99" s="168">
+      <c r="B99" s="1">
         <v>121.65</v>
       </c>
-      <c r="C99" s="168">
+      <c r="C99" s="1">
         <v>0.23630000000000001</v>
       </c>
-      <c r="D99" s="168">
+      <c r="D99" s="1">
         <v>0.23730000000000001</v>
       </c>
-      <c r="E99" s="168">
+      <c r="E99" s="1">
         <f t="shared" si="16"/>
         <v>1.0000000000000009E-3</v>
       </c>
-      <c r="F99" s="169">
+      <c r="F99" s="164">
         <f t="shared" si="17"/>
         <v>8.2203041512536039</v>
       </c>
-      <c r="G99" s="168">
+      <c r="G99" s="1">
         <v>0</v>
       </c>
-      <c r="H99" s="168"/>
-      <c r="I99" s="170"/>
-      <c r="J99" s="171">
+      <c r="H99" s="1"/>
+      <c r="I99" s="165"/>
+      <c r="J99" s="166">
         <v>1.538</v>
       </c>
-      <c r="K99" s="168"/>
-      <c r="L99" s="168"/>
-      <c r="M99" s="168"/>
-      <c r="N99" s="172">
+      <c r="K99" s="1"/>
+      <c r="L99" s="1"/>
+      <c r="M99" s="1"/>
+      <c r="N99" s="167">
         <v>120</v>
       </c>
-      <c r="O99" s="173">
+      <c r="O99" s="168">
         <v>44632</v>
       </c>
-      <c r="Q99" s="233" t="s">
+      <c r="Q99" s="219" t="s">
         <v>5</v>
       </c>
       <c r="R99">
         <v>0</v>
       </c>
-      <c r="S99" s="244">
+      <c r="S99" s="229">
         <f>AVERAGE(F90:F93)</f>
         <v>4.409564902766741</v>
       </c>
-      <c r="T99" s="244">
+      <c r="T99" s="229">
         <f>AVERAGE(L90:L93)</f>
         <v>2.6249999999999996E-2</v>
       </c>
-      <c r="U99" s="244">
+      <c r="U99" s="229">
         <f>AVERAGE(M90:M93)</f>
         <v>3.125E-2</v>
       </c>
       <c r="V99">
         <v>0</v>
       </c>
-      <c r="W99" s="245">
+      <c r="W99" s="230">
         <f>AVERAGE(I90:I93)</f>
         <v>2.8646407542883878</v>
       </c>
-      <c r="X99" s="244">
+      <c r="X99" s="229">
         <f>AVERAGE(J98:J101)</f>
         <v>1.754</v>
       </c>
     </row>
     <row r="100" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A100" s="168" t="s">
+      <c r="A100" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B100" s="168">
+      <c r="B100" s="1">
         <v>119.19</v>
       </c>
-      <c r="C100" s="168">
+      <c r="C100" s="1">
         <v>0.2397</v>
       </c>
-      <c r="D100" s="168">
+      <c r="D100" s="1">
         <v>0.2409</v>
       </c>
-      <c r="E100" s="168">
-        <f>D100-C100</f>
+      <c r="E100" s="1">
+        <f t="shared" ref="E100:E126" si="19">D100-C100</f>
         <v>1.2000000000000066E-3</v>
       </c>
-      <c r="F100" s="169">
-        <f>(E100*1000)/(B100/1000)</f>
+      <c r="F100" s="164">
+        <f t="shared" ref="F100:F126" si="20">(E100*1000)/(B100/1000)</f>
         <v>10.067958721369298</v>
       </c>
-      <c r="G100" s="168">
+      <c r="G100" s="1">
         <v>0</v>
       </c>
-      <c r="H100" s="168"/>
-      <c r="I100" s="170"/>
-      <c r="J100" s="168">
+      <c r="H100" s="1"/>
+      <c r="I100" s="165"/>
+      <c r="J100" s="1">
         <v>2.238</v>
       </c>
-      <c r="K100" s="168"/>
-      <c r="L100" s="168"/>
-      <c r="M100" s="168"/>
-      <c r="N100" s="172">
+      <c r="K100" s="1"/>
+      <c r="L100" s="1"/>
+      <c r="M100" s="1"/>
+      <c r="N100" s="167">
         <v>129</v>
       </c>
-      <c r="O100" s="173">
+      <c r="O100" s="168">
         <v>44638</v>
       </c>
-      <c r="Q100" s="234" t="s">
+      <c r="Q100" s="220" t="s">
         <v>6</v>
       </c>
       <c r="R100">
         <v>0</v>
       </c>
-      <c r="S100" s="244">
+      <c r="S100" s="229">
         <f>AVERAGE(F102:F103)</f>
         <v>2.9274423582748486</v>
       </c>
-      <c r="T100" s="244">
+      <c r="T100" s="229">
         <f>AVERAGE(L102:L103)</f>
         <v>1.9785000000000011E-3</v>
       </c>
-      <c r="U100" s="244">
+      <c r="U100" s="229">
         <f>AVERAGE(M94:M97)</f>
         <v>2.2749999999999999E-2</v>
       </c>
       <c r="V100">
         <v>0</v>
       </c>
-      <c r="W100" s="245">
+      <c r="W100" s="230">
         <f>AVERAGE(I94:I97)</f>
         <v>1.8198339631902867</v>
       </c>
-      <c r="X100" s="244">
+      <c r="X100" s="229">
         <f>AVERAGE(J102:J103)</f>
         <v>2.8035000000000001</v>
       </c>
     </row>
     <row r="101" spans="1:24" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="174" t="s">
+      <c r="A101" s="102" t="s">
         <v>140</v>
       </c>
-      <c r="B101" s="174">
+      <c r="B101" s="102">
         <v>120.77</v>
       </c>
-      <c r="C101" s="174">
+      <c r="C101" s="102">
         <v>0.23830000000000001</v>
       </c>
-      <c r="D101" s="174">
+      <c r="D101" s="102">
         <v>0.23899999999999999</v>
       </c>
-      <c r="E101" s="174">
-        <f>D101-C101</f>
+      <c r="E101" s="102">
+        <f t="shared" si="19"/>
         <v>6.9999999999997842E-4</v>
       </c>
-      <c r="F101" s="175">
-        <f>(E101*1000)/(B101/1000)</f>
+      <c r="F101" s="169">
+        <f t="shared" si="20"/>
         <v>5.7961414258506121</v>
       </c>
-      <c r="G101" s="174">
+      <c r="G101" s="102">
         <v>0</v>
       </c>
-      <c r="H101" s="174"/>
-      <c r="I101" s="176"/>
-      <c r="J101" s="177">
+      <c r="H101" s="102"/>
+      <c r="I101" s="170"/>
+      <c r="J101" s="171">
         <v>1.758</v>
       </c>
-      <c r="K101" s="174"/>
-      <c r="L101" s="178"/>
-      <c r="M101" s="174"/>
-      <c r="N101" s="179">
+      <c r="K101" s="102"/>
+      <c r="L101" s="103"/>
+      <c r="M101" s="102"/>
+      <c r="N101" s="172">
         <v>124</v>
       </c>
-      <c r="O101" s="180">
+      <c r="O101" s="173">
         <v>44638</v>
       </c>
-      <c r="Q101" s="235" t="s">
+      <c r="Q101" s="201" t="s">
         <v>56</v>
       </c>
       <c r="R101">
         <v>0</v>
       </c>
-      <c r="S101" s="244">
+      <c r="S101" s="229">
         <f>AVERAGE(F102:F103)</f>
         <v>2.9274423582748486</v>
       </c>
-      <c r="T101" s="244">
+      <c r="T101" s="229">
         <f>AVERAGE(L102:L103)</f>
         <v>1.9785000000000011E-3</v>
       </c>
-      <c r="U101" s="244">
+      <c r="U101" s="229">
         <f>AVERAGE(M94:M97)</f>
         <v>2.2749999999999999E-2</v>
       </c>
       <c r="V101">
         <v>0</v>
       </c>
-      <c r="W101" s="245">
+      <c r="W101" s="230">
         <f>I21</f>
         <v>1.5244913860512195</v>
       </c>
-      <c r="X101" s="244">
+      <c r="X101" s="229">
         <f>AVERAGE(J102:J103)</f>
         <v>2.8035000000000001</v>
       </c>
     </row>
     <row r="102" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A102" s="181" t="s">
+      <c r="A102" s="174" t="s">
         <v>141</v>
       </c>
-      <c r="B102" s="181">
+      <c r="B102" s="174">
         <v>119.31</v>
       </c>
-      <c r="C102" s="181">
+      <c r="C102" s="174">
         <v>0.2397</v>
       </c>
-      <c r="D102" s="181">
+      <c r="D102" s="174">
         <v>0.24030000000000001</v>
       </c>
-      <c r="E102" s="181">
-        <f>D102-C102</f>
+      <c r="E102" s="174">
+        <f t="shared" si="19"/>
         <v>6.0000000000001719E-4</v>
       </c>
-      <c r="F102" s="182">
-        <f>(E102*1000)/(B102/1000)</f>
+      <c r="F102" s="175">
+        <f t="shared" si="20"/>
         <v>5.0289162685442728</v>
       </c>
-      <c r="G102" s="181">
+      <c r="G102" s="174">
         <v>0</v>
       </c>
-      <c r="H102" s="181"/>
-      <c r="I102" s="183"/>
-      <c r="J102" s="184">
+      <c r="H102" s="174"/>
+      <c r="I102" s="176"/>
+      <c r="J102" s="177">
         <v>3.294</v>
       </c>
-      <c r="K102" s="181"/>
-      <c r="L102" s="185">
+      <c r="K102" s="174"/>
+      <c r="L102" s="178">
         <v>2.2415999999999998E-3</v>
       </c>
-      <c r="M102" s="181"/>
-      <c r="N102" s="186">
+      <c r="M102" s="174"/>
+      <c r="N102" s="179">
         <v>126</v>
       </c>
-      <c r="O102" s="187">
+      <c r="O102" s="180">
         <v>44754</v>
       </c>
-      <c r="Q102" s="236" t="s">
+      <c r="Q102" s="221" t="s">
         <v>58</v>
       </c>
       <c r="R102">
         <v>0</v>
       </c>
-      <c r="S102" s="245">
+      <c r="S102" s="230">
         <f>F124</f>
         <v>13.333333333333346</v>
       </c>
-      <c r="T102" s="244"/>
-      <c r="U102" s="244"/>
+      <c r="T102" s="229"/>
+      <c r="U102" s="229"/>
       <c r="V102">
         <v>0</v>
       </c>
-      <c r="W102" s="245">
+      <c r="W102" s="230">
         <f>I124</f>
         <v>8.767983246000001E-2</v>
       </c>
-      <c r="X102" s="244">
+      <c r="X102" s="229">
         <f>AVERAGE(J102:J103)</f>
         <v>2.8035000000000001</v>
       </c>
     </row>
     <row r="103" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A103" s="188" t="s">
+      <c r="A103" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B103" s="188">
+      <c r="B103" s="4">
         <v>121.07</v>
       </c>
-      <c r="C103" s="188">
+      <c r="C103" s="4">
         <v>0.24099999999999999</v>
       </c>
-      <c r="D103" s="188">
+      <c r="D103" s="4">
         <v>0.24110000000000001</v>
       </c>
-      <c r="E103" s="188">
-        <f>D103-C103</f>
+      <c r="E103" s="4">
+        <f t="shared" si="19"/>
         <v>1.0000000000001674E-4</v>
       </c>
-      <c r="F103" s="189">
-        <f>(E103*1000)/(B103/1000)</f>
+      <c r="F103" s="181">
+        <f t="shared" si="20"/>
         <v>0.82596844800542446</v>
       </c>
-      <c r="G103" s="188">
+      <c r="G103" s="4">
         <v>0</v>
       </c>
-      <c r="H103" s="188"/>
-      <c r="I103" s="190"/>
-      <c r="J103" s="191">
+      <c r="H103" s="4"/>
+      <c r="I103" s="182"/>
+      <c r="J103" s="183">
         <v>2.3130000000000002</v>
       </c>
-      <c r="K103" s="188"/>
-      <c r="L103" s="192">
+      <c r="K103" s="4"/>
+      <c r="L103" s="10">
         <v>1.7154000000000023E-3</v>
       </c>
-      <c r="M103" s="188"/>
-      <c r="N103" s="193">
+      <c r="M103" s="4"/>
+      <c r="N103" s="184">
         <v>123</v>
       </c>
-      <c r="O103" s="194">
+      <c r="O103" s="185">
         <v>44754</v>
       </c>
-      <c r="Q103" s="237" t="s">
+      <c r="Q103" s="222" t="s">
         <v>57</v>
       </c>
       <c r="R103">
         <v>0</v>
       </c>
-      <c r="S103" s="245">
+      <c r="S103" s="230">
         <f>F124</f>
         <v>13.333333333333346</v>
       </c>
-      <c r="T103" s="244"/>
-      <c r="U103" s="244"/>
+      <c r="T103" s="229"/>
+      <c r="U103" s="229"/>
       <c r="V103">
         <v>0</v>
       </c>
-      <c r="W103" s="245">
+      <c r="W103" s="230">
         <f>I124</f>
         <v>8.767983246000001E-2</v>
       </c>
-      <c r="X103" s="244">
+      <c r="X103" s="229">
         <f>AVERAGE(J106:J107)</f>
         <v>3.4509999999999996</v>
       </c>
     </row>
     <row r="104" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A104" s="188" t="s">
+      <c r="A104" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B104" s="188">
+      <c r="B104" s="4">
         <v>120.11</v>
       </c>
-      <c r="C104" s="188">
+      <c r="C104" s="4">
         <v>0.23680000000000001</v>
       </c>
-      <c r="D104" s="188">
+      <c r="D104" s="4">
         <v>0.23749999999999999</v>
       </c>
-      <c r="E104" s="188">
-        <f>D104-C104</f>
+      <c r="E104" s="4">
+        <f t="shared" si="19"/>
         <v>6.9999999999997842E-4</v>
       </c>
-      <c r="F104" s="189">
-        <f>(E104*1000)/(B104/1000)</f>
+      <c r="F104" s="181">
+        <f t="shared" si="20"/>
         <v>5.8279910082422646</v>
       </c>
-      <c r="G104" s="188">
+      <c r="G104" s="4">
         <v>0</v>
       </c>
-      <c r="H104" s="188"/>
-      <c r="I104" s="190"/>
-      <c r="J104" s="188">
+      <c r="H104" s="4"/>
+      <c r="I104" s="182"/>
+      <c r="J104" s="4">
         <v>3.6389999999999998</v>
       </c>
-      <c r="K104" s="188"/>
-      <c r="L104" s="192">
+      <c r="K104" s="4"/>
+      <c r="L104" s="10">
         <v>2.2415999999999998E-3</v>
       </c>
-      <c r="M104" s="188"/>
-      <c r="N104" s="193">
+      <c r="M104" s="4"/>
+      <c r="N104" s="184">
         <v>127</v>
       </c>
-      <c r="O104" s="194">
+      <c r="O104" s="185">
         <v>44784</v>
       </c>
-      <c r="Q104" s="238" t="s">
+      <c r="Q104" s="223" t="s">
         <v>59</v>
       </c>
       <c r="R104">
         <v>0</v>
       </c>
-      <c r="S104" s="245">
+      <c r="S104" s="230">
         <f>AVERAGE(F125:F126)</f>
         <v>5.52380952380949</v>
       </c>
-      <c r="T104" s="244"/>
-      <c r="U104" s="244"/>
+      <c r="T104" s="229"/>
+      <c r="U104" s="229"/>
       <c r="V104">
         <v>0</v>
       </c>
-      <c r="W104" s="245">
+      <c r="W104" s="230">
         <f>I124</f>
         <v>8.767983246000001E-2</v>
       </c>
-      <c r="X104" s="244">
+      <c r="X104" s="229">
         <f>AVERAGE(J125:J126)</f>
         <v>1.1215000000000002</v>
       </c>
     </row>
     <row r="105" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="188" t="s">
+      <c r="A105" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B105" s="188">
+      <c r="B105" s="4">
         <v>121.37</v>
       </c>
-      <c r="C105" s="188">
+      <c r="C105" s="4">
         <v>0.2329</v>
       </c>
-      <c r="D105" s="188">
+      <c r="D105" s="4">
         <v>0.2331</v>
       </c>
-      <c r="E105" s="188">
-        <f>D105-C105</f>
+      <c r="E105" s="4">
+        <f t="shared" si="19"/>
         <v>2.0000000000000573E-4</v>
       </c>
-      <c r="F105" s="189">
-        <f>(E105*1000)/(B105/1000)</f>
+      <c r="F105" s="181">
+        <f t="shared" si="20"/>
         <v>1.6478536705940983</v>
       </c>
-      <c r="G105" s="188">
+      <c r="G105" s="4">
         <v>0</v>
       </c>
-      <c r="H105" s="188"/>
-      <c r="I105" s="190"/>
-      <c r="J105" s="191">
+      <c r="H105" s="4"/>
+      <c r="I105" s="182"/>
+      <c r="J105" s="183">
         <v>3.1560000000000001</v>
       </c>
-      <c r="K105" s="188"/>
-      <c r="L105" s="192">
+      <c r="K105" s="4"/>
+      <c r="L105" s="10">
         <v>1.0137999999999987E-3</v>
       </c>
-      <c r="M105" s="188"/>
-      <c r="N105" s="193">
+      <c r="M105" s="4"/>
+      <c r="N105" s="184">
         <v>122</v>
       </c>
-      <c r="O105" s="194">
+      <c r="O105" s="185">
         <v>44784</v>
       </c>
-      <c r="Q105" s="239" t="s">
+      <c r="Q105" s="224" t="s">
         <v>60</v>
       </c>
       <c r="R105">
         <v>0</v>
       </c>
-      <c r="S105" s="245">
+      <c r="S105" s="230">
         <f>AVERAGE(F125:F126)</f>
         <v>5.52380952380949</v>
       </c>
-      <c r="T105" s="244"/>
-      <c r="U105" s="244"/>
+      <c r="T105" s="229"/>
+      <c r="U105" s="229"/>
       <c r="V105">
         <v>0</v>
       </c>
-      <c r="W105" s="245">
+      <c r="W105" s="230">
         <f>I124</f>
         <v>8.767983246000001E-2</v>
       </c>
-      <c r="X105" s="244">
+      <c r="X105" s="229">
         <f>AVERAGE(J125:J126)</f>
         <v>1.1215000000000002</v>
       </c>
     </row>
     <row r="106" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A106" s="188" t="s">
+      <c r="A106" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B106" s="188">
+      <c r="B106" s="4">
         <v>107.41</v>
       </c>
-      <c r="C106" s="188">
+      <c r="C106" s="4">
         <v>0.23749999999999999</v>
       </c>
-      <c r="D106" s="188">
+      <c r="D106" s="4">
         <v>0.23749999999999999</v>
       </c>
-      <c r="E106" s="188">
-        <f>D106-C106</f>
+      <c r="E106" s="4">
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="F106" s="189">
-        <f>(E106*1000)/(B106/1000)</f>
+      <c r="F106" s="181">
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="G106" s="188">
+      <c r="G106" s="4">
         <v>0</v>
       </c>
-      <c r="H106" s="188"/>
-      <c r="I106" s="190"/>
-      <c r="J106" s="188">
+      <c r="H106" s="4"/>
+      <c r="I106" s="182"/>
+      <c r="J106" s="4">
         <v>3.6909999999999998</v>
       </c>
-      <c r="K106" s="188"/>
-      <c r="L106" s="188"/>
-      <c r="M106" s="188"/>
-      <c r="N106" s="193">
+      <c r="K106" s="4"/>
+      <c r="L106" s="4"/>
+      <c r="M106" s="4"/>
+      <c r="N106" s="184">
         <v>128</v>
       </c>
-      <c r="O106" s="194">
+      <c r="O106" s="185">
         <v>44797</v>
       </c>
     </row>
     <row r="107" spans="1:24" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="195" t="s">
+      <c r="A107" s="61" t="s">
         <v>146</v>
       </c>
-      <c r="B107" s="195">
+      <c r="B107" s="61">
         <v>104.74</v>
       </c>
-      <c r="C107" s="195">
+      <c r="C107" s="61">
         <v>0.23330000000000001</v>
       </c>
-      <c r="D107" s="195">
+      <c r="D107" s="61">
         <v>0.2334</v>
       </c>
-      <c r="E107" s="195">
-        <f>D107-C107</f>
+      <c r="E107" s="61">
+        <f t="shared" si="19"/>
         <v>9.9999999999988987E-5</v>
       </c>
-      <c r="F107" s="196">
-        <f>(E107*1000)/(B107/1000)</f>
+      <c r="F107" s="186">
+        <f t="shared" si="20"/>
         <v>0.9547450830627171</v>
       </c>
-      <c r="G107" s="195">
+      <c r="G107" s="61">
         <v>0</v>
       </c>
-      <c r="H107" s="195"/>
-      <c r="I107" s="197"/>
-      <c r="J107" s="198">
+      <c r="H107" s="61"/>
+      <c r="I107" s="187"/>
+      <c r="J107" s="188">
         <v>3.2109999999999999</v>
       </c>
-      <c r="K107" s="195"/>
-      <c r="L107" s="199"/>
-      <c r="M107" s="195"/>
-      <c r="N107" s="200">
+      <c r="K107" s="61"/>
+      <c r="L107" s="62"/>
+      <c r="M107" s="61"/>
+      <c r="N107" s="189">
         <v>125</v>
       </c>
-      <c r="O107" s="201">
+      <c r="O107" s="190">
         <v>44797</v>
       </c>
     </row>
     <row r="108" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A108" s="202" t="s">
+      <c r="A108" s="191" t="s">
         <v>147</v>
       </c>
-      <c r="B108" s="203">
+      <c r="B108" s="6">
         <v>119.19</v>
       </c>
-      <c r="C108" s="203">
+      <c r="C108" s="6">
         <v>0.23039999999999999</v>
       </c>
-      <c r="D108" s="203">
+      <c r="D108" s="6">
         <v>0.23300000000000001</v>
       </c>
-      <c r="E108" s="203">
-        <f>D108-C108</f>
+      <c r="E108" s="6">
+        <f t="shared" si="19"/>
         <v>2.600000000000019E-3</v>
       </c>
-      <c r="F108" s="204">
-        <f>(E108*1000)/(B108/1000)</f>
+      <c r="F108" s="192">
+        <f t="shared" si="20"/>
         <v>21.813910562966853</v>
       </c>
-      <c r="G108" s="203">
+      <c r="G108" s="6">
         <v>0</v>
       </c>
-      <c r="H108" s="203"/>
-      <c r="I108" s="205"/>
-      <c r="J108" s="203">
+      <c r="H108" s="6"/>
+      <c r="I108" s="193"/>
+      <c r="J108" s="6">
         <v>2.319</v>
       </c>
-      <c r="K108" s="203"/>
-      <c r="L108" s="203"/>
-      <c r="M108" s="203"/>
-      <c r="N108" s="206">
+      <c r="K108" s="6"/>
+      <c r="L108" s="6"/>
+      <c r="M108" s="6"/>
+      <c r="N108" s="194">
         <v>136</v>
       </c>
-      <c r="O108" s="207">
+      <c r="O108" s="195">
         <v>45003</v>
       </c>
     </row>
     <row r="109" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A109" s="202" t="s">
+      <c r="A109" s="191" t="s">
         <v>148</v>
       </c>
-      <c r="B109" s="203">
+      <c r="B109" s="6">
         <v>200</v>
       </c>
-      <c r="C109" s="203">
+      <c r="C109" s="6">
         <v>0.223</v>
       </c>
-      <c r="D109" s="203">
+      <c r="D109" s="6">
         <v>0.2288</v>
       </c>
-      <c r="E109" s="203">
-        <f>D109-C109</f>
+      <c r="E109" s="6">
+        <f t="shared" si="19"/>
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="F109" s="204">
-        <f>(E109*1000)/(B109/1000)</f>
+      <c r="F109" s="192">
+        <f t="shared" si="20"/>
         <v>28.999999999999996</v>
       </c>
-      <c r="G109" s="203">
+      <c r="G109" s="6">
         <v>0</v>
       </c>
-      <c r="H109" s="203"/>
-      <c r="I109" s="205"/>
-      <c r="J109" s="203">
+      <c r="H109" s="6"/>
+      <c r="I109" s="193"/>
+      <c r="J109" s="6">
         <v>2.254</v>
       </c>
-      <c r="K109" s="203"/>
-      <c r="L109" s="203"/>
-      <c r="M109" s="203"/>
-      <c r="N109" s="206">
+      <c r="K109" s="6"/>
+      <c r="L109" s="6"/>
+      <c r="M109" s="6"/>
+      <c r="N109" s="194">
         <v>137</v>
       </c>
-      <c r="O109" s="207">
+      <c r="O109" s="195">
         <v>45003</v>
       </c>
     </row>
     <row r="110" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A110" s="208" t="s">
+      <c r="A110" s="196" t="s">
         <v>149</v>
       </c>
-      <c r="B110" s="209">
+      <c r="B110" s="67">
         <v>120.77</v>
       </c>
-      <c r="C110" s="209">
+      <c r="C110" s="67">
         <v>0.23499999999999999</v>
       </c>
-      <c r="D110" s="209">
+      <c r="D110" s="67">
         <v>0.23599999999999999</v>
       </c>
-      <c r="E110" s="209">
-        <f>D110-C110</f>
+      <c r="E110" s="67">
+        <f t="shared" si="19"/>
         <v>1.0000000000000009E-3</v>
       </c>
-      <c r="F110" s="210">
-        <f>(E110*1000)/(B110/1000)</f>
+      <c r="F110" s="197">
+        <f t="shared" si="20"/>
         <v>8.2802020369297082</v>
       </c>
-      <c r="G110" s="209">
+      <c r="G110" s="67">
         <v>0</v>
       </c>
-      <c r="H110" s="209"/>
-      <c r="I110" s="211"/>
-      <c r="J110" s="209">
+      <c r="H110" s="67"/>
+      <c r="I110" s="198"/>
+      <c r="J110" s="67">
         <v>2.4380000000000002</v>
       </c>
-      <c r="K110" s="209"/>
-      <c r="L110" s="209"/>
-      <c r="M110" s="209"/>
-      <c r="N110" s="212">
+      <c r="K110" s="67"/>
+      <c r="L110" s="67"/>
+      <c r="M110" s="67"/>
+      <c r="N110" s="199">
         <v>134</v>
       </c>
-      <c r="O110" s="213">
+      <c r="O110" s="200">
         <v>45003</v>
       </c>
     </row>
     <row r="111" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A111" s="202" t="s">
+      <c r="A111" s="191" t="s">
         <v>150</v>
       </c>
-      <c r="B111" s="203">
+      <c r="B111" s="6">
         <v>190</v>
       </c>
-      <c r="C111" s="203">
+      <c r="C111" s="6">
         <v>0.23300000000000001</v>
       </c>
-      <c r="D111" s="203">
+      <c r="D111" s="6">
         <v>0.23380000000000001</v>
       </c>
-      <c r="E111" s="203">
-        <f>D111-C111</f>
+      <c r="E111" s="6">
+        <f t="shared" si="19"/>
         <v>7.9999999999999516E-4</v>
       </c>
-      <c r="F111" s="204">
-        <f>(E111*1000)/(B111/1000)</f>
+      <c r="F111" s="192">
+        <f t="shared" si="20"/>
         <v>4.2105263157894486</v>
       </c>
-      <c r="G111" s="203">
+      <c r="G111" s="6">
         <v>0</v>
       </c>
-      <c r="H111" s="203"/>
-      <c r="I111" s="205"/>
-      <c r="J111" s="203">
+      <c r="H111" s="6"/>
+      <c r="I111" s="193"/>
+      <c r="J111" s="6">
         <v>2.302</v>
       </c>
-      <c r="K111" s="203"/>
-      <c r="L111" s="203"/>
-      <c r="M111" s="203"/>
-      <c r="N111" s="206">
+      <c r="K111" s="6"/>
+      <c r="L111" s="6"/>
+      <c r="M111" s="6"/>
+      <c r="N111" s="194">
         <v>135</v>
       </c>
-      <c r="O111" s="207">
+      <c r="O111" s="195">
         <v>45003</v>
       </c>
     </row>
     <row r="112" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A112" s="202" t="s">
+      <c r="A112" s="191" t="s">
         <v>151</v>
       </c>
-      <c r="B112" s="203">
+      <c r="B112" s="6">
         <v>210</v>
       </c>
-      <c r="C112" s="203">
+      <c r="C112" s="6">
         <v>0.23499999999999999</v>
       </c>
-      <c r="D112" s="203">
+      <c r="D112" s="6">
         <v>0.2404</v>
       </c>
-      <c r="E112" s="203">
-        <f>D112-C112</f>
+      <c r="E112" s="6">
+        <f t="shared" si="19"/>
         <v>5.4000000000000159E-3</v>
       </c>
-      <c r="F112" s="204">
-        <f>(E112*1000)/(B112/1000)</f>
+      <c r="F112" s="192">
+        <f t="shared" si="20"/>
         <v>25.714285714285793</v>
       </c>
-      <c r="G112" s="203">
+      <c r="G112" s="6">
         <v>0</v>
       </c>
-      <c r="H112" s="203"/>
-      <c r="I112" s="205"/>
-      <c r="J112" s="203">
+      <c r="H112" s="6"/>
+      <c r="I112" s="193"/>
+      <c r="J112" s="6">
         <v>2.1970000000000001</v>
       </c>
-      <c r="K112" s="203"/>
-      <c r="L112" s="203"/>
-      <c r="M112" s="203"/>
-      <c r="N112" s="206">
+      <c r="K112" s="6"/>
+      <c r="L112" s="6"/>
+      <c r="M112" s="6"/>
+      <c r="N112" s="194">
         <v>140</v>
       </c>
-      <c r="O112" s="207">
+      <c r="O112" s="195">
         <v>45004</v>
       </c>
     </row>
     <row r="113" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A113" s="202" t="s">
+      <c r="A113" s="191" t="s">
         <v>152</v>
       </c>
-      <c r="B113" s="203">
+      <c r="B113" s="6">
         <v>200</v>
       </c>
-      <c r="C113" s="203">
+      <c r="C113" s="6">
         <v>0.23300000000000001</v>
       </c>
-      <c r="D113" s="203">
+      <c r="D113" s="6">
         <v>0.23519999999999999</v>
       </c>
-      <c r="E113" s="203">
-        <f>D113-C113</f>
+      <c r="E113" s="6">
+        <f t="shared" si="19"/>
         <v>2.1999999999999797E-3</v>
       </c>
-      <c r="F113" s="204">
-        <f>(E113*1000)/(B113/1000)</f>
+      <c r="F113" s="192">
+        <f t="shared" si="20"/>
         <v>10.999999999999899</v>
       </c>
-      <c r="G113" s="203">
+      <c r="G113" s="6">
         <v>0</v>
       </c>
-      <c r="H113" s="203"/>
-      <c r="I113" s="205"/>
-      <c r="J113" s="203">
+      <c r="H113" s="6"/>
+      <c r="I113" s="193"/>
+      <c r="J113" s="6">
         <v>2.2629999999999999</v>
       </c>
-      <c r="K113" s="203"/>
-      <c r="L113" s="203"/>
-      <c r="M113" s="203"/>
-      <c r="N113" s="206">
+      <c r="K113" s="6"/>
+      <c r="L113" s="6"/>
+      <c r="M113" s="6"/>
+      <c r="N113" s="194">
         <v>141</v>
       </c>
-      <c r="O113" s="207">
+      <c r="O113" s="195">
         <v>45004</v>
       </c>
     </row>
     <row r="114" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A114" s="202" t="s">
+      <c r="A114" s="191" t="s">
         <v>153</v>
       </c>
-      <c r="B114" s="203">
+      <c r="B114" s="6">
         <v>200</v>
       </c>
-      <c r="C114" s="203">
+      <c r="C114" s="6">
         <v>0.23499999999999999</v>
       </c>
-      <c r="D114" s="203">
+      <c r="D114" s="6">
         <v>0.23649999999999999</v>
       </c>
-      <c r="E114" s="203">
-        <f>D114-C114</f>
+      <c r="E114" s="6">
+        <f t="shared" si="19"/>
         <v>1.5000000000000013E-3</v>
       </c>
-      <c r="F114" s="204">
-        <f>(E114*1000)/(B114/1000)</f>
+      <c r="F114" s="192">
+        <f t="shared" si="20"/>
         <v>7.5000000000000062</v>
       </c>
-      <c r="G114" s="203">
+      <c r="G114" s="6">
         <v>0</v>
       </c>
-      <c r="H114" s="203"/>
-      <c r="I114" s="205"/>
-      <c r="J114" s="203">
+      <c r="H114" s="6"/>
+      <c r="I114" s="193"/>
+      <c r="J114" s="6">
         <v>2.2879999999999998</v>
       </c>
-      <c r="K114" s="203"/>
-      <c r="L114" s="203"/>
-      <c r="M114" s="203"/>
-      <c r="N114" s="206">
+      <c r="K114" s="6"/>
+      <c r="L114" s="6"/>
+      <c r="M114" s="6"/>
+      <c r="N114" s="194">
         <v>138</v>
       </c>
-      <c r="O114" s="207">
+      <c r="O114" s="195">
         <v>45004</v>
       </c>
     </row>
     <row r="115" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A115" s="202" t="s">
+      <c r="A115" s="191" t="s">
         <v>154</v>
       </c>
-      <c r="B115" s="203">
+      <c r="B115" s="6">
         <v>190</v>
       </c>
-      <c r="C115" s="203">
+      <c r="C115" s="6">
         <v>0.23</v>
       </c>
-      <c r="D115" s="203">
+      <c r="D115" s="6">
         <v>0.2319</v>
       </c>
-      <c r="E115" s="203">
-        <f>D115-C115</f>
+      <c r="E115" s="6">
+        <f t="shared" si="19"/>
         <v>1.899999999999985E-3</v>
       </c>
-      <c r="F115" s="204">
-        <f>(E115*1000)/(B115/1000)</f>
+      <c r="F115" s="192">
+        <f t="shared" si="20"/>
         <v>9.9999999999999218</v>
       </c>
-      <c r="G115" s="203">
+      <c r="G115" s="6">
         <v>0</v>
       </c>
-      <c r="H115" s="203"/>
-      <c r="I115" s="205"/>
-      <c r="J115" s="203">
+      <c r="H115" s="6"/>
+      <c r="I115" s="193"/>
+      <c r="J115" s="6">
         <v>2.1789999999999998</v>
       </c>
-      <c r="K115" s="203"/>
-      <c r="L115" s="203"/>
-      <c r="M115" s="203"/>
-      <c r="N115" s="206">
+      <c r="K115" s="6"/>
+      <c r="L115" s="6"/>
+      <c r="M115" s="6"/>
+      <c r="N115" s="194">
         <v>139</v>
       </c>
-      <c r="O115" s="207">
+      <c r="O115" s="195">
         <v>45004</v>
       </c>
     </row>
     <row r="116" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A116" s="202" t="s">
+      <c r="A116" s="191" t="s">
         <v>155</v>
       </c>
-      <c r="B116" s="203">
+      <c r="B116" s="6">
         <v>200</v>
       </c>
-      <c r="C116" s="203">
+      <c r="C116" s="6">
         <v>0.23499999999999999</v>
       </c>
-      <c r="D116" s="203">
+      <c r="D116" s="6">
         <v>0.2424</v>
       </c>
-      <c r="E116" s="203">
-        <f>D116-C116</f>
+      <c r="E116" s="6">
+        <f t="shared" si="19"/>
         <v>7.4000000000000177E-3</v>
       </c>
-      <c r="F116" s="204">
-        <f>(E116*1000)/(B116/1000)</f>
+      <c r="F116" s="192">
+        <f t="shared" si="20"/>
         <v>37.000000000000085</v>
       </c>
-      <c r="G116" s="214"/>
-      <c r="H116" s="203"/>
-      <c r="I116" s="205"/>
-      <c r="J116" s="203">
+      <c r="G116" s="201"/>
+      <c r="H116" s="6"/>
+      <c r="I116" s="193"/>
+      <c r="J116" s="6">
         <v>2.1349999999999998</v>
       </c>
-      <c r="K116" s="203"/>
-      <c r="L116" s="203"/>
-      <c r="M116" s="203"/>
-      <c r="N116" s="206">
+      <c r="K116" s="6"/>
+      <c r="L116" s="6"/>
+      <c r="M116" s="6"/>
+      <c r="N116" s="194">
         <v>144</v>
       </c>
-      <c r="O116" s="207">
+      <c r="O116" s="195">
         <v>45007</v>
       </c>
     </row>
     <row r="117" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" s="202" t="s">
+      <c r="A117" s="191" t="s">
         <v>156</v>
       </c>
-      <c r="B117" s="203">
+      <c r="B117" s="6">
         <v>190</v>
       </c>
-      <c r="C117" s="203">
+      <c r="C117" s="6">
         <v>0.23330000000000001</v>
       </c>
-      <c r="D117" s="203">
+      <c r="D117" s="6">
         <v>0.23699999999999999</v>
       </c>
-      <c r="E117" s="203">
-        <f>D117-C117</f>
+      <c r="E117" s="6">
+        <f t="shared" si="19"/>
         <v>3.6999999999999811E-3</v>
       </c>
-      <c r="F117" s="204">
-        <f>(E117*1000)/(B117/1000)</f>
+      <c r="F117" s="192">
+        <f t="shared" si="20"/>
         <v>19.473684210526216</v>
       </c>
-      <c r="G117" s="203"/>
-      <c r="H117" s="203"/>
-      <c r="I117" s="205"/>
-      <c r="J117" s="203">
+      <c r="G117" s="6"/>
+      <c r="H117" s="6"/>
+      <c r="I117" s="193"/>
+      <c r="J117" s="6">
         <v>2.1480000000000001</v>
       </c>
-      <c r="K117" s="203"/>
-      <c r="L117" s="203"/>
-      <c r="M117" s="203"/>
-      <c r="N117" s="206">
+      <c r="K117" s="6"/>
+      <c r="L117" s="6"/>
+      <c r="M117" s="6"/>
+      <c r="N117" s="194">
         <v>143</v>
       </c>
-      <c r="O117" s="207">
+      <c r="O117" s="195">
         <v>45007</v>
       </c>
     </row>
     <row r="118" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A118" s="202" t="s">
+      <c r="A118" s="191" t="s">
         <v>157</v>
       </c>
-      <c r="B118" s="203">
+      <c r="B118" s="6">
         <v>200</v>
       </c>
-      <c r="C118" s="203">
+      <c r="C118" s="6">
         <v>0.222</v>
       </c>
-      <c r="D118" s="203">
+      <c r="D118" s="6">
         <v>0.22900000000000001</v>
       </c>
-      <c r="E118" s="203">
-        <f>D118-C118</f>
+      <c r="E118" s="6">
+        <f t="shared" si="19"/>
         <v>7.0000000000000062E-3</v>
       </c>
-      <c r="F118" s="204">
-        <f>(E118*1000)/(B118/1000)</f>
+      <c r="F118" s="192">
+        <f t="shared" si="20"/>
         <v>35.000000000000028</v>
       </c>
-      <c r="G118" s="203"/>
-      <c r="H118" s="203"/>
-      <c r="I118" s="205"/>
-      <c r="J118" s="203">
+      <c r="G118" s="6"/>
+      <c r="H118" s="6"/>
+      <c r="I118" s="193"/>
+      <c r="J118" s="6">
         <v>2.1960000000000002</v>
       </c>
-      <c r="K118" s="203"/>
-      <c r="L118" s="203"/>
-      <c r="M118" s="203"/>
-      <c r="N118" s="206">
+      <c r="K118" s="6"/>
+      <c r="L118" s="6"/>
+      <c r="M118" s="6"/>
+      <c r="N118" s="194">
         <v>142</v>
       </c>
-      <c r="O118" s="207">
+      <c r="O118" s="195">
         <v>45007</v>
       </c>
     </row>
     <row r="119" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A119" s="202" t="s">
+      <c r="A119" s="191" t="s">
         <v>158</v>
       </c>
-      <c r="B119" s="203">
+      <c r="B119" s="6">
         <v>200</v>
       </c>
-      <c r="C119" s="203">
+      <c r="C119" s="6">
         <v>0.23599999999999999</v>
       </c>
-      <c r="D119" s="203">
+      <c r="D119" s="6">
         <v>0.2366</v>
       </c>
-      <c r="E119" s="203">
-        <f>D119-C119</f>
+      <c r="E119" s="6">
+        <f t="shared" si="19"/>
         <v>6.0000000000001719E-4</v>
       </c>
-      <c r="F119" s="204">
-        <f>(E119*1000)/(B119/1000)</f>
+      <c r="F119" s="192">
+        <f t="shared" si="20"/>
         <v>3.0000000000000857</v>
       </c>
-      <c r="G119" s="203"/>
-      <c r="H119" s="203"/>
-      <c r="I119" s="205"/>
-      <c r="J119" s="203">
+      <c r="G119" s="6"/>
+      <c r="H119" s="6"/>
+      <c r="I119" s="193"/>
+      <c r="J119" s="6">
         <v>2.0670000000000002</v>
       </c>
-      <c r="K119" s="203"/>
-      <c r="L119" s="203"/>
-      <c r="M119" s="203"/>
-      <c r="N119" s="206">
+      <c r="K119" s="6"/>
+      <c r="L119" s="6"/>
+      <c r="M119" s="6"/>
+      <c r="N119" s="194">
         <v>145</v>
       </c>
-      <c r="O119" s="207">
+      <c r="O119" s="195">
         <v>45007</v>
       </c>
     </row>
     <row r="120" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A120" s="202" t="s">
+      <c r="A120" s="191" t="s">
         <v>159</v>
       </c>
-      <c r="B120" s="203">
+      <c r="B120" s="6">
         <v>150</v>
       </c>
-      <c r="C120" s="203">
+      <c r="C120" s="6">
         <v>0.23499999999999999</v>
       </c>
-      <c r="D120" s="203">
+      <c r="D120" s="6">
         <v>0.23669999999999999</v>
       </c>
-      <c r="E120" s="203">
-        <f>D120-C120</f>
+      <c r="E120" s="6">
+        <f t="shared" si="19"/>
         <v>1.7000000000000071E-3</v>
       </c>
-      <c r="F120" s="204">
-        <f>(E120*1000)/(B120/1000)</f>
+      <c r="F120" s="192">
+        <f t="shared" si="20"/>
         <v>11.33333333333338</v>
       </c>
       <c r="G120" s="9">
         <v>115.20499999999998</v>
       </c>
-      <c r="H120" s="203"/>
-      <c r="I120" s="205"/>
-      <c r="J120" s="203">
+      <c r="H120" s="6"/>
+      <c r="I120" s="193"/>
+      <c r="J120" s="6">
         <v>4.3840000000000003</v>
       </c>
-      <c r="K120" s="203"/>
-      <c r="L120" s="203"/>
-      <c r="M120" s="203"/>
-      <c r="N120" s="206">
+      <c r="K120" s="6"/>
+      <c r="L120" s="6"/>
+      <c r="M120" s="6"/>
+      <c r="N120" s="194">
         <v>132</v>
       </c>
-      <c r="O120" s="207">
+      <c r="O120" s="195">
         <v>45029</v>
       </c>
     </row>
     <row r="121" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A121" s="202" t="s">
+      <c r="A121" s="191" t="s">
         <v>160</v>
       </c>
-      <c r="B121" s="203">
+      <c r="B121" s="6">
         <v>145</v>
       </c>
-      <c r="C121" s="203">
+      <c r="C121" s="6">
         <v>0.22500000000000001</v>
       </c>
-      <c r="D121" s="203">
+      <c r="D121" s="6">
         <v>0.22739999999999999</v>
       </c>
-      <c r="E121" s="203">
-        <f>D121-C121</f>
+      <c r="E121" s="6">
+        <f t="shared" si="19"/>
         <v>2.3999999999999855E-3</v>
       </c>
-      <c r="F121" s="204">
-        <f>(E121*1000)/(B121/1000)</f>
+      <c r="F121" s="192">
+        <f t="shared" si="20"/>
         <v>16.551724137930933</v>
       </c>
       <c r="G121" s="9">
         <v>106.28000000000002</v>
       </c>
-      <c r="H121" s="203"/>
-      <c r="I121" s="205"/>
-      <c r="J121" s="203">
+      <c r="H121" s="6"/>
+      <c r="I121" s="193"/>
+      <c r="J121" s="6">
         <v>4.49</v>
       </c>
-      <c r="K121" s="203"/>
-      <c r="L121" s="203"/>
-      <c r="M121" s="203"/>
-      <c r="N121" s="206">
+      <c r="K121" s="6"/>
+      <c r="L121" s="6"/>
+      <c r="M121" s="6"/>
+      <c r="N121" s="194">
         <v>133</v>
       </c>
-      <c r="O121" s="207">
+      <c r="O121" s="195">
         <v>45029</v>
       </c>
     </row>
     <row r="122" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A122" s="202" t="s">
+      <c r="A122" s="191" t="s">
         <v>161</v>
       </c>
-      <c r="B122" s="203">
+      <c r="B122" s="6">
         <v>150</v>
       </c>
-      <c r="C122" s="203">
+      <c r="C122" s="6">
         <v>0.23899999999999999</v>
       </c>
-      <c r="D122" s="203">
+      <c r="D122" s="6">
         <v>0.24</v>
       </c>
-      <c r="E122" s="203">
-        <f>D122-C122</f>
+      <c r="E122" s="6">
+        <f t="shared" si="19"/>
         <v>1.0000000000000009E-3</v>
       </c>
-      <c r="F122" s="204">
-        <f>(E122*1000)/(B122/1000)</f>
+      <c r="F122" s="192">
+        <f t="shared" si="20"/>
         <v>6.6666666666666732</v>
       </c>
       <c r="G122" s="9">
         <v>118.6825</v>
       </c>
-      <c r="H122" s="203"/>
-      <c r="I122" s="205"/>
-      <c r="J122" s="203">
+      <c r="H122" s="6"/>
+      <c r="I122" s="193"/>
+      <c r="J122" s="6">
         <v>4.4930000000000003</v>
       </c>
-      <c r="K122" s="203"/>
-      <c r="L122" s="203"/>
-      <c r="M122" s="203"/>
-      <c r="N122" s="206">
+      <c r="K122" s="6"/>
+      <c r="L122" s="6"/>
+      <c r="M122" s="6"/>
+      <c r="N122" s="194">
         <v>131</v>
       </c>
-      <c r="O122" s="207">
+      <c r="O122" s="195">
         <v>45029</v>
       </c>
     </row>
     <row r="123" spans="1:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="215" t="s">
+      <c r="A123" s="202" t="s">
         <v>162</v>
       </c>
-      <c r="B123" s="216">
+      <c r="B123" s="90">
         <v>200</v>
       </c>
-      <c r="C123" s="216">
+      <c r="C123" s="90">
         <v>0.23400000000000001</v>
       </c>
-      <c r="D123" s="216">
+      <c r="D123" s="90">
         <v>0.23530000000000001</v>
       </c>
-      <c r="E123" s="216">
-        <f>D123-C123</f>
+      <c r="E123" s="90">
+        <f t="shared" si="19"/>
         <v>1.2999999999999956E-3</v>
       </c>
-      <c r="F123" s="217">
-        <f>(E123*1000)/(B123/1000)</f>
+      <c r="F123" s="203">
+        <f t="shared" si="20"/>
         <v>6.4999999999999778</v>
       </c>
       <c r="G123" s="140">
         <v>73.134999999999991</v>
       </c>
-      <c r="H123" s="216"/>
-      <c r="I123" s="218"/>
-      <c r="J123" s="216">
+      <c r="H123" s="90"/>
+      <c r="I123" s="204"/>
+      <c r="J123" s="90">
         <v>4.4409999999999998</v>
       </c>
-      <c r="K123" s="216"/>
-      <c r="L123" s="216"/>
-      <c r="M123" s="216"/>
-      <c r="N123" s="219">
+      <c r="K123" s="90"/>
+      <c r="L123" s="90"/>
+      <c r="M123" s="90"/>
+      <c r="N123" s="205">
         <v>130</v>
       </c>
-      <c r="O123" s="220">
+      <c r="O123" s="206">
         <v>45029</v>
       </c>
     </row>
     <row r="124" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A124" s="221" t="s">
+      <c r="A124" s="207" t="s">
         <v>163</v>
       </c>
-      <c r="B124" s="222">
+      <c r="B124" s="208">
         <v>150</v>
       </c>
-      <c r="C124" s="246">
+      <c r="C124" s="215">
         <v>0.23319999999999999</v>
       </c>
-      <c r="D124" s="246">
+      <c r="D124" s="215">
         <v>0.23519999999999999</v>
       </c>
-      <c r="E124" s="222">
-        <f>D124-C124</f>
+      <c r="E124" s="208">
+        <f t="shared" si="19"/>
         <v>2.0000000000000018E-3</v>
       </c>
-      <c r="F124" s="223">
-        <f>(E124*1000)/(B124/1000)</f>
+      <c r="F124" s="209">
+        <f t="shared" si="20"/>
         <v>13.333333333333346</v>
       </c>
-      <c r="G124" s="222">
+      <c r="G124" s="208">
         <v>0</v>
       </c>
-      <c r="H124" s="224">
+      <c r="H124" s="210">
         <v>1.3151974869000001E-2</v>
       </c>
-      <c r="I124" s="225">
+      <c r="I124" s="211">
         <f>H124/(B124/1000)</f>
         <v>8.767983246000001E-2</v>
       </c>
-      <c r="J124" s="222"/>
-      <c r="K124" s="222"/>
-      <c r="L124" s="222"/>
-      <c r="M124" s="222"/>
-      <c r="N124" s="226">
+      <c r="J124" s="208"/>
+      <c r="K124" s="208"/>
+      <c r="L124" s="208"/>
+      <c r="M124" s="208"/>
+      <c r="N124" s="212">
         <v>436</v>
       </c>
-      <c r="O124" s="227">
+      <c r="O124" s="213">
         <v>45127</v>
       </c>
     </row>
     <row r="125" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A125" s="228" t="s">
+      <c r="A125" s="214" t="s">
         <v>165</v>
       </c>
-      <c r="B125" s="229">
+      <c r="B125" s="215">
         <v>140</v>
       </c>
-      <c r="C125" s="246">
+      <c r="C125" s="215">
         <v>0.2331</v>
       </c>
-      <c r="D125" s="246">
+      <c r="D125" s="215">
         <v>0.2339</v>
       </c>
-      <c r="E125" s="229">
-        <f>D125-C125</f>
+      <c r="E125" s="215">
+        <f t="shared" si="19"/>
         <v>7.9999999999999516E-4</v>
       </c>
-      <c r="F125" s="230">
-        <f>(E125*1000)/(B125/1000)</f>
+      <c r="F125" s="216">
+        <f t="shared" si="20"/>
         <v>5.7142857142856789</v>
       </c>
-      <c r="G125" s="229">
+      <c r="G125" s="215">
         <v>0</v>
       </c>
-      <c r="H125" s="229"/>
-      <c r="I125" s="229"/>
-      <c r="J125" s="229">
+      <c r="H125" s="215"/>
+      <c r="I125" s="215"/>
+      <c r="J125" s="215">
         <v>1.127</v>
       </c>
-      <c r="K125" s="229"/>
-      <c r="L125" s="229"/>
-      <c r="M125" s="229"/>
-      <c r="N125" s="231">
+      <c r="K125" s="215"/>
+      <c r="L125" s="215"/>
+      <c r="M125" s="215"/>
+      <c r="N125" s="217">
         <v>475</v>
       </c>
-      <c r="O125" s="232">
+      <c r="O125" s="218">
         <v>45154</v>
       </c>
     </row>
     <row r="126" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A126" s="228" t="s">
+      <c r="A126" s="214" t="s">
         <v>164</v>
       </c>
-      <c r="B126" s="229">
+      <c r="B126" s="215">
         <v>150</v>
       </c>
-      <c r="C126" s="246">
+      <c r="C126" s="215">
         <v>0.24030000000000001</v>
       </c>
-      <c r="D126" s="246">
+      <c r="D126" s="215">
         <v>0.24110000000000001</v>
       </c>
-      <c r="E126" s="229">
-        <f>D126-C126</f>
+      <c r="E126" s="215">
+        <f t="shared" si="19"/>
         <v>7.9999999999999516E-4</v>
       </c>
-      <c r="F126" s="230">
-        <f>(E126*1000)/(B126/1000)</f>
+      <c r="F126" s="216">
+        <f t="shared" si="20"/>
         <v>5.3333333333333011</v>
       </c>
-      <c r="G126" s="229">
+      <c r="G126" s="215">
         <v>0</v>
       </c>
-      <c r="H126" s="229"/>
-      <c r="I126" s="229"/>
-      <c r="J126" s="229">
+      <c r="H126" s="215"/>
+      <c r="I126" s="215"/>
+      <c r="J126" s="215">
         <v>1.1160000000000001</v>
       </c>
-      <c r="K126" s="229"/>
-      <c r="L126" s="229"/>
-      <c r="M126" s="229"/>
-      <c r="N126" s="231">
+      <c r="K126" s="215"/>
+      <c r="L126" s="215"/>
+      <c r="M126" s="215"/>
+      <c r="N126" s="217">
         <v>474</v>
       </c>
-      <c r="O126" s="232">
+      <c r="O126" s="218">
         <v>45153</v>
       </c>
     </row>

--- a/data/constituents_summary.xlsx
+++ b/data/constituents_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\hysteresis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE01E7D-272E-44BD-842E-92E7BE1CA811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B62B9E93-34E1-40A3-9F62-B026CE237D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="623" xr2:uid="{FEC01F85-CDE9-417C-893C-E562E55652ED}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="623" xr2:uid="{FEC01F85-CDE9-417C-893C-E562E55652ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Spring" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="337">
   <si>
     <t>Volume filtered (mL)</t>
   </si>
@@ -2236,9 +2236,9 @@
           </c:trendline>
           <c:xVal>
             <c:strRef>
-              <c:f>Spring!$F$2:$F$87</c:f>
+              <c:f>Spring!$F$2:$F$167</c:f>
               <c:strCache>
-                <c:ptCount val="86"/>
+                <c:ptCount val="166"/>
                 <c:pt idx="0">
                   <c:v>12.38</c:v>
                 </c:pt>
@@ -2495,6 +2495,222 @@
                   <c:v>6.32</c:v>
                 </c:pt>
                 <c:pt idx="85">
+                  <c:v>-</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>10.00</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>6.82</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>21.50</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>11.05</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>18.00</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>6.50</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>8.00</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>12.00</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>6.00</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>8.89</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>12.22</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>6.88</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>4.67</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>5.33</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>6.00</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>17.86</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>4.00</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>6.67</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>5.52</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>5.33</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>8.00</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>7.33</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>-</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>11.25</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>5.16</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>8.67</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>8.57</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>-</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>15.00</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>7.14</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>4.12</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>7.14</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>-</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>5.52</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>11.33</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>6.67</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>5.29</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>-</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>7.50</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>-</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>8.12</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>11.61</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>8.12</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>6.67</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>3.75</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>11.25</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>4.67</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>14.55</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>9.29</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>6.88</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>2.50</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>12.67</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>45.00</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>14.00</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>10.00</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>8.12</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>13.53</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>20.00</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>10.00</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>4.38</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>3.33</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>5.00</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>10.67</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>24.37</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>5.62</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>1.29</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>5.71</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>2.14</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.67</c:v>
+                </c:pt>
+                <c:pt idx="165">
                   <c:v>-</c:v>
                 </c:pt>
               </c:strCache>
@@ -2502,237 +2718,507 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Spring!$G$2:$G$87</c:f>
+              <c:f>Spring!$G$2:$G$167</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="86"/>
-                <c:pt idx="10">
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="166"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="General">
                   <c:v>106.21</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="11" formatCode="General">
                   <c:v>51.232999999999997</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="12" formatCode="General">
                   <c:v>59.16</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="13" formatCode="General">
                   <c:v>48.47</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="14" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="15" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="16" formatCode="General">
                   <c:v>78.709999999999994</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="17" formatCode="General">
                   <c:v>45.42</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="18" formatCode="General">
                   <c:v>74.75</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="19" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="20" formatCode="General">
                   <c:v>56.59</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="21" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="22" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="23" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="24" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="25" formatCode="General">
                   <c:v>27.23</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="26" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="27" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="28" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="29" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="30" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="31" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="32" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="33" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="34" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="35" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="36" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="37" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="38" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="39" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="40" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="41" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="42" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="43" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="44" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="45" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="46" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="47" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="48" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="49" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="50" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="51" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="52" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="53" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="54" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="55" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="56" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="57" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="58" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="59" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="60" formatCode="General">
                   <c:v>63.56</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="61" formatCode="General">
                   <c:v>85.89</c:v>
                 </c:pt>
-                <c:pt idx="62">
+                <c:pt idx="62" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="63" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="64">
+                <c:pt idx="64" formatCode="General">
                   <c:v>50.13</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="0.0000">
                   <c:v>44.99</c:v>
                 </c:pt>
-                <c:pt idx="66">
+                <c:pt idx="66" formatCode="General">
                   <c:v>35.729999999999997</c:v>
                 </c:pt>
-                <c:pt idx="67">
+                <c:pt idx="67" formatCode="General">
                   <c:v>31.62</c:v>
                 </c:pt>
-                <c:pt idx="68">
+                <c:pt idx="68" formatCode="General">
                   <c:v>25.42</c:v>
                 </c:pt>
-                <c:pt idx="69">
+                <c:pt idx="69" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="70">
+                <c:pt idx="70" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="71">
+                <c:pt idx="71" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="72">
+                <c:pt idx="72" formatCode="General">
                   <c:v>68.760000000000005</c:v>
                 </c:pt>
-                <c:pt idx="73">
+                <c:pt idx="73" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="74">
+                <c:pt idx="74" formatCode="General">
                   <c:v>50.92</c:v>
                 </c:pt>
-                <c:pt idx="75">
+                <c:pt idx="75" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="76">
+                <c:pt idx="76" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="77">
+                <c:pt idx="77" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="78">
+                <c:pt idx="78" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="79" formatCode="0.0000">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="80">
+                <c:pt idx="80" formatCode="General">
                   <c:v>33.08</c:v>
                 </c:pt>
-                <c:pt idx="81">
+                <c:pt idx="81" formatCode="General">
                   <c:v>77.489999999999995</c:v>
                 </c:pt>
-                <c:pt idx="82">
+                <c:pt idx="82" formatCode="General">
                   <c:v>103.31</c:v>
                 </c:pt>
-                <c:pt idx="83">
+                <c:pt idx="83" formatCode="General">
                   <c:v>65.48</c:v>
                 </c:pt>
-                <c:pt idx="84">
+                <c:pt idx="84" formatCode="General">
                   <c:v>73.680000000000007</c:v>
                 </c:pt>
-                <c:pt idx="85">
+                <c:pt idx="85" formatCode="General">
                   <c:v>48.9</c:v>
+                </c:pt>
+                <c:pt idx="86" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="87" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="88" formatCode="General">
+                  <c:v>93.48</c:v>
+                </c:pt>
+                <c:pt idx="89" formatCode="General">
+                  <c:v>53.79</c:v>
+                </c:pt>
+                <c:pt idx="90" formatCode="General">
+                  <c:v>47.58</c:v>
+                </c:pt>
+                <c:pt idx="91" formatCode="General">
+                  <c:v>30.72</c:v>
+                </c:pt>
+                <c:pt idx="92" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="93" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="94" formatCode="General">
+                  <c:v>22.36</c:v>
+                </c:pt>
+                <c:pt idx="95" formatCode="General">
+                  <c:v>30.83</c:v>
+                </c:pt>
+                <c:pt idx="96" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="97" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="98" formatCode="General">
+                  <c:v>24.91</c:v>
+                </c:pt>
+                <c:pt idx="99" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="100" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="101" formatCode="General">
+                  <c:v>67.13</c:v>
+                </c:pt>
+                <c:pt idx="102" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="103" formatCode="General">
+                  <c:v>51.68</c:v>
+                </c:pt>
+                <c:pt idx="104" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="105" formatCode="General">
+                  <c:v>57.56</c:v>
+                </c:pt>
+                <c:pt idx="106" formatCode="General">
+                  <c:v>63.54</c:v>
+                </c:pt>
+                <c:pt idx="107" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="108" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="109" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="110" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="111" formatCode="General">
+                  <c:v>66.59</c:v>
+                </c:pt>
+                <c:pt idx="112" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="113" formatCode="General">
+                  <c:v>46.75</c:v>
+                </c:pt>
+                <c:pt idx="114" formatCode="General">
+                  <c:v>27.12</c:v>
+                </c:pt>
+                <c:pt idx="115" formatCode="General">
+                  <c:v>14.59</c:v>
+                </c:pt>
+                <c:pt idx="116" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="117" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="118" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="119" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="120" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="121" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="122" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="123" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="124" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="125" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="126" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="127" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="128" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="129" formatCode="General">
+                  <c:v>56.02</c:v>
+                </c:pt>
+                <c:pt idx="130" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="131" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="132" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="133" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="134" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="135" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="136" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="137" formatCode="General">
+                  <c:v>43.66</c:v>
+                </c:pt>
+                <c:pt idx="138" formatCode="General">
+                  <c:v>85.5</c:v>
+                </c:pt>
+                <c:pt idx="139" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="140" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="141" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="142" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="143" formatCode="General">
+                  <c:v>64.14</c:v>
+                </c:pt>
+                <c:pt idx="144" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="145" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="146" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="147" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="148" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="149" formatCode="General">
+                  <c:v>39.619999999999997</c:v>
+                </c:pt>
+                <c:pt idx="150" formatCode="General">
+                  <c:v>87.1</c:v>
+                </c:pt>
+                <c:pt idx="151" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="152" formatCode="General">
+                  <c:v>26.28</c:v>
+                </c:pt>
+                <c:pt idx="153" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="154" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="155" formatCode="General">
+                  <c:v>35.26</c:v>
+                </c:pt>
+                <c:pt idx="156" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="157" formatCode="General">
+                  <c:v>72.78</c:v>
+                </c:pt>
+                <c:pt idx="158" formatCode="General">
+                  <c:v>25.16</c:v>
+                </c:pt>
+                <c:pt idx="159" formatCode="General">
+                  <c:v>15.19</c:v>
+                </c:pt>
+                <c:pt idx="160" formatCode="General">
+                  <c:v>99.54</c:v>
+                </c:pt>
+                <c:pt idx="161" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="162" formatCode="General">
+                  <c:v>40.119999999999997</c:v>
+                </c:pt>
+                <c:pt idx="163" formatCode="General">
+                  <c:v>25.61</c:v>
+                </c:pt>
+                <c:pt idx="164" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="165" formatCode="General">
+                  <c:v>30.82</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2953,6 +3439,984 @@
             </a:p>
           </c:txPr>
         </c:title>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="734722767"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>SSC vs LISST</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Summer '!$F$2:$F$87</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="86"/>
+                <c:pt idx="0">
+                  <c:v>562.3258328827518</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>528.03483941208492</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>143.16904685207069</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>82.761404925313002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>36.920031971986397</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>22.011886418665991</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>68.980963045912645</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>124.47532204371103</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>359.22024838861807</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>86.111374932725383</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>37.228078044404583</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>30.434986187198604</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>57.726093867648203</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>48.064760941057514</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>55.003694277973992</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45.164039198977413</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17.425939756036765</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>11.446324912108677</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6.5306122448979194</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.4796065462560257</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>10.743801652892525</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>19.837989750371843</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>49.091801669121296</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>35.385121790651731</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>23.681202025150956</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>9.8887515451172572</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7.9500000000000943</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>4.080633314290381</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.6455487905216861</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.84473728670397652</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>5.7194215213659483</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>187.00000000000023</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>109.9999999999999</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>53.333333333333321</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>80.000000000000071</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>43.333333333333179</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>92.222222222222243</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>52.222222222222328</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>99.999999999999773</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>105.55555555555566</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>50.000000000000043</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>68.888888888888701</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>51.111111111111029</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>45.263157894736821</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>20.00000000000011</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>15.454545454545519</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>26.000000000000188</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>21.000000000000185</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>76.153846153846203</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>41.200000000000017</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>39.60000000000008</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>27.600000000000069</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>20.833333333333353</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>43.200000000000017</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>29.230769230769212</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>25.000000000000021</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>23.749999999999932</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>22.222222222222243</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>22.222222222222243</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>21.90476190476187</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>17.999999999999961</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>20.499999999999964</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>12.558139534883757</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>18.000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>20.000000000000018</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>16.666666666666682</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>77.894736842105289</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>42.999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>35.999999999999922</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>28.837209302325505</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>29.545454545454572</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>26.842105263157862</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>24.000000000000131</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>23.571428571428555</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>37.60000000000008</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>31.53846153846148</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>28.076923076923084</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>23.599999999999955</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>21.176470588235247</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>23.137254901960741</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>30.769230769230795</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>30.188679245282938</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>29.166666666666696</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>20.416666666666732</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>18.000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>18.999999999999851</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Summer '!$G$2:$G$87</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="86"/>
+                <c:pt idx="0">
+                  <c:v>339.78248000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>457.12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>152.79</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>168.45</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>43.15</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17.7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>92.06</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>95.69</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>403.51499999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>124.04</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>65.3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>42.87</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>206.82</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>142.53</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>55.06</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>66.040000000000006</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>39.15</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>23.32</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>52.87</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>204.03</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>105.77</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>68.83</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>36.65</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>25.92</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>21.67</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>19.05</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>18.36</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>271.06</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>249.50899999999999</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>244.85599999999999</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>233.25</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>124.5634</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>9.89</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>327.45299999999997</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>241.809</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>158.52500000000001</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>132.47200000000001</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>98.91</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>90.356999999999999</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>84.561999999999998</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>59.01</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>42.72</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>98.146000000000001</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>210.458</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>116.066</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>113.258</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>81.150000000000006</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>56.15</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>183.80799999999999</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>83.528000000000006</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>72.105000000000004</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>67.606999999999999</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>70.3</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>67.88</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>84.66</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>67.569999999999993</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>54.936</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>75.337999999999994</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>59.165999999999997</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>50.774000000000001</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>232.05199999999999</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>143.89599999999999</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>104.006</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>88.144000000000005</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>92.256</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>82.494</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>69.394999999999996</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>63.87</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>75.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>70.75</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>82.6</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>54.12</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>95.962999999999994</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>80.180000000000007</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>70.510000000000005</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>64.436999999999998</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>46.07</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>39.299999999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-27C1-4986-9C3E-74D8A497147B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="734722767"/>
+        <c:axId val="734720847"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="734722767"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>SSC</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> (from filters (mg/L)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="734720847"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="734720847"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>LISST concentration (uL/L)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -3046,7 +4510,1939 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>SSC vs POC</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Summer '!$F$2:$F$87</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="86"/>
+                <c:pt idx="0">
+                  <c:v>562.3258328827518</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>528.03483941208492</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>143.16904685207069</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>82.761404925313002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>36.920031971986397</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>22.011886418665991</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>68.980963045912645</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>124.47532204371103</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>359.22024838861807</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>86.111374932725383</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>37.228078044404583</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>30.434986187198604</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>57.726093867648203</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>48.064760941057514</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>55.003694277973992</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45.164039198977413</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17.425939756036765</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>11.446324912108677</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6.5306122448979194</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.4796065462560257</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>10.743801652892525</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>19.837989750371843</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>49.091801669121296</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>35.385121790651731</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>23.681202025150956</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>9.8887515451172572</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7.9500000000000943</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>4.080633314290381</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.6455487905216861</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.84473728670397652</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>5.7194215213659483</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>187.00000000000023</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>109.9999999999999</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>53.333333333333321</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>80.000000000000071</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>43.333333333333179</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>92.222222222222243</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>52.222222222222328</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>99.999999999999773</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>105.55555555555566</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>50.000000000000043</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>68.888888888888701</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>51.111111111111029</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>45.263157894736821</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>20.00000000000011</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>15.454545454545519</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>26.000000000000188</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>21.000000000000185</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>76.153846153846203</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>41.200000000000017</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>39.60000000000008</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>27.600000000000069</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>20.833333333333353</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>43.200000000000017</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>29.230769230769212</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>25.000000000000021</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>23.749999999999932</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>22.222222222222243</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>22.222222222222243</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>21.90476190476187</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>17.999999999999961</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>20.499999999999964</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>12.558139534883757</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>18.000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>20.000000000000018</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>16.666666666666682</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>77.894736842105289</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>42.999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>35.999999999999922</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>28.837209302325505</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>29.545454545454572</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>26.842105263157862</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>24.000000000000131</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>23.571428571428555</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>37.60000000000008</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>31.53846153846148</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>28.076923076923084</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>23.599999999999955</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>21.176470588235247</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>23.137254901960741</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>30.769230769230795</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>30.188679245282938</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>29.166666666666696</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>20.416666666666732</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>18.000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>18.999999999999851</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Summer '!$I$2:$I$87</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="86"/>
+                <c:pt idx="0">
+                  <c:v>51.659921769552554</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50.228119059076278</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14.502380030123016</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.68107543204323</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.4107928979951785</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.8049034388889487</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11.105057316639133</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>29.712120711541949</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>41.279350758196514</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.5240654624066199</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.5386440491243301</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.7074800685992573</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6.7843516799317234</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.7154758689570473</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.1903043978196211</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.4588115887677189</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.0882180227795768</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.1493521090486243</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.1601520222996071</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.5244913860512195</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.7083325626172676</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3.0587693766699737</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5.365091662580971</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5.1217720387423311</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.2666249098999622</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.9722023113621858</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.5392300064882425</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.5186721608603606</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.6114551232671432</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.7405149401873126</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.4926887941071181</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>29.943162613702402</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>9.5728041053928887</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>6.9336039123826678</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>7.4831808175628005</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>5.9264264545775553</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>8.2845715359535532</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>10.349461276137333</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>13.904536257107111</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>11.14636239930711</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>7.4518284032226658</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>7.5006815567144436</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>5.9197242463532636</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2.9482215924738182</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>4.2750517220431998</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>7.7777750198526157</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>4.5347124072625604</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>5.8892721735776004</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>4.8035399241483203</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2.9207235211948697</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>5.5554803410250004</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5.0814144091067215</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>4.7820987112927114</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>4.036574818279635</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5.1612909035896664</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>5.1244036630343253</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>3.2424658067957601</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>12.669565136980157</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>6.2713144462450501</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>5.6727429240268501</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>4.6491381895576511</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>5.4238349889706816</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>4.495745790718118</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>5.33941789117765</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>4.6129800011302597</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>4.3837682724738745</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>4.11019377056025</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>3.7641164783656667</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>5.1367506964227401</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>4.1936586314366027</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>4.1850851238478963</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>2.9662137312752392</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>4.7449365167919124</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7BDC-40B6-A929-02CCBE2717FF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="734722767"/>
+        <c:axId val="734720847"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="734722767"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>SSC</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> (from filters (mg/L)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="734720847"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="734720847"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>POC (mg/L)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="734722767"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>SSC vs DOC</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Summer '!$F$2:$F$87</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="86"/>
+                <c:pt idx="0">
+                  <c:v>562.3258328827518</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>528.03483941208492</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>143.16904685207069</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>82.761404925313002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>36.920031971986397</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>22.011886418665991</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>68.980963045912645</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>124.47532204371103</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>359.22024838861807</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>86.111374932725383</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>37.228078044404583</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>30.434986187198604</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>57.726093867648203</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>48.064760941057514</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>55.003694277973992</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45.164039198977413</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17.425939756036765</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>11.446324912108677</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6.5306122448979194</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.4796065462560257</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>10.743801652892525</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>19.837989750371843</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>49.091801669121296</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>35.385121790651731</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>23.681202025150956</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>9.8887515451172572</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7.9500000000000943</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>4.080633314290381</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.6455487905216861</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.84473728670397652</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>5.7194215213659483</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>187.00000000000023</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>109.9999999999999</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>53.333333333333321</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>80.000000000000071</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>43.333333333333179</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>92.222222222222243</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>52.222222222222328</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>99.999999999999773</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>105.55555555555566</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>50.000000000000043</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>68.888888888888701</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>51.111111111111029</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>45.263157894736821</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>20.00000000000011</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>15.454545454545519</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>26.000000000000188</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>21.000000000000185</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>76.153846153846203</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>41.200000000000017</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>39.60000000000008</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>27.600000000000069</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>20.833333333333353</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>43.200000000000017</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>29.230769230769212</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>25.000000000000021</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>23.749999999999932</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>22.222222222222243</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>22.222222222222243</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>21.90476190476187</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>17.999999999999961</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>20.499999999999964</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>12.558139534883757</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>18.000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>20.000000000000018</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>16.666666666666682</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>77.894736842105289</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>42.999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>35.999999999999922</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>28.837209302325505</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>29.545454545454572</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>26.842105263157862</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>24.000000000000131</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>23.571428571428555</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>37.60000000000008</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>31.53846153846148</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>28.076923076923084</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>23.599999999999955</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>21.176470588235247</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>23.137254901960741</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>30.769230769230795</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>30.188679245282938</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>29.166666666666696</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>20.416666666666732</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>18.000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>18.999999999999851</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Summer '!$J$2:$J$87</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="86"/>
+                <c:pt idx="0">
+                  <c:v>9.1790000000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12.625</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13.388</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12.997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12.868</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>11.551</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.5220000000000002</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.4359999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>12.442</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>12.977</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>13.108000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12.073</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="0.000">
+                  <c:v>4.9130000000000003</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0.000">
+                  <c:v>6.55</c:v>
+                </c:pt>
+                <c:pt idx="14" formatCode="0.000">
+                  <c:v>8.0350000000000001</c:v>
+                </c:pt>
+                <c:pt idx="15" formatCode="0.000">
+                  <c:v>8.6910000000000007</c:v>
+                </c:pt>
+                <c:pt idx="16" formatCode="0.000">
+                  <c:v>8.1240000000000006</c:v>
+                </c:pt>
+                <c:pt idx="17" formatCode="0.000">
+                  <c:v>8.0730000000000004</c:v>
+                </c:pt>
+                <c:pt idx="18" formatCode="0.000">
+                  <c:v>3.1280000000000001</c:v>
+                </c:pt>
+                <c:pt idx="19" formatCode="0.000">
+                  <c:v>3.359</c:v>
+                </c:pt>
+                <c:pt idx="20" formatCode="0.000">
+                  <c:v>3.4239999999999999</c:v>
+                </c:pt>
+                <c:pt idx="21" formatCode="0.000">
+                  <c:v>3.9</c:v>
+                </c:pt>
+                <c:pt idx="22" formatCode="0.000">
+                  <c:v>5.2789999999999999</c:v>
+                </c:pt>
+                <c:pt idx="23" formatCode="0.000">
+                  <c:v>7.2069999999999999</c:v>
+                </c:pt>
+                <c:pt idx="24" formatCode="0.000">
+                  <c:v>7.75</c:v>
+                </c:pt>
+                <c:pt idx="25" formatCode="0.000">
+                  <c:v>8.41</c:v>
+                </c:pt>
+                <c:pt idx="26" formatCode="0.000">
+                  <c:v>2.7050000000000001</c:v>
+                </c:pt>
+                <c:pt idx="27" formatCode="0.000">
+                  <c:v>8.4209999999999994</c:v>
+                </c:pt>
+                <c:pt idx="28" formatCode="0.000">
+                  <c:v>8.1829999999999998</c:v>
+                </c:pt>
+                <c:pt idx="29" formatCode="0.000">
+                  <c:v>2.742</c:v>
+                </c:pt>
+                <c:pt idx="30" formatCode="0.000">
+                  <c:v>8.0850000000000009</c:v>
+                </c:pt>
+                <c:pt idx="31" formatCode="General">
+                  <c:v>2.7629999999999999</c:v>
+                </c:pt>
+                <c:pt idx="32" formatCode="General">
+                  <c:v>3.1280000000000001</c:v>
+                </c:pt>
+                <c:pt idx="33" formatCode="General">
+                  <c:v>3.5529999999999999</c:v>
+                </c:pt>
+                <c:pt idx="34" formatCode="General">
+                  <c:v>3.9260000000000002</c:v>
+                </c:pt>
+                <c:pt idx="35" formatCode="General">
+                  <c:v>4.1580000000000004</c:v>
+                </c:pt>
+                <c:pt idx="36" formatCode="General">
+                  <c:v>4.5709999999999997</c:v>
+                </c:pt>
+                <c:pt idx="37" formatCode="General">
+                  <c:v>5.15</c:v>
+                </c:pt>
+                <c:pt idx="38" formatCode="General">
+                  <c:v>8.5760000000000005</c:v>
+                </c:pt>
+                <c:pt idx="39" formatCode="General">
+                  <c:v>4.0309999999999997</c:v>
+                </c:pt>
+                <c:pt idx="40" formatCode="General">
+                  <c:v>4.1859999999999999</c:v>
+                </c:pt>
+                <c:pt idx="41" formatCode="General">
+                  <c:v>4.351</c:v>
+                </c:pt>
+                <c:pt idx="42" formatCode="General">
+                  <c:v>4.3109999999999999</c:v>
+                </c:pt>
+                <c:pt idx="43" formatCode="General">
+                  <c:v>4.4720000000000004</c:v>
+                </c:pt>
+                <c:pt idx="44" formatCode="General">
+                  <c:v>4.6630000000000003</c:v>
+                </c:pt>
+                <c:pt idx="45" formatCode="General">
+                  <c:v>4.9740000000000002</c:v>
+                </c:pt>
+                <c:pt idx="46" formatCode="General">
+                  <c:v>4.9390000000000001</c:v>
+                </c:pt>
+                <c:pt idx="47" formatCode="General">
+                  <c:v>5.2530000000000001</c:v>
+                </c:pt>
+                <c:pt idx="48" formatCode="General">
+                  <c:v>4.4729999999999999</c:v>
+                </c:pt>
+                <c:pt idx="49" formatCode="General">
+                  <c:v>3.9359999999999999</c:v>
+                </c:pt>
+                <c:pt idx="50" formatCode="General">
+                  <c:v>3.9430000000000001</c:v>
+                </c:pt>
+                <c:pt idx="51" formatCode="General">
+                  <c:v>4.0389999999999997</c:v>
+                </c:pt>
+                <c:pt idx="52" formatCode="General">
+                  <c:v>2.786</c:v>
+                </c:pt>
+                <c:pt idx="53" formatCode="General">
+                  <c:v>9.9</c:v>
+                </c:pt>
+                <c:pt idx="54" formatCode="General">
+                  <c:v>3.379</c:v>
+                </c:pt>
+                <c:pt idx="55" formatCode="General">
+                  <c:v>3.1909999999999998</c:v>
+                </c:pt>
+                <c:pt idx="56" formatCode="General">
+                  <c:v>3.1280000000000001</c:v>
+                </c:pt>
+                <c:pt idx="57" formatCode="General">
+                  <c:v>3.3319999999999999</c:v>
+                </c:pt>
+                <c:pt idx="58" formatCode="General">
+                  <c:v>3.1309999999999998</c:v>
+                </c:pt>
+                <c:pt idx="59" formatCode="General">
+                  <c:v>3.286</c:v>
+                </c:pt>
+                <c:pt idx="60" formatCode="General">
+                  <c:v>2.9169999999999998</c:v>
+                </c:pt>
+                <c:pt idx="61" formatCode="General">
+                  <c:v>2.548</c:v>
+                </c:pt>
+                <c:pt idx="62" formatCode="General">
+                  <c:v>2.5049999999999999</c:v>
+                </c:pt>
+                <c:pt idx="63" formatCode="General">
+                  <c:v>2.508</c:v>
+                </c:pt>
+                <c:pt idx="64" formatCode="General">
+                  <c:v>2.4820000000000002</c:v>
+                </c:pt>
+                <c:pt idx="65" formatCode="General">
+                  <c:v>3.1379999999999999</c:v>
+                </c:pt>
+                <c:pt idx="66" formatCode="General">
+                  <c:v>3.1040000000000001</c:v>
+                </c:pt>
+                <c:pt idx="67" formatCode="General">
+                  <c:v>3.3050000000000002</c:v>
+                </c:pt>
+                <c:pt idx="68" formatCode="General">
+                  <c:v>3.3359999999999999</c:v>
+                </c:pt>
+                <c:pt idx="69" formatCode="General">
+                  <c:v>3.1989999999999998</c:v>
+                </c:pt>
+                <c:pt idx="70" formatCode="General">
+                  <c:v>3.226</c:v>
+                </c:pt>
+                <c:pt idx="71" formatCode="General">
+                  <c:v>3.206</c:v>
+                </c:pt>
+                <c:pt idx="72" formatCode="General">
+                  <c:v>3.262</c:v>
+                </c:pt>
+                <c:pt idx="73" formatCode="General">
+                  <c:v>4.2779999999999996</c:v>
+                </c:pt>
+                <c:pt idx="74" formatCode="General">
+                  <c:v>5.4009999999999998</c:v>
+                </c:pt>
+                <c:pt idx="75" formatCode="General">
+                  <c:v>4.8639999999999999</c:v>
+                </c:pt>
+                <c:pt idx="76" formatCode="General">
+                  <c:v>4.6319999999999997</c:v>
+                </c:pt>
+                <c:pt idx="77" formatCode="General">
+                  <c:v>4.1559999999999997</c:v>
+                </c:pt>
+                <c:pt idx="78" formatCode="General">
+                  <c:v>3.2890000000000001</c:v>
+                </c:pt>
+                <c:pt idx="79" formatCode="General">
+                  <c:v>8.7289999999999992</c:v>
+                </c:pt>
+                <c:pt idx="80" formatCode="General">
+                  <c:v>8.7050000000000001</c:v>
+                </c:pt>
+                <c:pt idx="81" formatCode="General">
+                  <c:v>3.1509999999999998</c:v>
+                </c:pt>
+                <c:pt idx="82" formatCode="General">
+                  <c:v>2.3119999999999998</c:v>
+                </c:pt>
+                <c:pt idx="83" formatCode="General">
+                  <c:v>0.74299999999999999</c:v>
+                </c:pt>
+                <c:pt idx="85" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B8FE-4DAA-A25F-A72323504F1C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="734722767"/>
+        <c:axId val="734720847"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="734722767"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>SSC</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> (from filters (mg/L)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="734720847"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="734720847"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>POC (mg/L)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="734722767"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -3952,7 +7348,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4744,7 +8140,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -5959,16 +9355,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="86"/>
                 <c:pt idx="12" formatCode="0.00000">
-                  <c:v>5.0931725250657894E-2</c:v>
+                  <c:v>1.3945106373630132</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="0.00000">
-                  <c:v>8.3630032185714284E-2</c:v>
+                  <c:v>2.2897902812448567</c:v>
                 </c:pt>
                 <c:pt idx="72" formatCode="0.00000">
-                  <c:v>0.11521676096666668</c:v>
+                  <c:v>3.1546349152673332</c:v>
                 </c:pt>
                 <c:pt idx="74" formatCode="0.00000">
-                  <c:v>8.1488476728124995E-2</c:v>
+                  <c:v>2.2311544928160623</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9493,7 +12889,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>SSC vs LISST</a:t>
+              <a:t>Downstream</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -9569,365 +12965,292 @@
               <a:effectLst/>
             </c:spPr>
             <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
           </c:trendline>
           <c:xVal>
-            <c:numRef>
-              <c:f>'Summer '!$F$2:$F$87</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="86"/>
+            <c:strRef>
+              <c:f>Spring!$F$12:$F$83</c:f>
+              <c:strCache>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
-                  <c:v>562.3258328827518</c:v>
+                  <c:v>23.16</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>528.03483941208492</c:v>
+                  <c:v>15.00</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>143.16904685207069</c:v>
+                  <c:v>8.95</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>82.761404925313002</c:v>
+                  <c:v>9.50</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>36.920031971986397</c:v>
+                  <c:v>4.29</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>22.011886418665991</c:v>
+                  <c:v>-</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>68.980963045912645</c:v>
+                  <c:v>23.00</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>124.47532204371103</c:v>
+                  <c:v>15.00</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>359.22024838861807</c:v>
+                  <c:v>9.09</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>86.111374932725383</c:v>
+                  <c:v>7.50</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>37.228078044404583</c:v>
+                  <c:v>4.38</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>30.434986187198604</c:v>
+                  <c:v>-</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>57.726093867648203</c:v>
+                  <c:v>5.62</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>48.064760941057514</c:v>
+                  <c:v>6.67</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>55.003694277973992</c:v>
+                  <c:v>-</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>45.164039198977413</c:v>
+                  <c:v>-</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>17.425939756036765</c:v>
+                  <c:v>-</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>11.446324912108677</c:v>
+                  <c:v>10.34</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>6.5306122448979194</c:v>
+                  <c:v>5.33</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>8.4796065462560257</c:v>
+                  <c:v>6.43</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>10.743801652892525</c:v>
+                  <c:v>6.43</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>19.837989750371843</c:v>
+                  <c:v>14.19</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>49.091801669121296</c:v>
+                  <c:v>14.74</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>35.385121790651731</c:v>
+                  <c:v>18.95</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>23.681202025150956</c:v>
+                  <c:v>26.09</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>9.8887515451172572</c:v>
+                  <c:v>7.27</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>7.9500000000000943</c:v>
+                  <c:v>-</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>4.080633314290381</c:v>
+                  <c:v>5.33</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.6455487905216861</c:v>
+                  <c:v>5.00</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.84473728670397652</c:v>
+                  <c:v>-</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>5.7194215213659483</c:v>
+                  <c:v>22.01</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>187.00000000000023</c:v>
+                  <c:v>12.14</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>109.9999999999999</c:v>
+                  <c:v>10.67</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>53.333333333333321</c:v>
+                  <c:v>5.29</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>80.000000000000071</c:v>
+                  <c:v>4.12</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>43.333333333333179</c:v>
+                  <c:v>8.13</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>92.222222222222243</c:v>
+                  <c:v>6.88</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>52.222222222222328</c:v>
+                  <c:v>4.83</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>99.999999999999773</c:v>
+                  <c:v>2.35</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>105.55555555555566</c:v>
+                  <c:v>5.33</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>50.000000000000043</c:v>
+                  <c:v>5.29</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>68.888888888888701</c:v>
+                  <c:v>3.23</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>51.111111111111029</c:v>
+                  <c:v>0.00</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>45.263157894736821</c:v>
+                  <c:v>3.33</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>20.00000000000011</c:v>
+                  <c:v>5.33</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>15.454545454545519</c:v>
+                  <c:v>12.67</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>26.000000000000188</c:v>
+                  <c:v>10.67</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>21.000000000000185</c:v>
+                  <c:v>7.86</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>76.153846153846203</c:v>
+                  <c:v>8.67</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>41.200000000000017</c:v>
+                  <c:v>9.38</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>39.60000000000008</c:v>
+                  <c:v>42.00</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>27.600000000000069</c:v>
+                  <c:v>17.42</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>20.833333333333353</c:v>
+                  <c:v>6.67</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>43.200000000000017</c:v>
+                  <c:v>2.50</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>29.230769230769212</c:v>
+                  <c:v>6.00</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>25.000000000000021</c:v>
+                  <c:v>22.14</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>23.749999999999932</c:v>
+                  <c:v>10.00</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>22.222222222222243</c:v>
+                  <c:v>6.43</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>22.222222222222243</c:v>
+                  <c:v>18.00</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>21.90476190476187</c:v>
+                  <c:v>9.33</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>17.999999999999961</c:v>
+                  <c:v>5.71</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>20.499999999999964</c:v>
+                  <c:v>2.86</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>12.558139534883757</c:v>
+                  <c:v>20.67</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>18.000000000000014</c:v>
+                  <c:v>-</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>20.000000000000018</c:v>
+                  <c:v>11.88</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>16.666666666666682</c:v>
+                  <c:v>-</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>77.894736842105289</c:v>
+                  <c:v>2.86</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>42.999999999999986</c:v>
+                  <c:v>-</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>35.999999999999922</c:v>
+                  <c:v>4.67</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>28.837209302325505</c:v>
+                  <c:v>8.75</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>29.545454545454572</c:v>
+                  <c:v>9.33</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>26.842105263157862</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>24.000000000000131</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>23.571428571428555</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>37.60000000000008</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>31.53846153846148</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>28.076923076923084</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>23.599999999999955</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>21.176470588235247</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>23.137254901960741</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>30.769230769230795</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>30.188679245282938</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>29.166666666666696</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>20.416666666666732</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>18.000000000000014</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>18.999999999999851</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>7.14</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Summer '!$G$2:$G$87</c:f>
+              <c:f>Spring!$G$12:$G$83</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="86"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
-                  <c:v>339.78248000000002</c:v>
+                  <c:v>106.21</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>457.12</c:v>
+                  <c:v>51.232999999999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>152.79</c:v>
+                  <c:v>59.16</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>168.45</c:v>
+                  <c:v>48.47</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>43.15</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>17.7</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>92.06</c:v>
+                  <c:v>78.709999999999994</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>95.69</c:v>
+                  <c:v>45.42</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>403.51499999999999</c:v>
+                  <c:v>74.75</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>124.04</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>65.3</c:v>
+                  <c:v>56.59</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>42.87</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>206.82</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>142.53</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>55.06</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>66.040000000000006</c:v>
+                  <c:v>27.23</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>39.15</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>23.32</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
@@ -9939,190 +13262,157 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>52.87</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>204.03</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>105.77</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>68.83</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>36.65</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>25.92</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>21.67</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>19.05</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>18.36</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
                 <c:pt idx="32">
-                  <c:v>271.06</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>249.50899999999999</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>244.85599999999999</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>233.25</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>124.5634</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>9.89</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>327.45299999999997</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>241.809</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>158.52500000000001</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>132.47200000000001</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>98.91</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>90.356999999999999</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>84.561999999999998</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>59.01</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>42.72</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>98.146000000000001</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>210.458</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>116.066</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>113.258</c:v>
+                  <c:v>63.56</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>81.150000000000006</c:v>
+                  <c:v>85.89</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>56.15</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>183.80799999999999</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>83.528000000000006</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>72.105000000000004</c:v>
+                  <c:v>50.13</c:v>
+                </c:pt>
+                <c:pt idx="55" formatCode="0.0000">
+                  <c:v>44.99</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>67.606999999999999</c:v>
+                  <c:v>35.729999999999997</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>70.3</c:v>
+                  <c:v>31.62</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>67.88</c:v>
+                  <c:v>25.42</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>84.66</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>67.569999999999993</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>54.936</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>75.337999999999994</c:v>
+                  <c:v>68.760000000000005</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>59.165999999999997</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>50.774000000000001</c:v>
+                  <c:v>50.92</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>232.05199999999999</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>143.89599999999999</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>104.006</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>88.144000000000005</c:v>
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="69" formatCode="0.0000">
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>92.256</c:v>
+                  <c:v>33.08</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>82.494</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>69.394999999999996</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>63.87</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>75.400000000000006</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>70.75</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>82.6</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>54.12</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>95.962999999999994</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>80.180000000000007</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>70.510000000000005</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>64.436999999999998</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>46.07</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>39.299999999999997</c:v>
+                  <c:v>77.489999999999995</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10130,7 +13420,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-27C1-4986-9C3E-74D8A497147B}"/>
+              <c16:uniqueId val="{00000001-38AC-4188-8457-8CB84F938DF0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10142,11 +13432,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="734722767"/>
-        <c:axId val="734720847"/>
+        <c:axId val="1387476335"/>
+        <c:axId val="1387477295"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="734722767"/>
+        <c:axId val="1387476335"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10187,13 +13477,8 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>SSC</a:t>
+                  <a:t>SSC (mg/L)</a:t>
                 </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:t> (from filters (mg/L)</a:t>
-                </a:r>
-                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -10226,7 +13511,6 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -10263,12 +13547,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="734720847"/>
+        <c:crossAx val="1387477295"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="734720847"/>
+        <c:axId val="1387477295"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10309,7 +13593,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>LISST concentration (uL/L)</a:t>
+                  <a:t>SSC (uL/L)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -10380,7 +13664,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="734722767"/>
+        <c:crossAx val="1387476335"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -10471,7 +13755,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>SSC vs POC</a:t>
+              <a:t>Upstream</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -10515,7 +13799,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
+            <a:ln w="38100" cap="rnd">
               <a:noFill/>
               <a:round/>
             </a:ln>
@@ -10547,530 +13831,502 @@
               <a:effectLst/>
             </c:spPr>
             <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
           </c:trendline>
           <c:xVal>
-            <c:numRef>
-              <c:f>'Summer '!$F$2:$F$87</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="86"/>
+            <c:strRef>
+              <c:f>Spring!$F$84:$F$167</c:f>
+              <c:strCache>
+                <c:ptCount val="84"/>
                 <c:pt idx="0">
-                  <c:v>562.3258328827518</c:v>
+                  <c:v>16.00</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>528.03483941208492</c:v>
+                  <c:v>0.50</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>143.16904685207069</c:v>
+                  <c:v>6.32</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>82.761404925313002</c:v>
+                  <c:v>-</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>36.920031971986397</c:v>
+                  <c:v>10.00</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>22.011886418665991</c:v>
+                  <c:v>6.82</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>68.980963045912645</c:v>
+                  <c:v>21.50</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>124.47532204371103</c:v>
+                  <c:v>11.05</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>359.22024838861807</c:v>
+                  <c:v>18.00</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>86.111374932725383</c:v>
+                  <c:v>6.50</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>37.228078044404583</c:v>
+                  <c:v>8.00</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>30.434986187198604</c:v>
+                  <c:v>12.00</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>57.726093867648203</c:v>
+                  <c:v>6.00</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>48.064760941057514</c:v>
+                  <c:v>8.89</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>55.003694277973992</c:v>
+                  <c:v>12.22</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>45.164039198977413</c:v>
+                  <c:v>6.88</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>17.425939756036765</c:v>
+                  <c:v>4.67</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>11.446324912108677</c:v>
+                  <c:v>5.33</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>6.5306122448979194</c:v>
+                  <c:v>6.00</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>8.4796065462560257</c:v>
+                  <c:v>17.86</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>10.743801652892525</c:v>
+                  <c:v>4.00</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>19.837989750371843</c:v>
+                  <c:v>6.67</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>49.091801669121296</c:v>
+                  <c:v>5.52</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>35.385121790651731</c:v>
+                  <c:v>5.33</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>23.681202025150956</c:v>
+                  <c:v>8.00</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>9.8887515451172572</c:v>
+                  <c:v>7.33</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>7.9500000000000943</c:v>
+                  <c:v>-</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>4.080633314290381</c:v>
+                  <c:v>11.25</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.6455487905216861</c:v>
+                  <c:v>5.16</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.84473728670397652</c:v>
+                  <c:v>8.67</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>5.7194215213659483</c:v>
+                  <c:v>8.57</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>187.00000000000023</c:v>
+                  <c:v>-</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>109.9999999999999</c:v>
+                  <c:v>15.00</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>53.333333333333321</c:v>
+                  <c:v>7.14</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>80.000000000000071</c:v>
+                  <c:v>4.12</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>43.333333333333179</c:v>
+                  <c:v>7.14</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>92.222222222222243</c:v>
+                  <c:v>-</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>52.222222222222328</c:v>
+                  <c:v>5.52</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>99.999999999999773</c:v>
+                  <c:v>11.33</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>105.55555555555566</c:v>
+                  <c:v>6.67</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>50.000000000000043</c:v>
+                  <c:v>5.29</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>68.888888888888701</c:v>
+                  <c:v>-</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>51.111111111111029</c:v>
+                  <c:v>7.50</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>45.263157894736821</c:v>
+                  <c:v>-</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>20.00000000000011</c:v>
+                  <c:v>8.12</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>15.454545454545519</c:v>
+                  <c:v>11.61</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>26.000000000000188</c:v>
+                  <c:v>8.12</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>21.000000000000185</c:v>
+                  <c:v>6.67</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>76.153846153846203</c:v>
+                  <c:v>3.75</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>41.200000000000017</c:v>
+                  <c:v>11.25</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>39.60000000000008</c:v>
+                  <c:v>4.67</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>27.600000000000069</c:v>
+                  <c:v>14.55</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>20.833333333333353</c:v>
+                  <c:v>9.29</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>43.200000000000017</c:v>
+                  <c:v>6.88</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>29.230769230769212</c:v>
+                  <c:v>2.50</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>25.000000000000021</c:v>
+                  <c:v>12.67</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>23.749999999999932</c:v>
+                  <c:v>45.00</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>22.222222222222243</c:v>
+                  <c:v>14.00</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>22.222222222222243</c:v>
+                  <c:v>10.00</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>21.90476190476187</c:v>
+                  <c:v>8.12</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>17.999999999999961</c:v>
+                  <c:v>13.53</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>20.499999999999964</c:v>
+                  <c:v>20.00</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>12.558139534883757</c:v>
+                  <c:v>10.00</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>18.000000000000014</c:v>
+                  <c:v>0.63</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>20.000000000000018</c:v>
+                  <c:v>4.38</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>16.666666666666682</c:v>
+                  <c:v>3.33</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>77.894736842105289</c:v>
+                  <c:v>5.00</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>42.999999999999986</c:v>
+                  <c:v>10.67</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>35.999999999999922</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>28.837209302325505</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>29.545454545454572</c:v>
+                  <c:v>24.37</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>26.842105263157862</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>24.000000000000131</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>23.571428571428555</c:v>
+                  <c:v>5.62</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>37.60000000000008</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>31.53846153846148</c:v>
+                  <c:v>1.29</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>28.076923076923084</c:v>
+                  <c:v>0.71</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>23.599999999999955</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>21.176470588235247</c:v>
+                  <c:v>5.71</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>23.137254901960741</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>30.769230769230795</c:v>
+                  <c:v>2.14</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>30.188679245282938</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>29.166666666666696</c:v>
+                  <c:v>0.67</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>20.416666666666732</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>18.000000000000014</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>18.999999999999851</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>-</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Summer '!$I$2:$I$87</c:f>
+              <c:f>Spring!$G$84:$G$167</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="86"/>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="84"/>
                 <c:pt idx="0">
-                  <c:v>51.659921769552554</c:v>
+                  <c:v>103.31</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>50.228119059076278</c:v>
+                  <c:v>65.48</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14.502380030123016</c:v>
+                  <c:v>73.680000000000007</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.68107543204323</c:v>
+                  <c:v>48.9</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.4107928979951785</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.8049034388889487</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>11.105057316639133</c:v>
+                  <c:v>93.48</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>29.712120711541949</c:v>
+                  <c:v>53.79</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>41.279350758196514</c:v>
+                  <c:v>47.58</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>9.5240654624066199</c:v>
+                  <c:v>30.72</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6.5386440491243301</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5.7074800685992573</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>6.7843516799317234</c:v>
+                  <c:v>22.36</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5.7154758689570473</c:v>
+                  <c:v>30.83</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>5.1903043978196211</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>5.4588115887677189</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2.0882180227795768</c:v>
+                  <c:v>24.91</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3.1493521090486243</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2.1601520222996071</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.5244913860512195</c:v>
+                  <c:v>67.13</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.7083325626172676</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>3.0587693766699737</c:v>
+                  <c:v>51.68</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>5.365091662580971</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>5.1217720387423311</c:v>
+                  <c:v>57.56</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2.2666249098999622</c:v>
+                  <c:v>63.54</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.9722023113621858</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.5392300064882425</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.5186721608603606</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.6114551232671432</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.7405149401873126</c:v>
+                  <c:v>66.59</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.4926887941071181</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>29.943162613702402</c:v>
+                  <c:v>46.75</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>9.5728041053928887</c:v>
+                  <c:v>27.12</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>6.9336039123826678</c:v>
+                  <c:v>14.59</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>7.4831808175628005</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>5.9264264545775553</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>8.2845715359535532</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>10.349461276137333</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>13.904536257107111</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>11.14636239930711</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>7.4518284032226658</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>7.5006815567144436</c:v>
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>5.9197242463532636</c:v>
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>2.9482215924738182</c:v>
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>4.2750517220431998</c:v>
+                  <c:v>56.02</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>7.7777750198526157</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>4.5347124072625604</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>5.8892721735776004</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>4.8035399241483203</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>2.9207235211948697</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>5.5554803410250004</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>5.0814144091067215</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>4.7820987112927114</c:v>
+                  <c:v>43.66</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>4.036574818279635</c:v>
+                  <c:v>85.5</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>5.1612909035896664</c:v>
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>5.1244036630343253</c:v>
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>64.14</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>3.2424658067957601</c:v>
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>12.669565136980157</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>6.2713144462450501</c:v>
+                  <c:v>39.619999999999997</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>5.6727429240268501</c:v>
+                  <c:v>87.1</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>4.6491381895576511</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>5.4238349889706816</c:v>
+                  <c:v>26.28</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>4.495745790718118</c:v>
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>35.26</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>5.33941789117765</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>4.6129800011302597</c:v>
+                  <c:v>72.78</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>4.3837682724738745</c:v>
+                  <c:v>25.16</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>4.11019377056025</c:v>
+                  <c:v>15.19</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>99.54</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>3.7641164783656667</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>5.1367506964227401</c:v>
+                  <c:v>40.119999999999997</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>4.1936586314366027</c:v>
+                  <c:v>25.61</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>4.1850851238478963</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>2.9662137312752392</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>4.7449365167919124</c:v>
+                  <c:v>30.82</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11078,7 +14334,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-7BDC-40B6-A929-02CCBE2717FF}"/>
+              <c16:uniqueId val="{00000001-E7BB-4EBE-83C2-3B674EAB830C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11090,11 +14346,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="734722767"/>
-        <c:axId val="734720847"/>
+        <c:axId val="1387476335"/>
+        <c:axId val="1387477295"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="734722767"/>
+        <c:axId val="1387476335"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11135,13 +14391,8 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>SSC</a:t>
+                  <a:t>SSC (mg/L)</a:t>
                 </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:t> (from filters (mg/L)</a:t>
-                </a:r>
-                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -11174,7 +14425,6 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -11211,12 +14461,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="734720847"/>
+        <c:crossAx val="1387477295"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="734720847"/>
+        <c:axId val="1387477295"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11257,7 +14507,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>POC (mg/L)</a:t>
+                  <a:t>SSC (uL/L)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -11291,7 +14541,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -11328,7 +14578,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="734722767"/>
+        <c:crossAx val="1387476335"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -11419,8 +14669,13 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>SSC vs DOC</a:t>
+              <a:t>SSC</a:t>
             </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> (mg/L vs uL/L) - No zeros</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -11463,7 +14718,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
+            <a:ln w="38100" cap="rnd">
               <a:noFill/>
               <a:round/>
             </a:ln>
@@ -11498,6 +14753,12 @@
             <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-1.202755905511811E-2"/>
+                  <c:y val="-5.8901283172936719E-2"/>
+                </c:manualLayout>
+              </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
               <c:spPr>
                 <a:noFill/>
@@ -11530,531 +14791,288 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'Summer '!$F$2:$F$87</c:f>
+              <c:f>Spring!$AI$1:$AI$45</c:f>
               <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="86"/>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
-                  <c:v>562.3258328827518</c:v>
+                  <c:v>23.157894736842042</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>528.03483941208492</c:v>
+                  <c:v>15.000000000000014</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>143.16904685207069</c:v>
+                  <c:v>8.9473684210526692</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>82.761404925313002</c:v>
+                  <c:v>9.4999999999999254</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>36.920031971986397</c:v>
+                  <c:v>23.000000000000103</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>22.011886418665991</c:v>
+                  <c:v>15.000000000000014</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>68.980963045912645</c:v>
+                  <c:v>9.0909090909090988</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>124.47532204371103</c:v>
+                  <c:v>4.3750000000000382</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>359.22024838861807</c:v>
+                  <c:v>41.999999999999993</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>86.111374932725383</c:v>
+                  <c:v>17.419354838709729</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>37.228078044404583</c:v>
+                  <c:v>6.000000000000079</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>30.434986187198604</c:v>
+                  <c:v>22.142857142857082</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>57.726093867648203</c:v>
+                  <c:v>10.000000000000009</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>48.064760941057514</c:v>
+                  <c:v>6.4285714285713151</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>55.003694277973992</c:v>
+                  <c:v>18.000000000000053</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>45.164039198977413</c:v>
+                  <c:v>20.666666666666611</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>17.425939756036765</c:v>
+                  <c:v>11.87500000000008</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>11.446324912108677</c:v>
+                  <c:v>9.3333333333334156</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>6.5306122448979194</c:v>
+                  <c:v>7.1428571428571495</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>8.4796065462560257</c:v>
+                  <c:v>16.000000000000043</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>10.743801652892525</c:v>
+                  <c:v>0.49999999999994493</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>19.837989750371843</c:v>
+                  <c:v>6.3157894736842453</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>49.091801669121296</c:v>
+                  <c:v>21.499999999999993</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>35.385121790651731</c:v>
+                  <c:v>11.05263157894732</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>23.681202025150956</c:v>
+                  <c:v>17.999999999999961</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>9.8887515451172572</c:v>
+                  <c:v>6.4999999999999778</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>7.9500000000000943</c:v>
+                  <c:v>5.9999999999998943</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>4.080633314290381</c:v>
+                  <c:v>8.888888888888836</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.6455487905216861</c:v>
+                  <c:v>4.6666666666667078</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.84473728670397652</c:v>
+                  <c:v>17.857142857142676</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>5.7194215213659483</c:v>
+                  <c:v>6.6666666666666723</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>187.00000000000023</c:v>
+                  <c:v>5.3333333333334858</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>109.9999999999999</c:v>
+                  <c:v>8.0000000000000444</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>53.333333333333321</c:v>
+                  <c:v>8.6666666666666377</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>80.000000000000071</c:v>
+                  <c:v>15.000000000000083</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>43.333333333333179</c:v>
+                  <c:v>7.1428571428571495</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>92.222222222222243</c:v>
+                  <c:v>6.6666666666666723</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>52.222222222222328</c:v>
+                  <c:v>12.666666666666751</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>99.999999999999773</c:v>
+                  <c:v>45.000000000000007</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>105.55555555555566</c:v>
+                  <c:v>20.000000000000018</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>50.000000000000043</c:v>
+                  <c:v>10.666666666666602</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>68.888888888888701</c:v>
+                  <c:v>24.374999999999918</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>51.111111111111029</c:v>
+                  <c:v>0.71428571428583387</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>45.263157894736821</c:v>
+                  <c:v>5.7142857142856798</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>20.00000000000011</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>15.454545454545519</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>26.000000000000188</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>21.000000000000185</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>76.153846153846203</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>41.200000000000017</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>39.60000000000008</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>27.600000000000069</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>20.833333333333353</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>43.200000000000017</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>29.230769230769212</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>25.000000000000021</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>23.749999999999932</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>22.222222222222243</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>22.222222222222243</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>21.90476190476187</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>17.999999999999961</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>20.499999999999964</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>12.558139534883757</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>18.000000000000014</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>20.000000000000018</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>16.666666666666682</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>77.894736842105289</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>42.999999999999986</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>35.999999999999922</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>28.837209302325505</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>29.545454545454572</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>26.842105263157862</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>24.000000000000131</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>23.571428571428555</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>37.60000000000008</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>31.53846153846148</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>28.076923076923084</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>23.599999999999955</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>21.176470588235247</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>23.137254901960741</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>30.769230769230795</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>30.188679245282938</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>29.166666666666696</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>20.416666666666732</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>18.000000000000014</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>18.999999999999851</c:v>
+                  <c:v>0.66666666666677832</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Summer '!$J$2:$J$87</c:f>
+              <c:f>Spring!$AJ$1:$AJ$45</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="86"/>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
-                  <c:v>9.1790000000000003</c:v>
+                  <c:v>106.21</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12.625</c:v>
+                  <c:v>51.232999999999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>13.388</c:v>
+                  <c:v>59.16</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12.997</c:v>
+                  <c:v>48.47</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>12.868</c:v>
+                  <c:v>78.709999999999994</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>11.551</c:v>
+                  <c:v>45.42</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.5220000000000002</c:v>
+                  <c:v>74.75</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.4359999999999999</c:v>
+                  <c:v>56.59</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>12.442</c:v>
+                  <c:v>63.56</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>12.977</c:v>
+                  <c:v>85.89</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>13.108000000000001</c:v>
+                  <c:v>50.13</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12.073</c:v>
-                </c:pt>
-                <c:pt idx="12" formatCode="0.000">
-                  <c:v>4.9130000000000003</c:v>
-                </c:pt>
-                <c:pt idx="13" formatCode="0.000">
-                  <c:v>6.55</c:v>
-                </c:pt>
-                <c:pt idx="14" formatCode="0.000">
-                  <c:v>8.0350000000000001</c:v>
-                </c:pt>
-                <c:pt idx="15" formatCode="0.000">
-                  <c:v>8.6910000000000007</c:v>
-                </c:pt>
-                <c:pt idx="16" formatCode="0.000">
-                  <c:v>8.1240000000000006</c:v>
-                </c:pt>
-                <c:pt idx="17" formatCode="0.000">
-                  <c:v>8.0730000000000004</c:v>
-                </c:pt>
-                <c:pt idx="18" formatCode="0.000">
-                  <c:v>3.1280000000000001</c:v>
-                </c:pt>
-                <c:pt idx="19" formatCode="0.000">
-                  <c:v>3.359</c:v>
-                </c:pt>
-                <c:pt idx="20" formatCode="0.000">
-                  <c:v>3.4239999999999999</c:v>
-                </c:pt>
-                <c:pt idx="21" formatCode="0.000">
-                  <c:v>3.9</c:v>
-                </c:pt>
-                <c:pt idx="22" formatCode="0.000">
-                  <c:v>5.2789999999999999</c:v>
-                </c:pt>
-                <c:pt idx="23" formatCode="0.000">
-                  <c:v>7.2069999999999999</c:v>
-                </c:pt>
-                <c:pt idx="24" formatCode="0.000">
-                  <c:v>7.75</c:v>
-                </c:pt>
-                <c:pt idx="25" formatCode="0.000">
-                  <c:v>8.41</c:v>
-                </c:pt>
-                <c:pt idx="26" formatCode="0.000">
-                  <c:v>2.7050000000000001</c:v>
-                </c:pt>
-                <c:pt idx="27" formatCode="0.000">
-                  <c:v>8.4209999999999994</c:v>
-                </c:pt>
-                <c:pt idx="28" formatCode="0.000">
-                  <c:v>8.1829999999999998</c:v>
-                </c:pt>
-                <c:pt idx="29" formatCode="0.000">
-                  <c:v>2.742</c:v>
-                </c:pt>
-                <c:pt idx="30" formatCode="0.000">
-                  <c:v>8.0850000000000009</c:v>
-                </c:pt>
-                <c:pt idx="31" formatCode="General">
-                  <c:v>2.7629999999999999</c:v>
-                </c:pt>
-                <c:pt idx="32" formatCode="General">
-                  <c:v>3.1280000000000001</c:v>
-                </c:pt>
-                <c:pt idx="33" formatCode="General">
-                  <c:v>3.5529999999999999</c:v>
-                </c:pt>
-                <c:pt idx="34" formatCode="General">
-                  <c:v>3.9260000000000002</c:v>
-                </c:pt>
-                <c:pt idx="35" formatCode="General">
-                  <c:v>4.1580000000000004</c:v>
-                </c:pt>
-                <c:pt idx="36" formatCode="General">
-                  <c:v>4.5709999999999997</c:v>
-                </c:pt>
-                <c:pt idx="37" formatCode="General">
-                  <c:v>5.15</c:v>
-                </c:pt>
-                <c:pt idx="38" formatCode="General">
-                  <c:v>8.5760000000000005</c:v>
-                </c:pt>
-                <c:pt idx="39" formatCode="General">
-                  <c:v>4.0309999999999997</c:v>
-                </c:pt>
-                <c:pt idx="40" formatCode="General">
-                  <c:v>4.1859999999999999</c:v>
-                </c:pt>
-                <c:pt idx="41" formatCode="General">
-                  <c:v>4.351</c:v>
-                </c:pt>
-                <c:pt idx="42" formatCode="General">
-                  <c:v>4.3109999999999999</c:v>
-                </c:pt>
-                <c:pt idx="43" formatCode="General">
-                  <c:v>4.4720000000000004</c:v>
-                </c:pt>
-                <c:pt idx="44" formatCode="General">
-                  <c:v>4.6630000000000003</c:v>
-                </c:pt>
-                <c:pt idx="45" formatCode="General">
-                  <c:v>4.9740000000000002</c:v>
-                </c:pt>
-                <c:pt idx="46" formatCode="General">
-                  <c:v>4.9390000000000001</c:v>
-                </c:pt>
-                <c:pt idx="47" formatCode="General">
-                  <c:v>5.2530000000000001</c:v>
-                </c:pt>
-                <c:pt idx="48" formatCode="General">
-                  <c:v>4.4729999999999999</c:v>
-                </c:pt>
-                <c:pt idx="49" formatCode="General">
-                  <c:v>3.9359999999999999</c:v>
-                </c:pt>
-                <c:pt idx="50" formatCode="General">
-                  <c:v>3.9430000000000001</c:v>
-                </c:pt>
-                <c:pt idx="51" formatCode="General">
-                  <c:v>4.0389999999999997</c:v>
-                </c:pt>
-                <c:pt idx="52" formatCode="General">
-                  <c:v>2.786</c:v>
-                </c:pt>
-                <c:pt idx="53" formatCode="General">
-                  <c:v>9.9</c:v>
-                </c:pt>
-                <c:pt idx="54" formatCode="General">
-                  <c:v>3.379</c:v>
-                </c:pt>
-                <c:pt idx="55" formatCode="General">
-                  <c:v>3.1909999999999998</c:v>
-                </c:pt>
-                <c:pt idx="56" formatCode="General">
-                  <c:v>3.1280000000000001</c:v>
-                </c:pt>
-                <c:pt idx="57" formatCode="General">
-                  <c:v>3.3319999999999999</c:v>
-                </c:pt>
-                <c:pt idx="58" formatCode="General">
-                  <c:v>3.1309999999999998</c:v>
-                </c:pt>
-                <c:pt idx="59" formatCode="General">
-                  <c:v>3.286</c:v>
-                </c:pt>
-                <c:pt idx="60" formatCode="General">
-                  <c:v>2.9169999999999998</c:v>
-                </c:pt>
-                <c:pt idx="61" formatCode="General">
-                  <c:v>2.548</c:v>
-                </c:pt>
-                <c:pt idx="62" formatCode="General">
-                  <c:v>2.5049999999999999</c:v>
-                </c:pt>
-                <c:pt idx="63" formatCode="General">
-                  <c:v>2.508</c:v>
-                </c:pt>
-                <c:pt idx="64" formatCode="General">
-                  <c:v>2.4820000000000002</c:v>
-                </c:pt>
-                <c:pt idx="65" formatCode="General">
-                  <c:v>3.1379999999999999</c:v>
-                </c:pt>
-                <c:pt idx="66" formatCode="General">
-                  <c:v>3.1040000000000001</c:v>
-                </c:pt>
-                <c:pt idx="67" formatCode="General">
-                  <c:v>3.3050000000000002</c:v>
-                </c:pt>
-                <c:pt idx="68" formatCode="General">
-                  <c:v>3.3359999999999999</c:v>
-                </c:pt>
-                <c:pt idx="69" formatCode="General">
-                  <c:v>3.1989999999999998</c:v>
-                </c:pt>
-                <c:pt idx="70" formatCode="General">
-                  <c:v>3.226</c:v>
-                </c:pt>
-                <c:pt idx="71" formatCode="General">
-                  <c:v>3.206</c:v>
-                </c:pt>
-                <c:pt idx="72" formatCode="General">
-                  <c:v>3.262</c:v>
-                </c:pt>
-                <c:pt idx="73" formatCode="General">
-                  <c:v>4.2779999999999996</c:v>
-                </c:pt>
-                <c:pt idx="74" formatCode="General">
-                  <c:v>5.4009999999999998</c:v>
-                </c:pt>
-                <c:pt idx="75" formatCode="General">
-                  <c:v>4.8639999999999999</c:v>
-                </c:pt>
-                <c:pt idx="76" formatCode="General">
-                  <c:v>4.6319999999999997</c:v>
-                </c:pt>
-                <c:pt idx="77" formatCode="General">
-                  <c:v>4.1559999999999997</c:v>
-                </c:pt>
-                <c:pt idx="78" formatCode="General">
-                  <c:v>3.2890000000000001</c:v>
-                </c:pt>
-                <c:pt idx="79" formatCode="General">
-                  <c:v>8.7289999999999992</c:v>
-                </c:pt>
-                <c:pt idx="80" formatCode="General">
-                  <c:v>8.7050000000000001</c:v>
-                </c:pt>
-                <c:pt idx="81" formatCode="General">
-                  <c:v>3.1509999999999998</c:v>
-                </c:pt>
-                <c:pt idx="82" formatCode="General">
-                  <c:v>2.3119999999999998</c:v>
-                </c:pt>
-                <c:pt idx="83" formatCode="General">
-                  <c:v>0.74299999999999999</c:v>
-                </c:pt>
-                <c:pt idx="85" formatCode="General">
-                  <c:v>0</c:v>
+                  <c:v>44.99</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>35.729999999999997</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>31.62</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>25.42</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>68.760000000000005</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>50.92</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>33.08</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>77.489999999999995</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>103.31</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>65.48</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>73.680000000000007</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>93.48</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>53.79</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>47.58</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>30.72</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>22.36</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>30.83</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>24.91</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>67.13</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>51.68</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>57.56</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>63.54</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>66.59</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>27.12</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>14.59</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>56.02</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>43.66</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>85.5</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>64.14</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>39.619999999999997</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>87.1</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>25.16</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>15.19</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>25.61</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12062,7 +15080,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-B8FE-4DAA-A25F-A72323504F1C}"/>
+              <c16:uniqueId val="{00000000-255F-4867-870A-984FAC909D51}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12074,11 +15092,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="734722767"/>
-        <c:axId val="734720847"/>
+        <c:axId val="1387530095"/>
+        <c:axId val="1387521935"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="734722767"/>
+        <c:axId val="1387530095"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12098,67 +15116,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>SSC</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:t> (from filters (mg/L)</a:t>
-                </a:r>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -12195,12 +15153,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="734720847"/>
+        <c:crossAx val="1387521935"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="734720847"/>
+        <c:axId val="1387521935"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12220,62 +15178,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>POC (mg/L)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -12312,7 +15215,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="734722767"/>
+        <c:crossAx val="1387530095"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -12489,6 +15392,126 @@
 </file>
 
 <file path=xl/charts/colors12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors14.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors15.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -14912,6 +17935,1554 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style15.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -19265,6 +23836,120 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>229517</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>165252</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>504939</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>89970</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Chart 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8907B7BF-D0C1-4170-B168-9BFD4F34CF1B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>174433</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>9180</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>449855</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>117513</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="10" name="Chart 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C55DF24-D1C6-402F-95E1-C60C6A2AE4EC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>422314</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>358048</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>146892</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>154236</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="12" name="Chart 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C01DEB5-CF62-44A7-A26C-F8DC929CECC3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -19821,7 +24506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E5F5147-870F-4065-86F1-3AC0DA635208}">
-  <dimension ref="A1:T167"/>
+  <dimension ref="A1:AJ167"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="5" customWidth="1"/>
@@ -19839,7 +24524,7 @@
     <col min="20" max="20" width="16.88671875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="144" t="s">
         <v>1</v>
       </c>
@@ -19885,8 +24570,17 @@
       <c r="T1" s="146" t="s">
         <v>119</v>
       </c>
+      <c r="AH1" t="s">
+        <v>192</v>
+      </c>
+      <c r="AI1">
+        <v>23.157894736842042</v>
+      </c>
+      <c r="AJ1">
+        <v>106.21</v>
+      </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" s="233" t="s">
         <v>182</v>
       </c>
@@ -19907,7 +24601,9 @@
         <f>E2/B2*1000*1000</f>
         <v>12.380952380952339</v>
       </c>
-      <c r="G2" s="2"/>
+      <c r="G2" s="149" t="s">
+        <v>179</v>
+      </c>
       <c r="H2" s="234"/>
       <c r="I2" s="31"/>
       <c r="J2" s="2">
@@ -19925,8 +24621,17 @@
       <c r="R2" s="232"/>
       <c r="S2" s="232"/>
       <c r="T2" s="232"/>
+      <c r="AH2" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI2">
+        <v>15.000000000000014</v>
+      </c>
+      <c r="AJ2">
+        <v>51.232999999999997</v>
+      </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A3" s="233" t="s">
         <v>183</v>
       </c>
@@ -19947,7 +24652,9 @@
         <f t="shared" ref="F3:F14" si="1">E3/B3*1000*1000</f>
         <v>9.4736842105262955</v>
       </c>
-      <c r="G3" s="2"/>
+      <c r="G3" s="149" t="s">
+        <v>179</v>
+      </c>
       <c r="H3" s="234"/>
       <c r="I3" s="31"/>
       <c r="J3" s="236">
@@ -19965,8 +24672,17 @@
       <c r="R3" s="232"/>
       <c r="S3" s="232"/>
       <c r="T3" s="232"/>
+      <c r="AH3" t="s">
+        <v>195</v>
+      </c>
+      <c r="AI3">
+        <v>8.9473684210526692</v>
+      </c>
+      <c r="AJ3">
+        <v>59.16</v>
+      </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A4" s="233" t="s">
         <v>184</v>
       </c>
@@ -19987,7 +24703,9 @@
         <f t="shared" si="1"/>
         <v>5.0000000000000044</v>
       </c>
-      <c r="G4" s="2"/>
+      <c r="G4" s="149" t="s">
+        <v>179</v>
+      </c>
       <c r="H4" s="234"/>
       <c r="I4" s="31"/>
       <c r="J4" s="236">
@@ -20003,8 +24721,17 @@
       <c r="R4" s="232"/>
       <c r="S4" s="232"/>
       <c r="T4" s="232"/>
+      <c r="AH4" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI4">
+        <v>9.4999999999999254</v>
+      </c>
+      <c r="AJ4">
+        <v>48.47</v>
+      </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A5" s="233" t="s">
         <v>185</v>
       </c>
@@ -20025,7 +24752,9 @@
         <f t="shared" si="1"/>
         <v>3.999999999999976</v>
       </c>
-      <c r="G5" s="2"/>
+      <c r="G5" s="149" t="s">
+        <v>179</v>
+      </c>
       <c r="H5" s="234"/>
       <c r="I5" s="31"/>
       <c r="J5" s="236">
@@ -20041,8 +24770,17 @@
       <c r="R5" s="232"/>
       <c r="S5" s="232"/>
       <c r="T5" s="232"/>
+      <c r="AH5" t="s">
+        <v>198</v>
+      </c>
+      <c r="AI5">
+        <v>23.000000000000103</v>
+      </c>
+      <c r="AJ5">
+        <v>78.709999999999994</v>
+      </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A6" s="233" t="s">
         <v>186</v>
       </c>
@@ -20063,7 +24801,9 @@
         <f t="shared" si="1"/>
         <v>10.476190476190512</v>
       </c>
-      <c r="G6" s="2"/>
+      <c r="G6" s="149" t="s">
+        <v>179</v>
+      </c>
       <c r="H6" s="234"/>
       <c r="I6" s="31"/>
       <c r="J6" s="236">
@@ -20079,8 +24819,17 @@
       <c r="R6" s="232"/>
       <c r="S6" s="232"/>
       <c r="T6" s="232"/>
+      <c r="AH6" t="s">
+        <v>199</v>
+      </c>
+      <c r="AI6">
+        <v>15.000000000000014</v>
+      </c>
+      <c r="AJ6">
+        <v>45.42</v>
+      </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A7" s="233" t="s">
         <v>187</v>
       </c>
@@ -20101,7 +24850,9 @@
         <f t="shared" si="1"/>
         <v>9.3333333333332309</v>
       </c>
-      <c r="G7" s="2"/>
+      <c r="G7" s="149" t="s">
+        <v>179</v>
+      </c>
       <c r="H7" s="234"/>
       <c r="I7" s="31"/>
       <c r="J7" s="236">
@@ -20117,8 +24868,17 @@
       <c r="R7" s="232"/>
       <c r="S7" s="232"/>
       <c r="T7" s="232"/>
+      <c r="AH7" t="s">
+        <v>200</v>
+      </c>
+      <c r="AI7">
+        <v>9.0909090909090988</v>
+      </c>
+      <c r="AJ7">
+        <v>74.75</v>
+      </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A8" s="233" t="s">
         <v>188</v>
       </c>
@@ -20139,7 +24899,9 @@
         <f t="shared" si="1"/>
         <v>9.6551724137929966</v>
       </c>
-      <c r="G8" s="2"/>
+      <c r="G8" s="149" t="s">
+        <v>179</v>
+      </c>
       <c r="H8" s="234"/>
       <c r="I8" s="31"/>
       <c r="J8" s="236">
@@ -20155,8 +24917,17 @@
       <c r="R8" s="232"/>
       <c r="S8" s="232"/>
       <c r="T8" s="232"/>
+      <c r="AH8" t="s">
+        <v>202</v>
+      </c>
+      <c r="AI8">
+        <v>4.3750000000000382</v>
+      </c>
+      <c r="AJ8">
+        <v>56.59</v>
+      </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" s="233" t="s">
         <v>189</v>
       </c>
@@ -20177,7 +24948,9 @@
         <f t="shared" si="1"/>
         <v>3.9999999999999298</v>
       </c>
-      <c r="G9" s="2"/>
+      <c r="G9" s="149" t="s">
+        <v>179</v>
+      </c>
       <c r="H9" s="234"/>
       <c r="I9" s="31"/>
       <c r="J9" s="236">
@@ -20192,8 +24965,17 @@
       <c r="R9" s="232"/>
       <c r="S9" s="232"/>
       <c r="T9" s="232"/>
+      <c r="AH9" t="s">
+        <v>242</v>
+      </c>
+      <c r="AI9">
+        <v>41.999999999999993</v>
+      </c>
+      <c r="AJ9">
+        <v>63.56</v>
+      </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A10" s="233" t="s">
         <v>190</v>
       </c>
@@ -20214,7 +24996,9 @@
         <f t="shared" si="1"/>
         <v>1.4999999999999736</v>
       </c>
-      <c r="G10" s="2"/>
+      <c r="G10" s="149" t="s">
+        <v>179</v>
+      </c>
       <c r="H10" s="234"/>
       <c r="I10" s="31"/>
       <c r="J10" s="236">
@@ -20229,8 +25013,17 @@
       <c r="R10" s="232"/>
       <c r="S10" s="232"/>
       <c r="T10" s="232"/>
+      <c r="AH10" t="s">
+        <v>243</v>
+      </c>
+      <c r="AI10">
+        <v>17.419354838709729</v>
+      </c>
+      <c r="AJ10">
+        <v>85.89</v>
+      </c>
     </row>
-    <row r="11" spans="1:20" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="233" t="s">
         <v>191</v>
       </c>
@@ -20251,7 +25044,9 @@
         <f t="shared" si="1"/>
         <v>5.5000000000000879</v>
       </c>
-      <c r="G11" s="2"/>
+      <c r="G11" s="149" t="s">
+        <v>179</v>
+      </c>
       <c r="H11" s="234"/>
       <c r="I11" s="31"/>
       <c r="J11" s="236">
@@ -20266,8 +25061,17 @@
       <c r="R11" s="232"/>
       <c r="S11" s="232"/>
       <c r="T11" s="232"/>
+      <c r="AH11" t="s">
+        <v>246</v>
+      </c>
+      <c r="AI11">
+        <v>6.000000000000079</v>
+      </c>
+      <c r="AJ11">
+        <v>50.13</v>
+      </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" s="233" t="s">
         <v>192</v>
       </c>
@@ -20305,8 +25109,17 @@
       <c r="R12" s="232"/>
       <c r="S12" s="232"/>
       <c r="T12" s="232"/>
+      <c r="AH12" t="s">
+        <v>247</v>
+      </c>
+      <c r="AI12">
+        <v>22.142857142857082</v>
+      </c>
+      <c r="AJ12">
+        <v>44.99</v>
+      </c>
     </row>
-    <row r="13" spans="1:20" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="233" t="s">
         <v>193</v>
       </c>
@@ -20344,8 +25157,17 @@
       <c r="R13" s="232"/>
       <c r="S13" s="232"/>
       <c r="T13" s="232"/>
+      <c r="AH13" t="s">
+        <v>248</v>
+      </c>
+      <c r="AI13">
+        <v>10.000000000000009</v>
+      </c>
+      <c r="AJ13">
+        <v>35.729999999999997</v>
+      </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A14" s="233" t="s">
         <v>195</v>
       </c>
@@ -20370,11 +25192,12 @@
         <v>59.16</v>
       </c>
       <c r="H14" s="30">
-        <v>9.6770277976250003E-3</v>
+        <f>0.009677027797625*27.38</f>
+        <v>0.26495702109897251</v>
       </c>
       <c r="I14" s="238">
-        <f>H14/(B14/1000)</f>
-        <v>5.0931725250657894E-2</v>
+        <f>H14/B14*1000</f>
+        <v>1.3945106373630132</v>
       </c>
       <c r="J14" s="236">
         <v>3.806</v>
@@ -20388,8 +25211,17 @@
       <c r="R14" s="232"/>
       <c r="S14" s="232"/>
       <c r="T14" s="232"/>
+      <c r="AH14" t="s">
+        <v>249</v>
+      </c>
+      <c r="AI14">
+        <v>6.4285714285713151</v>
+      </c>
+      <c r="AJ14">
+        <v>31.62</v>
+      </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" s="233" t="s">
         <v>194</v>
       </c>
@@ -20427,8 +25259,17 @@
       <c r="R15" s="232"/>
       <c r="S15" s="232"/>
       <c r="T15" s="232"/>
+      <c r="AH15" t="s">
+        <v>250</v>
+      </c>
+      <c r="AI15">
+        <v>18.000000000000053</v>
+      </c>
+      <c r="AJ15">
+        <v>25.42</v>
+      </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A16" s="233" t="s">
         <v>196</v>
       </c>
@@ -20467,8 +25308,17 @@
       <c r="R16" s="232"/>
       <c r="S16" s="232"/>
       <c r="T16" s="232"/>
+      <c r="AH16" t="s">
+        <v>254</v>
+      </c>
+      <c r="AI16">
+        <v>20.666666666666611</v>
+      </c>
+      <c r="AJ16">
+        <v>68.760000000000005</v>
+      </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A17" s="233" t="s">
         <v>197</v>
       </c>
@@ -20504,8 +25354,17 @@
       <c r="R17" s="232"/>
       <c r="S17" s="232"/>
       <c r="T17" s="232"/>
+      <c r="AH17" t="s">
+        <v>255</v>
+      </c>
+      <c r="AI17">
+        <v>11.87500000000008</v>
+      </c>
+      <c r="AJ17">
+        <v>50.92</v>
+      </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A18" s="233" t="s">
         <v>198</v>
       </c>
@@ -20543,8 +25402,17 @@
       <c r="R18" s="232"/>
       <c r="S18" s="232"/>
       <c r="T18" s="232"/>
+      <c r="AH18" t="s">
+        <v>259</v>
+      </c>
+      <c r="AI18">
+        <v>9.3333333333334156</v>
+      </c>
+      <c r="AJ18">
+        <v>33.08</v>
+      </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A19" s="233" t="s">
         <v>199</v>
       </c>
@@ -20584,8 +25452,17 @@
       <c r="R19" s="232"/>
       <c r="S19" s="232"/>
       <c r="T19" s="232"/>
+      <c r="AH19" t="s">
+        <v>260</v>
+      </c>
+      <c r="AI19">
+        <v>7.1428571428571495</v>
+      </c>
+      <c r="AJ19">
+        <v>77.489999999999995</v>
+      </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A20" s="233" t="s">
         <v>200</v>
       </c>
@@ -20623,8 +25500,17 @@
       <c r="R20" s="232"/>
       <c r="S20" s="232"/>
       <c r="T20" s="232"/>
+      <c r="AH20" t="s">
+        <v>261</v>
+      </c>
+      <c r="AI20">
+        <v>16.000000000000043</v>
+      </c>
+      <c r="AJ20">
+        <v>103.31</v>
+      </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A21" s="233" t="s">
         <v>201</v>
       </c>
@@ -20662,8 +25548,17 @@
       <c r="R21" s="232"/>
       <c r="S21" s="232"/>
       <c r="T21" s="232"/>
+      <c r="AH21" t="s">
+        <v>262</v>
+      </c>
+      <c r="AI21">
+        <v>0.49999999999994493</v>
+      </c>
+      <c r="AJ21">
+        <v>65.48</v>
+      </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A22" s="233" t="s">
         <v>202</v>
       </c>
@@ -20701,8 +25596,17 @@
       <c r="R22" s="232"/>
       <c r="S22" s="232"/>
       <c r="T22" s="232"/>
+      <c r="AH22" t="s">
+        <v>263</v>
+      </c>
+      <c r="AI22">
+        <v>6.3157894736842453</v>
+      </c>
+      <c r="AJ22">
+        <v>73.680000000000007</v>
+      </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A23" s="233" t="s">
         <v>203</v>
       </c>
@@ -20738,8 +25642,17 @@
       <c r="R23" s="232"/>
       <c r="S23" s="232"/>
       <c r="T23" s="232"/>
+      <c r="AH23" t="s">
+        <v>267</v>
+      </c>
+      <c r="AI23">
+        <v>21.499999999999993</v>
+      </c>
+      <c r="AJ23">
+        <v>93.48</v>
+      </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A24" s="233" t="s">
         <v>204</v>
       </c>
@@ -20777,8 +25690,17 @@
       <c r="R24" s="232"/>
       <c r="S24" s="232"/>
       <c r="T24" s="232"/>
+      <c r="AH24" t="s">
+        <v>268</v>
+      </c>
+      <c r="AI24">
+        <v>11.05263157894732</v>
+      </c>
+      <c r="AJ24">
+        <v>53.79</v>
+      </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A25" s="233" t="s">
         <v>205</v>
       </c>
@@ -20816,8 +25738,17 @@
       <c r="R25" s="232"/>
       <c r="S25" s="232"/>
       <c r="T25" s="232"/>
+      <c r="AH25" t="s">
+        <v>269</v>
+      </c>
+      <c r="AI25">
+        <v>17.999999999999961</v>
+      </c>
+      <c r="AJ25">
+        <v>47.58</v>
+      </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A26" s="233" t="s">
         <v>206</v>
       </c>
@@ -20854,8 +25785,17 @@
       <c r="R26" s="232"/>
       <c r="S26" s="232"/>
       <c r="T26" s="232"/>
+      <c r="AH26" t="s">
+        <v>270</v>
+      </c>
+      <c r="AI26">
+        <v>6.4999999999999778</v>
+      </c>
+      <c r="AJ26">
+        <v>30.72</v>
+      </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A27" s="233" t="s">
         <v>207</v>
       </c>
@@ -20892,8 +25832,17 @@
       <c r="R27" s="232"/>
       <c r="S27" s="232"/>
       <c r="T27" s="232"/>
+      <c r="AH27" t="s">
+        <v>273</v>
+      </c>
+      <c r="AI27">
+        <v>5.9999999999998943</v>
+      </c>
+      <c r="AJ27">
+        <v>22.36</v>
+      </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A28" s="233" t="s">
         <v>208</v>
       </c>
@@ -20930,8 +25879,17 @@
       <c r="R28" s="231"/>
       <c r="S28" s="232"/>
       <c r="T28" s="231"/>
+      <c r="AH28" t="s">
+        <v>274</v>
+      </c>
+      <c r="AI28">
+        <v>8.888888888888836</v>
+      </c>
+      <c r="AJ28">
+        <v>30.83</v>
+      </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A29" s="233" t="s">
         <v>209</v>
       </c>
@@ -20969,8 +25927,17 @@
       <c r="R29" s="232"/>
       <c r="S29" s="232"/>
       <c r="T29" s="232"/>
+      <c r="AH29" t="s">
+        <v>277</v>
+      </c>
+      <c r="AI29">
+        <v>4.6666666666667078</v>
+      </c>
+      <c r="AJ29">
+        <v>24.91</v>
+      </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A30" s="233" t="s">
         <v>210</v>
       </c>
@@ -21008,8 +25975,17 @@
       <c r="R30" s="232"/>
       <c r="S30" s="232"/>
       <c r="T30" s="232"/>
+      <c r="AH30" t="s">
+        <v>280</v>
+      </c>
+      <c r="AI30">
+        <v>17.857142857142676</v>
+      </c>
+      <c r="AJ30">
+        <v>67.13</v>
+      </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A31" s="233" t="s">
         <v>211</v>
       </c>
@@ -21047,8 +26023,17 @@
       <c r="R31" s="232"/>
       <c r="S31" s="232"/>
       <c r="T31" s="232"/>
+      <c r="AH31" t="s">
+        <v>282</v>
+      </c>
+      <c r="AI31">
+        <v>6.6666666666666723</v>
+      </c>
+      <c r="AJ31">
+        <v>51.68</v>
+      </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A32" s="233" t="s">
         <v>212</v>
       </c>
@@ -21086,8 +26071,17 @@
       <c r="R32" s="232"/>
       <c r="S32" s="232"/>
       <c r="T32" s="232"/>
+      <c r="AH32" t="s">
+        <v>284</v>
+      </c>
+      <c r="AI32">
+        <v>5.3333333333334858</v>
+      </c>
+      <c r="AJ32">
+        <v>57.56</v>
+      </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A33" s="233" t="s">
         <v>213</v>
       </c>
@@ -21125,8 +26119,17 @@
       <c r="R33" s="232"/>
       <c r="S33" s="232"/>
       <c r="T33" s="232"/>
+      <c r="AH33" t="s">
+        <v>285</v>
+      </c>
+      <c r="AI33">
+        <v>8.0000000000000444</v>
+      </c>
+      <c r="AJ33">
+        <v>63.54</v>
+      </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A34" s="233" t="s">
         <v>214</v>
       </c>
@@ -21164,8 +26167,17 @@
       <c r="R34" s="232"/>
       <c r="S34" s="232"/>
       <c r="T34" s="232"/>
+      <c r="AH34" t="s">
+        <v>290</v>
+      </c>
+      <c r="AI34">
+        <v>8.6666666666666377</v>
+      </c>
+      <c r="AJ34">
+        <v>66.59</v>
+      </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A35" s="233" t="s">
         <v>215</v>
       </c>
@@ -21203,8 +26215,17 @@
       <c r="R35" s="232"/>
       <c r="S35" s="232"/>
       <c r="T35" s="232"/>
+      <c r="AH35" t="s">
+        <v>293</v>
+      </c>
+      <c r="AI35">
+        <v>15.000000000000083</v>
+      </c>
+      <c r="AJ35">
+        <v>27.12</v>
+      </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A36" s="233" t="s">
         <v>216</v>
       </c>
@@ -21242,8 +26263,17 @@
       <c r="R36" s="232"/>
       <c r="S36" s="232"/>
       <c r="T36" s="232"/>
+      <c r="AH36" t="s">
+        <v>299</v>
+      </c>
+      <c r="AI36">
+        <v>7.1428571428571495</v>
+      </c>
+      <c r="AJ36">
+        <v>14.59</v>
+      </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A37" s="233" t="s">
         <v>217</v>
       </c>
@@ -21281,8 +26311,17 @@
       <c r="R37" s="232"/>
       <c r="S37" s="232"/>
       <c r="T37" s="232"/>
+      <c r="AH37" t="s">
+        <v>308</v>
+      </c>
+      <c r="AI37">
+        <v>6.6666666666666723</v>
+      </c>
+      <c r="AJ37">
+        <v>56.02</v>
+      </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A38" s="233" t="s">
         <v>218</v>
       </c>
@@ -21319,8 +26358,17 @@
       <c r="R38" s="232"/>
       <c r="S38" s="232"/>
       <c r="T38" s="232"/>
+      <c r="AH38" t="s">
+        <v>316</v>
+      </c>
+      <c r="AI38">
+        <v>12.666666666666751</v>
+      </c>
+      <c r="AJ38">
+        <v>43.66</v>
+      </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A39" s="233" t="s">
         <v>219</v>
       </c>
@@ -21358,8 +26406,17 @@
       <c r="R39" s="232"/>
       <c r="S39" s="232"/>
       <c r="T39" s="232"/>
+      <c r="AH39" t="s">
+        <v>317</v>
+      </c>
+      <c r="AI39">
+        <v>45.000000000000007</v>
+      </c>
+      <c r="AJ39">
+        <v>85.5</v>
+      </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A40" s="233" t="s">
         <v>220</v>
       </c>
@@ -21397,8 +26454,17 @@
       <c r="R40" s="232"/>
       <c r="S40" s="232"/>
       <c r="T40" s="232"/>
+      <c r="AH40" t="s">
+        <v>322</v>
+      </c>
+      <c r="AI40">
+        <v>20.000000000000018</v>
+      </c>
+      <c r="AJ40">
+        <v>64.14</v>
+      </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A41" s="233" t="s">
         <v>221</v>
       </c>
@@ -21434,8 +26500,17 @@
       <c r="R41" s="232"/>
       <c r="S41" s="232"/>
       <c r="T41" s="232"/>
+      <c r="AH41" t="s">
+        <v>328</v>
+      </c>
+      <c r="AI41">
+        <v>10.666666666666602</v>
+      </c>
+      <c r="AJ41">
+        <v>39.619999999999997</v>
+      </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A42" s="233" t="s">
         <v>222</v>
       </c>
@@ -21473,8 +26548,17 @@
       <c r="R42" s="232"/>
       <c r="S42" s="232"/>
       <c r="T42" s="232"/>
+      <c r="AH42" t="s">
+        <v>329</v>
+      </c>
+      <c r="AI42">
+        <v>24.374999999999918</v>
+      </c>
+      <c r="AJ42">
+        <v>87.1</v>
+      </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A43" s="233" t="s">
         <v>223</v>
       </c>
@@ -21512,8 +26596,17 @@
       <c r="R43" s="232"/>
       <c r="S43" s="232"/>
       <c r="T43" s="232"/>
+      <c r="AH43" t="s">
+        <v>332</v>
+      </c>
+      <c r="AI43">
+        <v>0.71428571428583387</v>
+      </c>
+      <c r="AJ43">
+        <v>25.16</v>
+      </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A44" s="233" t="s">
         <v>224</v>
       </c>
@@ -21551,8 +26644,17 @@
       <c r="R44" s="232"/>
       <c r="S44" s="232"/>
       <c r="T44" s="232"/>
+      <c r="AH44" t="s">
+        <v>333</v>
+      </c>
+      <c r="AI44">
+        <v>5.7142857142856798</v>
+      </c>
+      <c r="AJ44">
+        <v>15.19</v>
+      </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A45" s="233" t="s">
         <v>225</v>
       </c>
@@ -21590,8 +26692,17 @@
       <c r="R45" s="232"/>
       <c r="S45" s="232"/>
       <c r="T45" s="232"/>
+      <c r="AH45" t="s">
+        <v>335</v>
+      </c>
+      <c r="AI45">
+        <v>0.66666666666677832</v>
+      </c>
+      <c r="AJ45">
+        <v>25.61</v>
+      </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A46" s="233" t="s">
         <v>226</v>
       </c>
@@ -21630,7 +26741,7 @@
       <c r="S46" s="232"/>
       <c r="T46" s="232"/>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A47" s="233" t="s">
         <v>227</v>
       </c>
@@ -21669,7 +26780,7 @@
       <c r="S47" s="232"/>
       <c r="T47" s="232"/>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A48" s="233" t="s">
         <v>228</v>
       </c>
@@ -22435,11 +27546,12 @@
         <v>44.99</v>
       </c>
       <c r="H67" s="30">
-        <v>1.1708204506E-2</v>
+        <f>0.011708204506*27.38</f>
+        <v>0.32057063937427999</v>
       </c>
       <c r="I67" s="238">
         <f t="shared" ref="I67:I76" si="4">H67/(B67/1000)</f>
-        <v>8.3630032185714284E-2</v>
+        <v>2.2897902812448567</v>
       </c>
       <c r="J67" s="236">
         <v>3.5409999999999999</v>
@@ -22713,11 +27825,12 @@
         <v>68.760000000000005</v>
       </c>
       <c r="H74" s="30">
-        <v>1.7282514145E-2</v>
+        <f>0.017282514145*27.38</f>
+        <v>0.47319523729009999</v>
       </c>
       <c r="I74" s="238">
         <f t="shared" si="4"/>
-        <v>0.11521676096666668</v>
+        <v>3.1546349152673332</v>
       </c>
       <c r="J74" s="236">
         <v>3.5110000000000001</v>
@@ -22792,11 +27905,12 @@
         <v>50.92</v>
       </c>
       <c r="H76" s="30">
-        <v>1.30381562765E-2</v>
+        <f>0.0130381562765*27.38</f>
+        <v>0.35698471885056998</v>
       </c>
       <c r="I76" s="238">
         <f t="shared" si="4"/>
-        <v>8.1488476728124995E-2</v>
+        <v>2.2311544928160623</v>
       </c>
       <c r="J76" s="236">
         <v>3.1459999999999999</v>
@@ -23418,11 +28532,12 @@
         <v>47.58</v>
       </c>
       <c r="H92" s="240">
-        <v>1.1515777695E-2</v>
+        <f>0.011515777695*27.38</f>
+        <v>0.31530199328909997</v>
       </c>
       <c r="I92" s="245">
         <f>H92/(B92/1000)</f>
-        <v>5.7578888474999999E-2</v>
+        <v>1.5765099664454998</v>
       </c>
       <c r="J92" s="9">
         <v>3.5859999999999999</v>
@@ -23969,11 +29084,12 @@
         <v>51.68</v>
       </c>
       <c r="H105" s="240">
-        <v>5.8357639970625002E-3</v>
+        <f>0.0058357639970625*27.38</f>
+        <v>0.15978321823957126</v>
       </c>
       <c r="I105" s="245">
         <f>H105/(B105/1000)</f>
-        <v>3.890509331375E-2</v>
+        <v>1.065221454930475</v>
       </c>
       <c r="J105" s="9">
         <v>3.1840000000000002</v>
@@ -24391,11 +29507,12 @@
         <v>46.75</v>
       </c>
       <c r="H115" s="240">
-        <v>6.9204867741875006E-3</v>
+        <f>0.0069204867741875*27.38</f>
+        <v>0.18948292787725374</v>
       </c>
       <c r="I115" s="245">
         <f>H115/(B115/1000)</f>
-        <v>4.6136578494583337E-2</v>
+        <v>1.2632195191816917</v>
       </c>
       <c r="J115" s="9">
         <v>3.6640000000000001</v>
@@ -24438,11 +29555,12 @@
         <v>27.12</v>
       </c>
       <c r="H116" s="240">
-        <v>9.508337120500001E-3</v>
+        <f>0.0095083371205*27.38</f>
+        <v>0.26033827035928997</v>
       </c>
       <c r="I116" s="245">
         <f>H116/(B116/1000)</f>
-        <v>5.9427107003125007E-2</v>
+        <v>1.6271141897455623</v>
       </c>
       <c r="J116" s="9">
         <v>4.5410000000000004</v>
@@ -24485,11 +29603,12 @@
         <v>14.59</v>
       </c>
       <c r="H117" s="240">
-        <v>8.3706300997500004E-3</v>
+        <f>0.00837063009975*27.38</f>
+        <v>0.229187852131155</v>
       </c>
       <c r="I117" s="245">
         <f>H117/(B117/1000)</f>
-        <v>5.9790214998214283E-2</v>
+        <v>1.637056086651107</v>
       </c>
       <c r="J117" s="9">
         <v>3.4580000000000002</v>
@@ -25513,11 +30632,11 @@
         <v>0.2382</v>
       </c>
       <c r="E144" s="9">
-        <f t="shared" ref="E144:E160" si="7">D144-C144</f>
+        <f t="shared" ref="E144:E152" si="7">D144-C144</f>
         <v>2.2999999999999965E-3</v>
       </c>
       <c r="F144" s="243">
-        <f t="shared" ref="F144:F159" si="8">E144/B144*1000*1000</f>
+        <f t="shared" ref="F144:F152" si="8">E144/B144*1000*1000</f>
         <v>13.529411764705863</v>
       </c>
       <c r="G144" s="9">
@@ -26030,11 +31149,12 @@
         <v>25.16</v>
       </c>
       <c r="H160" s="240">
-        <v>1.17180656445E-2</v>
+        <f>0.0117180656445*27.38</f>
+        <v>0.32084063734641</v>
       </c>
       <c r="I160" s="245">
-        <f t="shared" ref="I118:I167" si="9">H160/(B160/1000)</f>
-        <v>8.3700468889285701E-2</v>
+        <f>H160/(B160/1000)</f>
+        <v>2.2917188381886424</v>
       </c>
       <c r="J160" s="9">
         <v>3.5750000000000002</v>
@@ -26071,11 +31191,12 @@
         <v>15.19</v>
       </c>
       <c r="H161" s="240">
-        <v>8.6452595395000009E-3</v>
+        <f>0.0086452595395*27.38</f>
+        <v>0.23670720619151001</v>
       </c>
       <c r="I161" s="245">
-        <f t="shared" si="9"/>
-        <v>6.1751853853571431E-2</v>
+        <f t="shared" ref="I161:I167" si="9">H161/(B161/1000)</f>
+        <v>1.6907657585107856</v>
       </c>
       <c r="J161" s="9">
         <v>3.2189999999999999</v>
@@ -26192,11 +31313,12 @@
         <v>25.61</v>
       </c>
       <c r="H165" s="240">
-        <v>7.4314243210000007E-3</v>
+        <f>0.007431424321*27.38</f>
+        <v>0.20347239790898</v>
       </c>
       <c r="I165" s="245">
         <f t="shared" si="9"/>
-        <v>4.9542828806666675E-2</v>
+        <v>1.3564826527265335</v>
       </c>
       <c r="J165" s="9">
         <v>2.7170000000000001</v>
@@ -26254,11 +31376,12 @@
         <v>30.82</v>
       </c>
       <c r="H167" s="240">
-        <v>9.3669671855000011E-3</v>
+        <f>0.0093669671855*27.38</f>
+        <v>0.25646756153898997</v>
       </c>
       <c r="I167" s="245">
         <f t="shared" si="9"/>
-        <v>6.2446447903333341E-2</v>
+        <v>1.7097837435932666</v>
       </c>
       <c r="J167" s="9">
         <v>3.8330000000000002</v>

--- a/data/constituents_summary.xlsx
+++ b/data/constituents_summary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\hysteresis\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huck4481\Documents\GitHub\hysteresis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B62B9E93-34E1-40A3-9F62-B026CE237D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4236C70-D767-4CB7-973E-BFCDCD2F3039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="623" xr2:uid="{FEC01F85-CDE9-417C-893C-E562E55652ED}"/>
+    <workbookView xWindow="-25320" yWindow="360" windowWidth="25440" windowHeight="15270" tabRatio="623" xr2:uid="{FEC01F85-CDE9-417C-893C-E562E55652ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Spring" sheetId="4" r:id="rId1"/>
@@ -1343,7 +1343,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="248">
+  <cellXfs count="250">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2050,26 +2050,32 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -24507,24 +24513,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E5F5147-870F-4065-86F1-3AC0DA635208}">
   <dimension ref="A1:AJ167"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.6640625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="15.44140625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" style="5" customWidth="1"/>
     <col min="3" max="3" width="18" style="5" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="22.44140625" style="5" customWidth="1"/>
-    <col min="6" max="10" width="16.88671875" style="5" customWidth="1"/>
-    <col min="11" max="11" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="22.42578125" style="5" customWidth="1"/>
+    <col min="6" max="10" width="16.85546875" style="5" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="16" max="16" width="18.44140625" customWidth="1"/>
-    <col min="17" max="17" width="15.5546875" customWidth="1"/>
-    <col min="18" max="18" width="15.44140625" style="5" customWidth="1"/>
-    <col min="19" max="19" width="16.33203125" style="5" customWidth="1"/>
-    <col min="20" max="20" width="16.88671875" style="5" customWidth="1"/>
+    <col min="16" max="16" width="18.42578125" customWidth="1"/>
+    <col min="17" max="17" width="15.5703125" customWidth="1"/>
+    <col min="18" max="18" width="15.42578125" style="5" customWidth="1"/>
+    <col min="19" max="19" width="16.28515625" style="5" customWidth="1"/>
+    <col min="20" max="20" width="16.85546875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="144" t="s">
         <v>1</v>
       </c>
@@ -24580,7 +24586,7 @@
         <v>106.21</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="233" t="s">
         <v>182</v>
       </c>
@@ -24631,7 +24637,7 @@
         <v>51.232999999999997</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" s="233" t="s">
         <v>183</v>
       </c>
@@ -24682,7 +24688,7 @@
         <v>59.16</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="233" t="s">
         <v>184</v>
       </c>
@@ -24731,7 +24737,7 @@
         <v>48.47</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="233" t="s">
         <v>185</v>
       </c>
@@ -24780,7 +24786,7 @@
         <v>78.709999999999994</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="233" t="s">
         <v>186</v>
       </c>
@@ -24829,7 +24835,7 @@
         <v>45.42</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="233" t="s">
         <v>187</v>
       </c>
@@ -24878,7 +24884,7 @@
         <v>74.75</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" s="233" t="s">
         <v>188</v>
       </c>
@@ -24927,7 +24933,7 @@
         <v>56.59</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" s="233" t="s">
         <v>189</v>
       </c>
@@ -24975,7 +24981,7 @@
         <v>63.56</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" s="233" t="s">
         <v>190</v>
       </c>
@@ -25023,7 +25029,7 @@
         <v>85.89</v>
       </c>
     </row>
-    <row r="11" spans="1:36" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="233" t="s">
         <v>191</v>
       </c>
@@ -25071,7 +25077,7 @@
         <v>50.13</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="233" t="s">
         <v>192</v>
       </c>
@@ -25119,7 +25125,7 @@
         <v>44.99</v>
       </c>
     </row>
-    <row r="13" spans="1:36" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="233" t="s">
         <v>193</v>
       </c>
@@ -25167,7 +25173,7 @@
         <v>35.729999999999997</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="233" t="s">
         <v>195</v>
       </c>
@@ -25221,7 +25227,7 @@
         <v>31.62</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="233" t="s">
         <v>194</v>
       </c>
@@ -25269,7 +25275,7 @@
         <v>25.42</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="233" t="s">
         <v>196</v>
       </c>
@@ -25318,7 +25324,7 @@
         <v>68.760000000000005</v>
       </c>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="233" t="s">
         <v>197</v>
       </c>
@@ -25364,7 +25370,7 @@
         <v>50.92</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="233" t="s">
         <v>198</v>
       </c>
@@ -25412,7 +25418,7 @@
         <v>33.08</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="233" t="s">
         <v>199</v>
       </c>
@@ -25462,7 +25468,7 @@
         <v>77.489999999999995</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="233" t="s">
         <v>200</v>
       </c>
@@ -25510,7 +25516,7 @@
         <v>103.31</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="233" t="s">
         <v>201</v>
       </c>
@@ -25558,7 +25564,7 @@
         <v>65.48</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="233" t="s">
         <v>202</v>
       </c>
@@ -25606,7 +25612,7 @@
         <v>73.680000000000007</v>
       </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="233" t="s">
         <v>203</v>
       </c>
@@ -25652,7 +25658,7 @@
         <v>93.48</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="233" t="s">
         <v>204</v>
       </c>
@@ -25700,7 +25706,7 @@
         <v>53.79</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" s="233" t="s">
         <v>205</v>
       </c>
@@ -25748,7 +25754,7 @@
         <v>47.58</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="233" t="s">
         <v>206</v>
       </c>
@@ -25795,7 +25801,7 @@
         <v>30.72</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="233" t="s">
         <v>207</v>
       </c>
@@ -25842,7 +25848,7 @@
         <v>22.36</v>
       </c>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="233" t="s">
         <v>208</v>
       </c>
@@ -25889,7 +25895,7 @@
         <v>30.83</v>
       </c>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="233" t="s">
         <v>209</v>
       </c>
@@ -25937,7 +25943,7 @@
         <v>24.91</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" s="233" t="s">
         <v>210</v>
       </c>
@@ -25985,7 +25991,7 @@
         <v>67.13</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="233" t="s">
         <v>211</v>
       </c>
@@ -26033,7 +26039,7 @@
         <v>51.68</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" s="233" t="s">
         <v>212</v>
       </c>
@@ -26081,7 +26087,7 @@
         <v>57.56</v>
       </c>
     </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" s="233" t="s">
         <v>213</v>
       </c>
@@ -26129,7 +26135,7 @@
         <v>63.54</v>
       </c>
     </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" s="233" t="s">
         <v>214</v>
       </c>
@@ -26177,7 +26183,7 @@
         <v>66.59</v>
       </c>
     </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" s="233" t="s">
         <v>215</v>
       </c>
@@ -26225,7 +26231,7 @@
         <v>27.12</v>
       </c>
     </row>
-    <row r="36" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" s="233" t="s">
         <v>216</v>
       </c>
@@ -26273,7 +26279,7 @@
         <v>14.59</v>
       </c>
     </row>
-    <row r="37" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" s="233" t="s">
         <v>217</v>
       </c>
@@ -26321,7 +26327,7 @@
         <v>56.02</v>
       </c>
     </row>
-    <row r="38" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38" s="233" t="s">
         <v>218</v>
       </c>
@@ -26368,7 +26374,7 @@
         <v>43.66</v>
       </c>
     </row>
-    <row r="39" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" s="233" t="s">
         <v>219</v>
       </c>
@@ -26416,7 +26422,7 @@
         <v>85.5</v>
       </c>
     </row>
-    <row r="40" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40" s="233" t="s">
         <v>220</v>
       </c>
@@ -26464,7 +26470,7 @@
         <v>64.14</v>
       </c>
     </row>
-    <row r="41" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41" s="233" t="s">
         <v>221</v>
       </c>
@@ -26510,7 +26516,7 @@
         <v>39.619999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A42" s="233" t="s">
         <v>222</v>
       </c>
@@ -26558,7 +26564,7 @@
         <v>87.1</v>
       </c>
     </row>
-    <row r="43" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" s="233" t="s">
         <v>223</v>
       </c>
@@ -26606,7 +26612,7 @@
         <v>25.16</v>
       </c>
     </row>
-    <row r="44" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44" s="233" t="s">
         <v>224</v>
       </c>
@@ -26654,7 +26660,7 @@
         <v>15.19</v>
       </c>
     </row>
-    <row r="45" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45" s="233" t="s">
         <v>225</v>
       </c>
@@ -26702,7 +26708,7 @@
         <v>25.61</v>
       </c>
     </row>
-    <row r="46" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A46" s="233" t="s">
         <v>226</v>
       </c>
@@ -26741,7 +26747,7 @@
       <c r="S46" s="232"/>
       <c r="T46" s="232"/>
     </row>
-    <row r="47" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" s="233" t="s">
         <v>227</v>
       </c>
@@ -26780,7 +26786,7 @@
       <c r="S47" s="232"/>
       <c r="T47" s="232"/>
     </row>
-    <row r="48" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A48" s="233" t="s">
         <v>228</v>
       </c>
@@ -26819,7 +26825,7 @@
       <c r="S48" s="232"/>
       <c r="T48" s="232"/>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="233" t="s">
         <v>229</v>
       </c>
@@ -26858,7 +26864,7 @@
       <c r="S49" s="232"/>
       <c r="T49" s="232"/>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="233" t="s">
         <v>230</v>
       </c>
@@ -26897,7 +26903,7 @@
       <c r="S50" s="232"/>
       <c r="T50" s="232"/>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="233" t="s">
         <v>231</v>
       </c>
@@ -26936,7 +26942,7 @@
       <c r="S51" s="232"/>
       <c r="T51" s="232"/>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="233" t="s">
         <v>232</v>
       </c>
@@ -26975,7 +26981,7 @@
       <c r="S52" s="232"/>
       <c r="T52" s="232"/>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="233" t="s">
         <v>233</v>
       </c>
@@ -27014,7 +27020,7 @@
       <c r="S53" s="232"/>
       <c r="T53" s="232"/>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="233" t="s">
         <v>234</v>
       </c>
@@ -27053,7 +27059,7 @@
       <c r="S54" s="232"/>
       <c r="T54" s="232"/>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" s="233" t="s">
         <v>235</v>
       </c>
@@ -27092,7 +27098,7 @@
       <c r="S55" s="232"/>
       <c r="T55" s="232"/>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" s="233" t="s">
         <v>236</v>
       </c>
@@ -27131,7 +27137,7 @@
       <c r="S56" s="232"/>
       <c r="T56" s="232"/>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="233" t="s">
         <v>237</v>
       </c>
@@ -27170,7 +27176,7 @@
       <c r="S57" s="232"/>
       <c r="T57" s="232"/>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="233" t="s">
         <v>238</v>
       </c>
@@ -27209,7 +27215,7 @@
       <c r="S58" s="232"/>
       <c r="T58" s="232"/>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" s="233" t="s">
         <v>239</v>
       </c>
@@ -27248,7 +27254,7 @@
       <c r="S59" s="232"/>
       <c r="T59" s="232"/>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" s="233" t="s">
         <v>240</v>
       </c>
@@ -27287,7 +27293,7 @@
       <c r="S60" s="232"/>
       <c r="T60" s="232"/>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" s="233" t="s">
         <v>241</v>
       </c>
@@ -27326,7 +27332,7 @@
       <c r="S61" s="232"/>
       <c r="T61" s="232"/>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" s="233" t="s">
         <v>242</v>
       </c>
@@ -27365,7 +27371,7 @@
       <c r="S62" s="232"/>
       <c r="T62" s="232"/>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" s="233" t="s">
         <v>243</v>
       </c>
@@ -27404,7 +27410,7 @@
       <c r="S63" s="232"/>
       <c r="T63" s="232"/>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" s="233" t="s">
         <v>244</v>
       </c>
@@ -27443,7 +27449,7 @@
       <c r="S64" s="232"/>
       <c r="T64" s="232"/>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" s="233" t="s">
         <v>245</v>
       </c>
@@ -27482,7 +27488,7 @@
       <c r="S65" s="232"/>
       <c r="T65" s="232"/>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" s="233" t="s">
         <v>246</v>
       </c>
@@ -27521,7 +27527,7 @@
       <c r="S66" s="232"/>
       <c r="T66" s="232"/>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>247</v>
       </c>
@@ -27566,7 +27572,7 @@
       <c r="S67" s="232"/>
       <c r="T67" s="232"/>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>248</v>
       </c>
@@ -27605,7 +27611,7 @@
       <c r="S68" s="232"/>
       <c r="T68" s="232"/>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>249</v>
       </c>
@@ -27644,124 +27650,124 @@
       <c r="S69" s="232"/>
       <c r="T69" s="232"/>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B70" s="2">
+      <c r="B70" s="39">
         <v>150</v>
       </c>
-      <c r="C70" s="2">
+      <c r="C70" s="39">
         <v>0.23319999999999999</v>
       </c>
-      <c r="D70" s="2">
+      <c r="D70" s="39">
         <v>0.2359</v>
       </c>
-      <c r="E70" s="2">
+      <c r="E70" s="39">
         <f t="shared" si="2"/>
         <v>2.7000000000000079E-3</v>
       </c>
-      <c r="F70" s="149">
+      <c r="F70" s="241">
         <f t="shared" si="3"/>
         <v>18.000000000000053</v>
       </c>
-      <c r="G70" s="2">
+      <c r="G70" s="39">
         <v>25.42</v>
       </c>
       <c r="H70" s="31"/>
-      <c r="I70" s="238"/>
-      <c r="J70" s="236">
+      <c r="I70" s="242"/>
+      <c r="J70" s="243">
         <v>2.9209999999999998</v>
       </c>
-      <c r="K70" s="2">
+      <c r="K70" s="39">
         <v>346</v>
       </c>
-      <c r="L70" s="235">
+      <c r="L70" s="244">
         <v>45048.708333333336</v>
       </c>
       <c r="R70" s="232"/>
       <c r="S70" s="232"/>
       <c r="T70" s="232"/>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B71" s="2">
+      <c r="B71" s="39">
         <v>150</v>
       </c>
-      <c r="C71" s="2">
+      <c r="C71" s="39">
         <v>0.22939999999999999</v>
       </c>
-      <c r="D71" s="2">
+      <c r="D71" s="39">
         <v>0.23080000000000001</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E71" s="39">
         <f t="shared" si="2"/>
         <v>1.4000000000000123E-3</v>
       </c>
-      <c r="F71" s="149">
+      <c r="F71" s="241">
         <f t="shared" si="3"/>
         <v>9.3333333333334156</v>
       </c>
-      <c r="G71" s="2">
+      <c r="G71" s="39">
         <v>0</v>
       </c>
       <c r="H71" s="31"/>
-      <c r="I71" s="238"/>
-      <c r="J71" s="236">
+      <c r="I71" s="242"/>
+      <c r="J71" s="243">
         <v>3.0609999999999999</v>
       </c>
-      <c r="K71" s="2">
+      <c r="K71" s="39">
         <v>347</v>
       </c>
-      <c r="L71" s="235">
+      <c r="L71" s="244">
         <v>45049</v>
       </c>
       <c r="R71" s="232"/>
       <c r="S71" s="232"/>
       <c r="T71" s="232"/>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B72" s="2">
+      <c r="B72" s="39">
         <v>140</v>
       </c>
-      <c r="C72" s="2">
+      <c r="C72" s="39">
         <v>0.2346</v>
       </c>
-      <c r="D72" s="2">
+      <c r="D72" s="39">
         <v>0.2354</v>
       </c>
-      <c r="E72" s="2">
+      <c r="E72" s="39">
         <f t="shared" si="2"/>
         <v>7.9999999999999516E-4</v>
       </c>
-      <c r="F72" s="149">
+      <c r="F72" s="241">
         <f t="shared" si="3"/>
         <v>5.7142857142856798</v>
       </c>
-      <c r="G72" s="2">
+      <c r="G72" s="39">
         <v>0</v>
       </c>
       <c r="H72" s="31"/>
-      <c r="I72" s="238"/>
-      <c r="J72" s="236">
+      <c r="I72" s="242"/>
+      <c r="J72" s="243">
         <v>2.823</v>
       </c>
-      <c r="K72" s="2">
+      <c r="K72" s="39">
         <v>348</v>
       </c>
-      <c r="L72" s="235">
+      <c r="L72" s="244">
         <v>45049.291666666664</v>
       </c>
       <c r="R72" s="232"/>
       <c r="S72" s="232"/>
       <c r="T72" s="232"/>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>253</v>
       </c>
@@ -27800,7 +27806,7 @@
       <c r="S73" s="232"/>
       <c r="T73" s="232"/>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>254</v>
       </c>
@@ -27845,7 +27851,7 @@
       <c r="S74" s="232"/>
       <c r="T74" s="232"/>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="2" t="s">
         <v>179</v>
@@ -27880,7 +27886,7 @@
       <c r="S75" s="232"/>
       <c r="T75" s="232"/>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>255</v>
       </c>
@@ -27925,7 +27931,7 @@
       <c r="S76" s="232"/>
       <c r="T76" s="232"/>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="2" t="s">
         <v>179</v>
@@ -27960,7 +27966,7 @@
       <c r="S77" s="232"/>
       <c r="T77" s="232"/>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>256</v>
       </c>
@@ -27999,7 +28005,7 @@
       <c r="S78" s="232"/>
       <c r="T78" s="232"/>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="2" t="s">
         <v>179</v>
@@ -28034,7 +28040,7 @@
       <c r="S79" s="232"/>
       <c r="T79" s="232"/>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>257</v>
       </c>
@@ -28073,7 +28079,7 @@
       <c r="S80" s="232"/>
       <c r="T80" s="232"/>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>258</v>
       </c>
@@ -28112,7 +28118,7 @@
       <c r="S81" s="232"/>
       <c r="T81" s="232"/>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>259</v>
       </c>
@@ -28151,7 +28157,7 @@
       <c r="S82" s="232"/>
       <c r="T82" s="232"/>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>260</v>
       </c>
@@ -28190,230 +28196,230 @@
       <c r="S83" s="232"/>
       <c r="T83" s="232"/>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A84" s="241" t="s">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A84" s="191" t="s">
         <v>261</v>
       </c>
-      <c r="B84" s="9">
+      <c r="B84" s="6">
         <v>200</v>
       </c>
-      <c r="C84" s="9">
+      <c r="C84" s="6">
         <v>0.23849999999999999</v>
       </c>
-      <c r="D84" s="9">
+      <c r="D84" s="6">
         <v>0.2417</v>
       </c>
-      <c r="E84" s="9">
+      <c r="E84" s="6">
         <f t="shared" si="5"/>
         <v>3.2000000000000084E-3</v>
       </c>
-      <c r="F84" s="243">
+      <c r="F84" s="193">
         <f t="shared" si="6"/>
         <v>16.000000000000043</v>
       </c>
-      <c r="G84" s="9">
+      <c r="G84" s="6">
         <v>103.31</v>
       </c>
-      <c r="H84" s="240"/>
-      <c r="I84" s="246"/>
-      <c r="J84" s="9">
+      <c r="H84" s="17"/>
+      <c r="I84" s="248"/>
+      <c r="J84" s="6">
         <v>3.8290000000000002</v>
       </c>
-      <c r="K84" s="9">
+      <c r="K84" s="6">
         <v>190</v>
       </c>
-      <c r="L84" s="244">
+      <c r="L84" s="246">
         <v>45033.6875</v>
       </c>
       <c r="R84" s="232"/>
       <c r="S84" s="232"/>
       <c r="T84" s="232"/>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A85" s="241" t="s">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A85" s="191" t="s">
         <v>262</v>
       </c>
-      <c r="B85" s="9">
+      <c r="B85" s="6">
         <v>200</v>
       </c>
-      <c r="C85" s="9">
+      <c r="C85" s="6">
         <v>0.23760000000000001</v>
       </c>
-      <c r="D85" s="9">
+      <c r="D85" s="6">
         <v>0.23769999999999999</v>
       </c>
-      <c r="E85" s="9">
+      <c r="E85" s="6">
         <f t="shared" si="5"/>
         <v>9.9999999999988987E-5</v>
       </c>
-      <c r="F85" s="243">
+      <c r="F85" s="193">
         <f t="shared" si="6"/>
         <v>0.49999999999994493</v>
       </c>
-      <c r="G85" s="9">
+      <c r="G85" s="6">
         <v>65.48</v>
       </c>
-      <c r="H85" s="240"/>
-      <c r="I85" s="246"/>
-      <c r="J85" s="9">
+      <c r="H85" s="17"/>
+      <c r="I85" s="248"/>
+      <c r="J85" s="6">
         <v>3.4729999999999999</v>
       </c>
-      <c r="K85" s="9">
+      <c r="K85" s="6">
         <v>191</v>
       </c>
-      <c r="L85" s="244">
+      <c r="L85" s="246">
         <v>45033.854166666664</v>
       </c>
       <c r="R85" s="232"/>
       <c r="S85" s="232"/>
       <c r="T85" s="232"/>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A86" s="241" t="s">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A86" s="191" t="s">
         <v>263</v>
       </c>
-      <c r="B86" s="9">
+      <c r="B86" s="6">
         <v>190</v>
       </c>
-      <c r="C86" s="9">
+      <c r="C86" s="6">
         <v>0.23649999999999999</v>
       </c>
-      <c r="D86" s="9">
+      <c r="D86" s="6">
         <v>0.23769999999999999</v>
       </c>
-      <c r="E86" s="9">
+      <c r="E86" s="6">
         <f t="shared" si="5"/>
         <v>1.2000000000000066E-3</v>
       </c>
-      <c r="F86" s="243">
+      <c r="F86" s="193">
         <f t="shared" si="6"/>
         <v>6.3157894736842453</v>
       </c>
-      <c r="G86" s="9">
+      <c r="G86" s="6">
         <v>73.680000000000007</v>
       </c>
-      <c r="H86" s="240"/>
-      <c r="I86" s="246"/>
-      <c r="J86" s="9">
+      <c r="H86" s="17"/>
+      <c r="I86" s="248"/>
+      <c r="J86" s="6">
         <v>3.4209999999999998</v>
       </c>
-      <c r="K86" s="9">
+      <c r="K86" s="6">
         <v>192</v>
       </c>
-      <c r="L86" s="244">
+      <c r="L86" s="246">
         <v>45034.020833333336</v>
       </c>
       <c r="R86" s="232"/>
       <c r="S86" s="232"/>
       <c r="T86" s="232"/>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A87" s="241" t="s">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A87" s="191" t="s">
         <v>264</v>
       </c>
-      <c r="B87" s="9" t="s">
+      <c r="B87" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="C87" s="9">
+      <c r="C87" s="6">
         <v>0.23749999999999999</v>
       </c>
-      <c r="D87" s="9">
+      <c r="D87" s="6">
         <v>0.23780000000000001</v>
       </c>
-      <c r="E87" s="9">
+      <c r="E87" s="6">
         <f t="shared" si="5"/>
         <v>3.0000000000002247E-4</v>
       </c>
-      <c r="F87" s="243" t="s">
+      <c r="F87" s="193" t="s">
         <v>179</v>
       </c>
-      <c r="G87" s="9">
+      <c r="G87" s="6">
         <v>48.9</v>
       </c>
-      <c r="H87" s="240"/>
-      <c r="I87" s="246"/>
-      <c r="J87" s="9">
+      <c r="H87" s="17"/>
+      <c r="I87" s="248"/>
+      <c r="J87" s="6">
         <v>3.3460000000000001</v>
       </c>
-      <c r="K87" s="9">
+      <c r="K87" s="6">
         <v>193</v>
       </c>
-      <c r="L87" s="244">
+      <c r="L87" s="246">
         <v>45034.1875</v>
       </c>
       <c r="R87" s="232"/>
       <c r="S87" s="232"/>
       <c r="T87" s="232"/>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A88" s="241" t="s">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A88" s="191" t="s">
         <v>265</v>
       </c>
-      <c r="B88" s="9">
+      <c r="B88" s="6">
         <v>190</v>
       </c>
-      <c r="C88" s="9">
+      <c r="C88" s="6">
         <v>0.23039999999999999</v>
       </c>
-      <c r="D88" s="9">
+      <c r="D88" s="6">
         <v>0.23230000000000001</v>
       </c>
-      <c r="E88" s="9">
+      <c r="E88" s="6">
         <f t="shared" si="5"/>
         <v>1.9000000000000128E-3</v>
       </c>
-      <c r="F88" s="243">
+      <c r="F88" s="193">
         <f t="shared" si="6"/>
         <v>10.000000000000066</v>
       </c>
-      <c r="G88" s="9">
+      <c r="G88" s="6">
         <v>0</v>
       </c>
-      <c r="H88" s="9"/>
-      <c r="I88" s="9"/>
-      <c r="J88" s="9">
+      <c r="H88" s="6"/>
+      <c r="I88" s="6"/>
+      <c r="J88" s="6">
         <v>3.2709999999999999</v>
       </c>
-      <c r="K88" s="9">
+      <c r="K88" s="6">
         <v>211</v>
       </c>
-      <c r="L88" s="244">
+      <c r="L88" s="246">
         <v>45034.354166666664</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A89" s="241" t="s">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A89" s="191" t="s">
         <v>266</v>
       </c>
-      <c r="B89" s="9">
+      <c r="B89" s="6">
         <v>220</v>
       </c>
-      <c r="C89" s="9">
+      <c r="C89" s="6">
         <v>0.22720000000000001</v>
       </c>
-      <c r="D89" s="9">
+      <c r="D89" s="6">
         <v>0.22869999999999999</v>
       </c>
-      <c r="E89" s="9">
+      <c r="E89" s="6">
         <f t="shared" si="5"/>
         <v>1.4999999999999736E-3</v>
       </c>
-      <c r="F89" s="243">
+      <c r="F89" s="193">
         <f t="shared" si="6"/>
         <v>6.8181818181816984</v>
       </c>
-      <c r="G89" s="9">
+      <c r="G89" s="6">
         <v>0</v>
       </c>
-      <c r="H89" s="242"/>
-      <c r="I89" s="242"/>
-      <c r="J89" s="9">
+      <c r="H89" s="245"/>
+      <c r="I89" s="245"/>
+      <c r="J89" s="6">
         <v>3.4089999999999998</v>
       </c>
-      <c r="K89" s="9">
+      <c r="K89" s="6">
         <v>212</v>
       </c>
-      <c r="L89" s="244">
+      <c r="L89" s="246">
         <v>45034.520833333336</v>
       </c>
       <c r="M89" s="5"/>
@@ -28423,39 +28429,39 @@
       <c r="S89"/>
       <c r="T89"/>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A90" s="241" t="s">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A90" s="240" t="s">
         <v>267</v>
       </c>
-      <c r="B90" s="9">
+      <c r="B90" s="6">
         <v>200</v>
       </c>
-      <c r="C90" s="9">
+      <c r="C90" s="6">
         <v>0.23100000000000001</v>
       </c>
-      <c r="D90" s="9">
+      <c r="D90" s="6">
         <v>0.23530000000000001</v>
       </c>
-      <c r="E90" s="9">
+      <c r="E90" s="6">
         <f t="shared" si="5"/>
         <v>4.2999999999999983E-3</v>
       </c>
-      <c r="F90" s="243">
+      <c r="F90" s="193">
         <f t="shared" si="6"/>
         <v>21.499999999999993</v>
       </c>
-      <c r="G90" s="9">
+      <c r="G90" s="6">
         <v>93.48</v>
       </c>
-      <c r="H90" s="242"/>
-      <c r="I90" s="242"/>
-      <c r="J90" s="9">
+      <c r="H90" s="245"/>
+      <c r="I90" s="245"/>
+      <c r="J90" s="6">
         <v>4.6630000000000003</v>
       </c>
-      <c r="K90" s="9">
+      <c r="K90" s="6">
         <v>213</v>
       </c>
-      <c r="L90" s="244">
+      <c r="L90" s="246">
         <v>45034.6875</v>
       </c>
       <c r="M90" s="5"/>
@@ -28465,39 +28471,39 @@
       <c r="S90"/>
       <c r="T90"/>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A91" s="241" t="s">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A91" s="240" t="s">
         <v>268</v>
       </c>
-      <c r="B91" s="9">
+      <c r="B91" s="6">
         <v>190</v>
       </c>
-      <c r="C91" s="9">
+      <c r="C91" s="6">
         <v>0.2281</v>
       </c>
-      <c r="D91" s="9">
+      <c r="D91" s="6">
         <v>0.23019999999999999</v>
       </c>
-      <c r="E91" s="9">
+      <c r="E91" s="6">
         <f t="shared" si="5"/>
         <v>2.0999999999999908E-3</v>
       </c>
-      <c r="F91" s="243">
+      <c r="F91" s="193">
         <f t="shared" si="6"/>
         <v>11.05263157894732</v>
       </c>
-      <c r="G91" s="9">
+      <c r="G91" s="6">
         <v>53.79</v>
       </c>
-      <c r="H91" s="242"/>
-      <c r="I91" s="242"/>
-      <c r="J91" s="9">
+      <c r="H91" s="245"/>
+      <c r="I91" s="245"/>
+      <c r="J91" s="6">
         <v>3.581</v>
       </c>
-      <c r="K91" s="9">
+      <c r="K91" s="6">
         <v>214</v>
       </c>
-      <c r="L91" s="244">
+      <c r="L91" s="246">
         <v>45034.895833333336</v>
       </c>
       <c r="M91" s="5"/>
@@ -28507,45 +28513,45 @@
       <c r="S91"/>
       <c r="T91"/>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A92" s="241" t="s">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A92" s="240" t="s">
         <v>269</v>
       </c>
-      <c r="B92" s="9">
+      <c r="B92" s="6">
         <v>200</v>
       </c>
-      <c r="C92" s="9">
+      <c r="C92" s="6">
         <v>0.22850000000000001</v>
       </c>
-      <c r="D92" s="9">
+      <c r="D92" s="6">
         <v>0.2321</v>
       </c>
-      <c r="E92" s="9">
+      <c r="E92" s="6">
         <f t="shared" si="5"/>
         <v>3.5999999999999921E-3</v>
       </c>
-      <c r="F92" s="243">
+      <c r="F92" s="193">
         <f t="shared" si="6"/>
         <v>17.999999999999961</v>
       </c>
-      <c r="G92" s="9">
+      <c r="G92" s="6">
         <v>47.58</v>
       </c>
-      <c r="H92" s="240">
+      <c r="H92" s="17">
         <f>0.011515777695*27.38</f>
         <v>0.31530199328909997</v>
       </c>
-      <c r="I92" s="245">
+      <c r="I92" s="247">
         <f>H92/(B92/1000)</f>
         <v>1.5765099664454998</v>
       </c>
-      <c r="J92" s="9">
+      <c r="J92" s="6">
         <v>3.5859999999999999</v>
       </c>
-      <c r="K92" s="9">
+      <c r="K92" s="6">
         <v>215</v>
       </c>
-      <c r="L92" s="244">
+      <c r="L92" s="246">
         <v>45035.104166666664</v>
       </c>
       <c r="M92" s="5"/>
@@ -28555,39 +28561,39 @@
       <c r="S92"/>
       <c r="T92"/>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A93" s="241" t="s">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A93" s="240" t="s">
         <v>270</v>
       </c>
-      <c r="B93" s="9">
+      <c r="B93" s="6">
         <v>200</v>
       </c>
-      <c r="C93" s="9">
+      <c r="C93" s="6">
         <v>0.2339</v>
       </c>
-      <c r="D93" s="9">
+      <c r="D93" s="6">
         <v>0.23519999999999999</v>
       </c>
-      <c r="E93" s="9">
+      <c r="E93" s="6">
         <f t="shared" si="5"/>
         <v>1.2999999999999956E-3</v>
       </c>
-      <c r="F93" s="243">
+      <c r="F93" s="193">
         <f t="shared" si="6"/>
         <v>6.4999999999999778</v>
       </c>
-      <c r="G93" s="9">
+      <c r="G93" s="6">
         <v>30.72</v>
       </c>
-      <c r="H93" s="242"/>
-      <c r="I93" s="242"/>
-      <c r="J93" s="9">
+      <c r="H93" s="245"/>
+      <c r="I93" s="245"/>
+      <c r="J93" s="6">
         <v>3.4009999999999998</v>
       </c>
-      <c r="K93" s="9">
+      <c r="K93" s="6">
         <v>216</v>
       </c>
-      <c r="L93" s="244">
+      <c r="L93" s="246">
         <v>45035.3125</v>
       </c>
       <c r="M93" s="5"/>
@@ -28597,39 +28603,39 @@
       <c r="S93"/>
       <c r="T93"/>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A94" s="241" t="s">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A94" s="240" t="s">
         <v>271</v>
       </c>
-      <c r="B94" s="9">
+      <c r="B94" s="6">
         <v>200</v>
       </c>
-      <c r="C94" s="9">
+      <c r="C94" s="6">
         <v>0.23300000000000001</v>
       </c>
-      <c r="D94" s="9">
+      <c r="D94" s="6">
         <v>0.2346</v>
       </c>
-      <c r="E94" s="9">
+      <c r="E94" s="6">
         <f t="shared" si="5"/>
         <v>1.5999999999999903E-3</v>
       </c>
-      <c r="F94" s="243">
+      <c r="F94" s="193">
         <f t="shared" si="6"/>
         <v>7.999999999999952</v>
       </c>
-      <c r="G94" s="9">
+      <c r="G94" s="6">
         <v>0</v>
       </c>
-      <c r="H94" s="242"/>
-      <c r="I94" s="242"/>
-      <c r="J94" s="9">
+      <c r="H94" s="245"/>
+      <c r="I94" s="245"/>
+      <c r="J94" s="6">
         <v>3.1459999999999999</v>
       </c>
-      <c r="K94" s="9">
+      <c r="K94" s="6">
         <v>217</v>
       </c>
-      <c r="L94" s="244">
+      <c r="L94" s="246">
         <v>45035.520833333336</v>
       </c>
       <c r="M94" s="5"/>
@@ -28639,39 +28645,39 @@
       <c r="S94"/>
       <c r="T94"/>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A95" s="241" t="s">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A95" s="240" t="s">
         <v>272</v>
       </c>
-      <c r="B95" s="9">
+      <c r="B95" s="6">
         <v>100</v>
       </c>
-      <c r="C95" s="9">
+      <c r="C95" s="6">
         <v>0.23480000000000001</v>
       </c>
-      <c r="D95" s="9">
+      <c r="D95" s="6">
         <v>0.23599999999999999</v>
       </c>
-      <c r="E95" s="9">
+      <c r="E95" s="6">
         <f t="shared" si="5"/>
         <v>1.1999999999999789E-3</v>
       </c>
-      <c r="F95" s="243">
+      <c r="F95" s="193">
         <f t="shared" si="6"/>
         <v>11.999999999999789</v>
       </c>
-      <c r="G95" s="9">
+      <c r="G95" s="6">
         <v>0</v>
       </c>
-      <c r="H95" s="242"/>
-      <c r="I95" s="242"/>
-      <c r="J95" s="9">
+      <c r="H95" s="245"/>
+      <c r="I95" s="245"/>
+      <c r="J95" s="6">
         <v>3.9940000000000002</v>
       </c>
-      <c r="K95" s="9">
+      <c r="K95" s="6">
         <v>218</v>
       </c>
-      <c r="L95" s="244">
+      <c r="L95" s="246">
         <v>45035.729166666664</v>
       </c>
       <c r="M95" s="5"/>
@@ -28681,39 +28687,39 @@
       <c r="S95"/>
       <c r="T95"/>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A96" s="241" t="s">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A96" s="240" t="s">
         <v>273</v>
       </c>
-      <c r="B96" s="9">
+      <c r="B96" s="6">
         <v>100</v>
       </c>
-      <c r="C96" s="9">
+      <c r="C96" s="6">
         <v>0.23530000000000001</v>
       </c>
-      <c r="D96" s="9">
+      <c r="D96" s="6">
         <v>0.2359</v>
       </c>
-      <c r="E96" s="9">
+      <c r="E96" s="6">
         <f t="shared" si="5"/>
         <v>5.9999999999998943E-4</v>
       </c>
-      <c r="F96" s="243">
+      <c r="F96" s="193">
         <f t="shared" si="6"/>
         <v>5.9999999999998943</v>
       </c>
-      <c r="G96" s="9">
+      <c r="G96" s="6">
         <v>22.36</v>
       </c>
-      <c r="H96" s="242"/>
-      <c r="I96" s="242"/>
-      <c r="J96" s="9">
+      <c r="H96" s="245"/>
+      <c r="I96" s="245"/>
+      <c r="J96" s="6">
         <v>3.5329999999999999</v>
       </c>
-      <c r="K96" s="9">
+      <c r="K96" s="6">
         <v>219</v>
       </c>
-      <c r="L96" s="244">
+      <c r="L96" s="246">
         <v>45035.9375</v>
       </c>
       <c r="M96" s="5"/>
@@ -28723,39 +28729,39 @@
       <c r="S96"/>
       <c r="T96"/>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A97" s="241" t="s">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A97" s="240" t="s">
         <v>274</v>
       </c>
-      <c r="B97" s="9">
+      <c r="B97" s="6">
         <v>90</v>
       </c>
-      <c r="C97" s="9">
+      <c r="C97" s="6">
         <v>0.2346</v>
       </c>
-      <c r="D97" s="9">
+      <c r="D97" s="6">
         <v>0.2354</v>
       </c>
-      <c r="E97" s="9">
+      <c r="E97" s="6">
         <f t="shared" si="5"/>
         <v>7.9999999999999516E-4</v>
       </c>
-      <c r="F97" s="243">
+      <c r="F97" s="193">
         <f t="shared" si="6"/>
         <v>8.888888888888836</v>
       </c>
-      <c r="G97" s="9">
+      <c r="G97" s="6">
         <v>30.83</v>
       </c>
-      <c r="H97" s="242"/>
-      <c r="I97" s="242"/>
-      <c r="J97" s="9">
+      <c r="H97" s="245"/>
+      <c r="I97" s="245"/>
+      <c r="J97" s="6">
         <v>3.4340000000000002</v>
       </c>
-      <c r="K97" s="9">
+      <c r="K97" s="6">
         <v>220</v>
       </c>
-      <c r="L97" s="244">
+      <c r="L97" s="246">
         <v>45036.145833333336</v>
       </c>
       <c r="M97" s="5"/>
@@ -28765,39 +28771,39 @@
       <c r="S97"/>
       <c r="T97"/>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A98" s="241" t="s">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A98" s="240" t="s">
         <v>275</v>
       </c>
-      <c r="B98" s="9">
+      <c r="B98" s="6">
         <v>90</v>
       </c>
-      <c r="C98" s="9">
+      <c r="C98" s="6">
         <v>0.2369</v>
       </c>
-      <c r="D98" s="9">
+      <c r="D98" s="6">
         <v>0.23799999999999999</v>
       </c>
-      <c r="E98" s="9">
+      <c r="E98" s="6">
         <f t="shared" si="5"/>
         <v>1.0999999999999899E-3</v>
       </c>
-      <c r="F98" s="243">
+      <c r="F98" s="193">
         <f t="shared" si="6"/>
         <v>12.222222222222108</v>
       </c>
-      <c r="G98" s="9">
+      <c r="G98" s="6">
         <v>0</v>
       </c>
-      <c r="H98" s="242"/>
-      <c r="I98" s="242"/>
-      <c r="J98" s="9">
+      <c r="H98" s="245"/>
+      <c r="I98" s="245"/>
+      <c r="J98" s="6">
         <v>3.4279999999999999</v>
       </c>
-      <c r="K98" s="9">
+      <c r="K98" s="6">
         <v>221</v>
       </c>
-      <c r="L98" s="244">
+      <c r="L98" s="246">
         <v>45036.354166666664</v>
       </c>
       <c r="M98" s="5"/>
@@ -28807,39 +28813,39 @@
       <c r="S98"/>
       <c r="T98"/>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A99" s="241" t="s">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A99" s="240" t="s">
         <v>276</v>
       </c>
-      <c r="B99" s="9">
+      <c r="B99" s="6">
         <v>160</v>
       </c>
-      <c r="C99" s="9">
+      <c r="C99" s="6">
         <v>0.23549999999999999</v>
       </c>
-      <c r="D99" s="9">
+      <c r="D99" s="6">
         <v>0.2366</v>
       </c>
-      <c r="E99" s="9">
+      <c r="E99" s="6">
         <f t="shared" si="5"/>
         <v>1.1000000000000176E-3</v>
       </c>
-      <c r="F99" s="243">
+      <c r="F99" s="193">
         <f t="shared" si="6"/>
         <v>6.8750000000001101</v>
       </c>
-      <c r="G99" s="9">
+      <c r="G99" s="6">
         <v>0</v>
       </c>
-      <c r="H99" s="242"/>
-      <c r="I99" s="242"/>
-      <c r="J99" s="9">
+      <c r="H99" s="245"/>
+      <c r="I99" s="245"/>
+      <c r="J99" s="6">
         <v>3.4809999999999999</v>
       </c>
-      <c r="K99" s="9">
+      <c r="K99" s="6">
         <v>236</v>
       </c>
-      <c r="L99" s="244">
+      <c r="L99" s="246">
         <v>45036.770833333336</v>
       </c>
       <c r="M99" s="5"/>
@@ -28849,39 +28855,39 @@
       <c r="S99"/>
       <c r="T99"/>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A100" s="241" t="s">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A100" s="240" t="s">
         <v>277</v>
       </c>
-      <c r="B100" s="9">
+      <c r="B100" s="6">
         <v>150</v>
       </c>
-      <c r="C100" s="9">
+      <c r="C100" s="6">
         <v>0.23280000000000001</v>
       </c>
-      <c r="D100" s="9">
+      <c r="D100" s="6">
         <v>0.23350000000000001</v>
       </c>
-      <c r="E100" s="9">
+      <c r="E100" s="6">
         <f t="shared" si="5"/>
         <v>7.0000000000000617E-4</v>
       </c>
-      <c r="F100" s="243">
+      <c r="F100" s="193">
         <f t="shared" si="6"/>
         <v>4.6666666666667078</v>
       </c>
-      <c r="G100" s="9">
+      <c r="G100" s="6">
         <v>24.91</v>
       </c>
-      <c r="H100" s="242"/>
-      <c r="I100" s="242"/>
-      <c r="J100" s="9">
+      <c r="H100" s="245"/>
+      <c r="I100" s="245"/>
+      <c r="J100" s="6">
         <v>3.2829999999999999</v>
       </c>
-      <c r="K100" s="9">
+      <c r="K100" s="6">
         <v>237</v>
       </c>
-      <c r="L100" s="244">
+      <c r="L100" s="246">
         <v>45036.979166666664</v>
       </c>
       <c r="M100" s="5"/>
@@ -28891,39 +28897,39 @@
       <c r="S100"/>
       <c r="T100"/>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A101" s="241" t="s">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A101" s="240" t="s">
         <v>278</v>
       </c>
-      <c r="B101" s="9">
+      <c r="B101" s="6">
         <v>150</v>
       </c>
-      <c r="C101" s="9">
+      <c r="C101" s="6">
         <v>0.23530000000000001</v>
       </c>
-      <c r="D101" s="9">
+      <c r="D101" s="6">
         <v>0.2361</v>
       </c>
-      <c r="E101" s="9">
+      <c r="E101" s="6">
         <f t="shared" si="5"/>
         <v>7.9999999999999516E-4</v>
       </c>
-      <c r="F101" s="243">
+      <c r="F101" s="193">
         <f t="shared" si="6"/>
         <v>5.3333333333333011</v>
       </c>
-      <c r="G101" s="9">
+      <c r="G101" s="6">
         <v>0</v>
       </c>
-      <c r="H101" s="242"/>
-      <c r="I101" s="242"/>
-      <c r="J101" s="9">
+      <c r="H101" s="245"/>
+      <c r="I101" s="245"/>
+      <c r="J101" s="6">
         <v>3.0840000000000001</v>
       </c>
-      <c r="K101" s="9">
+      <c r="K101" s="6">
         <v>238</v>
       </c>
-      <c r="L101" s="244">
+      <c r="L101" s="246">
         <v>45037.395833333336</v>
       </c>
       <c r="M101" s="5"/>
@@ -28933,39 +28939,39 @@
       <c r="S101"/>
       <c r="T101"/>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A102" s="241" t="s">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A102" s="240" t="s">
         <v>279</v>
       </c>
-      <c r="B102" s="9">
+      <c r="B102" s="6">
         <v>150</v>
       </c>
-      <c r="C102" s="9">
+      <c r="C102" s="6">
         <v>0.23719999999999999</v>
       </c>
-      <c r="D102" s="9">
+      <c r="D102" s="6">
         <v>0.23810000000000001</v>
       </c>
-      <c r="E102" s="9">
+      <c r="E102" s="6">
         <f t="shared" si="5"/>
         <v>9.000000000000119E-4</v>
       </c>
-      <c r="F102" s="243">
+      <c r="F102" s="193">
         <f t="shared" si="6"/>
         <v>6.000000000000079</v>
       </c>
-      <c r="G102" s="9">
+      <c r="G102" s="6">
         <v>0</v>
       </c>
-      <c r="H102" s="242"/>
-      <c r="I102" s="242"/>
-      <c r="J102" s="9">
+      <c r="H102" s="245"/>
+      <c r="I102" s="245"/>
+      <c r="J102" s="6">
         <v>3.2890000000000001</v>
       </c>
-      <c r="K102" s="9">
+      <c r="K102" s="6">
         <v>239</v>
       </c>
-      <c r="L102" s="244">
+      <c r="L102" s="246">
         <v>45037.604166666664</v>
       </c>
       <c r="M102" s="5"/>
@@ -28975,39 +28981,39 @@
       <c r="S102"/>
       <c r="T102"/>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A103" s="241" t="s">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A103" s="240" t="s">
         <v>280</v>
       </c>
-      <c r="B103" s="9">
+      <c r="B103" s="6">
         <v>140</v>
       </c>
-      <c r="C103" s="9">
+      <c r="C103" s="6">
         <v>0.23400000000000001</v>
       </c>
-      <c r="D103" s="9">
+      <c r="D103" s="6">
         <v>0.23649999999999999</v>
       </c>
-      <c r="E103" s="9">
+      <c r="E103" s="6">
         <f t="shared" si="5"/>
         <v>2.4999999999999745E-3</v>
       </c>
-      <c r="F103" s="243">
+      <c r="F103" s="193">
         <f t="shared" si="6"/>
         <v>17.857142857142676</v>
       </c>
-      <c r="G103" s="9">
+      <c r="G103" s="6">
         <v>67.13</v>
       </c>
-      <c r="H103" s="242"/>
-      <c r="I103" s="242"/>
-      <c r="J103" s="9">
+      <c r="H103" s="245"/>
+      <c r="I103" s="245"/>
+      <c r="J103" s="6">
         <v>3.8639999999999999</v>
       </c>
-      <c r="K103" s="9">
+      <c r="K103" s="6">
         <v>240</v>
       </c>
-      <c r="L103" s="244">
+      <c r="L103" s="246">
         <v>45037.8125</v>
       </c>
       <c r="M103" s="5"/>
@@ -29017,39 +29023,39 @@
       <c r="S103"/>
       <c r="T103"/>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A104" s="241" t="s">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A104" s="240" t="s">
         <v>281</v>
       </c>
-      <c r="B104" s="9">
+      <c r="B104" s="6">
         <v>150</v>
       </c>
-      <c r="C104" s="9">
+      <c r="C104" s="6">
         <v>0.2336</v>
       </c>
-      <c r="D104" s="9">
+      <c r="D104" s="6">
         <v>0.23419999999999999</v>
       </c>
-      <c r="E104" s="9">
+      <c r="E104" s="6">
         <f t="shared" si="5"/>
         <v>5.9999999999998943E-4</v>
       </c>
-      <c r="F104" s="243">
+      <c r="F104" s="193">
         <f t="shared" si="6"/>
         <v>3.9999999999999298</v>
       </c>
-      <c r="G104" s="9">
+      <c r="G104" s="6">
         <v>0</v>
       </c>
-      <c r="H104" s="242"/>
-      <c r="I104" s="242"/>
-      <c r="J104" s="9">
+      <c r="H104" s="245"/>
+      <c r="I104" s="245"/>
+      <c r="J104" s="6">
         <v>3.3439999999999999</v>
       </c>
-      <c r="K104" s="9">
+      <c r="K104" s="6">
         <v>241</v>
       </c>
-      <c r="L104" s="244">
+      <c r="L104" s="246">
         <v>45038.020833333336</v>
       </c>
       <c r="M104" s="5"/>
@@ -29059,45 +29065,45 @@
       <c r="S104"/>
       <c r="T104"/>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A105" s="241" t="s">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A105" s="240" t="s">
         <v>282</v>
       </c>
-      <c r="B105" s="9">
+      <c r="B105" s="6">
         <v>150</v>
       </c>
-      <c r="C105" s="9">
+      <c r="C105" s="6">
         <v>0.23469999999999999</v>
       </c>
-      <c r="D105" s="9">
+      <c r="D105" s="6">
         <v>0.23569999999999999</v>
       </c>
-      <c r="E105" s="9">
+      <c r="E105" s="6">
         <f t="shared" si="5"/>
         <v>1.0000000000000009E-3</v>
       </c>
-      <c r="F105" s="243">
+      <c r="F105" s="193">
         <f t="shared" si="6"/>
         <v>6.6666666666666723</v>
       </c>
-      <c r="G105" s="9">
+      <c r="G105" s="6">
         <v>51.68</v>
       </c>
-      <c r="H105" s="240">
+      <c r="H105" s="17">
         <f>0.0058357639970625*27.38</f>
         <v>0.15978321823957126</v>
       </c>
-      <c r="I105" s="245">
+      <c r="I105" s="247">
         <f>H105/(B105/1000)</f>
         <v>1.065221454930475</v>
       </c>
-      <c r="J105" s="9">
+      <c r="J105" s="6">
         <v>3.1840000000000002</v>
       </c>
-      <c r="K105" s="9">
+      <c r="K105" s="6">
         <v>242</v>
       </c>
-      <c r="L105" s="244">
+      <c r="L105" s="246">
         <v>45038.229166666664</v>
       </c>
       <c r="M105" s="5"/>
@@ -29107,39 +29113,39 @@
       <c r="S105"/>
       <c r="T105"/>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A106" s="241" t="s">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A106" s="240" t="s">
         <v>283</v>
       </c>
-      <c r="B106" s="9">
+      <c r="B106" s="6">
         <v>145</v>
       </c>
-      <c r="C106" s="9">
+      <c r="C106" s="6">
         <v>0.23680000000000001</v>
       </c>
-      <c r="D106" s="9">
+      <c r="D106" s="6">
         <v>0.23760000000000001</v>
       </c>
-      <c r="E106" s="9">
+      <c r="E106" s="6">
         <f t="shared" si="5"/>
         <v>7.9999999999999516E-4</v>
       </c>
-      <c r="F106" s="243">
+      <c r="F106" s="193">
         <f t="shared" si="6"/>
         <v>5.5172413793103114</v>
       </c>
-      <c r="G106" s="9">
+      <c r="G106" s="6">
         <v>0</v>
       </c>
-      <c r="H106" s="242"/>
-      <c r="I106" s="242"/>
-      <c r="J106" s="9">
+      <c r="H106" s="245"/>
+      <c r="I106" s="245"/>
+      <c r="J106" s="6">
         <v>3.246</v>
       </c>
-      <c r="K106" s="9">
+      <c r="K106" s="6">
         <v>243</v>
       </c>
-      <c r="L106" s="244">
+      <c r="L106" s="246">
         <v>45038.4375</v>
       </c>
       <c r="M106" s="5"/>
@@ -29149,39 +29155,39 @@
       <c r="S106"/>
       <c r="T106"/>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A107" s="241" t="s">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A107" s="240" t="s">
         <v>284</v>
       </c>
-      <c r="B107" s="9">
+      <c r="B107" s="6">
         <v>150</v>
       </c>
-      <c r="C107" s="9">
+      <c r="C107" s="6">
         <v>0.23799999999999999</v>
       </c>
-      <c r="D107" s="9">
+      <c r="D107" s="6">
         <v>0.23880000000000001</v>
       </c>
-      <c r="E107" s="9">
+      <c r="E107" s="6">
         <f t="shared" si="5"/>
         <v>8.0000000000002292E-4</v>
       </c>
-      <c r="F107" s="243">
+      <c r="F107" s="193">
         <f t="shared" si="6"/>
         <v>5.3333333333334858</v>
       </c>
-      <c r="G107" s="9">
+      <c r="G107" s="6">
         <v>57.56</v>
       </c>
-      <c r="H107" s="242"/>
-      <c r="I107" s="242"/>
-      <c r="J107" s="9">
+      <c r="H107" s="245"/>
+      <c r="I107" s="245"/>
+      <c r="J107" s="6">
         <v>3.8860000000000001</v>
       </c>
-      <c r="K107" s="9">
+      <c r="K107" s="6">
         <v>244</v>
       </c>
-      <c r="L107" s="244">
+      <c r="L107" s="246">
         <v>45038.645833333336</v>
       </c>
       <c r="M107" s="5"/>
@@ -29191,39 +29197,39 @@
       <c r="S107"/>
       <c r="T107"/>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A108" s="241" t="s">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A108" s="240" t="s">
         <v>285</v>
       </c>
-      <c r="B108" s="9">
+      <c r="B108" s="6">
         <v>150</v>
       </c>
-      <c r="C108" s="9">
+      <c r="C108" s="6">
         <v>0.23319999999999999</v>
       </c>
-      <c r="D108" s="9">
+      <c r="D108" s="6">
         <v>0.2344</v>
       </c>
-      <c r="E108" s="9">
+      <c r="E108" s="6">
         <f t="shared" si="5"/>
         <v>1.2000000000000066E-3</v>
       </c>
-      <c r="F108" s="243">
+      <c r="F108" s="193">
         <f t="shared" si="6"/>
         <v>8.0000000000000444</v>
       </c>
-      <c r="G108" s="9">
+      <c r="G108" s="6">
         <v>63.54</v>
       </c>
-      <c r="H108" s="242"/>
-      <c r="I108" s="242"/>
-      <c r="J108" s="9">
+      <c r="H108" s="245"/>
+      <c r="I108" s="245"/>
+      <c r="J108" s="6">
         <v>3.4710000000000001</v>
       </c>
-      <c r="K108" s="9">
+      <c r="K108" s="6">
         <v>245</v>
       </c>
-      <c r="L108" s="244">
+      <c r="L108" s="246">
         <v>45038.854166666664</v>
       </c>
       <c r="M108" s="5"/>
@@ -29233,39 +29239,39 @@
       <c r="S108"/>
       <c r="T108"/>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A109" s="241" t="s">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A109" s="240" t="s">
         <v>286</v>
       </c>
-      <c r="B109" s="9">
+      <c r="B109" s="6">
         <v>150</v>
       </c>
-      <c r="C109" s="9">
+      <c r="C109" s="6">
         <v>0.2382</v>
       </c>
-      <c r="D109" s="9">
+      <c r="D109" s="6">
         <v>0.23930000000000001</v>
       </c>
-      <c r="E109" s="9">
+      <c r="E109" s="6">
         <f t="shared" si="5"/>
         <v>1.1000000000000176E-3</v>
       </c>
-      <c r="F109" s="243">
+      <c r="F109" s="193">
         <f t="shared" si="6"/>
         <v>7.3333333333334512</v>
       </c>
-      <c r="G109" s="9">
+      <c r="G109" s="6">
         <v>0</v>
       </c>
-      <c r="H109" s="242"/>
-      <c r="I109" s="242"/>
-      <c r="J109" s="9">
+      <c r="H109" s="245"/>
+      <c r="I109" s="245"/>
+      <c r="J109" s="6">
         <v>3.3780000000000001</v>
       </c>
-      <c r="K109" s="9">
+      <c r="K109" s="6">
         <v>246</v>
       </c>
-      <c r="L109" s="244">
+      <c r="L109" s="246">
         <v>45039.0625</v>
       </c>
       <c r="M109" s="5"/>
@@ -29275,38 +29281,38 @@
       <c r="S109"/>
       <c r="T109"/>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A110" s="241" t="s">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A110" s="240" t="s">
         <v>287</v>
       </c>
-      <c r="B110" s="9" t="s">
+      <c r="B110" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="C110" s="9">
+      <c r="C110" s="6">
         <v>0.24210000000000001</v>
       </c>
-      <c r="D110" s="9">
+      <c r="D110" s="6">
         <v>0.24349999999999999</v>
       </c>
-      <c r="E110" s="9">
+      <c r="E110" s="6">
         <f t="shared" si="5"/>
         <v>1.3999999999999846E-3</v>
       </c>
-      <c r="F110" s="243" t="s">
+      <c r="F110" s="193" t="s">
         <v>179</v>
       </c>
-      <c r="G110" s="9">
+      <c r="G110" s="6">
         <v>0</v>
       </c>
-      <c r="H110" s="242"/>
-      <c r="I110" s="242"/>
-      <c r="J110" s="9">
+      <c r="H110" s="245"/>
+      <c r="I110" s="245"/>
+      <c r="J110" s="6">
         <v>3.1680000000000001</v>
       </c>
-      <c r="K110" s="9">
+      <c r="K110" s="6">
         <v>247</v>
       </c>
-      <c r="L110" s="244">
+      <c r="L110" s="246">
         <v>45039.479166666664</v>
       </c>
       <c r="M110" s="5"/>
@@ -29316,39 +29322,39 @@
       <c r="S110"/>
       <c r="T110"/>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A111" s="241" t="s">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A111" s="240" t="s">
         <v>288</v>
       </c>
-      <c r="B111" s="9">
+      <c r="B111" s="6">
         <v>160</v>
       </c>
-      <c r="C111" s="9">
+      <c r="C111" s="6">
         <v>0.22800000000000001</v>
       </c>
-      <c r="D111" s="9">
+      <c r="D111" s="6">
         <v>0.2298</v>
       </c>
-      <c r="E111" s="9">
+      <c r="E111" s="6">
         <f t="shared" si="5"/>
         <v>1.799999999999996E-3</v>
       </c>
-      <c r="F111" s="243">
+      <c r="F111" s="193">
         <f t="shared" si="6"/>
         <v>11.249999999999975</v>
       </c>
-      <c r="G111" s="9">
+      <c r="G111" s="6">
         <v>0</v>
       </c>
-      <c r="H111" s="242"/>
-      <c r="I111" s="242"/>
-      <c r="J111" s="9">
+      <c r="H111" s="245"/>
+      <c r="I111" s="245"/>
+      <c r="J111" s="6">
         <v>3.7970000000000002</v>
       </c>
-      <c r="K111" s="9">
+      <c r="K111" s="6">
         <v>248</v>
       </c>
-      <c r="L111" s="244">
+      <c r="L111" s="246">
         <v>45039.666666666664</v>
       </c>
       <c r="M111" s="5"/>
@@ -29358,39 +29364,39 @@
       <c r="S111"/>
       <c r="T111"/>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A112" s="241" t="s">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A112" s="240" t="s">
         <v>289</v>
       </c>
-      <c r="B112" s="9">
+      <c r="B112" s="6">
         <v>155</v>
       </c>
-      <c r="C112" s="9">
+      <c r="C112" s="6">
         <v>0.23250000000000001</v>
       </c>
-      <c r="D112" s="9">
+      <c r="D112" s="6">
         <v>0.23330000000000001</v>
       </c>
-      <c r="E112" s="9">
+      <c r="E112" s="6">
         <f t="shared" si="5"/>
         <v>7.9999999999999516E-4</v>
       </c>
-      <c r="F112" s="243">
+      <c r="F112" s="193">
         <f t="shared" si="6"/>
         <v>5.1612903225806139</v>
       </c>
-      <c r="G112" s="9">
+      <c r="G112" s="6">
         <v>0</v>
       </c>
-      <c r="H112" s="242"/>
-      <c r="I112" s="242"/>
-      <c r="J112" s="9">
+      <c r="H112" s="245"/>
+      <c r="I112" s="245"/>
+      <c r="J112" s="6">
         <v>3.1840000000000002</v>
       </c>
-      <c r="K112" s="9">
+      <c r="K112" s="6">
         <v>249</v>
       </c>
-      <c r="L112" s="244">
+      <c r="L112" s="246">
         <v>45039.875</v>
       </c>
       <c r="M112" s="5"/>
@@ -29400,39 +29406,39 @@
       <c r="S112"/>
       <c r="T112"/>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A113" s="241" t="s">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A113" s="240" t="s">
         <v>290</v>
       </c>
-      <c r="B113" s="9">
+      <c r="B113" s="6">
         <v>150</v>
       </c>
-      <c r="C113" s="9">
+      <c r="C113" s="6">
         <v>0.23519999999999999</v>
       </c>
-      <c r="D113" s="9">
+      <c r="D113" s="6">
         <v>0.23649999999999999</v>
       </c>
-      <c r="E113" s="9">
+      <c r="E113" s="6">
         <f t="shared" si="5"/>
         <v>1.2999999999999956E-3</v>
       </c>
-      <c r="F113" s="243">
+      <c r="F113" s="193">
         <f t="shared" si="6"/>
         <v>8.6666666666666377</v>
       </c>
-      <c r="G113" s="9">
+      <c r="G113" s="6">
         <v>66.59</v>
       </c>
-      <c r="H113" s="242"/>
-      <c r="I113" s="242"/>
-      <c r="J113" s="9">
+      <c r="H113" s="245"/>
+      <c r="I113" s="245"/>
+      <c r="J113" s="6">
         <v>3.399</v>
       </c>
-      <c r="K113" s="9">
+      <c r="K113" s="6">
         <v>250</v>
       </c>
-      <c r="L113" s="244">
+      <c r="L113" s="246">
         <v>45040.083333333336</v>
       </c>
       <c r="M113" s="5"/>
@@ -29442,39 +29448,39 @@
       <c r="S113"/>
       <c r="T113"/>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A114" s="241" t="s">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A114" s="240" t="s">
         <v>291</v>
       </c>
-      <c r="B114" s="9">
+      <c r="B114" s="6">
         <v>140</v>
       </c>
-      <c r="C114" s="9">
+      <c r="C114" s="6">
         <v>0.2288</v>
       </c>
-      <c r="D114" s="9">
+      <c r="D114" s="6">
         <v>0.23</v>
       </c>
-      <c r="E114" s="9">
+      <c r="E114" s="6">
         <f t="shared" si="5"/>
         <v>1.2000000000000066E-3</v>
       </c>
-      <c r="F114" s="243">
+      <c r="F114" s="193">
         <f t="shared" si="6"/>
         <v>8.5714285714286191</v>
       </c>
-      <c r="G114" s="9">
+      <c r="G114" s="6">
         <v>0</v>
       </c>
-      <c r="H114" s="242"/>
-      <c r="I114" s="242"/>
-      <c r="J114" s="9">
+      <c r="H114" s="245"/>
+      <c r="I114" s="245"/>
+      <c r="J114" s="6">
         <v>3.23</v>
       </c>
-      <c r="K114" s="9">
+      <c r="K114" s="6">
         <v>251</v>
       </c>
-      <c r="L114" s="244">
+      <c r="L114" s="246">
         <v>45040.291666666664</v>
       </c>
       <c r="M114" s="5"/>
@@ -29484,43 +29490,43 @@
       <c r="S114"/>
       <c r="T114"/>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A115" s="241" t="s">
+    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A115" s="240" t="s">
         <v>292</v>
       </c>
-      <c r="B115" s="9">
+      <c r="B115" s="6">
         <v>150</v>
       </c>
-      <c r="C115" s="9">
+      <c r="C115" s="6">
         <v>0.23319999999999999</v>
       </c>
-      <c r="D115" s="9" t="s">
+      <c r="D115" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="E115" s="9" t="s">
+      <c r="E115" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="F115" s="243" t="s">
+      <c r="F115" s="193" t="s">
         <v>179</v>
       </c>
-      <c r="G115" s="9">
+      <c r="G115" s="6">
         <v>46.75</v>
       </c>
-      <c r="H115" s="240">
+      <c r="H115" s="17">
         <f>0.0069204867741875*27.38</f>
         <v>0.18948292787725374</v>
       </c>
-      <c r="I115" s="245">
+      <c r="I115" s="247">
         <f>H115/(B115/1000)</f>
         <v>1.2632195191816917</v>
       </c>
-      <c r="J115" s="9">
+      <c r="J115" s="6">
         <v>3.6640000000000001</v>
       </c>
-      <c r="K115" s="9">
+      <c r="K115" s="6">
         <v>252</v>
       </c>
-      <c r="L115" s="244">
+      <c r="L115" s="246">
         <v>45040.5</v>
       </c>
       <c r="M115" s="5"/>
@@ -29530,45 +29536,45 @@
       <c r="S115"/>
       <c r="T115"/>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A116" s="241" t="s">
+    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A116" s="240" t="s">
         <v>293</v>
       </c>
-      <c r="B116" s="9">
+      <c r="B116" s="6">
         <v>160</v>
       </c>
-      <c r="C116" s="9">
+      <c r="C116" s="6">
         <v>0.2311</v>
       </c>
-      <c r="D116" s="9">
+      <c r="D116" s="6">
         <v>0.23350000000000001</v>
       </c>
-      <c r="E116" s="9">
+      <c r="E116" s="6">
         <f t="shared" si="5"/>
         <v>2.4000000000000132E-3</v>
       </c>
-      <c r="F116" s="243">
+      <c r="F116" s="193">
         <f t="shared" si="6"/>
         <v>15.000000000000083</v>
       </c>
-      <c r="G116" s="9">
+      <c r="G116" s="6">
         <v>27.12</v>
       </c>
-      <c r="H116" s="240">
+      <c r="H116" s="17">
         <f>0.0095083371205*27.38</f>
         <v>0.26033827035928997</v>
       </c>
-      <c r="I116" s="245">
+      <c r="I116" s="247">
         <f>H116/(B116/1000)</f>
         <v>1.6271141897455623</v>
       </c>
-      <c r="J116" s="9">
+      <c r="J116" s="6">
         <v>4.5410000000000004</v>
       </c>
-      <c r="K116" s="9">
+      <c r="K116" s="6">
         <v>253</v>
       </c>
-      <c r="L116" s="244">
+      <c r="L116" s="246">
         <v>45040.708333333336</v>
       </c>
       <c r="M116" s="5"/>
@@ -29578,45 +29584,45 @@
       <c r="S116"/>
       <c r="T116"/>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A117" s="241" t="s">
+    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A117" s="240" t="s">
         <v>299</v>
       </c>
-      <c r="B117" s="9">
+      <c r="B117" s="6">
         <v>140</v>
       </c>
-      <c r="C117" s="9">
+      <c r="C117" s="6">
         <v>0.23089999999999999</v>
       </c>
-      <c r="D117" s="9">
+      <c r="D117" s="6">
         <v>0.2319</v>
       </c>
-      <c r="E117" s="9">
+      <c r="E117" s="6">
         <f t="shared" si="5"/>
         <v>1.0000000000000009E-3</v>
       </c>
-      <c r="F117" s="243">
+      <c r="F117" s="193">
         <f t="shared" si="6"/>
         <v>7.1428571428571495</v>
       </c>
-      <c r="G117" s="9">
+      <c r="G117" s="6">
         <v>14.59</v>
       </c>
-      <c r="H117" s="240">
+      <c r="H117" s="17">
         <f>0.00837063009975*27.38</f>
         <v>0.229187852131155</v>
       </c>
-      <c r="I117" s="245">
+      <c r="I117" s="247">
         <f>H117/(B117/1000)</f>
         <v>1.637056086651107</v>
       </c>
-      <c r="J117" s="9">
+      <c r="J117" s="6">
         <v>3.4580000000000002</v>
       </c>
-      <c r="K117" s="9">
+      <c r="K117" s="6">
         <v>269</v>
       </c>
-      <c r="L117" s="244">
+      <c r="L117" s="246">
         <v>45040.916666666664</v>
       </c>
       <c r="M117" s="5"/>
@@ -29626,39 +29632,39 @@
       <c r="S117"/>
       <c r="T117"/>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A118" s="241" t="s">
+    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A118" s="240" t="s">
         <v>294</v>
       </c>
-      <c r="B118" s="9">
+      <c r="B118" s="6">
         <v>170</v>
       </c>
-      <c r="C118" s="9">
+      <c r="C118" s="6">
         <v>0.23269999999999999</v>
       </c>
-      <c r="D118" s="9">
+      <c r="D118" s="6">
         <v>0.2334</v>
       </c>
-      <c r="E118" s="9">
+      <c r="E118" s="6">
         <f t="shared" si="5"/>
         <v>7.0000000000000617E-4</v>
       </c>
-      <c r="F118" s="243">
+      <c r="F118" s="193">
         <f t="shared" si="6"/>
         <v>4.1176470588235654</v>
       </c>
-      <c r="G118" s="9">
+      <c r="G118" s="6">
         <v>0</v>
       </c>
-      <c r="H118" s="242"/>
-      <c r="I118" s="245"/>
-      <c r="J118" s="9">
+      <c r="H118" s="245"/>
+      <c r="I118" s="247"/>
+      <c r="J118" s="6">
         <v>3.2360000000000002</v>
       </c>
-      <c r="K118" s="9">
+      <c r="K118" s="6">
         <v>270</v>
       </c>
-      <c r="L118" s="244">
+      <c r="L118" s="246">
         <v>45041.125</v>
       </c>
       <c r="M118" s="5"/>
@@ -29668,39 +29674,39 @@
       <c r="S118"/>
       <c r="T118"/>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A119" s="241" t="s">
+    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A119" s="240" t="s">
         <v>295</v>
       </c>
-      <c r="B119" s="9">
+      <c r="B119" s="6">
         <v>140</v>
       </c>
-      <c r="C119" s="9">
+      <c r="C119" s="6">
         <v>0.2359</v>
       </c>
-      <c r="D119" s="9">
+      <c r="D119" s="6">
         <v>0.2369</v>
       </c>
-      <c r="E119" s="9">
+      <c r="E119" s="6">
         <f t="shared" si="5"/>
         <v>1.0000000000000009E-3</v>
       </c>
-      <c r="F119" s="243">
+      <c r="F119" s="193">
         <f t="shared" si="6"/>
         <v>7.1428571428571495</v>
       </c>
-      <c r="G119" s="9">
+      <c r="G119" s="6">
         <v>0</v>
       </c>
-      <c r="H119" s="242"/>
-      <c r="I119" s="245"/>
-      <c r="J119" s="9">
+      <c r="H119" s="245"/>
+      <c r="I119" s="247"/>
+      <c r="J119" s="6">
         <v>3.2829999999999999</v>
       </c>
-      <c r="K119" s="9">
+      <c r="K119" s="6">
         <v>271</v>
       </c>
-      <c r="L119" s="244">
+      <c r="L119" s="246">
         <v>45041.541666666664</v>
       </c>
       <c r="M119" s="5"/>
@@ -29710,38 +29716,38 @@
       <c r="S119"/>
       <c r="T119"/>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A120" s="241" t="s">
+    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A120" s="240" t="s">
         <v>296</v>
       </c>
-      <c r="B120" s="9" t="s">
+      <c r="B120" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="C120" s="9">
+      <c r="C120" s="6">
         <v>0.2306</v>
       </c>
-      <c r="D120" s="9">
+      <c r="D120" s="6">
         <v>0.23139999999999999</v>
       </c>
-      <c r="E120" s="9">
+      <c r="E120" s="6">
         <f t="shared" si="5"/>
         <v>7.9999999999999516E-4</v>
       </c>
-      <c r="F120" s="243" t="s">
+      <c r="F120" s="193" t="s">
         <v>179</v>
       </c>
-      <c r="G120" s="9">
+      <c r="G120" s="6">
         <v>0</v>
       </c>
-      <c r="H120" s="242"/>
-      <c r="I120" s="245"/>
-      <c r="J120" s="9">
+      <c r="H120" s="245"/>
+      <c r="I120" s="247"/>
+      <c r="J120" s="6">
         <v>3.1280000000000001</v>
       </c>
-      <c r="K120" s="9">
+      <c r="K120" s="6">
         <v>272</v>
       </c>
-      <c r="L120" s="244">
+      <c r="L120" s="246">
         <v>45041.75</v>
       </c>
       <c r="M120" s="5"/>
@@ -29751,39 +29757,39 @@
       <c r="S120"/>
       <c r="T120"/>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A121" s="241" t="s">
+    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A121" s="240" t="s">
         <v>297</v>
       </c>
-      <c r="B121" s="9">
+      <c r="B121" s="6">
         <v>145</v>
       </c>
-      <c r="C121" s="9">
+      <c r="C121" s="6">
         <v>0.23280000000000001</v>
       </c>
-      <c r="D121" s="9">
+      <c r="D121" s="6">
         <v>0.2336</v>
       </c>
-      <c r="E121" s="9">
+      <c r="E121" s="6">
         <f t="shared" si="5"/>
         <v>7.9999999999999516E-4</v>
       </c>
-      <c r="F121" s="243">
+      <c r="F121" s="193">
         <f t="shared" si="6"/>
         <v>5.5172413793103114</v>
       </c>
-      <c r="G121" s="9">
+      <c r="G121" s="6">
         <v>0</v>
       </c>
-      <c r="H121" s="242"/>
-      <c r="I121" s="245"/>
-      <c r="J121" s="9">
+      <c r="H121" s="245"/>
+      <c r="I121" s="247"/>
+      <c r="J121" s="6">
         <v>3.044</v>
       </c>
-      <c r="K121" s="9">
+      <c r="K121" s="6">
         <v>273</v>
       </c>
-      <c r="L121" s="244">
+      <c r="L121" s="246">
         <v>45042.5625</v>
       </c>
       <c r="M121" s="5"/>
@@ -29793,39 +29799,39 @@
       <c r="S121"/>
       <c r="T121"/>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A122" s="241" t="s">
+    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A122" s="240" t="s">
         <v>298</v>
       </c>
-      <c r="B122" s="9">
+      <c r="B122" s="6">
         <v>150</v>
       </c>
-      <c r="C122" s="9">
+      <c r="C122" s="6">
         <v>0.2356</v>
       </c>
-      <c r="D122" s="9">
+      <c r="D122" s="6">
         <v>0.23730000000000001</v>
       </c>
-      <c r="E122" s="9">
+      <c r="E122" s="6">
         <f t="shared" si="5"/>
         <v>1.7000000000000071E-3</v>
       </c>
-      <c r="F122" s="243">
+      <c r="F122" s="193">
         <f t="shared" si="6"/>
         <v>11.33333333333338</v>
       </c>
-      <c r="G122" s="9">
+      <c r="G122" s="6">
         <v>0</v>
       </c>
-      <c r="H122" s="242"/>
-      <c r="I122" s="245"/>
-      <c r="J122" s="9">
+      <c r="H122" s="245"/>
+      <c r="I122" s="247"/>
+      <c r="J122" s="6">
         <v>3.0270000000000001</v>
       </c>
-      <c r="K122" s="9">
+      <c r="K122" s="6">
         <v>274</v>
       </c>
-      <c r="L122" s="244">
+      <c r="L122" s="246">
         <v>45042.791666666664</v>
       </c>
       <c r="M122" s="5"/>
@@ -29835,39 +29841,39 @@
       <c r="S122"/>
       <c r="T122"/>
     </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A123" s="241" t="s">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A123" s="240" t="s">
         <v>300</v>
       </c>
-      <c r="B123" s="9">
+      <c r="B123" s="6">
         <v>150</v>
       </c>
-      <c r="C123" s="9">
+      <c r="C123" s="6">
         <v>0.2394</v>
       </c>
-      <c r="D123" s="9">
+      <c r="D123" s="6">
         <v>0.2404</v>
       </c>
-      <c r="E123" s="9">
+      <c r="E123" s="6">
         <f t="shared" si="5"/>
         <v>1.0000000000000009E-3</v>
       </c>
-      <c r="F123" s="243">
+      <c r="F123" s="193">
         <f t="shared" si="6"/>
         <v>6.6666666666666723</v>
       </c>
-      <c r="G123" s="9">
+      <c r="G123" s="6">
         <v>0</v>
       </c>
-      <c r="H123" s="242"/>
-      <c r="I123" s="245"/>
-      <c r="J123" s="9">
+      <c r="H123" s="245"/>
+      <c r="I123" s="247"/>
+      <c r="J123" s="6">
         <v>2.9550000000000001</v>
       </c>
-      <c r="K123" s="9">
+      <c r="K123" s="6">
         <v>283</v>
       </c>
-      <c r="L123" s="244">
+      <c r="L123" s="246">
         <v>45043</v>
       </c>
       <c r="M123" s="5"/>
@@ -29877,39 +29883,39 @@
       <c r="S123"/>
       <c r="T123"/>
     </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A124" s="241" t="s">
+    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A124" s="240" t="s">
         <v>301</v>
       </c>
-      <c r="B124" s="9">
+      <c r="B124" s="6">
         <v>170</v>
       </c>
-      <c r="C124" s="9">
+      <c r="C124" s="6">
         <v>0.2349</v>
       </c>
-      <c r="D124" s="9">
+      <c r="D124" s="6">
         <v>0.23580000000000001</v>
       </c>
-      <c r="E124" s="9">
+      <c r="E124" s="6">
         <f t="shared" si="5"/>
         <v>9.000000000000119E-4</v>
       </c>
-      <c r="F124" s="243">
+      <c r="F124" s="193">
         <f t="shared" si="6"/>
         <v>5.2941176470588935</v>
       </c>
-      <c r="G124" s="9">
+      <c r="G124" s="6">
         <v>0</v>
       </c>
-      <c r="H124" s="242"/>
-      <c r="I124" s="245"/>
-      <c r="J124" s="9">
+      <c r="H124" s="245"/>
+      <c r="I124" s="247"/>
+      <c r="J124" s="6">
         <v>2.5230000000000001</v>
       </c>
-      <c r="K124" s="9">
+      <c r="K124" s="6">
         <v>284</v>
       </c>
-      <c r="L124" s="244">
+      <c r="L124" s="246">
         <v>45043.208333333336</v>
       </c>
       <c r="M124" s="5"/>
@@ -29919,37 +29925,37 @@
       <c r="S124"/>
       <c r="T124"/>
     </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A125" s="241" t="s">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A125" s="240" t="s">
         <v>302</v>
       </c>
-      <c r="B125" s="9" t="s">
+      <c r="B125" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="C125" s="9" t="s">
+      <c r="C125" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="D125" s="9" t="s">
+      <c r="D125" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="E125" s="9" t="s">
+      <c r="E125" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="F125" s="243" t="s">
+      <c r="F125" s="193" t="s">
         <v>179</v>
       </c>
-      <c r="G125" s="9">
+      <c r="G125" s="6">
         <v>0</v>
       </c>
-      <c r="H125" s="242"/>
-      <c r="I125" s="245"/>
-      <c r="J125" s="9">
+      <c r="H125" s="245"/>
+      <c r="I125" s="247"/>
+      <c r="J125" s="6">
         <v>2.681</v>
       </c>
-      <c r="K125" s="9">
+      <c r="K125" s="6">
         <v>285</v>
       </c>
-      <c r="L125" s="244">
+      <c r="L125" s="246">
         <v>45043.416666666664</v>
       </c>
       <c r="M125" s="5"/>
@@ -29959,39 +29965,39 @@
       <c r="S125"/>
       <c r="T125"/>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A126" s="241" t="s">
+    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A126" s="240" t="s">
         <v>303</v>
       </c>
-      <c r="B126" s="9">
+      <c r="B126" s="6">
         <v>160</v>
       </c>
-      <c r="C126" s="9">
+      <c r="C126" s="6">
         <v>0.2339</v>
       </c>
-      <c r="D126" s="9">
+      <c r="D126" s="6">
         <v>0.2351</v>
       </c>
-      <c r="E126" s="9">
+      <c r="E126" s="6">
         <f t="shared" si="5"/>
         <v>1.2000000000000066E-3</v>
       </c>
-      <c r="F126" s="243">
+      <c r="F126" s="193">
         <f t="shared" si="6"/>
         <v>7.5000000000000417</v>
       </c>
-      <c r="G126" s="9">
+      <c r="G126" s="6">
         <v>0</v>
       </c>
-      <c r="H126" s="242"/>
-      <c r="I126" s="245"/>
-      <c r="J126" s="9">
+      <c r="H126" s="245"/>
+      <c r="I126" s="247"/>
+      <c r="J126" s="6">
         <v>3.456</v>
       </c>
-      <c r="K126" s="9">
+      <c r="K126" s="6">
         <v>286</v>
       </c>
-      <c r="L126" s="244">
+      <c r="L126" s="246">
         <v>45043.625</v>
       </c>
       <c r="M126" s="5"/>
@@ -30001,38 +30007,38 @@
       <c r="S126"/>
       <c r="T126"/>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A127" s="241" t="s">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A127" s="240" t="s">
         <v>304</v>
       </c>
-      <c r="B127" s="9" t="s">
+      <c r="B127" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="C127" s="9">
+      <c r="C127" s="6">
         <v>0.23080000000000001</v>
       </c>
-      <c r="D127" s="9">
+      <c r="D127" s="6">
         <v>0.23230000000000001</v>
       </c>
-      <c r="E127" s="9">
+      <c r="E127" s="6">
         <f t="shared" si="5"/>
         <v>1.5000000000000013E-3</v>
       </c>
-      <c r="F127" s="243" t="s">
+      <c r="F127" s="193" t="s">
         <v>179</v>
       </c>
-      <c r="G127" s="9">
+      <c r="G127" s="6">
         <v>0</v>
       </c>
-      <c r="H127" s="242"/>
-      <c r="I127" s="245"/>
-      <c r="J127" s="9">
+      <c r="H127" s="245"/>
+      <c r="I127" s="247"/>
+      <c r="J127" s="6">
         <v>3.1459999999999999</v>
       </c>
-      <c r="K127" s="9">
+      <c r="K127" s="6">
         <v>287</v>
       </c>
-      <c r="L127" s="244">
+      <c r="L127" s="246">
         <v>45043.833333333336</v>
       </c>
       <c r="M127" s="5"/>
@@ -30042,1354 +30048,1354 @@
       <c r="S127"/>
       <c r="T127"/>
     </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A128" s="241" t="s">
+    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A128" s="240" t="s">
         <v>305</v>
       </c>
-      <c r="B128" s="9">
+      <c r="B128" s="6">
         <v>160</v>
       </c>
-      <c r="C128" s="9">
+      <c r="C128" s="6">
         <v>0.2321</v>
       </c>
-      <c r="D128" s="9">
+      <c r="D128" s="6">
         <v>0.2334</v>
       </c>
-      <c r="E128" s="9">
+      <c r="E128" s="6">
         <f t="shared" si="5"/>
         <v>1.2999999999999956E-3</v>
       </c>
-      <c r="F128" s="243">
+      <c r="F128" s="193">
         <f t="shared" si="6"/>
         <v>8.1249999999999734</v>
       </c>
-      <c r="G128" s="9">
+      <c r="G128" s="6">
         <v>0</v>
       </c>
-      <c r="H128" s="9"/>
-      <c r="I128" s="245"/>
-      <c r="J128" s="9">
+      <c r="H128" s="6"/>
+      <c r="I128" s="247"/>
+      <c r="J128" s="6">
         <v>3.0259999999999998</v>
       </c>
-      <c r="K128" s="9">
+      <c r="K128" s="6">
         <v>288</v>
       </c>
-      <c r="L128" s="244">
+      <c r="L128" s="246">
         <v>45044.041666666664</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A129" s="241" t="s">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A129" s="240" t="s">
         <v>306</v>
       </c>
-      <c r="B129" s="9">
+      <c r="B129" s="6">
         <v>155</v>
       </c>
-      <c r="C129" s="9">
+      <c r="C129" s="6">
         <v>0.2331</v>
       </c>
-      <c r="D129" s="9">
+      <c r="D129" s="6">
         <v>0.2349</v>
       </c>
-      <c r="E129" s="9">
+      <c r="E129" s="6">
         <f t="shared" si="5"/>
         <v>1.799999999999996E-3</v>
       </c>
-      <c r="F129" s="243">
+      <c r="F129" s="193">
         <f t="shared" si="6"/>
         <v>11.612903225806427</v>
       </c>
-      <c r="G129" s="9">
+      <c r="G129" s="6">
         <v>0</v>
       </c>
-      <c r="H129" s="9"/>
-      <c r="I129" s="245"/>
-      <c r="J129" s="9">
+      <c r="H129" s="6"/>
+      <c r="I129" s="247"/>
+      <c r="J129" s="6">
         <v>2.7909999999999999</v>
       </c>
-      <c r="K129" s="9">
+      <c r="K129" s="6">
         <v>289</v>
       </c>
-      <c r="L129" s="244">
+      <c r="L129" s="246">
         <v>45044.25</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A130" s="241" t="s">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A130" s="240" t="s">
         <v>307</v>
       </c>
-      <c r="B130" s="9">
+      <c r="B130" s="6">
         <v>160</v>
       </c>
-      <c r="C130" s="9">
+      <c r="C130" s="6">
         <v>0.23139999999999999</v>
       </c>
-      <c r="D130" s="9">
+      <c r="D130" s="6">
         <v>0.23269999999999999</v>
       </c>
-      <c r="E130" s="9">
+      <c r="E130" s="6">
         <f t="shared" si="5"/>
         <v>1.2999999999999956E-3</v>
       </c>
-      <c r="F130" s="243">
+      <c r="F130" s="193">
         <f t="shared" si="6"/>
         <v>8.1249999999999734</v>
       </c>
-      <c r="G130" s="9">
+      <c r="G130" s="6">
         <v>0</v>
       </c>
-      <c r="H130" s="9"/>
-      <c r="I130" s="245"/>
-      <c r="J130" s="9">
+      <c r="H130" s="6"/>
+      <c r="I130" s="247"/>
+      <c r="J130" s="6">
         <v>2.6970000000000001</v>
       </c>
-      <c r="K130" s="9">
+      <c r="K130" s="6">
         <v>290</v>
       </c>
-      <c r="L130" s="244">
+      <c r="L130" s="246">
         <v>45044.458333333336</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A131" s="241" t="s">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A131" s="240" t="s">
         <v>308</v>
       </c>
-      <c r="B131" s="9">
+      <c r="B131" s="6">
         <v>150</v>
       </c>
-      <c r="C131" s="9">
+      <c r="C131" s="6">
         <v>0.2321</v>
       </c>
-      <c r="D131" s="9">
+      <c r="D131" s="6">
         <v>0.2331</v>
       </c>
-      <c r="E131" s="9">
+      <c r="E131" s="6">
         <f t="shared" si="5"/>
         <v>1.0000000000000009E-3</v>
       </c>
-      <c r="F131" s="243">
+      <c r="F131" s="193">
         <f t="shared" si="6"/>
         <v>6.6666666666666723</v>
       </c>
-      <c r="G131" s="9">
+      <c r="G131" s="6">
         <v>56.02</v>
       </c>
-      <c r="H131" s="9"/>
-      <c r="I131" s="245"/>
-      <c r="J131" s="9">
+      <c r="H131" s="6"/>
+      <c r="I131" s="247"/>
+      <c r="J131" s="6">
         <v>3.1160000000000001</v>
       </c>
-      <c r="K131" s="9">
+      <c r="K131" s="6">
         <v>291</v>
       </c>
-      <c r="L131" s="244">
+      <c r="L131" s="246">
         <v>45044.666666666664</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A132" s="241" t="s">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A132" s="240" t="s">
         <v>309</v>
       </c>
-      <c r="B132" s="9">
+      <c r="B132" s="6">
         <v>160</v>
       </c>
-      <c r="C132" s="9">
+      <c r="C132" s="6">
         <v>0.2354</v>
       </c>
-      <c r="D132" s="9">
+      <c r="D132" s="6">
         <v>0.23599999999999999</v>
       </c>
-      <c r="E132" s="9">
+      <c r="E132" s="6">
         <f t="shared" si="5"/>
         <v>5.9999999999998943E-4</v>
       </c>
-      <c r="F132" s="243">
+      <c r="F132" s="193">
         <f t="shared" si="6"/>
         <v>3.7499999999999338</v>
       </c>
-      <c r="G132" s="9">
+      <c r="G132" s="6">
         <v>0</v>
       </c>
-      <c r="H132" s="9"/>
-      <c r="I132" s="245"/>
-      <c r="J132" s="9">
+      <c r="H132" s="6"/>
+      <c r="I132" s="247"/>
+      <c r="J132" s="6">
         <v>2.9769999999999999</v>
       </c>
-      <c r="K132" s="9">
+      <c r="K132" s="6">
         <v>302</v>
       </c>
-      <c r="L132" s="247">
+      <c r="L132" s="249">
         <v>45044.875</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A133" s="241" t="s">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A133" s="240" t="s">
         <v>310</v>
       </c>
-      <c r="B133" s="9">
+      <c r="B133" s="6">
         <v>160</v>
       </c>
-      <c r="C133" s="9">
+      <c r="C133" s="6">
         <v>0.23300000000000001</v>
       </c>
-      <c r="D133" s="9">
+      <c r="D133" s="6">
         <v>0.23480000000000001</v>
       </c>
-      <c r="E133" s="9">
+      <c r="E133" s="6">
         <f t="shared" si="5"/>
         <v>1.799999999999996E-3</v>
       </c>
-      <c r="F133" s="243">
+      <c r="F133" s="193">
         <f t="shared" si="6"/>
         <v>11.249999999999975</v>
       </c>
-      <c r="G133" s="9">
+      <c r="G133" s="6">
         <v>0</v>
       </c>
-      <c r="H133" s="9"/>
-      <c r="I133" s="245"/>
-      <c r="J133" s="9">
+      <c r="H133" s="6"/>
+      <c r="I133" s="247"/>
+      <c r="J133" s="6">
         <v>2.8260000000000001</v>
       </c>
-      <c r="K133" s="9">
+      <c r="K133" s="6">
         <v>303</v>
       </c>
-      <c r="L133" s="244">
+      <c r="L133" s="246">
         <v>45045.083333333336</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A134" s="241" t="s">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A134" s="240" t="s">
         <v>311</v>
       </c>
-      <c r="B134" s="9">
+      <c r="B134" s="6">
         <v>150</v>
       </c>
-      <c r="C134" s="9">
+      <c r="C134" s="6">
         <v>0.23630000000000001</v>
       </c>
-      <c r="D134" s="9">
+      <c r="D134" s="6">
         <v>0.23699999999999999</v>
       </c>
-      <c r="E134" s="9">
+      <c r="E134" s="6">
         <f t="shared" si="5"/>
         <v>6.9999999999997842E-4</v>
       </c>
-      <c r="F134" s="243">
+      <c r="F134" s="193">
         <f t="shared" si="6"/>
         <v>4.6666666666665231</v>
       </c>
-      <c r="G134" s="9">
+      <c r="G134" s="6">
         <v>0</v>
       </c>
-      <c r="H134" s="9"/>
-      <c r="I134" s="245"/>
-      <c r="J134" s="9">
+      <c r="H134" s="6"/>
+      <c r="I134" s="247"/>
+      <c r="J134" s="6">
         <v>2.944</v>
       </c>
-      <c r="K134" s="9">
+      <c r="K134" s="6">
         <v>304</v>
       </c>
-      <c r="L134" s="244">
+      <c r="L134" s="246">
         <v>45045.5</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A135" s="241" t="s">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A135" s="240" t="s">
         <v>312</v>
       </c>
-      <c r="B135" s="9">
+      <c r="B135" s="6">
         <v>165</v>
       </c>
-      <c r="C135" s="9">
+      <c r="C135" s="6">
         <v>0.2321</v>
       </c>
-      <c r="D135" s="9">
+      <c r="D135" s="6">
         <v>0.23449999999999999</v>
       </c>
-      <c r="E135" s="9">
+      <c r="E135" s="6">
         <f t="shared" si="5"/>
         <v>2.3999999999999855E-3</v>
       </c>
-      <c r="F135" s="243">
+      <c r="F135" s="193">
         <f t="shared" si="6"/>
         <v>14.545454545454458</v>
       </c>
-      <c r="G135" s="9">
+      <c r="G135" s="6">
         <v>0</v>
       </c>
-      <c r="H135" s="9"/>
-      <c r="I135" s="245"/>
-      <c r="J135" s="9">
+      <c r="H135" s="6"/>
+      <c r="I135" s="247"/>
+      <c r="J135" s="6">
         <v>4.681</v>
       </c>
-      <c r="K135" s="9">
+      <c r="K135" s="6">
         <v>305</v>
       </c>
-      <c r="L135" s="244">
+      <c r="L135" s="246">
         <v>45045.708333333336</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A136" s="241" t="s">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A136" s="240" t="s">
         <v>313</v>
       </c>
-      <c r="B136" s="9">
+      <c r="B136" s="6">
         <v>140</v>
       </c>
-      <c r="C136" s="9">
+      <c r="C136" s="6">
         <v>0.2331</v>
       </c>
-      <c r="D136" s="9">
+      <c r="D136" s="6">
         <v>0.2344</v>
       </c>
-      <c r="E136" s="9">
+      <c r="E136" s="6">
         <f t="shared" si="5"/>
         <v>1.2999999999999956E-3</v>
       </c>
-      <c r="F136" s="243">
+      <c r="F136" s="193">
         <f t="shared" si="6"/>
         <v>9.2857142857142527</v>
       </c>
-      <c r="G136" s="9">
+      <c r="G136" s="6">
         <v>0</v>
       </c>
-      <c r="H136" s="9"/>
-      <c r="I136" s="245"/>
-      <c r="J136" s="9">
+      <c r="H136" s="6"/>
+      <c r="I136" s="247"/>
+      <c r="J136" s="6">
         <v>3.395</v>
       </c>
-      <c r="K136" s="9">
+      <c r="K136" s="6">
         <v>306</v>
       </c>
-      <c r="L136" s="244">
+      <c r="L136" s="246">
         <v>45045.916666666664</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A137" s="241" t="s">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A137" s="240" t="s">
         <v>314</v>
       </c>
-      <c r="B137" s="9">
+      <c r="B137" s="6">
         <v>160</v>
       </c>
-      <c r="C137" s="9">
+      <c r="C137" s="6">
         <v>0.23719999999999999</v>
       </c>
-      <c r="D137" s="9">
+      <c r="D137" s="6">
         <v>0.23830000000000001</v>
       </c>
-      <c r="E137" s="9">
+      <c r="E137" s="6">
         <f t="shared" si="5"/>
         <v>1.1000000000000176E-3</v>
       </c>
-      <c r="F137" s="243">
+      <c r="F137" s="193">
         <f t="shared" si="6"/>
         <v>6.8750000000001101</v>
       </c>
-      <c r="G137" s="9">
+      <c r="G137" s="6">
         <v>0</v>
       </c>
-      <c r="H137" s="9"/>
-      <c r="I137" s="245"/>
-      <c r="J137" s="9">
+      <c r="H137" s="6"/>
+      <c r="I137" s="247"/>
+      <c r="J137" s="6">
         <v>3.1139999999999999</v>
       </c>
-      <c r="K137" s="9">
+      <c r="K137" s="6">
         <v>307</v>
       </c>
-      <c r="L137" s="244">
+      <c r="L137" s="246">
         <v>45046.125</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A138" s="241" t="s">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A138" s="240" t="s">
         <v>315</v>
       </c>
-      <c r="B138" s="9">
+      <c r="B138" s="6">
         <v>160</v>
       </c>
-      <c r="C138" s="9">
+      <c r="C138" s="6">
         <v>0.23089999999999999</v>
       </c>
-      <c r="D138" s="9">
+      <c r="D138" s="6">
         <v>0.23130000000000001</v>
       </c>
-      <c r="E138" s="9">
+      <c r="E138" s="6">
         <f t="shared" si="5"/>
         <v>4.0000000000001146E-4</v>
       </c>
-      <c r="F138" s="243">
+      <c r="F138" s="193">
         <f t="shared" si="6"/>
         <v>2.5000000000000715</v>
       </c>
-      <c r="G138" s="9">
+      <c r="G138" s="6">
         <v>0</v>
       </c>
-      <c r="H138" s="9"/>
-      <c r="I138" s="245"/>
-      <c r="J138" s="9">
+      <c r="H138" s="6"/>
+      <c r="I138" s="247"/>
+      <c r="J138" s="6">
         <v>2.9430000000000001</v>
       </c>
-      <c r="K138" s="9">
+      <c r="K138" s="6">
         <v>308</v>
       </c>
-      <c r="L138" s="244">
+      <c r="L138" s="246">
         <v>45046.333333333336</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A139" s="241" t="s">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A139" s="240" t="s">
         <v>316</v>
       </c>
-      <c r="B139" s="9">
+      <c r="B139" s="6">
         <v>150</v>
       </c>
-      <c r="C139" s="9">
+      <c r="C139" s="6">
         <v>0.2354</v>
       </c>
-      <c r="D139" s="9">
+      <c r="D139" s="6">
         <v>0.23730000000000001</v>
       </c>
-      <c r="E139" s="9">
+      <c r="E139" s="6">
         <f t="shared" si="5"/>
         <v>1.9000000000000128E-3</v>
       </c>
-      <c r="F139" s="243">
+      <c r="F139" s="193">
         <f t="shared" si="6"/>
         <v>12.666666666666751</v>
       </c>
-      <c r="G139" s="9">
+      <c r="G139" s="6">
         <v>43.66</v>
       </c>
-      <c r="H139" s="9"/>
-      <c r="I139" s="245"/>
-      <c r="J139" s="9">
+      <c r="H139" s="6"/>
+      <c r="I139" s="247"/>
+      <c r="J139" s="6">
         <v>4.1040000000000001</v>
       </c>
-      <c r="K139" s="9">
+      <c r="K139" s="6">
         <v>309</v>
       </c>
-      <c r="L139" s="244">
+      <c r="L139" s="246">
         <v>45046.541666666664</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A140" s="241" t="s">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A140" s="240" t="s">
         <v>317</v>
       </c>
-      <c r="B140" s="9">
+      <c r="B140" s="6">
         <v>140</v>
       </c>
-      <c r="C140" s="9">
+      <c r="C140" s="6">
         <v>0.2351</v>
       </c>
-      <c r="D140" s="9">
+      <c r="D140" s="6">
         <v>0.2414</v>
       </c>
-      <c r="E140" s="9">
+      <c r="E140" s="6">
         <f t="shared" si="5"/>
         <v>6.3E-3</v>
       </c>
-      <c r="F140" s="243">
+      <c r="F140" s="193">
         <f t="shared" si="6"/>
         <v>45.000000000000007</v>
       </c>
-      <c r="G140" s="9">
+      <c r="G140" s="6">
         <v>85.5</v>
       </c>
-      <c r="H140" s="9"/>
-      <c r="I140" s="245"/>
-      <c r="J140" s="9">
+      <c r="H140" s="6"/>
+      <c r="I140" s="247"/>
+      <c r="J140" s="6">
         <v>4.9790000000000001</v>
       </c>
-      <c r="K140" s="9">
+      <c r="K140" s="6">
         <v>310</v>
       </c>
-      <c r="L140" s="244">
+      <c r="L140" s="246">
         <v>45046.75</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A141" s="241" t="s">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A141" s="240" t="s">
         <v>318</v>
       </c>
-      <c r="B141" s="9">
+      <c r="B141" s="6">
         <v>150</v>
       </c>
-      <c r="C141" s="9">
+      <c r="C141" s="6">
         <v>0.2346</v>
       </c>
-      <c r="D141" s="9">
+      <c r="D141" s="6">
         <v>0.23669999999999999</v>
       </c>
-      <c r="E141" s="9">
+      <c r="E141" s="6">
         <f t="shared" si="5"/>
         <v>2.0999999999999908E-3</v>
       </c>
-      <c r="F141" s="243">
+      <c r="F141" s="193">
         <f t="shared" si="6"/>
         <v>13.99999999999994</v>
       </c>
-      <c r="G141" s="9">
+      <c r="G141" s="6">
         <v>0</v>
       </c>
-      <c r="H141" s="9"/>
-      <c r="I141" s="245"/>
-      <c r="J141" s="9">
+      <c r="H141" s="6"/>
+      <c r="I141" s="247"/>
+      <c r="J141" s="6">
         <v>3.871</v>
       </c>
-      <c r="K141" s="9">
+      <c r="K141" s="6">
         <v>311</v>
       </c>
-      <c r="L141" s="244">
+      <c r="L141" s="246">
         <v>45046.958333333336</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A142" s="241" t="s">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A142" s="240" t="s">
         <v>319</v>
       </c>
-      <c r="B142" s="9">
+      <c r="B142" s="6">
         <v>150</v>
       </c>
-      <c r="C142" s="9">
+      <c r="C142" s="6">
         <v>0.23499999999999999</v>
       </c>
-      <c r="D142" s="9">
+      <c r="D142" s="6">
         <v>0.23649999999999999</v>
       </c>
-      <c r="E142" s="9">
+      <c r="E142" s="6">
         <f t="shared" si="5"/>
         <v>1.5000000000000013E-3</v>
       </c>
-      <c r="F142" s="243">
+      <c r="F142" s="193">
         <f t="shared" si="6"/>
         <v>10.000000000000009</v>
       </c>
-      <c r="G142" s="9">
+      <c r="G142" s="6">
         <v>0</v>
       </c>
-      <c r="H142" s="9"/>
-      <c r="I142" s="245"/>
-      <c r="J142" s="9">
+      <c r="H142" s="6"/>
+      <c r="I142" s="247"/>
+      <c r="J142" s="6">
         <v>3.4740000000000002</v>
       </c>
-      <c r="K142" s="9">
+      <c r="K142" s="6">
         <v>312</v>
       </c>
-      <c r="L142" s="244">
+      <c r="L142" s="246">
         <v>45047.166666666664</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A143" s="241" t="s">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A143" s="240" t="s">
         <v>320</v>
       </c>
-      <c r="B143" s="9">
+      <c r="B143" s="6">
         <v>160</v>
       </c>
-      <c r="C143" s="9">
+      <c r="C143" s="6">
         <v>0.2334</v>
       </c>
-      <c r="D143" s="9">
+      <c r="D143" s="6">
         <v>0.23469999999999999</v>
       </c>
-      <c r="E143" s="9">
+      <c r="E143" s="6">
         <f t="shared" si="5"/>
         <v>1.2999999999999956E-3</v>
       </c>
-      <c r="F143" s="243">
+      <c r="F143" s="193">
         <f t="shared" si="6"/>
         <v>8.1249999999999734</v>
       </c>
-      <c r="G143" s="9">
+      <c r="G143" s="6">
         <v>0</v>
       </c>
-      <c r="H143" s="9"/>
-      <c r="I143" s="245"/>
-      <c r="J143" s="9">
+      <c r="H143" s="6"/>
+      <c r="I143" s="247"/>
+      <c r="J143" s="6">
         <v>3.2690000000000001</v>
       </c>
-      <c r="K143" s="9">
+      <c r="K143" s="6">
         <v>313</v>
       </c>
-      <c r="L143" s="244">
+      <c r="L143" s="246">
         <v>45047.375</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A144" s="241" t="s">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A144" s="240" t="s">
         <v>321</v>
       </c>
-      <c r="B144" s="9">
+      <c r="B144" s="6">
         <v>170</v>
       </c>
-      <c r="C144" s="9">
+      <c r="C144" s="6">
         <v>0.2359</v>
       </c>
-      <c r="D144" s="9">
+      <c r="D144" s="6">
         <v>0.2382</v>
       </c>
-      <c r="E144" s="9">
+      <c r="E144" s="6">
         <f t="shared" ref="E144:E152" si="7">D144-C144</f>
         <v>2.2999999999999965E-3</v>
       </c>
-      <c r="F144" s="243">
+      <c r="F144" s="193">
         <f t="shared" ref="F144:F152" si="8">E144/B144*1000*1000</f>
         <v>13.529411764705863</v>
       </c>
-      <c r="G144" s="9">
+      <c r="G144" s="6">
         <v>0</v>
       </c>
-      <c r="H144" s="9"/>
-      <c r="I144" s="245"/>
-      <c r="J144" s="9">
+      <c r="H144" s="6"/>
+      <c r="I144" s="247"/>
+      <c r="J144" s="6">
         <v>4.6879999999999997</v>
       </c>
-      <c r="K144" s="9">
+      <c r="K144" s="6">
         <v>314</v>
       </c>
-      <c r="L144" s="244">
+      <c r="L144" s="246">
         <v>45047.583333333336</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A145" s="241" t="s">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A145" s="240" t="s">
         <v>322</v>
       </c>
-      <c r="B145" s="9">
+      <c r="B145" s="6">
         <v>150</v>
       </c>
-      <c r="C145" s="9">
+      <c r="C145" s="6">
         <v>0.23849999999999999</v>
       </c>
-      <c r="D145" s="9">
+      <c r="D145" s="6">
         <v>0.24149999999999999</v>
       </c>
-      <c r="E145" s="9">
+      <c r="E145" s="6">
         <f t="shared" si="7"/>
         <v>3.0000000000000027E-3</v>
       </c>
-      <c r="F145" s="243">
+      <c r="F145" s="193">
         <f t="shared" si="8"/>
         <v>20.000000000000018</v>
       </c>
-      <c r="G145" s="9">
+      <c r="G145" s="6">
         <v>64.14</v>
       </c>
-      <c r="H145" s="9"/>
-      <c r="I145" s="245"/>
-      <c r="J145" s="120">
+      <c r="H145" s="6"/>
+      <c r="I145" s="247"/>
+      <c r="J145" s="67">
         <v>3.9550000000000001</v>
       </c>
-      <c r="K145" s="120">
+      <c r="K145" s="67">
         <v>328</v>
       </c>
-      <c r="L145" s="244">
+      <c r="L145" s="246">
         <v>45047.833333333336</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A146" s="241" t="s">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A146" s="240" t="s">
         <v>323</v>
       </c>
-      <c r="B146" s="9">
+      <c r="B146" s="6">
         <v>160</v>
       </c>
-      <c r="C146" s="9">
+      <c r="C146" s="6">
         <v>0.24010000000000001</v>
       </c>
-      <c r="D146" s="9">
+      <c r="D146" s="6">
         <v>0.2417</v>
       </c>
-      <c r="E146" s="9">
+      <c r="E146" s="6">
         <f t="shared" si="7"/>
         <v>1.5999999999999903E-3</v>
       </c>
-      <c r="F146" s="243">
+      <c r="F146" s="193">
         <f t="shared" si="8"/>
         <v>9.9999999999999396</v>
       </c>
-      <c r="G146" s="9">
+      <c r="G146" s="6">
         <v>0</v>
       </c>
-      <c r="H146" s="9"/>
-      <c r="I146" s="245"/>
-      <c r="J146" s="9">
+      <c r="H146" s="6"/>
+      <c r="I146" s="247"/>
+      <c r="J146" s="6">
         <v>3.2229999999999999</v>
       </c>
-      <c r="K146" s="9">
+      <c r="K146" s="6">
         <v>329</v>
       </c>
-      <c r="L146" s="244">
+      <c r="L146" s="246">
         <v>45048.125</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A147" s="241" t="s">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A147" s="240" t="s">
         <v>324</v>
       </c>
-      <c r="B147" s="9">
+      <c r="B147" s="6">
         <v>160</v>
       </c>
-      <c r="C147" s="9">
+      <c r="C147" s="6">
         <v>0.23649999999999999</v>
       </c>
-      <c r="D147" s="9">
+      <c r="D147" s="6">
         <v>0.2366</v>
       </c>
-      <c r="E147" s="9">
+      <c r="E147" s="6">
         <f t="shared" si="7"/>
         <v>1.0000000000001674E-4</v>
       </c>
-      <c r="F147" s="243">
+      <c r="F147" s="193">
         <f t="shared" si="8"/>
         <v>0.62500000000010458</v>
       </c>
-      <c r="G147" s="9">
+      <c r="G147" s="6">
         <v>0</v>
       </c>
-      <c r="H147" s="9"/>
-      <c r="I147" s="245"/>
-      <c r="J147" s="9">
+      <c r="H147" s="6"/>
+      <c r="I147" s="247"/>
+      <c r="J147" s="6">
         <v>3.044</v>
       </c>
-      <c r="K147" s="9">
+      <c r="K147" s="6">
         <v>330</v>
       </c>
-      <c r="L147" s="244">
+      <c r="L147" s="246">
         <v>45048.416666666664</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A148" s="241" t="s">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A148" s="240" t="s">
         <v>325</v>
       </c>
-      <c r="B148" s="9">
+      <c r="B148" s="6">
         <v>160</v>
       </c>
-      <c r="C148" s="9">
+      <c r="C148" s="6">
         <v>0.2344</v>
       </c>
-      <c r="D148" s="9">
+      <c r="D148" s="6">
         <v>0.2351</v>
       </c>
-      <c r="E148" s="9">
+      <c r="E148" s="6">
         <f t="shared" si="7"/>
         <v>7.0000000000000617E-4</v>
       </c>
-      <c r="F148" s="243">
+      <c r="F148" s="193">
         <f t="shared" si="8"/>
         <v>4.3750000000000382</v>
       </c>
-      <c r="G148" s="9">
+      <c r="G148" s="6">
         <v>0</v>
       </c>
-      <c r="H148" s="9"/>
-      <c r="I148" s="245"/>
-      <c r="J148" s="9">
+      <c r="H148" s="6"/>
+      <c r="I148" s="247"/>
+      <c r="J148" s="6">
         <v>3.4780000000000002</v>
       </c>
-      <c r="K148" s="9">
+      <c r="K148" s="6">
         <v>331</v>
       </c>
-      <c r="L148" s="244">
+      <c r="L148" s="246">
         <v>45048.708333333336</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A149" s="241" t="s">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A149" s="240" t="s">
         <v>326</v>
       </c>
-      <c r="B149" s="9">
+      <c r="B149" s="6">
         <v>150</v>
       </c>
-      <c r="C149" s="9">
+      <c r="C149" s="6">
         <v>0.23019999999999999</v>
       </c>
-      <c r="D149" s="9">
+      <c r="D149" s="6">
         <v>0.23069999999999999</v>
       </c>
-      <c r="E149" s="9">
+      <c r="E149" s="6">
         <f t="shared" si="7"/>
         <v>5.0000000000000044E-4</v>
       </c>
-      <c r="F149" s="243">
+      <c r="F149" s="193">
         <f t="shared" si="8"/>
         <v>3.3333333333333361</v>
       </c>
-      <c r="G149" s="9">
+      <c r="G149" s="6">
         <v>0</v>
       </c>
-      <c r="H149" s="9"/>
-      <c r="I149" s="245"/>
-      <c r="J149" s="9">
+      <c r="H149" s="6"/>
+      <c r="I149" s="247"/>
+      <c r="J149" s="6">
         <v>3.1890000000000001</v>
       </c>
-      <c r="K149" s="9">
+      <c r="K149" s="6">
         <v>332</v>
       </c>
-      <c r="L149" s="244">
+      <c r="L149" s="246">
         <v>45049</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="B150" s="9">
+      <c r="B150" s="6">
         <v>140</v>
       </c>
-      <c r="C150" s="9">
+      <c r="C150" s="6">
         <v>0.22739999999999999</v>
       </c>
-      <c r="D150" s="9">
+      <c r="D150" s="6">
         <v>0.2281</v>
       </c>
-      <c r="E150" s="9">
+      <c r="E150" s="6">
         <f t="shared" si="7"/>
         <v>7.0000000000000617E-4</v>
       </c>
-      <c r="F150" s="243">
+      <c r="F150" s="193">
         <f t="shared" si="8"/>
         <v>5.0000000000000444</v>
       </c>
-      <c r="G150" s="9">
+      <c r="G150" s="6">
         <v>0</v>
       </c>
-      <c r="H150" s="9"/>
-      <c r="I150" s="245"/>
-      <c r="J150" s="9">
+      <c r="H150" s="6"/>
+      <c r="I150" s="247"/>
+      <c r="J150" s="6">
         <v>2.7290000000000001</v>
       </c>
-      <c r="K150" s="9">
+      <c r="K150" s="6">
         <v>333</v>
       </c>
-      <c r="L150" s="244">
+      <c r="L150" s="246">
         <v>45049.291666666664</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="B151" s="9">
+      <c r="B151" s="6">
         <v>150</v>
       </c>
-      <c r="C151" s="9">
+      <c r="C151" s="6">
         <v>0.23150000000000001</v>
       </c>
-      <c r="D151" s="9">
+      <c r="D151" s="6">
         <v>0.2331</v>
       </c>
-      <c r="E151" s="9">
+      <c r="E151" s="6">
         <f t="shared" si="7"/>
         <v>1.5999999999999903E-3</v>
       </c>
-      <c r="F151" s="243">
+      <c r="F151" s="193">
         <f t="shared" si="8"/>
         <v>10.666666666666602</v>
       </c>
-      <c r="G151" s="9">
+      <c r="G151" s="6">
         <v>39.619999999999997</v>
       </c>
-      <c r="H151" s="9"/>
-      <c r="I151" s="245"/>
-      <c r="J151" s="9">
+      <c r="H151" s="6"/>
+      <c r="I151" s="247"/>
+      <c r="J151" s="6">
         <v>3.419</v>
       </c>
-      <c r="K151" s="9">
+      <c r="K151" s="6">
         <v>334</v>
       </c>
-      <c r="L151" s="244">
+      <c r="L151" s="246">
         <v>45049.583333333336</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="B152" s="9">
+      <c r="B152" s="6">
         <v>160</v>
       </c>
-      <c r="C152" s="9">
+      <c r="C152" s="6">
         <v>0.23280000000000001</v>
       </c>
-      <c r="D152" s="9">
+      <c r="D152" s="6">
         <v>0.23669999999999999</v>
       </c>
-      <c r="E152" s="9">
+      <c r="E152" s="6">
         <f t="shared" si="7"/>
         <v>3.8999999999999868E-3</v>
       </c>
-      <c r="F152" s="243">
+      <c r="F152" s="193">
         <f t="shared" si="8"/>
         <v>24.374999999999918</v>
       </c>
-      <c r="G152" s="9">
+      <c r="G152" s="6">
         <v>87.1</v>
       </c>
-      <c r="H152" s="9"/>
-      <c r="I152" s="245"/>
-      <c r="J152" s="9">
+      <c r="H152" s="6"/>
+      <c r="I152" s="247"/>
+      <c r="J152" s="6">
         <v>4.0039999999999996</v>
       </c>
-      <c r="K152" s="9">
+      <c r="K152" s="6">
         <v>335</v>
       </c>
-      <c r="L152" s="244">
+      <c r="L152" s="246">
         <v>45049.833333333336</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" s="9"/>
-      <c r="B153" s="9"/>
-      <c r="C153" s="9"/>
-      <c r="D153" s="9"/>
-      <c r="E153" s="9"/>
-      <c r="F153" s="9"/>
-      <c r="G153" s="9">
+      <c r="B153" s="6"/>
+      <c r="C153" s="6"/>
+      <c r="D153" s="6"/>
+      <c r="E153" s="6"/>
+      <c r="F153" s="6"/>
+      <c r="G153" s="6">
         <v>0</v>
       </c>
-      <c r="H153" s="9"/>
-      <c r="I153" s="245"/>
-      <c r="J153" s="9" t="s">
+      <c r="H153" s="6"/>
+      <c r="I153" s="247"/>
+      <c r="J153" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="K153" s="9" t="s">
+      <c r="K153" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="L153" s="244">
+      <c r="L153" s="246">
         <v>45049.958333333336</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" s="9"/>
-      <c r="B154" s="9"/>
-      <c r="C154" s="9"/>
-      <c r="D154" s="9"/>
-      <c r="E154" s="9"/>
-      <c r="F154" s="9"/>
-      <c r="G154" s="9">
+      <c r="B154" s="6"/>
+      <c r="C154" s="6"/>
+      <c r="D154" s="6"/>
+      <c r="E154" s="6"/>
+      <c r="F154" s="6"/>
+      <c r="G154" s="6">
         <v>26.28</v>
       </c>
-      <c r="H154" s="9"/>
-      <c r="I154" s="245"/>
-      <c r="J154" s="9" t="s">
+      <c r="H154" s="6"/>
+      <c r="I154" s="247"/>
+      <c r="J154" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="K154" s="9" t="s">
+      <c r="K154" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="L154" s="244">
+      <c r="L154" s="246">
         <v>45050.083333333336</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A155" s="9" t="s">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A155" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="B155" s="9">
+      <c r="B155" s="6">
         <v>160</v>
       </c>
-      <c r="C155" s="9">
+      <c r="C155" s="6">
         <v>0.2341</v>
       </c>
-      <c r="D155" s="9">
+      <c r="D155" s="6">
         <v>0.23499999999999999</v>
       </c>
-      <c r="E155" s="9">
+      <c r="E155" s="6">
         <f>D155-C155</f>
         <v>8.9999999999998415E-4</v>
       </c>
-      <c r="F155" s="243">
+      <c r="F155" s="193">
         <f>E155/B155*1000*1000</f>
         <v>5.6249999999999005</v>
       </c>
-      <c r="G155" s="9">
+      <c r="G155" s="6">
         <v>0</v>
       </c>
-      <c r="H155" s="9"/>
-      <c r="I155" s="245"/>
-      <c r="J155" s="9">
+      <c r="H155" s="6"/>
+      <c r="I155" s="247"/>
+      <c r="J155" s="6">
         <v>2.944</v>
       </c>
-      <c r="K155" s="9">
+      <c r="K155" s="6">
         <v>336</v>
       </c>
-      <c r="L155" s="244">
+      <c r="L155" s="246">
         <v>45050.208333333336</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A156" s="9"/>
-      <c r="B156" s="9"/>
-      <c r="C156" s="9"/>
-      <c r="D156" s="9"/>
-      <c r="E156" s="9"/>
-      <c r="F156" s="9"/>
-      <c r="G156" s="9">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A156" s="6"/>
+      <c r="B156" s="6"/>
+      <c r="C156" s="6"/>
+      <c r="D156" s="6"/>
+      <c r="E156" s="6"/>
+      <c r="F156" s="6"/>
+      <c r="G156" s="6">
         <v>0</v>
       </c>
-      <c r="H156" s="9"/>
-      <c r="I156" s="245"/>
-      <c r="J156" s="9" t="s">
+      <c r="H156" s="6"/>
+      <c r="I156" s="247"/>
+      <c r="J156" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="K156" s="9" t="s">
+      <c r="K156" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="L156" s="244">
+      <c r="L156" s="246">
         <v>45050.333333333336</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A157" s="9"/>
-      <c r="B157" s="9"/>
-      <c r="C157" s="9"/>
-      <c r="D157" s="9"/>
-      <c r="E157" s="9"/>
-      <c r="F157" s="9"/>
-      <c r="G157" s="9">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A157" s="6"/>
+      <c r="B157" s="6"/>
+      <c r="C157" s="6"/>
+      <c r="D157" s="6"/>
+      <c r="E157" s="6"/>
+      <c r="F157" s="6"/>
+      <c r="G157" s="6">
         <v>35.26</v>
       </c>
-      <c r="H157" s="9"/>
-      <c r="I157" s="245"/>
-      <c r="J157" s="9" t="s">
+      <c r="H157" s="6"/>
+      <c r="I157" s="247"/>
+      <c r="J157" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="K157" s="9" t="s">
+      <c r="K157" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="L157" s="244">
+      <c r="L157" s="246">
         <v>45050.458333333336</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A158" s="9" t="s">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A158" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="B158" s="9">
+      <c r="B158" s="6">
         <v>155</v>
       </c>
-      <c r="C158" s="9">
+      <c r="C158" s="6">
         <v>0.222</v>
       </c>
-      <c r="D158" s="9">
+      <c r="D158" s="6">
         <v>0.22220000000000001</v>
       </c>
-      <c r="E158" s="9">
+      <c r="E158" s="6">
         <f>D158-C158</f>
         <v>2.0000000000000573E-4</v>
       </c>
-      <c r="F158" s="243">
+      <c r="F158" s="193">
         <f>E158/B158*1000*1000</f>
         <v>1.2903225806451981</v>
       </c>
-      <c r="G158" s="9">
+      <c r="G158" s="6">
         <v>0</v>
       </c>
-      <c r="H158" s="9"/>
-      <c r="I158" s="245"/>
-      <c r="J158" s="9">
+      <c r="H158" s="6"/>
+      <c r="I158" s="247"/>
+      <c r="J158" s="6">
         <v>3.504</v>
       </c>
-      <c r="K158" s="9">
+      <c r="K158" s="6">
         <v>337</v>
       </c>
-      <c r="L158" s="244">
+      <c r="L158" s="246">
         <v>45050.583333333336</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A159" s="9"/>
-      <c r="B159" s="9"/>
-      <c r="C159" s="9"/>
-      <c r="D159" s="9"/>
-      <c r="E159" s="9"/>
-      <c r="F159" s="9"/>
-      <c r="G159" s="9">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A159" s="6"/>
+      <c r="B159" s="6"/>
+      <c r="C159" s="6"/>
+      <c r="D159" s="6"/>
+      <c r="E159" s="6"/>
+      <c r="F159" s="6"/>
+      <c r="G159" s="6">
         <v>72.78</v>
       </c>
-      <c r="H159" s="9"/>
-      <c r="I159" s="245"/>
-      <c r="J159" s="9" t="s">
+      <c r="H159" s="6"/>
+      <c r="I159" s="247"/>
+      <c r="J159" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="K159" s="9" t="s">
+      <c r="K159" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="L159" s="244">
+      <c r="L159" s="246">
         <v>45050.708333333336</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A160" s="9" t="s">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A160" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="B160" s="9">
+      <c r="B160" s="6">
         <v>140</v>
       </c>
-      <c r="C160" s="9">
+      <c r="C160" s="6">
         <v>0.23089999999999999</v>
       </c>
-      <c r="D160" s="9">
+      <c r="D160" s="6">
         <v>0.23100000000000001</v>
       </c>
-      <c r="E160" s="9">
+      <c r="E160" s="6">
         <f>D160-C160</f>
         <v>1.0000000000001674E-4</v>
       </c>
-      <c r="F160" s="243">
+      <c r="F160" s="193">
         <f>E160/B160*1000*1000</f>
         <v>0.71428571428583387</v>
       </c>
-      <c r="G160" s="9">
+      <c r="G160" s="6">
         <v>25.16</v>
       </c>
-      <c r="H160" s="240">
+      <c r="H160" s="17">
         <f>0.0117180656445*27.38</f>
         <v>0.32084063734641</v>
       </c>
-      <c r="I160" s="245">
+      <c r="I160" s="247">
         <f>H160/(B160/1000)</f>
         <v>2.2917188381886424</v>
       </c>
-      <c r="J160" s="9">
+      <c r="J160" s="6">
         <v>3.5750000000000002</v>
       </c>
-      <c r="K160" s="9">
+      <c r="K160" s="6">
         <v>338</v>
       </c>
-      <c r="L160" s="244">
+      <c r="L160" s="246">
         <v>45050.833333333336</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A161" s="9" t="s">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A161" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="B161" s="9">
+      <c r="B161" s="6">
         <v>140</v>
       </c>
-      <c r="C161" s="9">
+      <c r="C161" s="6">
         <v>0.23469999999999999</v>
       </c>
-      <c r="D161" s="9">
+      <c r="D161" s="6">
         <v>0.23549999999999999</v>
       </c>
-      <c r="E161" s="9">
+      <c r="E161" s="6">
         <f>D161-C161</f>
         <v>7.9999999999999516E-4</v>
       </c>
-      <c r="F161" s="243">
+      <c r="F161" s="193">
         <f>E161/B161*1000*1000</f>
         <v>5.7142857142856798</v>
       </c>
-      <c r="G161" s="9">
+      <c r="G161" s="6">
         <v>15.19</v>
       </c>
-      <c r="H161" s="240">
+      <c r="H161" s="17">
         <f>0.0086452595395*27.38</f>
         <v>0.23670720619151001</v>
       </c>
-      <c r="I161" s="245">
+      <c r="I161" s="247">
         <f t="shared" ref="I161:I167" si="9">H161/(B161/1000)</f>
         <v>1.6907657585107856</v>
       </c>
-      <c r="J161" s="9">
+      <c r="J161" s="6">
         <v>3.2189999999999999</v>
       </c>
-      <c r="K161" s="9">
+      <c r="K161" s="6">
         <v>339</v>
       </c>
-      <c r="L161" s="244">
+      <c r="L161" s="246">
         <v>45050.958333333336</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A162" s="9"/>
-      <c r="B162" s="9"/>
-      <c r="C162" s="9"/>
-      <c r="D162" s="9"/>
-      <c r="E162" s="9"/>
-      <c r="F162" s="9"/>
-      <c r="G162" s="9">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A162" s="6"/>
+      <c r="B162" s="6"/>
+      <c r="C162" s="6"/>
+      <c r="D162" s="6"/>
+      <c r="E162" s="6"/>
+      <c r="F162" s="6"/>
+      <c r="G162" s="6">
         <v>99.54</v>
       </c>
-      <c r="H162" s="9"/>
-      <c r="I162" s="245"/>
-      <c r="J162" s="9" t="s">
+      <c r="H162" s="6"/>
+      <c r="I162" s="247"/>
+      <c r="J162" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="K162" s="9" t="s">
+      <c r="K162" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="L162" s="244">
+      <c r="L162" s="246">
         <v>45051.083333333336</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A163" s="9" t="s">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A163" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="B163" s="9">
+      <c r="B163" s="6">
         <v>140</v>
       </c>
-      <c r="C163" s="9">
+      <c r="C163" s="6">
         <v>0.23580000000000001</v>
       </c>
-      <c r="D163" s="9">
+      <c r="D163" s="6">
         <v>0.2361</v>
       </c>
-      <c r="E163" s="9">
+      <c r="E163" s="6">
         <f>D163-C163</f>
         <v>2.9999999999999472E-4</v>
       </c>
-      <c r="F163" s="243">
+      <c r="F163" s="193">
         <f>E163/B163*1000*1000</f>
         <v>2.142857142857105</v>
       </c>
-      <c r="G163" s="9">
+      <c r="G163" s="6">
         <v>0</v>
       </c>
-      <c r="H163" s="9"/>
-      <c r="I163" s="245"/>
-      <c r="J163" s="9">
+      <c r="H163" s="6"/>
+      <c r="I163" s="247"/>
+      <c r="J163" s="6">
         <v>2.7109999999999999</v>
       </c>
-      <c r="K163" s="9">
+      <c r="K163" s="6">
         <v>340</v>
       </c>
-      <c r="L163" s="244">
+      <c r="L163" s="246">
         <v>45051.208333333336</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A164" s="9"/>
-      <c r="B164" s="9"/>
-      <c r="C164" s="9"/>
-      <c r="D164" s="9"/>
-      <c r="E164" s="9"/>
-      <c r="F164" s="9"/>
-      <c r="G164" s="9">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A164" s="6"/>
+      <c r="B164" s="6"/>
+      <c r="C164" s="6"/>
+      <c r="D164" s="6"/>
+      <c r="E164" s="6"/>
+      <c r="F164" s="6"/>
+      <c r="G164" s="6">
         <v>40.119999999999997</v>
       </c>
-      <c r="H164" s="9"/>
-      <c r="I164" s="245"/>
-      <c r="J164" s="9" t="s">
+      <c r="H164" s="6"/>
+      <c r="I164" s="247"/>
+      <c r="J164" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="K164" s="9" t="s">
+      <c r="K164" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="L164" s="244">
+      <c r="L164" s="246">
         <v>45051.333333333336</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A165" s="9" t="s">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A165" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="B165" s="9">
+      <c r="B165" s="6">
         <v>150</v>
       </c>
-      <c r="C165" s="9">
+      <c r="C165" s="6">
         <v>0.2329</v>
       </c>
-      <c r="D165" s="9">
+      <c r="D165" s="6">
         <v>0.23300000000000001</v>
       </c>
-      <c r="E165" s="9">
+      <c r="E165" s="6">
         <f>D165-C165</f>
         <v>1.0000000000001674E-4</v>
       </c>
-      <c r="F165" s="243">
+      <c r="F165" s="193">
         <f>E165/B165*1000*1000</f>
         <v>0.66666666666677832</v>
       </c>
-      <c r="G165" s="9">
+      <c r="G165" s="6">
         <v>25.61</v>
       </c>
-      <c r="H165" s="240">
+      <c r="H165" s="17">
         <f>0.007431424321*27.38</f>
         <v>0.20347239790898</v>
       </c>
-      <c r="I165" s="245">
+      <c r="I165" s="247">
         <f t="shared" si="9"/>
         <v>1.3564826527265335</v>
       </c>
-      <c r="J165" s="9">
+      <c r="J165" s="6">
         <v>2.7170000000000001</v>
       </c>
-      <c r="K165" s="9">
+      <c r="K165" s="6">
         <v>341</v>
       </c>
-      <c r="L165" s="244">
+      <c r="L165" s="246">
         <v>45051.458333333336</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A166" s="9"/>
-      <c r="B166" s="9"/>
-      <c r="C166" s="9"/>
-      <c r="D166" s="9"/>
-      <c r="E166" s="9"/>
-      <c r="F166" s="9"/>
-      <c r="G166" s="9">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A166" s="6"/>
+      <c r="B166" s="6"/>
+      <c r="C166" s="6"/>
+      <c r="D166" s="6"/>
+      <c r="E166" s="6"/>
+      <c r="F166" s="6"/>
+      <c r="G166" s="6">
         <v>0</v>
       </c>
-      <c r="H166" s="9"/>
-      <c r="I166" s="245"/>
-      <c r="J166" s="9" t="s">
+      <c r="H166" s="6"/>
+      <c r="I166" s="247"/>
+      <c r="J166" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="K166" s="9" t="s">
+      <c r="K166" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="L166" s="244">
+      <c r="L166" s="246">
         <v>45051.583333333336</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A167" s="9" t="s">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A167" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="B167" s="9">
+      <c r="B167" s="6">
         <v>150</v>
       </c>
-      <c r="C167" s="9">
+      <c r="C167" s="6">
         <v>0.23180000000000001</v>
       </c>
-      <c r="D167" s="9">
+      <c r="D167" s="6">
         <v>0.23319999999999999</v>
       </c>
-      <c r="E167" s="9">
+      <c r="E167" s="6">
         <f>D167-C167</f>
         <v>1.3999999999999846E-3</v>
       </c>
-      <c r="F167" s="243" t="s">
+      <c r="F167" s="193" t="s">
         <v>179</v>
       </c>
-      <c r="G167" s="9">
+      <c r="G167" s="6">
         <v>30.82</v>
       </c>
-      <c r="H167" s="240">
+      <c r="H167" s="17">
         <f>0.0093669671855*27.38</f>
         <v>0.25646756153898997</v>
       </c>
-      <c r="I167" s="245">
+      <c r="I167" s="247">
         <f t="shared" si="9"/>
         <v>1.7097837435932666</v>
       </c>
-      <c r="J167" s="9">
+      <c r="J167" s="6">
         <v>3.8330000000000002</v>
       </c>
-      <c r="K167" s="9">
+      <c r="K167" s="6">
         <v>342</v>
       </c>
-      <c r="L167" s="244">
+      <c r="L167" s="246">
         <v>45051.708333333336</v>
       </c>
     </row>
@@ -31402,24 +31408,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E898195B-C2B1-40DF-A713-EC36D1F92D07}">
   <dimension ref="A1:Q87"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.6640625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="15.44140625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="22.44140625" style="5" customWidth="1"/>
-    <col min="6" max="10" width="16.88671875" style="5" customWidth="1"/>
-    <col min="11" max="11" width="15.44140625" style="5" customWidth="1"/>
-    <col min="12" max="12" width="16.33203125" style="5" customWidth="1"/>
-    <col min="13" max="13" width="16.88671875" style="5" customWidth="1"/>
-    <col min="14" max="14" width="12.109375" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="22.42578125" style="5" customWidth="1"/>
+    <col min="6" max="10" width="16.85546875" style="5" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" style="5" customWidth="1"/>
+    <col min="12" max="12" width="16.28515625" style="5" customWidth="1"/>
+    <col min="13" max="13" width="16.85546875" style="5" customWidth="1"/>
+    <col min="14" max="14" width="12.140625" customWidth="1"/>
     <col min="15" max="15" width="18" customWidth="1"/>
-    <col min="16" max="16" width="18.44140625" customWidth="1"/>
-    <col min="17" max="17" width="15.5546875" customWidth="1"/>
+    <col min="16" max="16" width="18.42578125" customWidth="1"/>
+    <col min="17" max="17" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="144" t="s">
         <v>1</v>
       </c>
@@ -31466,7 +31472,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="55" t="s">
         <v>85</v>
       </c>
@@ -31519,7 +31525,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="55" t="s">
         <v>86</v>
       </c>
@@ -31572,7 +31578,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="55" t="s">
         <v>87</v>
       </c>
@@ -31625,7 +31631,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="55" t="s">
         <v>88</v>
       </c>
@@ -31678,7 +31684,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="55" t="s">
         <v>89</v>
       </c>
@@ -31731,7 +31737,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>90</v>
       </c>
@@ -31784,7 +31790,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>91</v>
       </c>
@@ -31837,7 +31843,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>92</v>
       </c>
@@ -31887,7 +31893,7 @@
         <v>44400.626388888886</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>93</v>
       </c>
@@ -31937,7 +31943,7 @@
         <v>44400.675694444442</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>94</v>
       </c>
@@ -31987,7 +31993,7 @@
         <v>44400.706944444442</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>95</v>
       </c>
@@ -32037,7 +32043,7 @@
         <v>44400.748611111114</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="61" t="s">
         <v>96</v>
       </c>
@@ -32087,7 +32093,7 @@
         <v>44400.842361111114</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="70" t="s">
         <v>98</v>
       </c>
@@ -32137,7 +32143,7 @@
         <v>44776.626388888886</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>99</v>
       </c>
@@ -32187,7 +32193,7 @@
         <v>44776.636805555558</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>100</v>
       </c>
@@ -32238,7 +32244,7 @@
       </c>
       <c r="P16" s="42"/>
     </row>
-    <row r="17" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>101</v>
       </c>
@@ -32282,7 +32288,7 @@
         <v>44776.678472222222</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>102</v>
       </c>
@@ -32326,7 +32332,7 @@
         <v>44776.751388888886</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>103</v>
       </c>
@@ -32378,7 +32384,7 @@
       <c r="P19" s="5"/>
       <c r="Q19" s="5"/>
     </row>
-    <row r="20" spans="1:17" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="78" t="s">
         <v>104</v>
       </c>
@@ -32422,7 +32428,7 @@
         <v>44776.793055555558</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="84" t="s">
         <v>105</v>
       </c>
@@ -32466,7 +32472,7 @@
         <v>44781.571527777778</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>106</v>
       </c>
@@ -32516,7 +32522,7 @@
         <v>44781.581944444442</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>107</v>
       </c>
@@ -32560,7 +32566,7 @@
         <v>44781.592361111114</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>108</v>
       </c>
@@ -32610,7 +32616,7 @@
         <v>44781.602777777778</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>109</v>
       </c>
@@ -32654,7 +32660,7 @@
         <v>44781.613194444442</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>110</v>
       </c>
@@ -32704,7 +32710,7 @@
         <v>44781.640972222223</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>111</v>
       </c>
@@ -32754,7 +32760,7 @@
         <v>44781.675694444442</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>112</v>
       </c>
@@ -32798,7 +32804,7 @@
         <v>44781.696527777778</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>113</v>
       </c>
@@ -32842,7 +32848,7 @@
         <v>44781.706944444442</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>114</v>
       </c>
@@ -32886,7 +32892,7 @@
         <v>44781.727777777778</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>115</v>
       </c>
@@ -32930,7 +32936,7 @@
         <v>44781.748611111114</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="90" t="s">
         <v>116</v>
       </c>
@@ -32980,7 +32986,7 @@
         <v>44781.759027777778</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="96" t="s">
         <v>62</v>
       </c>
@@ -33024,7 +33030,7 @@
         <v>45136.619444444441</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="43" t="s">
         <v>24</v>
       </c>
@@ -33070,7 +33076,7 @@
         <v>45136.629861111112</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="43" t="s">
         <v>25</v>
       </c>
@@ -33116,7 +33122,7 @@
         <v>45136.640277777777</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="43" t="s">
         <v>26</v>
       </c>
@@ -33162,7 +33168,7 @@
         <v>45136.650694444441</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="43" t="s">
         <v>27</v>
       </c>
@@ -33208,7 +33214,7 @@
         <v>45136.661111111112</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="43" t="s">
         <v>63</v>
       </c>
@@ -33253,7 +33259,7 @@
         <v>45136.671527777777</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="43" t="s">
         <v>64</v>
       </c>
@@ -33298,7 +33304,7 @@
         <v>45136.681944444441</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>28</v>
       </c>
@@ -33344,7 +33350,7 @@
         <v>45136.636111111111</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>29</v>
       </c>
@@ -33390,7 +33396,7 @@
         <v>45136.646527777775</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>30</v>
       </c>
@@ -33436,7 +33442,7 @@
         <v>45136.656944444447</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>31</v>
       </c>
@@ -33482,7 +33488,7 @@
         <v>45136.667361111111</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>32</v>
       </c>
@@ -33525,7 +33531,7 @@
         <v>45136.677777777775</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>33</v>
       </c>
@@ -33571,7 +33577,7 @@
         <v>45136.688194444447</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>34</v>
       </c>
@@ -33612,7 +33618,7 @@
         <v>45136.698611111111</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>35</v>
       </c>
@@ -33658,7 +33664,7 @@
         <v>45136.719444444447</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>36</v>
       </c>
@@ -33701,7 +33707,7 @@
         <v>45136.740277777775</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="102" t="s">
         <v>37</v>
       </c>
@@ -33745,7 +33751,7 @@
         <v>45136.771527777775</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="108" t="s">
         <v>7</v>
       </c>
@@ -33791,7 +33797,7 @@
         <v>45151.78125</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="49" t="s">
         <v>8</v>
       </c>
@@ -33837,7 +33843,7 @@
         <v>45151.790277777778</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="49" t="s">
         <v>9</v>
       </c>
@@ -33883,7 +33889,7 @@
         <v>45151.793055555558</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="49" t="s">
         <v>10</v>
       </c>
@@ -33929,7 +33935,7 @@
         <v>45151.798611111109</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="49" t="s">
         <v>11</v>
       </c>
@@ -33975,7 +33981,7 @@
         <v>45151.876388888886</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>12</v>
       </c>
@@ -34021,7 +34027,7 @@
         <v>45151.791666666664</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>13</v>
       </c>
@@ -34067,7 +34073,7 @@
         <v>45151.802083333336</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>14</v>
       </c>
@@ -34113,7 +34119,7 @@
         <v>45151.8125</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>15</v>
       </c>
@@ -34159,7 +34165,7 @@
         <v>45151.822916666664</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>16</v>
       </c>
@@ -34200,7 +34206,7 @@
         <v>45151.833333333336</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>17</v>
       </c>
@@ -34246,7 +34252,7 @@
         <v>45151.84375</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>18</v>
       </c>
@@ -34287,7 +34293,7 @@
         <v>45151.854166666664</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>19</v>
       </c>
@@ -34333,7 +34339,7 @@
         <v>45151.864583333336</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>20</v>
       </c>
@@ -34374,7 +34380,7 @@
         <v>45151.875</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>21</v>
       </c>
@@ -34415,7 +34421,7 @@
         <v>45151.885416666664</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>22</v>
       </c>
@@ -34456,7 +34462,7 @@
         <v>45151.895833333336</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>23</v>
       </c>
@@ -34502,7 +34508,7 @@
         <v>45151.90625</v>
       </c>
     </row>
-    <row r="67" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="114" t="s">
         <v>65</v>
       </c>
@@ -34539,7 +34545,7 @@
         <v>45151.916666666664</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="124" t="s">
         <v>38</v>
       </c>
@@ -34585,7 +34591,7 @@
         <v>45166.513888888891</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
         <v>39</v>
       </c>
@@ -34631,7 +34637,7 @@
         <v>45166.524305555555</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
         <v>40</v>
       </c>
@@ -34677,7 +34683,7 @@
         <v>45166.534722222219</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
         <v>41</v>
       </c>
@@ -34723,7 +34729,7 @@
         <v>45166.545138888891</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="8" t="s">
         <v>42</v>
       </c>
@@ -34769,7 +34775,7 @@
         <v>45166.555555555555</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
         <v>43</v>
       </c>
@@ -34813,7 +34819,7 @@
         <v>45166.586805555555</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
         <v>44</v>
       </c>
@@ -34856,7 +34862,7 @@
         <v>45166.607638888891</v>
       </c>
     </row>
-    <row r="75" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="130" t="s">
         <v>66</v>
       </c>
@@ -34897,7 +34903,7 @@
         <v>45166.638888888891</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="136" t="s">
         <v>45</v>
       </c>
@@ -34941,7 +34947,7 @@
         <v>45183.744444444441</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="9" t="s">
         <v>46</v>
       </c>
@@ -34985,7 +34991,7 @@
         <v>45183.754861111112</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="9" t="s">
         <v>47</v>
       </c>
@@ -35029,7 +35035,7 @@
         <v>45183.765277777777</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="9" t="s">
         <v>48</v>
       </c>
@@ -35073,7 +35079,7 @@
         <v>45183.775694444441</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="9" t="s">
         <v>49</v>
       </c>
@@ -35114,7 +35120,7 @@
         <v>45183.786111111112</v>
       </c>
     </row>
-    <row r="81" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="140" t="s">
         <v>50</v>
       </c>
@@ -35156,7 +35162,7 @@
         <v>45183.79791666667</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="120" t="s">
         <v>51</v>
       </c>
@@ -35200,7 +35206,7 @@
         <v>45183.739583333336</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="9" t="s">
         <v>52</v>
       </c>
@@ -35244,7 +35250,7 @@
         <v>45183.75</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="9" t="s">
         <v>53</v>
       </c>
@@ -35288,7 +35294,7 @@
         <v>45183.760416666664</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="9" t="s">
         <v>54</v>
       </c>
@@ -35332,7 +35338,7 @@
         <v>45183.78125</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="9" t="s">
         <v>55</v>
       </c>
@@ -35371,7 +35377,7 @@
         <v>45183.802083333336</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="9" t="s">
         <v>68</v>
       </c>
@@ -35425,27 +35431,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7B56A85-9129-45FB-97F4-6550137620EC}">
   <dimension ref="A1:X38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.5546875" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-    <col min="5" max="5" width="18.44140625" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="18.6640625" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="11.44140625" customWidth="1"/>
-    <col min="12" max="12" width="10.33203125" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" customWidth="1"/>
+    <col min="12" max="12" width="10.28515625" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
     <col min="14" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="14.88671875" customWidth="1"/>
-    <col min="16" max="16" width="16.5546875" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="144" t="s">
         <v>120</v>
       </c>
@@ -35495,7 +35501,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>129</v>
       </c>
@@ -35544,7 +35550,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>130</v>
       </c>
@@ -35593,7 +35599,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>131</v>
       </c>
@@ -35642,7 +35648,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>132</v>
       </c>
@@ -35691,7 +35697,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>133</v>
       </c>
@@ -35740,7 +35746,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>135</v>
       </c>
@@ -35786,7 +35792,7 @@
         <v>44413</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>136</v>
       </c>
@@ -35832,7 +35838,7 @@
         <v>44421</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="114" t="s">
         <v>134</v>
       </c>
@@ -35881,7 +35887,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="157" t="s">
         <v>137</v>
       </c>
@@ -35941,7 +35947,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>138</v>
       </c>
@@ -36009,7 +36015,7 @@
         <v>1.754</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>139</v>
       </c>
@@ -36077,7 +36083,7 @@
         <v>2.8035000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:24" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="102" t="s">
         <v>140</v>
       </c>
@@ -36145,7 +36151,7 @@
         <v>2.8035000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="174" t="s">
         <v>141</v>
       </c>
@@ -36209,7 +36215,7 @@
         <v>2.8035000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>142</v>
       </c>
@@ -36273,7 +36279,7 @@
         <v>3.4509999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>143</v>
       </c>
@@ -36337,7 +36343,7 @@
         <v>1.1215000000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>144</v>
       </c>
@@ -36401,7 +36407,7 @@
         <v>1.1215000000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>145</v>
       </c>
@@ -36440,7 +36446,7 @@
         <v>44797</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:24" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="61" t="s">
         <v>146</v>
       </c>
@@ -36479,7 +36485,7 @@
         <v>44797</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="191" t="s">
         <v>147</v>
       </c>
@@ -36518,7 +36524,7 @@
         <v>45003</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="191" t="s">
         <v>148</v>
       </c>
@@ -36557,7 +36563,7 @@
         <v>45003</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="196" t="s">
         <v>149</v>
       </c>
@@ -36596,7 +36602,7 @@
         <v>45003</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="191" t="s">
         <v>150</v>
       </c>
@@ -36635,7 +36641,7 @@
         <v>45003</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="191" t="s">
         <v>151</v>
       </c>
@@ -36674,7 +36680,7 @@
         <v>45004</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="191" t="s">
         <v>152</v>
       </c>
@@ -36713,7 +36719,7 @@
         <v>45004</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="191" t="s">
         <v>153</v>
       </c>
@@ -36752,7 +36758,7 @@
         <v>45004</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="191" t="s">
         <v>154</v>
       </c>
@@ -36791,7 +36797,7 @@
         <v>45004</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="191" t="s">
         <v>155</v>
       </c>
@@ -36828,7 +36834,7 @@
         <v>45007</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="191" t="s">
         <v>156</v>
       </c>
@@ -36865,7 +36871,7 @@
         <v>45007</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
         <v>157</v>
       </c>
@@ -36902,7 +36908,7 @@
         <v>45007</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
         <v>158</v>
       </c>
@@ -36939,7 +36945,7 @@
         <v>45007</v>
       </c>
     </row>
-    <row r="32" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
         <v>159</v>
       </c>
@@ -36978,7 +36984,7 @@
         <v>45029</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="191" t="s">
         <v>160</v>
       </c>
@@ -37017,7 +37023,7 @@
         <v>45029</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="191" t="s">
         <v>161</v>
       </c>
@@ -37056,7 +37062,7 @@
         <v>45029</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="202" t="s">
         <v>162</v>
       </c>
@@ -37095,7 +37101,7 @@
         <v>45029</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="207" t="s">
         <v>163</v>
       </c>
@@ -37137,7 +37143,7 @@
         <v>45127</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="214" t="s">
         <v>165</v>
       </c>
@@ -37176,7 +37182,7 @@
         <v>45154</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="214" t="s">
         <v>164</v>
       </c>
